--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:sector-name</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
     <t>codeforiati:sector-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Formation technique supérieure de gestion</t>
   </si>
   <si>
+    <t>Education Post Secondaire</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
     <t>11430</t>
   </si>
   <si>
-    <t>Education Post Secondaire</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -67,15 +67,15 @@
     <t>Recherche pour la prévention et le contrôle des MNT</t>
   </si>
   <si>
+    <t>Maladies non-transmissibles (MNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
     <t>12382</t>
   </si>
   <si>
-    <t>Maladies non-transmissibles (MNT)</t>
-  </si>
-  <si>
     <t>130</t>
   </si>
   <si>
@@ -109,15 +109,15 @@
     <t>Enfants soldats (Prévention et démobilisation)</t>
   </si>
   <si>
+    <t>Conflits, Paix et Sécurité</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
     <t>15261</t>
   </si>
   <si>
-    <t>Conflits, Paix et Sécurité</t>
-  </si>
-  <si>
     <t>160</t>
   </si>
   <si>
@@ -163,15 +163,15 @@
     <t>Infrastructures électriques à l'usage de la mobilité</t>
   </si>
   <si>
+    <t>Distribution de l'énergie</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
     <t>23642</t>
   </si>
   <si>
-    <t>Distribution de l'énergie</t>
-  </si>
-  <si>
     <t>240</t>
   </si>
   <si>
@@ -205,15 +205,15 @@
     <t>Services dans le domaine de la pêche</t>
   </si>
   <si>
+    <t>Pêche</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
     <t>31391</t>
   </si>
   <si>
-    <t>Pêche</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -223,13 +223,13 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
     <t>32310</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>331</t>
@@ -815,13 +815,13 @@
         <v>22</v>
       </c>
       <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -838,13 +838,13 @@
         <v>26</v>
       </c>
       <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>27</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -884,13 +884,13 @@
         <v>36</v>
       </c>
       <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>37</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -907,13 +907,13 @@
         <v>40</v>
       </c>
       <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>41</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -930,13 +930,13 @@
         <v>44</v>
       </c>
       <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
         <v>42</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>45</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -976,13 +976,13 @@
         <v>54</v>
       </c>
       <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
         <v>52</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>55</v>
-      </c>
-      <c r="G11" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -999,13 +999,13 @@
         <v>58</v>
       </c>
       <c r="E12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" t="s">
         <v>56</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>59</v>
-      </c>
-      <c r="G12" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1068,13 +1068,13 @@
         <v>74</v>
       </c>
       <c r="E15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s">
         <v>72</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>75</v>
-      </c>
-      <c r="G15" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1091,13 +1091,13 @@
         <v>78</v>
       </c>
       <c r="E16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s">
         <v>76</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>79</v>
-      </c>
-      <c r="G16" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1114,13 +1114,13 @@
         <v>82</v>
       </c>
       <c r="E17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" t="s">
         <v>80</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>83</v>
-      </c>
-      <c r="G17" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1137,13 +1137,13 @@
         <v>86</v>
       </c>
       <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
         <v>84</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>87</v>
-      </c>
-      <c r="G18" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1160,13 +1160,13 @@
         <v>90</v>
       </c>
       <c r="E19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" t="s">
         <v>88</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>91</v>
-      </c>
-      <c r="G19" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1183,13 +1183,13 @@
         <v>94</v>
       </c>
       <c r="E20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" t="s">
         <v>92</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>95</v>
-      </c>
-      <c r="G20" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1206,13 +1206,13 @@
         <v>98</v>
       </c>
       <c r="E21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" t="s">
         <v>96</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>99</v>
-      </c>
-      <c r="G21" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1229,13 +1229,13 @@
         <v>102</v>
       </c>
       <c r="E22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" t="s">
         <v>100</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>103</v>
-      </c>
-      <c r="G22" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1252,13 +1252,13 @@
         <v>106</v>
       </c>
       <c r="E23" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" t="s">
         <v>104</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>107</v>
-      </c>
-      <c r="G23" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1275,13 +1275,13 @@
         <v>110</v>
       </c>
       <c r="E24" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" t="s">
         <v>108</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>111</v>
-      </c>
-      <c r="G24" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1298,13 +1298,13 @@
         <v>114</v>
       </c>
       <c r="E25" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" t="s">
         <v>112</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>115</v>
-      </c>
-      <c r="G25" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1321,13 +1321,13 @@
         <v>118</v>
       </c>
       <c r="E26" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" t="s">
         <v>116</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>119</v>
-      </c>
-      <c r="G26" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1344,13 +1344,13 @@
         <v>122</v>
       </c>
       <c r="E27" t="s">
+        <v>121</v>
+      </c>
+      <c r="F27" t="s">
         <v>120</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>123</v>
-      </c>
-      <c r="G27" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1367,13 +1367,13 @@
         <v>126</v>
       </c>
       <c r="E28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" t="s">
         <v>124</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>127</v>
-      </c>
-      <c r="G28" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:sector-name</t>
   </si>
   <si>
+    <t>codeforiati:sector-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:sector-code</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Formation technique supérieure de gestion</t>
   </si>
   <si>
+    <t>11430</t>
+  </si>
+  <si>
     <t>Education Post Secondaire</t>
   </si>
   <si>
     <t>114</t>
   </si>
   <si>
-    <t>11430</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -67,15 +67,15 @@
     <t>Recherche pour la prévention et le contrôle des MNT</t>
   </si>
   <si>
+    <t>12382</t>
+  </si>
+  <si>
     <t>Maladies non-transmissibles (MNT)</t>
   </si>
   <si>
     <t>123</t>
   </si>
   <si>
-    <t>12382</t>
-  </si>
-  <si>
     <t>130</t>
   </si>
   <si>
@@ -109,15 +109,15 @@
     <t>Enfants soldats (Prévention et démobilisation)</t>
   </si>
   <si>
+    <t>15261</t>
+  </si>
+  <si>
     <t>Conflits, Paix et Sécurité</t>
   </si>
   <si>
     <t>152</t>
   </si>
   <si>
-    <t>15261</t>
-  </si>
-  <si>
     <t>160</t>
   </si>
   <si>
@@ -163,15 +163,15 @@
     <t>Infrastructures électriques à l'usage de la mobilité</t>
   </si>
   <si>
+    <t>23642</t>
+  </si>
+  <si>
     <t>Distribution de l'énergie</t>
   </si>
   <si>
     <t>236</t>
   </si>
   <si>
-    <t>23642</t>
-  </si>
-  <si>
     <t>240</t>
   </si>
   <si>
@@ -205,15 +205,15 @@
     <t>Services dans le domaine de la pêche</t>
   </si>
   <si>
+    <t>31391</t>
+  </si>
+  <si>
     <t>Pêche</t>
   </si>
   <si>
     <t>313</t>
   </si>
   <si>
-    <t>31391</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -223,13 +223,13 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>32310</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>32310</t>
   </si>
   <si>
     <t>331</t>
@@ -815,13 +815,13 @@
         <v>22</v>
       </c>
       <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -838,13 +838,13 @@
         <v>26</v>
       </c>
       <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -884,13 +884,13 @@
         <v>36</v>
       </c>
       <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
         <v>35</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>34</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -907,13 +907,13 @@
         <v>40</v>
       </c>
       <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
         <v>39</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>38</v>
-      </c>
-      <c r="G8" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -930,13 +930,13 @@
         <v>44</v>
       </c>
       <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
         <v>43</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>42</v>
-      </c>
-      <c r="G9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -976,13 +976,13 @@
         <v>54</v>
       </c>
       <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" t="s">
         <v>53</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>52</v>
-      </c>
-      <c r="G11" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -999,13 +999,13 @@
         <v>58</v>
       </c>
       <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
         <v>57</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>56</v>
-      </c>
-      <c r="G12" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1068,13 +1068,13 @@
         <v>74</v>
       </c>
       <c r="E15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s">
         <v>73</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>72</v>
-      </c>
-      <c r="G15" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1091,13 +1091,13 @@
         <v>78</v>
       </c>
       <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" t="s">
         <v>77</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>76</v>
-      </c>
-      <c r="G16" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1114,13 +1114,13 @@
         <v>82</v>
       </c>
       <c r="E17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" t="s">
         <v>81</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>80</v>
-      </c>
-      <c r="G17" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1137,13 +1137,13 @@
         <v>86</v>
       </c>
       <c r="E18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" t="s">
         <v>85</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>84</v>
-      </c>
-      <c r="G18" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1160,13 +1160,13 @@
         <v>90</v>
       </c>
       <c r="E19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" t="s">
         <v>89</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>88</v>
-      </c>
-      <c r="G19" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1183,13 +1183,13 @@
         <v>94</v>
       </c>
       <c r="E20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" t="s">
         <v>93</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>92</v>
-      </c>
-      <c r="G20" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1206,13 +1206,13 @@
         <v>98</v>
       </c>
       <c r="E21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" t="s">
         <v>97</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>96</v>
-      </c>
-      <c r="G21" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1229,13 +1229,13 @@
         <v>102</v>
       </c>
       <c r="E22" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" t="s">
         <v>101</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>100</v>
-      </c>
-      <c r="G22" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1252,13 +1252,13 @@
         <v>106</v>
       </c>
       <c r="E23" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" t="s">
         <v>105</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>104</v>
-      </c>
-      <c r="G23" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1275,13 +1275,13 @@
         <v>110</v>
       </c>
       <c r="E24" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" t="s">
         <v>109</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>108</v>
-      </c>
-      <c r="G24" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1298,13 +1298,13 @@
         <v>114</v>
       </c>
       <c r="E25" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" t="s">
         <v>113</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>112</v>
-      </c>
-      <c r="G25" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1321,13 +1321,13 @@
         <v>118</v>
       </c>
       <c r="E26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" t="s">
         <v>117</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>116</v>
-      </c>
-      <c r="G26" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1344,13 +1344,13 @@
         <v>122</v>
       </c>
       <c r="E27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27" t="s">
         <v>121</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>120</v>
-      </c>
-      <c r="G27" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1367,13 +1367,13 @@
         <v>126</v>
       </c>
       <c r="E28" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" t="s">
         <v>125</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>124</v>
-      </c>
-      <c r="G28" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>Education de Base</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Education de Base</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>Education Secondaire</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Education Secondaire</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>Education Post Secondaire</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Education Post Secondaire</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>Santé de Base</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Santé de Base</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>Maladies non-transmissibles (MNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Maladies non-transmissibles (MNT)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>Distribution d'Eau et Assainissement</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Distribution d'Eau et Assainissement</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>Conflits, Paix et Sécurité</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflits, Paix et Sécurité</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>Infrastructure et Services Sociaux Divers</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Infrastructure et Services Sociaux Divers</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>Transports et Entreposage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transports et Entreposage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
     <t>230</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>Production d'électricité, sources renouvelables</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Production d'électricité, sources renouvelables</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>Production d'électricité, sources non renouvelables</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Production d'électricité, sources non renouvelables</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>Centrales nucléaires</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrales nucléaires</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>Distribution de l'énergie</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribution de l'énergie</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>Banques et Services Financiers</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banques et Services Financiers</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>Entreprises et Autres Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Entreprises et Autres Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,15 +967,15 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>310</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>Sylviculture</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Sylviculture</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>Pêche</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pêche</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,15 +1165,15 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Extractives</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Industries Extractives</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,24 +1357,24 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>Politique Commerciale et Réglementations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Politique Commerciale et Réglementations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>Tourisme</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourisme</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>Protection de l'Environnement Général</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protection de l'Environnement Général</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>Autres Multisecteurs</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Autres Multisecteurs</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>Soutien Budgétaire</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Soutien Budgétaire</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>Aide Alimentaire Dévelopmentale</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Aide Alimentaire Dévelopmentale</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>Aide sous forme de Produits, Autre</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Aide sous forme de Produits, Autre</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>Actions se Rapportant a la Dette</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actions se Rapportant a la Dette</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>Intervention d'Urgence</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Intervention d'Urgence</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>Reconstruction &amp; Réhabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction &amp; Réhabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>Prévention catastrophes/Préparation à leur survenue</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prévention catastrophes/Préparation à leur survenue</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>Frais Administratifs des Donneurs</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Frais Administratifs des Donneurs</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>Refugiés dans les Pays Donneurs</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiés dans les Pays Donneurs</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>Non Affecté / Non Specifié</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Non Affecté / Non Specifié</t>
   </si>
   <si>
     <t>99820</t>
@@ -2764,13 +2764,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2787,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2810,13 +2810,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2833,13 +2833,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2856,13 +2856,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2879,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2902,13 +2902,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2925,13 +2925,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2971,13 +2971,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2994,13 +2994,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3017,13 +3017,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3040,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3063,13 +3063,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3086,13 +3086,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3109,13 +3109,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3638,13 +3638,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3661,13 +3661,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3684,13 +3684,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3707,13 +3707,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3730,13 +3730,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3753,13 +3753,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3776,13 +3776,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3799,13 +3799,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3822,13 +3822,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3845,13 +3845,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3868,13 +3868,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3891,13 +3891,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3914,13 +3914,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3937,13 +3937,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3960,13 +3960,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3983,13 +3983,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4006,13 +4006,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4029,13 +4029,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4052,13 +4052,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4075,13 +4075,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4098,13 +4098,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4121,13 +4121,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4578,13 +4578,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4788,13 +4788,13 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F120" t="s">
         <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4811,13 +4811,13 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F121" t="s">
         <v>294</v>
       </c>
       <c r="G121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4834,13 +4834,13 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F122" t="s">
         <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4857,13 +4857,13 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F123" t="s">
         <v>294</v>
       </c>
       <c r="G123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4880,13 +4880,13 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F124" t="s">
         <v>294</v>
       </c>
       <c r="G124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4903,13 +4903,13 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F125" t="s">
         <v>294</v>
       </c>
       <c r="G125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4926,13 +4926,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F126" t="s">
         <v>308</v>
       </c>
       <c r="G126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4949,13 +4949,13 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F127" t="s">
         <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4972,13 +4972,13 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F128" t="s">
         <v>308</v>
       </c>
       <c r="G128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4995,13 +4995,13 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F129" t="s">
         <v>308</v>
       </c>
       <c r="G129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6375,13 +6375,13 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F189" t="s">
         <v>452</v>
       </c>
       <c r="G189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6398,13 +6398,13 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F190" t="s">
         <v>452</v>
       </c>
       <c r="G190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6421,13 +6421,13 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F191" t="s">
         <v>452</v>
       </c>
       <c r="G191" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6444,13 +6444,13 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F192" t="s">
         <v>452</v>
       </c>
       <c r="G192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6467,13 +6467,13 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F193" t="s">
         <v>452</v>
       </c>
       <c r="G193" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6490,13 +6490,13 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F194" t="s">
         <v>452</v>
       </c>
       <c r="G194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6513,13 +6513,13 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F195" t="s">
         <v>466</v>
       </c>
       <c r="G195" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6536,13 +6536,13 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F196" t="s">
         <v>470</v>
       </c>
       <c r="G196" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6559,13 +6559,13 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F197" t="s">
         <v>470</v>
       </c>
       <c r="G197" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6582,13 +6582,13 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F198" t="s">
         <v>470</v>
       </c>
       <c r="G198" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6605,13 +6605,13 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F199" t="s">
         <v>470</v>
       </c>
       <c r="G199" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6628,13 +6628,13 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F200" t="s">
         <v>470</v>
       </c>
       <c r="G200" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6651,13 +6651,13 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F201" t="s">
         <v>470</v>
       </c>
       <c r="G201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6674,13 +6674,13 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F202" t="s">
         <v>484</v>
       </c>
       <c r="G202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6697,13 +6697,13 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F203" t="s">
         <v>484</v>
       </c>
       <c r="G203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6720,13 +6720,13 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F204" t="s">
         <v>484</v>
       </c>
       <c r="G204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6743,13 +6743,13 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F205" t="s">
         <v>484</v>
       </c>
       <c r="G205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6766,13 +6766,13 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F206" t="s">
         <v>484</v>
       </c>
       <c r="G206" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6789,13 +6789,13 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F207" t="s">
         <v>484</v>
       </c>
       <c r="G207" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6812,13 +6812,13 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F208" t="s">
         <v>484</v>
       </c>
       <c r="G208" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6835,13 +6835,13 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F209" t="s">
         <v>484</v>
       </c>
       <c r="G209" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6858,13 +6858,13 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F210" t="s">
         <v>484</v>
       </c>
       <c r="G210" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6881,13 +6881,13 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F211" t="s">
         <v>484</v>
       </c>
       <c r="G211" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6904,13 +6904,13 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F212" t="s">
         <v>506</v>
       </c>
       <c r="G212" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6927,13 +6927,13 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F213" t="s">
         <v>510</v>
       </c>
       <c r="G213" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6950,13 +6950,13 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F214" t="s">
         <v>514</v>
       </c>
       <c r="G214" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6973,13 +6973,13 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F215" t="s">
         <v>514</v>
       </c>
       <c r="G215" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6996,13 +6996,13 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F216" t="s">
         <v>520</v>
       </c>
       <c r="G216" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7019,13 +7019,13 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F217" t="s">
         <v>520</v>
       </c>
       <c r="G217" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7042,13 +7042,13 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F218" t="s">
         <v>520</v>
       </c>
       <c r="G218" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7065,13 +7065,13 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F219" t="s">
         <v>520</v>
       </c>
       <c r="G219" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7088,13 +7088,13 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F220" t="s">
         <v>520</v>
       </c>
       <c r="G220" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7111,13 +7111,13 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F221" t="s">
         <v>520</v>
       </c>
       <c r="G221" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7134,13 +7134,13 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F222" t="s">
         <v>520</v>
       </c>
       <c r="G222" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7157,13 +7157,13 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F223" t="s">
         <v>536</v>
       </c>
       <c r="G223" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7180,13 +7180,13 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F224" t="s">
         <v>536</v>
       </c>
       <c r="G224" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7203,13 +7203,13 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F225" t="s">
         <v>536</v>
       </c>
       <c r="G225" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7226,13 +7226,13 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F226" t="s">
         <v>544</v>
       </c>
       <c r="G226" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7249,13 +7249,13 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F227" t="s">
         <v>548</v>
       </c>
       <c r="G227" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7272,13 +7272,13 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F228" t="s">
         <v>552</v>
       </c>
       <c r="G228" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7295,13 +7295,13 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F229" t="s">
         <v>556</v>
       </c>
       <c r="G229" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7318,13 +7318,13 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F230" t="s">
         <v>560</v>
       </c>
       <c r="G230" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7341,13 +7341,13 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F231" t="s">
         <v>560</v>
       </c>
       <c r="G231" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Education de Base</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Education Secondaire</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Education Post Secondaire</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
     <t>Santé</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Santé de Base</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Maladies non-transmissibles (MNT)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Distribution d'Eau et Assainissement</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflits, Paix et Sécurité</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Infrastructure et Services Sociaux Divers</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transports et Entreposage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
     <t>Energie</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources renouvelables</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources non renouvelables</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Centrales nucléaires</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Distribution de l'énergie</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banques et Services Financiers</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Entreprises et Autres Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Sylviculture</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Pêche</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Industries Extractives</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,24 +1357,24 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Politique Commerciale et Réglementations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourisme</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>Protection de l'Environnement Général</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Autres Multisecteurs</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>Soutien Budgétaire</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Aide Alimentaire Dévelopmentale</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Aide sous forme de Produits, Autre</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Actions se Rapportant a la Dette</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Intervention d'Urgence</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction &amp; Réhabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Prévention catastrophes/Préparation à leur survenue</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Frais Administratifs des Donneurs</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugiés dans les Pays Donneurs</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Non Affecté / Non Specifié</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -4578,13 +4578,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -28,12 +28,12 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
@@ -49,12 +49,12 @@
     <t>111</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
     <t>Education</t>
   </si>
   <si>
@@ -151,12 +151,12 @@
     <t>121</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
     <t>Santé</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>151</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>231</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
     <t>Energie</t>
   </si>
   <si>
@@ -970,12 +970,12 @@
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
@@ -1168,10 +1168,10 @@
     <t>321</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
   </si>
   <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
@@ -2166,10 +2166,10 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2189,10 +2189,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2212,10 +2212,10 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2235,10 +2235,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2258,10 +2258,10 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2281,10 +2281,10 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2304,10 +2304,10 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2327,10 +2327,10 @@
         <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2442,10 +2442,10 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2465,10 +2465,10 @@
         <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2488,10 +2488,10 @@
         <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2511,10 +2511,10 @@
         <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2534,10 +2534,10 @@
         <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2557,10 +2557,10 @@
         <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2580,10 +2580,10 @@
         <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2603,10 +2603,10 @@
         <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2626,10 +2626,10 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2649,10 +2649,10 @@
         <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2672,10 +2672,10 @@
         <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2695,10 +2695,10 @@
         <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2718,10 +2718,10 @@
         <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2741,10 +2741,10 @@
         <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -2764,10 +2764,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" t="s">
-        <v>89</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2787,10 +2787,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" t="s">
         <v>88</v>
-      </c>
-      <c r="F33" t="s">
-        <v>89</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2810,10 +2810,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" t="s">
         <v>88</v>
-      </c>
-      <c r="F34" t="s">
-        <v>89</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2833,10 +2833,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" t="s">
         <v>88</v>
-      </c>
-      <c r="F35" t="s">
-        <v>89</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2856,10 +2856,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" t="s">
         <v>88</v>
-      </c>
-      <c r="F36" t="s">
-        <v>89</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2879,10 +2879,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
         <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>101</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2902,10 +2902,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" t="s">
         <v>100</v>
-      </c>
-      <c r="F38" t="s">
-        <v>101</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2925,10 +2925,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
         <v>100</v>
-      </c>
-      <c r="F39" t="s">
-        <v>101</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2948,10 +2948,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
         <v>100</v>
-      </c>
-      <c r="F40" t="s">
-        <v>101</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2971,10 +2971,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
         <v>100</v>
-      </c>
-      <c r="F41" t="s">
-        <v>101</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2994,10 +2994,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
         <v>100</v>
-      </c>
-      <c r="F42" t="s">
-        <v>101</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3017,10 +3017,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
         <v>100</v>
-      </c>
-      <c r="F43" t="s">
-        <v>101</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3040,10 +3040,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
         <v>100</v>
-      </c>
-      <c r="F44" t="s">
-        <v>101</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3063,10 +3063,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" t="s">
         <v>100</v>
-      </c>
-      <c r="F45" t="s">
-        <v>101</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3086,10 +3086,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
         <v>100</v>
-      </c>
-      <c r="F46" t="s">
-        <v>101</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3109,10 +3109,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
         <v>100</v>
-      </c>
-      <c r="F47" t="s">
-        <v>101</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3500,10 +3500,10 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3523,10 +3523,10 @@
         <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3546,10 +3546,10 @@
         <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3569,10 +3569,10 @@
         <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3592,10 +3592,10 @@
         <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3615,10 +3615,10 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -3638,10 +3638,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s">
         <v>174</v>
-      </c>
-      <c r="F70" t="s">
-        <v>175</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3661,10 +3661,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71" t="s">
         <v>174</v>
-      </c>
-      <c r="F71" t="s">
-        <v>175</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3684,10 +3684,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>175</v>
+      </c>
+      <c r="F72" t="s">
         <v>174</v>
-      </c>
-      <c r="F72" t="s">
-        <v>175</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3707,10 +3707,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" t="s">
         <v>174</v>
-      </c>
-      <c r="F73" t="s">
-        <v>175</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3730,10 +3730,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" t="s">
         <v>174</v>
-      </c>
-      <c r="F74" t="s">
-        <v>175</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3753,10 +3753,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>175</v>
+      </c>
+      <c r="F75" t="s">
         <v>174</v>
-      </c>
-      <c r="F75" t="s">
-        <v>175</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3776,10 +3776,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>175</v>
+      </c>
+      <c r="F76" t="s">
         <v>174</v>
-      </c>
-      <c r="F76" t="s">
-        <v>175</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3799,10 +3799,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>175</v>
+      </c>
+      <c r="F77" t="s">
         <v>174</v>
-      </c>
-      <c r="F77" t="s">
-        <v>175</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3822,10 +3822,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>175</v>
+      </c>
+      <c r="F78" t="s">
         <v>174</v>
-      </c>
-      <c r="F78" t="s">
-        <v>175</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3845,10 +3845,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>175</v>
+      </c>
+      <c r="F79" t="s">
         <v>174</v>
-      </c>
-      <c r="F79" t="s">
-        <v>175</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3868,10 +3868,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>175</v>
+      </c>
+      <c r="F80" t="s">
         <v>174</v>
-      </c>
-      <c r="F80" t="s">
-        <v>175</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3891,10 +3891,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" t="s">
         <v>198</v>
-      </c>
-      <c r="F81" t="s">
-        <v>199</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3914,10 +3914,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>199</v>
+      </c>
+      <c r="F82" t="s">
         <v>198</v>
-      </c>
-      <c r="F82" t="s">
-        <v>199</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3937,10 +3937,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>199</v>
+      </c>
+      <c r="F83" t="s">
         <v>198</v>
-      </c>
-      <c r="F83" t="s">
-        <v>199</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3960,10 +3960,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>199</v>
+      </c>
+      <c r="F84" t="s">
         <v>198</v>
-      </c>
-      <c r="F84" t="s">
-        <v>199</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3983,10 +3983,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>199</v>
+      </c>
+      <c r="F85" t="s">
         <v>198</v>
-      </c>
-      <c r="F85" t="s">
-        <v>199</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4006,10 +4006,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" t="s">
         <v>198</v>
-      </c>
-      <c r="F86" t="s">
-        <v>199</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4029,10 +4029,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>199</v>
+      </c>
+      <c r="F87" t="s">
         <v>198</v>
-      </c>
-      <c r="F87" t="s">
-        <v>199</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4052,10 +4052,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>215</v>
+      </c>
+      <c r="F88" t="s">
         <v>214</v>
-      </c>
-      <c r="F88" t="s">
-        <v>215</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4075,10 +4075,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>215</v>
+      </c>
+      <c r="F89" t="s">
         <v>214</v>
-      </c>
-      <c r="F89" t="s">
-        <v>215</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4098,10 +4098,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>215</v>
+      </c>
+      <c r="F90" t="s">
         <v>214</v>
-      </c>
-      <c r="F90" t="s">
-        <v>215</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4121,10 +4121,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>215</v>
+      </c>
+      <c r="F91" t="s">
         <v>214</v>
-      </c>
-      <c r="F91" t="s">
-        <v>215</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4236,10 +4236,10 @@
         <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4259,10 +4259,10 @@
         <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4282,10 +4282,10 @@
         <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4305,10 +4305,10 @@
         <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4328,10 +4328,10 @@
         <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4351,10 +4351,10 @@
         <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4374,10 +4374,10 @@
         <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4397,10 +4397,10 @@
         <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4420,10 +4420,10 @@
         <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4443,10 +4443,10 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4466,10 +4466,10 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4489,10 +4489,10 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4512,10 +4512,10 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4535,10 +4535,10 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4558,10 +4558,10 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4581,10 +4581,10 @@
         <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="F111" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4604,10 +4604,10 @@
         <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="F112" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4627,10 +4627,10 @@
         <v>277</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4650,10 +4650,10 @@
         <v>277</v>
       </c>
       <c r="E114" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F114" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4673,10 +4673,10 @@
         <v>277</v>
       </c>
       <c r="E115" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F115" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4696,10 +4696,10 @@
         <v>277</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F116" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4719,10 +4719,10 @@
         <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4742,10 +4742,10 @@
         <v>277</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4765,10 +4765,10 @@
         <v>277</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F119" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -4788,10 +4788,10 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
+        <v>294</v>
+      </c>
+      <c r="F120" t="s">
         <v>293</v>
-      </c>
-      <c r="F120" t="s">
-        <v>294</v>
       </c>
       <c r="G120" t="s">
         <v>294</v>
@@ -4811,10 +4811,10 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
+        <v>294</v>
+      </c>
+      <c r="F121" t="s">
         <v>293</v>
-      </c>
-      <c r="F121" t="s">
-        <v>294</v>
       </c>
       <c r="G121" t="s">
         <v>294</v>
@@ -4834,10 +4834,10 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
+        <v>294</v>
+      </c>
+      <c r="F122" t="s">
         <v>293</v>
-      </c>
-      <c r="F122" t="s">
-        <v>294</v>
       </c>
       <c r="G122" t="s">
         <v>294</v>
@@ -4857,10 +4857,10 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
+        <v>294</v>
+      </c>
+      <c r="F123" t="s">
         <v>293</v>
-      </c>
-      <c r="F123" t="s">
-        <v>294</v>
       </c>
       <c r="G123" t="s">
         <v>294</v>
@@ -4880,10 +4880,10 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
+        <v>294</v>
+      </c>
+      <c r="F124" t="s">
         <v>293</v>
-      </c>
-      <c r="F124" t="s">
-        <v>294</v>
       </c>
       <c r="G124" t="s">
         <v>294</v>
@@ -4903,10 +4903,10 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
+        <v>294</v>
+      </c>
+      <c r="F125" t="s">
         <v>293</v>
-      </c>
-      <c r="F125" t="s">
-        <v>294</v>
       </c>
       <c r="G125" t="s">
         <v>294</v>
@@ -4926,10 +4926,10 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
+        <v>308</v>
+      </c>
+      <c r="F126" t="s">
         <v>307</v>
-      </c>
-      <c r="F126" t="s">
-        <v>308</v>
       </c>
       <c r="G126" t="s">
         <v>308</v>
@@ -4949,10 +4949,10 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
+        <v>308</v>
+      </c>
+      <c r="F127" t="s">
         <v>307</v>
-      </c>
-      <c r="F127" t="s">
-        <v>308</v>
       </c>
       <c r="G127" t="s">
         <v>308</v>
@@ -4972,10 +4972,10 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
+        <v>308</v>
+      </c>
+      <c r="F128" t="s">
         <v>307</v>
-      </c>
-      <c r="F128" t="s">
-        <v>308</v>
       </c>
       <c r="G128" t="s">
         <v>308</v>
@@ -4995,10 +4995,10 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
+        <v>308</v>
+      </c>
+      <c r="F129" t="s">
         <v>307</v>
-      </c>
-      <c r="F129" t="s">
-        <v>308</v>
       </c>
       <c r="G129" t="s">
         <v>308</v>
@@ -5432,10 +5432,10 @@
         <v>357</v>
       </c>
       <c r="E148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F148" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G148" t="s">
         <v>320</v>
@@ -5455,10 +5455,10 @@
         <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F149" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G149" t="s">
         <v>320</v>
@@ -5478,10 +5478,10 @@
         <v>357</v>
       </c>
       <c r="E150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F150" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G150" t="s">
         <v>320</v>
@@ -5501,10 +5501,10 @@
         <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F151" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G151" t="s">
         <v>320</v>
@@ -5524,10 +5524,10 @@
         <v>357</v>
       </c>
       <c r="E152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F152" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G152" t="s">
         <v>320</v>
@@ -5547,10 +5547,10 @@
         <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F153" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G153" t="s">
         <v>320</v>
@@ -5570,10 +5570,10 @@
         <v>371</v>
       </c>
       <c r="E154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F154" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G154" t="s">
         <v>320</v>
@@ -5593,10 +5593,10 @@
         <v>371</v>
       </c>
       <c r="E155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F155" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G155" t="s">
         <v>320</v>
@@ -5616,10 +5616,10 @@
         <v>371</v>
       </c>
       <c r="E156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F156" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G156" t="s">
         <v>320</v>
@@ -5639,10 +5639,10 @@
         <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G157" t="s">
         <v>320</v>
@@ -5662,10 +5662,10 @@
         <v>371</v>
       </c>
       <c r="E158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F158" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G158" t="s">
         <v>320</v>
@@ -6122,10 +6122,10 @@
         <v>425</v>
       </c>
       <c r="E178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F178" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G178" t="s">
         <v>386</v>
@@ -6145,10 +6145,10 @@
         <v>425</v>
       </c>
       <c r="E179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F179" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G179" t="s">
         <v>386</v>
@@ -6168,10 +6168,10 @@
         <v>425</v>
       </c>
       <c r="E180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F180" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G180" t="s">
         <v>386</v>
@@ -6191,10 +6191,10 @@
         <v>425</v>
       </c>
       <c r="E181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F181" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G181" t="s">
         <v>386</v>
@@ -6214,10 +6214,10 @@
         <v>425</v>
       </c>
       <c r="E182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F182" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G182" t="s">
         <v>386</v>
@@ -6237,10 +6237,10 @@
         <v>425</v>
       </c>
       <c r="E183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F183" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G183" t="s">
         <v>386</v>
@@ -6260,10 +6260,10 @@
         <v>425</v>
       </c>
       <c r="E184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F184" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G184" t="s">
         <v>386</v>
@@ -6283,10 +6283,10 @@
         <v>425</v>
       </c>
       <c r="E185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F185" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G185" t="s">
         <v>386</v>
@@ -6306,10 +6306,10 @@
         <v>425</v>
       </c>
       <c r="E186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F186" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G186" t="s">
         <v>386</v>
@@ -6329,10 +6329,10 @@
         <v>425</v>
       </c>
       <c r="E187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F187" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G187" t="s">
         <v>386</v>
@@ -6352,10 +6352,10 @@
         <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="F188" t="s">
-        <v>448</v>
+        <v>385</v>
       </c>
       <c r="G188" t="s">
         <v>386</v>
@@ -6375,10 +6375,10 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
+        <v>452</v>
+      </c>
+      <c r="F189" t="s">
         <v>451</v>
-      </c>
-      <c r="F189" t="s">
-        <v>452</v>
       </c>
       <c r="G189" t="s">
         <v>452</v>
@@ -6398,10 +6398,10 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
+        <v>452</v>
+      </c>
+      <c r="F190" t="s">
         <v>451</v>
-      </c>
-      <c r="F190" t="s">
-        <v>452</v>
       </c>
       <c r="G190" t="s">
         <v>452</v>
@@ -6421,10 +6421,10 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
+        <v>452</v>
+      </c>
+      <c r="F191" t="s">
         <v>451</v>
-      </c>
-      <c r="F191" t="s">
-        <v>452</v>
       </c>
       <c r="G191" t="s">
         <v>452</v>
@@ -6444,10 +6444,10 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
+        <v>452</v>
+      </c>
+      <c r="F192" t="s">
         <v>451</v>
-      </c>
-      <c r="F192" t="s">
-        <v>452</v>
       </c>
       <c r="G192" t="s">
         <v>452</v>
@@ -6467,10 +6467,10 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
+        <v>452</v>
+      </c>
+      <c r="F193" t="s">
         <v>451</v>
-      </c>
-      <c r="F193" t="s">
-        <v>452</v>
       </c>
       <c r="G193" t="s">
         <v>452</v>
@@ -6490,10 +6490,10 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
+        <v>452</v>
+      </c>
+      <c r="F194" t="s">
         <v>451</v>
-      </c>
-      <c r="F194" t="s">
-        <v>452</v>
       </c>
       <c r="G194" t="s">
         <v>452</v>
@@ -6513,10 +6513,10 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
+        <v>466</v>
+      </c>
+      <c r="F195" t="s">
         <v>465</v>
-      </c>
-      <c r="F195" t="s">
-        <v>466</v>
       </c>
       <c r="G195" t="s">
         <v>466</v>
@@ -6536,10 +6536,10 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
+        <v>470</v>
+      </c>
+      <c r="F196" t="s">
         <v>469</v>
-      </c>
-      <c r="F196" t="s">
-        <v>470</v>
       </c>
       <c r="G196" t="s">
         <v>470</v>
@@ -6559,10 +6559,10 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
+        <v>470</v>
+      </c>
+      <c r="F197" t="s">
         <v>469</v>
-      </c>
-      <c r="F197" t="s">
-        <v>470</v>
       </c>
       <c r="G197" t="s">
         <v>470</v>
@@ -6582,10 +6582,10 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
+        <v>470</v>
+      </c>
+      <c r="F198" t="s">
         <v>469</v>
-      </c>
-      <c r="F198" t="s">
-        <v>470</v>
       </c>
       <c r="G198" t="s">
         <v>470</v>
@@ -6605,10 +6605,10 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
+        <v>470</v>
+      </c>
+      <c r="F199" t="s">
         <v>469</v>
-      </c>
-      <c r="F199" t="s">
-        <v>470</v>
       </c>
       <c r="G199" t="s">
         <v>470</v>
@@ -6628,10 +6628,10 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
+        <v>470</v>
+      </c>
+      <c r="F200" t="s">
         <v>469</v>
-      </c>
-      <c r="F200" t="s">
-        <v>470</v>
       </c>
       <c r="G200" t="s">
         <v>470</v>
@@ -6651,10 +6651,10 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
+        <v>470</v>
+      </c>
+      <c r="F201" t="s">
         <v>469</v>
-      </c>
-      <c r="F201" t="s">
-        <v>470</v>
       </c>
       <c r="G201" t="s">
         <v>470</v>
@@ -6674,10 +6674,10 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
+        <v>484</v>
+      </c>
+      <c r="F202" t="s">
         <v>483</v>
-      </c>
-      <c r="F202" t="s">
-        <v>484</v>
       </c>
       <c r="G202" t="s">
         <v>484</v>
@@ -6697,10 +6697,10 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
+        <v>484</v>
+      </c>
+      <c r="F203" t="s">
         <v>483</v>
-      </c>
-      <c r="F203" t="s">
-        <v>484</v>
       </c>
       <c r="G203" t="s">
         <v>484</v>
@@ -6720,10 +6720,10 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
+        <v>484</v>
+      </c>
+      <c r="F204" t="s">
         <v>483</v>
-      </c>
-      <c r="F204" t="s">
-        <v>484</v>
       </c>
       <c r="G204" t="s">
         <v>484</v>
@@ -6743,10 +6743,10 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
+        <v>484</v>
+      </c>
+      <c r="F205" t="s">
         <v>483</v>
-      </c>
-      <c r="F205" t="s">
-        <v>484</v>
       </c>
       <c r="G205" t="s">
         <v>484</v>
@@ -6766,10 +6766,10 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
+        <v>484</v>
+      </c>
+      <c r="F206" t="s">
         <v>483</v>
-      </c>
-      <c r="F206" t="s">
-        <v>484</v>
       </c>
       <c r="G206" t="s">
         <v>484</v>
@@ -6789,10 +6789,10 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
+        <v>484</v>
+      </c>
+      <c r="F207" t="s">
         <v>483</v>
-      </c>
-      <c r="F207" t="s">
-        <v>484</v>
       </c>
       <c r="G207" t="s">
         <v>484</v>
@@ -6812,10 +6812,10 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
+        <v>484</v>
+      </c>
+      <c r="F208" t="s">
         <v>483</v>
-      </c>
-      <c r="F208" t="s">
-        <v>484</v>
       </c>
       <c r="G208" t="s">
         <v>484</v>
@@ -6835,10 +6835,10 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
+        <v>484</v>
+      </c>
+      <c r="F209" t="s">
         <v>483</v>
-      </c>
-      <c r="F209" t="s">
-        <v>484</v>
       </c>
       <c r="G209" t="s">
         <v>484</v>
@@ -6858,10 +6858,10 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
+        <v>484</v>
+      </c>
+      <c r="F210" t="s">
         <v>483</v>
-      </c>
-      <c r="F210" t="s">
-        <v>484</v>
       </c>
       <c r="G210" t="s">
         <v>484</v>
@@ -6881,10 +6881,10 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
+        <v>484</v>
+      </c>
+      <c r="F211" t="s">
         <v>483</v>
-      </c>
-      <c r="F211" t="s">
-        <v>484</v>
       </c>
       <c r="G211" t="s">
         <v>484</v>
@@ -6904,10 +6904,10 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
+        <v>506</v>
+      </c>
+      <c r="F212" t="s">
         <v>505</v>
-      </c>
-      <c r="F212" t="s">
-        <v>506</v>
       </c>
       <c r="G212" t="s">
         <v>506</v>
@@ -6927,10 +6927,10 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
+        <v>510</v>
+      </c>
+      <c r="F213" t="s">
         <v>509</v>
-      </c>
-      <c r="F213" t="s">
-        <v>510</v>
       </c>
       <c r="G213" t="s">
         <v>510</v>
@@ -6950,10 +6950,10 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
+        <v>514</v>
+      </c>
+      <c r="F214" t="s">
         <v>513</v>
-      </c>
-      <c r="F214" t="s">
-        <v>514</v>
       </c>
       <c r="G214" t="s">
         <v>514</v>
@@ -6973,10 +6973,10 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
+        <v>514</v>
+      </c>
+      <c r="F215" t="s">
         <v>513</v>
-      </c>
-      <c r="F215" t="s">
-        <v>514</v>
       </c>
       <c r="G215" t="s">
         <v>514</v>
@@ -6996,10 +6996,10 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
+        <v>520</v>
+      </c>
+      <c r="F216" t="s">
         <v>519</v>
-      </c>
-      <c r="F216" t="s">
-        <v>520</v>
       </c>
       <c r="G216" t="s">
         <v>520</v>
@@ -7019,10 +7019,10 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
+        <v>520</v>
+      </c>
+      <c r="F217" t="s">
         <v>519</v>
-      </c>
-      <c r="F217" t="s">
-        <v>520</v>
       </c>
       <c r="G217" t="s">
         <v>520</v>
@@ -7042,10 +7042,10 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
+        <v>520</v>
+      </c>
+      <c r="F218" t="s">
         <v>519</v>
-      </c>
-      <c r="F218" t="s">
-        <v>520</v>
       </c>
       <c r="G218" t="s">
         <v>520</v>
@@ -7065,10 +7065,10 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
+        <v>520</v>
+      </c>
+      <c r="F219" t="s">
         <v>519</v>
-      </c>
-      <c r="F219" t="s">
-        <v>520</v>
       </c>
       <c r="G219" t="s">
         <v>520</v>
@@ -7088,10 +7088,10 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
+        <v>520</v>
+      </c>
+      <c r="F220" t="s">
         <v>519</v>
-      </c>
-      <c r="F220" t="s">
-        <v>520</v>
       </c>
       <c r="G220" t="s">
         <v>520</v>
@@ -7111,10 +7111,10 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
+        <v>520</v>
+      </c>
+      <c r="F221" t="s">
         <v>519</v>
-      </c>
-      <c r="F221" t="s">
-        <v>520</v>
       </c>
       <c r="G221" t="s">
         <v>520</v>
@@ -7134,10 +7134,10 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
+        <v>520</v>
+      </c>
+      <c r="F222" t="s">
         <v>519</v>
-      </c>
-      <c r="F222" t="s">
-        <v>520</v>
       </c>
       <c r="G222" t="s">
         <v>520</v>
@@ -7157,10 +7157,10 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
+        <v>536</v>
+      </c>
+      <c r="F223" t="s">
         <v>535</v>
-      </c>
-      <c r="F223" t="s">
-        <v>536</v>
       </c>
       <c r="G223" t="s">
         <v>536</v>
@@ -7180,10 +7180,10 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
+        <v>536</v>
+      </c>
+      <c r="F224" t="s">
         <v>535</v>
-      </c>
-      <c r="F224" t="s">
-        <v>536</v>
       </c>
       <c r="G224" t="s">
         <v>536</v>
@@ -7203,10 +7203,10 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
+        <v>536</v>
+      </c>
+      <c r="F225" t="s">
         <v>535</v>
-      </c>
-      <c r="F225" t="s">
-        <v>536</v>
       </c>
       <c r="G225" t="s">
         <v>536</v>
@@ -7226,10 +7226,10 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
+        <v>544</v>
+      </c>
+      <c r="F226" t="s">
         <v>543</v>
-      </c>
-      <c r="F226" t="s">
-        <v>544</v>
       </c>
       <c r="G226" t="s">
         <v>544</v>
@@ -7249,10 +7249,10 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
+        <v>548</v>
+      </c>
+      <c r="F227" t="s">
         <v>547</v>
-      </c>
-      <c r="F227" t="s">
-        <v>548</v>
       </c>
       <c r="G227" t="s">
         <v>548</v>
@@ -7272,10 +7272,10 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
+        <v>552</v>
+      </c>
+      <c r="F228" t="s">
         <v>551</v>
-      </c>
-      <c r="F228" t="s">
-        <v>552</v>
       </c>
       <c r="G228" t="s">
         <v>552</v>
@@ -7295,10 +7295,10 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
+        <v>556</v>
+      </c>
+      <c r="F229" t="s">
         <v>555</v>
-      </c>
-      <c r="F229" t="s">
-        <v>556</v>
       </c>
       <c r="G229" t="s">
         <v>556</v>
@@ -7318,10 +7318,10 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
+        <v>560</v>
+      </c>
+      <c r="F230" t="s">
         <v>559</v>
-      </c>
-      <c r="F230" t="s">
-        <v>560</v>
       </c>
       <c r="G230" t="s">
         <v>560</v>
@@ -7341,10 +7341,10 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
+        <v>560</v>
+      </c>
+      <c r="F231" t="s">
         <v>559</v>
-      </c>
-      <c r="F231" t="s">
-        <v>560</v>
       </c>
       <c r="G231" t="s">
         <v>560</v>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>Santé, Général</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>Politique de l'énergie</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Agriculture</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1171,10 +1171,10 @@
     <t>Industries Manufacturières</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
     <t>32120</t>
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>293</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>293</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>293</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>293</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>293</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>293</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>307</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>307</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>307</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>307</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>451</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>451</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>451</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>451</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>451</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>451</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>465</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>469</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>469</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>469</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>469</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>469</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>469</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>483</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>483</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>483</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>483</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>483</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>483</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>483</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>483</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>483</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>483</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>505</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>509</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>513</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>513</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>519</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>519</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>519</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>519</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>519</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>519</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>519</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>535</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>535</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>535</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>543</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>547</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>551</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>555</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>559</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>559</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>Education de Base</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Education de Base</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>Education Secondaire</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Education Secondaire</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>Education Post Secondaire</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Education Post Secondaire</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>Santé de Base</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Santé de Base</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>Maladies non-transmissibles (MNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Maladies non-transmissibles (MNT)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>Conflits, Paix et Sécurité</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflits, Paix et Sécurité</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>Production d'électricité, sources renouvelables</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Production d'électricité, sources renouvelables</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>Production d'électricité, sources non renouvelables</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Production d'électricité, sources non renouvelables</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>Centrales nucléaires</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrales nucléaires</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>Distribution de l'énergie</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribution de l'énergie</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>Sylviculture</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Sylviculture</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>Pêche</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pêche</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Extractives</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Industries Extractives</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,10 +1357,10 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>33110</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>39</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>39</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
-      </c>
-      <c r="E18" t="s">
-        <v>57</v>
       </c>
       <c r="F18" t="s">
         <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>57</v>
       </c>
       <c r="F19" t="s">
         <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>57</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
-      </c>
-      <c r="E21" t="s">
-        <v>57</v>
       </c>
       <c r="F21" t="s">
         <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
-      </c>
-      <c r="E22" t="s">
-        <v>57</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
-      </c>
-      <c r="E23" t="s">
-        <v>57</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
-      </c>
-      <c r="E24" t="s">
-        <v>57</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
-      </c>
-      <c r="E25" t="s">
-        <v>57</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
       </c>
       <c r="G25" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
-      </c>
-      <c r="E26" t="s">
-        <v>75</v>
       </c>
       <c r="F26" t="s">
         <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
-      </c>
-      <c r="E27" t="s">
-        <v>75</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
-      </c>
-      <c r="E28" t="s">
-        <v>75</v>
       </c>
       <c r="F28" t="s">
         <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
-      </c>
-      <c r="E29" t="s">
-        <v>75</v>
       </c>
       <c r="F29" t="s">
         <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
-      </c>
-      <c r="E30" t="s">
-        <v>75</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
-      </c>
-      <c r="E31" t="s">
-        <v>75</v>
       </c>
       <c r="F31" t="s">
         <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
-      </c>
-      <c r="E64" t="s">
-        <v>161</v>
       </c>
       <c r="F64" t="s">
         <v>126</v>
       </c>
       <c r="G64" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
-      </c>
-      <c r="E65" t="s">
-        <v>161</v>
       </c>
       <c r="F65" t="s">
         <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
-      </c>
-      <c r="E66" t="s">
-        <v>161</v>
       </c>
       <c r="F66" t="s">
         <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
-      </c>
-      <c r="E67" t="s">
-        <v>161</v>
       </c>
       <c r="F67" t="s">
         <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
-      </c>
-      <c r="E68" t="s">
-        <v>161</v>
       </c>
       <c r="F68" t="s">
         <v>126</v>
       </c>
       <c r="G68" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
-      </c>
-      <c r="E69" t="s">
-        <v>161</v>
       </c>
       <c r="F69" t="s">
         <v>126</v>
       </c>
       <c r="G69" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
-      </c>
-      <c r="E96" t="s">
-        <v>237</v>
       </c>
       <c r="F96" t="s">
         <v>226</v>
       </c>
       <c r="G96" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
-      </c>
-      <c r="E97" t="s">
-        <v>237</v>
       </c>
       <c r="F97" t="s">
         <v>226</v>
       </c>
       <c r="G97" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
-      </c>
-      <c r="E98" t="s">
-        <v>237</v>
       </c>
       <c r="F98" t="s">
         <v>226</v>
       </c>
       <c r="G98" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
-      </c>
-      <c r="E99" t="s">
-        <v>237</v>
       </c>
       <c r="F99" t="s">
         <v>226</v>
       </c>
       <c r="G99" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
-      </c>
-      <c r="E100" t="s">
-        <v>237</v>
       </c>
       <c r="F100" t="s">
         <v>226</v>
       </c>
       <c r="G100" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
-      </c>
-      <c r="E101" t="s">
-        <v>237</v>
       </c>
       <c r="F101" t="s">
         <v>226</v>
       </c>
       <c r="G101" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
-      </c>
-      <c r="E102" t="s">
-        <v>237</v>
       </c>
       <c r="F102" t="s">
         <v>226</v>
       </c>
       <c r="G102" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
-      </c>
-      <c r="E103" t="s">
-        <v>237</v>
       </c>
       <c r="F103" t="s">
         <v>226</v>
       </c>
       <c r="G103" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
-      </c>
-      <c r="E104" t="s">
-        <v>237</v>
       </c>
       <c r="F104" t="s">
         <v>226</v>
       </c>
       <c r="G104" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
-      </c>
-      <c r="E105" t="s">
-        <v>257</v>
       </c>
       <c r="F105" t="s">
         <v>226</v>
       </c>
       <c r="G105" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
-      </c>
-      <c r="E106" t="s">
-        <v>257</v>
       </c>
       <c r="F106" t="s">
         <v>226</v>
       </c>
       <c r="G106" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
-      </c>
-      <c r="E107" t="s">
-        <v>257</v>
       </c>
       <c r="F107" t="s">
         <v>226</v>
       </c>
       <c r="G107" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
-      </c>
-      <c r="E108" t="s">
-        <v>257</v>
       </c>
       <c r="F108" t="s">
         <v>226</v>
       </c>
       <c r="G108" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
-      </c>
-      <c r="E109" t="s">
-        <v>257</v>
       </c>
       <c r="F109" t="s">
         <v>226</v>
       </c>
       <c r="G109" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
-      </c>
-      <c r="E110" t="s">
-        <v>257</v>
       </c>
       <c r="F110" t="s">
         <v>226</v>
       </c>
       <c r="G110" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,7 +4578,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="E111" t="s">
         <v>269</v>
@@ -4587,7 +4587,7 @@
         <v>226</v>
       </c>
       <c r="G111" t="s">
-        <v>227</v>
+        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>273</v>
-      </c>
-      <c r="E112" t="s">
-        <v>274</v>
       </c>
       <c r="F112" t="s">
         <v>226</v>
       </c>
       <c r="G112" t="s">
-        <v>227</v>
+        <v>274</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>277</v>
-      </c>
-      <c r="E113" t="s">
-        <v>278</v>
       </c>
       <c r="F113" t="s">
         <v>226</v>
       </c>
       <c r="G113" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>277</v>
-      </c>
-      <c r="E114" t="s">
-        <v>278</v>
       </c>
       <c r="F114" t="s">
         <v>226</v>
       </c>
       <c r="G114" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>277</v>
-      </c>
-      <c r="E115" t="s">
-        <v>278</v>
       </c>
       <c r="F115" t="s">
         <v>226</v>
       </c>
       <c r="G115" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>277</v>
-      </c>
-      <c r="E116" t="s">
-        <v>278</v>
       </c>
       <c r="F116" t="s">
         <v>226</v>
       </c>
       <c r="G116" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>277</v>
-      </c>
-      <c r="E117" t="s">
-        <v>278</v>
       </c>
       <c r="F117" t="s">
         <v>226</v>
       </c>
       <c r="G117" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>277</v>
-      </c>
-      <c r="E118" t="s">
-        <v>278</v>
       </c>
       <c r="F118" t="s">
         <v>226</v>
       </c>
       <c r="G118" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>277</v>
-      </c>
-      <c r="E119" t="s">
-        <v>278</v>
       </c>
       <c r="F119" t="s">
         <v>226</v>
       </c>
       <c r="G119" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>317</v>
+      </c>
+      <c r="E148" t="s">
         <v>357</v>
-      </c>
-      <c r="E148" t="s">
-        <v>358</v>
       </c>
       <c r="F148" t="s">
         <v>319</v>
       </c>
       <c r="G148" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>317</v>
+      </c>
+      <c r="E149" t="s">
         <v>357</v>
-      </c>
-      <c r="E149" t="s">
-        <v>358</v>
       </c>
       <c r="F149" t="s">
         <v>319</v>
       </c>
       <c r="G149" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>317</v>
+      </c>
+      <c r="E150" t="s">
         <v>357</v>
-      </c>
-      <c r="E150" t="s">
-        <v>358</v>
       </c>
       <c r="F150" t="s">
         <v>319</v>
       </c>
       <c r="G150" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>317</v>
+      </c>
+      <c r="E151" t="s">
         <v>357</v>
-      </c>
-      <c r="E151" t="s">
-        <v>358</v>
       </c>
       <c r="F151" t="s">
         <v>319</v>
       </c>
       <c r="G151" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>317</v>
+      </c>
+      <c r="E152" t="s">
         <v>357</v>
-      </c>
-      <c r="E152" t="s">
-        <v>358</v>
       </c>
       <c r="F152" t="s">
         <v>319</v>
       </c>
       <c r="G152" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>317</v>
+      </c>
+      <c r="E153" t="s">
         <v>357</v>
-      </c>
-      <c r="E153" t="s">
-        <v>358</v>
       </c>
       <c r="F153" t="s">
         <v>319</v>
       </c>
       <c r="G153" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>317</v>
+      </c>
+      <c r="E154" t="s">
         <v>371</v>
-      </c>
-      <c r="E154" t="s">
-        <v>372</v>
       </c>
       <c r="F154" t="s">
         <v>319</v>
       </c>
       <c r="G154" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>317</v>
+      </c>
+      <c r="E155" t="s">
         <v>371</v>
-      </c>
-      <c r="E155" t="s">
-        <v>372</v>
       </c>
       <c r="F155" t="s">
         <v>319</v>
       </c>
       <c r="G155" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>317</v>
+      </c>
+      <c r="E156" t="s">
         <v>371</v>
-      </c>
-      <c r="E156" t="s">
-        <v>372</v>
       </c>
       <c r="F156" t="s">
         <v>319</v>
       </c>
       <c r="G156" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>317</v>
+      </c>
+      <c r="E157" t="s">
         <v>371</v>
-      </c>
-      <c r="E157" t="s">
-        <v>372</v>
       </c>
       <c r="F157" t="s">
         <v>319</v>
       </c>
       <c r="G157" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>317</v>
+      </c>
+      <c r="E158" t="s">
         <v>371</v>
-      </c>
-      <c r="E158" t="s">
-        <v>372</v>
       </c>
       <c r="F158" t="s">
         <v>319</v>
       </c>
       <c r="G158" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>383</v>
+      </c>
+      <c r="E178" t="s">
         <v>425</v>
-      </c>
-      <c r="E178" t="s">
-        <v>426</v>
       </c>
       <c r="F178" t="s">
         <v>385</v>
       </c>
       <c r="G178" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>383</v>
+      </c>
+      <c r="E179" t="s">
         <v>425</v>
-      </c>
-      <c r="E179" t="s">
-        <v>426</v>
       </c>
       <c r="F179" t="s">
         <v>385</v>
       </c>
       <c r="G179" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>383</v>
+      </c>
+      <c r="E180" t="s">
         <v>425</v>
-      </c>
-      <c r="E180" t="s">
-        <v>426</v>
       </c>
       <c r="F180" t="s">
         <v>385</v>
       </c>
       <c r="G180" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>383</v>
+      </c>
+      <c r="E181" t="s">
         <v>425</v>
-      </c>
-      <c r="E181" t="s">
-        <v>426</v>
       </c>
       <c r="F181" t="s">
         <v>385</v>
       </c>
       <c r="G181" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>383</v>
+      </c>
+      <c r="E182" t="s">
         <v>425</v>
-      </c>
-      <c r="E182" t="s">
-        <v>426</v>
       </c>
       <c r="F182" t="s">
         <v>385</v>
       </c>
       <c r="G182" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6234,16 +6234,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>383</v>
+      </c>
+      <c r="E183" t="s">
         <v>425</v>
-      </c>
-      <c r="E183" t="s">
-        <v>426</v>
       </c>
       <c r="F183" t="s">
         <v>385</v>
       </c>
       <c r="G183" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6257,16 +6257,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>383</v>
+      </c>
+      <c r="E184" t="s">
         <v>425</v>
-      </c>
-      <c r="E184" t="s">
-        <v>426</v>
       </c>
       <c r="F184" t="s">
         <v>385</v>
       </c>
       <c r="G184" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6280,16 +6280,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>383</v>
+      </c>
+      <c r="E185" t="s">
         <v>425</v>
-      </c>
-      <c r="E185" t="s">
-        <v>426</v>
       </c>
       <c r="F185" t="s">
         <v>385</v>
       </c>
       <c r="G185" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6303,16 +6303,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>383</v>
+      </c>
+      <c r="E186" t="s">
         <v>425</v>
-      </c>
-      <c r="E186" t="s">
-        <v>426</v>
       </c>
       <c r="F186" t="s">
         <v>385</v>
       </c>
       <c r="G186" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6326,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>383</v>
+      </c>
+      <c r="E187" t="s">
         <v>425</v>
-      </c>
-      <c r="E187" t="s">
-        <v>426</v>
       </c>
       <c r="F187" t="s">
         <v>385</v>
       </c>
       <c r="G187" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6349,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>383</v>
+      </c>
+      <c r="E188" t="s">
         <v>447</v>
-      </c>
-      <c r="E188" t="s">
-        <v>448</v>
       </c>
       <c r="F188" t="s">
         <v>385</v>
       </c>
       <c r="G188" t="s">
-        <v>386</v>
+        <v>448</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>Distribution d'Eau et Assainissement</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Distribution d'Eau et Assainissement</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>Infrastructure et Services Sociaux Divers</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Infrastructure et Services Sociaux Divers</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>Transports et Entreposage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transports et Entreposage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>Banques et Services Financiers</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banques et Services Financiers</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>Entreprises et Autres Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Entreprises et Autres Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,15 +967,15 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1165,15 +1165,15 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>Politique Commerciale et Réglementations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Politique Commerciale et Réglementations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>Tourisme</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourisme</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>Protection de l'Environnement Général</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protection de l'Environnement Général</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>Autres Multisecteurs</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Autres Multisecteurs</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>Soutien Budgétaire</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Soutien Budgétaire</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>Aide Alimentaire Dévelopmentale</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Aide Alimentaire Dévelopmentale</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>Aide sous forme de Produits, Autre</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Aide sous forme de Produits, Autre</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>Actions se Rapportant a la Dette</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actions se Rapportant a la Dette</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>Intervention d'Urgence</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Intervention d'Urgence</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>Reconstruction &amp; Réhabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction &amp; Réhabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>Prévention catastrophes/Préparation à leur survenue</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prévention catastrophes/Préparation à leur survenue</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>Frais Administratifs des Donneurs</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Frais Administratifs des Donneurs</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>Refugiés dans les Pays Donneurs</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiés dans les Pays Donneurs</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>Non Affecté / Non Specifié</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Non Affecté / Non Specifié</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,10 +2163,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -2186,10 +2186,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -2209,10 +2209,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -2232,10 +2232,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -2255,10 +2255,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -2278,10 +2278,10 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -2301,10 +2301,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -2324,10 +2324,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -2439,10 +2439,10 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>46</v>
@@ -2462,10 +2462,10 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>46</v>
@@ -2485,10 +2485,10 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
@@ -2508,10 +2508,10 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>46</v>
@@ -2531,10 +2531,10 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
@@ -2554,10 +2554,10 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
@@ -2577,10 +2577,10 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
@@ -2600,10 +2600,10 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
@@ -2623,10 +2623,10 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>46</v>
@@ -2646,10 +2646,10 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
@@ -2669,10 +2669,10 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>46</v>
@@ -2692,10 +2692,10 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>46</v>
@@ -2715,10 +2715,10 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
@@ -2738,10 +2738,10 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>46</v>
@@ -2764,13 +2764,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2787,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2810,13 +2810,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2833,13 +2833,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2856,13 +2856,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2879,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2902,13 +2902,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2925,13 +2925,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2971,13 +2971,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2994,13 +2994,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3017,13 +3017,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3040,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3063,13 +3063,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3086,13 +3086,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3109,13 +3109,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3497,10 +3497,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
         <v>126</v>
@@ -3520,10 +3520,10 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
         <v>126</v>
@@ -3543,10 +3543,10 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
         <v>126</v>
@@ -3566,10 +3566,10 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
         <v>126</v>
@@ -3589,10 +3589,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
         <v>126</v>
@@ -3612,10 +3612,10 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
         <v>126</v>
@@ -3638,13 +3638,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3661,13 +3661,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3684,13 +3684,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3707,13 +3707,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3730,13 +3730,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3753,13 +3753,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3776,13 +3776,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3799,13 +3799,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3822,13 +3822,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3845,13 +3845,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3868,13 +3868,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3891,13 +3891,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3914,13 +3914,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3937,13 +3937,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3960,13 +3960,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3983,13 +3983,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4006,13 +4006,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4029,13 +4029,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4052,13 +4052,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4075,13 +4075,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4098,13 +4098,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4121,13 +4121,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4233,10 +4233,10 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
         <v>226</v>
@@ -4256,10 +4256,10 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
         <v>226</v>
@@ -4279,10 +4279,10 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F98" t="s">
         <v>226</v>
@@ -4302,10 +4302,10 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>226</v>
@@ -4325,10 +4325,10 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
         <v>226</v>
@@ -4348,10 +4348,10 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>226</v>
@@ -4371,10 +4371,10 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F102" t="s">
         <v>226</v>
@@ -4394,10 +4394,10 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F103" t="s">
         <v>226</v>
@@ -4417,10 +4417,10 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>226</v>
@@ -4440,10 +4440,10 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>226</v>
@@ -4463,10 +4463,10 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>226</v>
@@ -4486,10 +4486,10 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F107" t="s">
         <v>226</v>
@@ -4509,10 +4509,10 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
         <v>226</v>
@@ -4532,10 +4532,10 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F109" t="s">
         <v>226</v>
@@ -4555,10 +4555,10 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>226</v>
@@ -4578,10 +4578,10 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="E111" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
         <v>226</v>
@@ -4601,10 +4601,10 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>273</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
         <v>226</v>
@@ -4624,10 +4624,10 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F113" t="s">
         <v>226</v>
@@ -4647,10 +4647,10 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F114" t="s">
         <v>226</v>
@@ -4670,10 +4670,10 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F115" t="s">
         <v>226</v>
@@ -4693,10 +4693,10 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
         <v>226</v>
@@ -4716,10 +4716,10 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
         <v>226</v>
@@ -4739,10 +4739,10 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E118" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F118" t="s">
         <v>226</v>
@@ -4762,10 +4762,10 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E119" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F119" t="s">
         <v>226</v>
@@ -4788,13 +4788,13 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F120" t="s">
         <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4811,13 +4811,13 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F121" t="s">
         <v>294</v>
       </c>
       <c r="G121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4834,13 +4834,13 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F122" t="s">
         <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4857,13 +4857,13 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F123" t="s">
         <v>294</v>
       </c>
       <c r="G123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4880,13 +4880,13 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F124" t="s">
         <v>294</v>
       </c>
       <c r="G124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4903,13 +4903,13 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F125" t="s">
         <v>294</v>
       </c>
       <c r="G125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4926,13 +4926,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F126" t="s">
         <v>308</v>
       </c>
       <c r="G126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4949,13 +4949,13 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F127" t="s">
         <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4972,13 +4972,13 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F128" t="s">
         <v>308</v>
       </c>
       <c r="G128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4995,13 +4995,13 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F129" t="s">
         <v>308</v>
       </c>
       <c r="G129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5429,10 +5429,10 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E148" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F148" t="s">
         <v>319</v>
@@ -5452,10 +5452,10 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F149" t="s">
         <v>319</v>
@@ -5475,10 +5475,10 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E150" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F150" t="s">
         <v>319</v>
@@ -5498,10 +5498,10 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F151" t="s">
         <v>319</v>
@@ -5521,10 +5521,10 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E152" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F152" t="s">
         <v>319</v>
@@ -5544,10 +5544,10 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F153" t="s">
         <v>319</v>
@@ -5567,10 +5567,10 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E154" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F154" t="s">
         <v>319</v>
@@ -5590,10 +5590,10 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E155" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F155" t="s">
         <v>319</v>
@@ -5613,10 +5613,10 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F156" t="s">
         <v>319</v>
@@ -5636,10 +5636,10 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F157" t="s">
         <v>319</v>
@@ -5659,10 +5659,10 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E158" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F158" t="s">
         <v>319</v>
@@ -6119,10 +6119,10 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E178" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F178" t="s">
         <v>385</v>
@@ -6142,10 +6142,10 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E179" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F179" t="s">
         <v>385</v>
@@ -6165,10 +6165,10 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E180" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F180" t="s">
         <v>385</v>
@@ -6188,10 +6188,10 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E181" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F181" t="s">
         <v>385</v>
@@ -6211,10 +6211,10 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E182" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F182" t="s">
         <v>385</v>
@@ -6234,10 +6234,10 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E183" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F183" t="s">
         <v>385</v>
@@ -6257,10 +6257,10 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E184" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F184" t="s">
         <v>385</v>
@@ -6280,10 +6280,10 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E185" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F185" t="s">
         <v>385</v>
@@ -6303,10 +6303,10 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E186" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F186" t="s">
         <v>385</v>
@@ -6326,10 +6326,10 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E187" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F187" t="s">
         <v>385</v>
@@ -6349,10 +6349,10 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>447</v>
+        <v>384</v>
       </c>
       <c r="F188" t="s">
         <v>385</v>
@@ -6375,13 +6375,13 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F189" t="s">
         <v>452</v>
       </c>
       <c r="G189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6398,13 +6398,13 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F190" t="s">
         <v>452</v>
       </c>
       <c r="G190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6421,13 +6421,13 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F191" t="s">
         <v>452</v>
       </c>
       <c r="G191" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6444,13 +6444,13 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F192" t="s">
         <v>452</v>
       </c>
       <c r="G192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6467,13 +6467,13 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F193" t="s">
         <v>452</v>
       </c>
       <c r="G193" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6490,13 +6490,13 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F194" t="s">
         <v>452</v>
       </c>
       <c r="G194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6513,13 +6513,13 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F195" t="s">
         <v>466</v>
       </c>
       <c r="G195" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6536,13 +6536,13 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F196" t="s">
         <v>470</v>
       </c>
       <c r="G196" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6559,13 +6559,13 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F197" t="s">
         <v>470</v>
       </c>
       <c r="G197" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6582,13 +6582,13 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F198" t="s">
         <v>470</v>
       </c>
       <c r="G198" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6605,13 +6605,13 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F199" t="s">
         <v>470</v>
       </c>
       <c r="G199" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6628,13 +6628,13 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F200" t="s">
         <v>470</v>
       </c>
       <c r="G200" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6651,13 +6651,13 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F201" t="s">
         <v>470</v>
       </c>
       <c r="G201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6674,13 +6674,13 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F202" t="s">
         <v>484</v>
       </c>
       <c r="G202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6697,13 +6697,13 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F203" t="s">
         <v>484</v>
       </c>
       <c r="G203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6720,13 +6720,13 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F204" t="s">
         <v>484</v>
       </c>
       <c r="G204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6743,13 +6743,13 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F205" t="s">
         <v>484</v>
       </c>
       <c r="G205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6766,13 +6766,13 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F206" t="s">
         <v>484</v>
       </c>
       <c r="G206" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6789,13 +6789,13 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F207" t="s">
         <v>484</v>
       </c>
       <c r="G207" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6812,13 +6812,13 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F208" t="s">
         <v>484</v>
       </c>
       <c r="G208" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6835,13 +6835,13 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F209" t="s">
         <v>484</v>
       </c>
       <c r="G209" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6858,13 +6858,13 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F210" t="s">
         <v>484</v>
       </c>
       <c r="G210" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6881,13 +6881,13 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F211" t="s">
         <v>484</v>
       </c>
       <c r="G211" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6904,13 +6904,13 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F212" t="s">
         <v>506</v>
       </c>
       <c r="G212" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6927,13 +6927,13 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F213" t="s">
         <v>510</v>
       </c>
       <c r="G213" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6950,13 +6950,13 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F214" t="s">
         <v>514</v>
       </c>
       <c r="G214" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6973,13 +6973,13 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F215" t="s">
         <v>514</v>
       </c>
       <c r="G215" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6996,13 +6996,13 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F216" t="s">
         <v>520</v>
       </c>
       <c r="G216" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7019,13 +7019,13 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F217" t="s">
         <v>520</v>
       </c>
       <c r="G217" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7042,13 +7042,13 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F218" t="s">
         <v>520</v>
       </c>
       <c r="G218" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7065,13 +7065,13 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F219" t="s">
         <v>520</v>
       </c>
       <c r="G219" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7088,13 +7088,13 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F220" t="s">
         <v>520</v>
       </c>
       <c r="G220" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7111,13 +7111,13 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F221" t="s">
         <v>520</v>
       </c>
       <c r="G221" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7134,13 +7134,13 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F222" t="s">
         <v>520</v>
       </c>
       <c r="G222" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7157,13 +7157,13 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F223" t="s">
         <v>536</v>
       </c>
       <c r="G223" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7180,13 +7180,13 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F224" t="s">
         <v>536</v>
       </c>
       <c r="G224" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7203,13 +7203,13 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F225" t="s">
         <v>536</v>
       </c>
       <c r="G225" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7226,13 +7226,13 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F226" t="s">
         <v>544</v>
       </c>
       <c r="G226" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7249,13 +7249,13 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F227" t="s">
         <v>548</v>
       </c>
       <c r="G227" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7272,13 +7272,13 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F228" t="s">
         <v>552</v>
       </c>
       <c r="G228" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7295,13 +7295,13 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F229" t="s">
         <v>556</v>
       </c>
       <c r="G229" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7318,13 +7318,13 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F230" t="s">
         <v>560</v>
       </c>
       <c r="G230" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7341,13 +7341,13 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F231" t="s">
         <v>560</v>
       </c>
       <c r="G231" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Education de Base</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Education Secondaire</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Education Post Secondaire</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Santé de Base</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Maladies non-transmissibles (MNT)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Distribution d'Eau et Assainissement</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflits, Paix et Sécurité</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Infrastructure et Services Sociaux Divers</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transports et Entreposage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources renouvelables</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources non renouvelables</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Centrales nucléaires</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Distribution de l'énergie</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banques et Services Financiers</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Entreprises et Autres Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Sylviculture</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Pêche</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Industries Extractives</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,24 +1357,24 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Politique Commerciale et Réglementations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourisme</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>Protection de l'Environnement Général</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Autres Multisecteurs</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>Soutien Budgétaire</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Aide Alimentaire Dévelopmentale</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Aide sous forme de Produits, Autre</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Actions se Rapportant a la Dette</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Intervention d'Urgence</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction &amp; Réhabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Prévention catastrophes/Préparation à leur survenue</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Frais Administratifs des Donneurs</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugiés dans les Pays Donneurs</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Non Affecté / Non Specifié</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,13 +2163,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2209,13 +2209,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2232,13 +2232,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2255,13 +2255,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2278,13 +2278,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2301,13 +2301,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2324,13 +2324,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2439,13 +2439,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2462,13 +2462,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2485,13 +2485,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2508,13 +2508,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2531,13 +2531,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2554,13 +2554,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2577,13 +2577,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2600,13 +2600,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2623,13 +2623,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2646,13 +2646,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2669,13 +2669,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2692,13 +2692,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2715,13 +2715,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2738,13 +2738,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -2764,10 +2764,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" t="s">
-        <v>89</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2787,10 +2787,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" t="s">
         <v>88</v>
-      </c>
-      <c r="F33" t="s">
-        <v>89</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2810,10 +2810,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" t="s">
         <v>88</v>
-      </c>
-      <c r="F34" t="s">
-        <v>89</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2833,10 +2833,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" t="s">
         <v>88</v>
-      </c>
-      <c r="F35" t="s">
-        <v>89</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2856,10 +2856,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" t="s">
         <v>88</v>
-      </c>
-      <c r="F36" t="s">
-        <v>89</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2879,10 +2879,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
         <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>101</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2902,10 +2902,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" t="s">
         <v>100</v>
-      </c>
-      <c r="F38" t="s">
-        <v>101</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2925,10 +2925,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
         <v>100</v>
-      </c>
-      <c r="F39" t="s">
-        <v>101</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2948,10 +2948,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
         <v>100</v>
-      </c>
-      <c r="F40" t="s">
-        <v>101</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2971,10 +2971,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
         <v>100</v>
-      </c>
-      <c r="F41" t="s">
-        <v>101</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2994,10 +2994,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
         <v>100</v>
-      </c>
-      <c r="F42" t="s">
-        <v>101</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3017,10 +3017,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
         <v>100</v>
-      </c>
-      <c r="F43" t="s">
-        <v>101</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3040,10 +3040,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
         <v>100</v>
-      </c>
-      <c r="F44" t="s">
-        <v>101</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3063,10 +3063,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" t="s">
         <v>100</v>
-      </c>
-      <c r="F45" t="s">
-        <v>101</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3086,10 +3086,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
         <v>100</v>
-      </c>
-      <c r="F46" t="s">
-        <v>101</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3109,10 +3109,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
         <v>100</v>
-      </c>
-      <c r="F47" t="s">
-        <v>101</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3497,13 +3497,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3520,13 +3520,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3543,13 +3543,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3566,13 +3566,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3589,13 +3589,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3612,13 +3612,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -3638,10 +3638,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s">
         <v>174</v>
-      </c>
-      <c r="F70" t="s">
-        <v>175</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3661,10 +3661,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71" t="s">
         <v>174</v>
-      </c>
-      <c r="F71" t="s">
-        <v>175</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3684,10 +3684,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>175</v>
+      </c>
+      <c r="F72" t="s">
         <v>174</v>
-      </c>
-      <c r="F72" t="s">
-        <v>175</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3707,10 +3707,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" t="s">
         <v>174</v>
-      </c>
-      <c r="F73" t="s">
-        <v>175</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3730,10 +3730,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" t="s">
         <v>174</v>
-      </c>
-      <c r="F74" t="s">
-        <v>175</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3753,10 +3753,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>175</v>
+      </c>
+      <c r="F75" t="s">
         <v>174</v>
-      </c>
-      <c r="F75" t="s">
-        <v>175</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3776,10 +3776,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>175</v>
+      </c>
+      <c r="F76" t="s">
         <v>174</v>
-      </c>
-      <c r="F76" t="s">
-        <v>175</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3799,10 +3799,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>175</v>
+      </c>
+      <c r="F77" t="s">
         <v>174</v>
-      </c>
-      <c r="F77" t="s">
-        <v>175</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3822,10 +3822,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>175</v>
+      </c>
+      <c r="F78" t="s">
         <v>174</v>
-      </c>
-      <c r="F78" t="s">
-        <v>175</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3845,10 +3845,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>175</v>
+      </c>
+      <c r="F79" t="s">
         <v>174</v>
-      </c>
-      <c r="F79" t="s">
-        <v>175</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3868,10 +3868,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>175</v>
+      </c>
+      <c r="F80" t="s">
         <v>174</v>
-      </c>
-      <c r="F80" t="s">
-        <v>175</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3891,10 +3891,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" t="s">
         <v>198</v>
-      </c>
-      <c r="F81" t="s">
-        <v>199</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3914,10 +3914,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>199</v>
+      </c>
+      <c r="F82" t="s">
         <v>198</v>
-      </c>
-      <c r="F82" t="s">
-        <v>199</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3937,10 +3937,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>199</v>
+      </c>
+      <c r="F83" t="s">
         <v>198</v>
-      </c>
-      <c r="F83" t="s">
-        <v>199</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3960,10 +3960,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>199</v>
+      </c>
+      <c r="F84" t="s">
         <v>198</v>
-      </c>
-      <c r="F84" t="s">
-        <v>199</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3983,10 +3983,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>199</v>
+      </c>
+      <c r="F85" t="s">
         <v>198</v>
-      </c>
-      <c r="F85" t="s">
-        <v>199</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4006,10 +4006,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" t="s">
         <v>198</v>
-      </c>
-      <c r="F86" t="s">
-        <v>199</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4029,10 +4029,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>199</v>
+      </c>
+      <c r="F87" t="s">
         <v>198</v>
-      </c>
-      <c r="F87" t="s">
-        <v>199</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4052,10 +4052,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>215</v>
+      </c>
+      <c r="F88" t="s">
         <v>214</v>
-      </c>
-      <c r="F88" t="s">
-        <v>215</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4075,10 +4075,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>215</v>
+      </c>
+      <c r="F89" t="s">
         <v>214</v>
-      </c>
-      <c r="F89" t="s">
-        <v>215</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4098,10 +4098,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>215</v>
+      </c>
+      <c r="F90" t="s">
         <v>214</v>
-      </c>
-      <c r="F90" t="s">
-        <v>215</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4121,10 +4121,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>215</v>
+      </c>
+      <c r="F91" t="s">
         <v>214</v>
-      </c>
-      <c r="F91" t="s">
-        <v>215</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4233,13 +4233,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4256,13 +4256,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4279,13 +4279,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4302,13 +4302,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4325,13 +4325,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4348,13 +4348,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4371,13 +4371,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4394,13 +4394,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4417,13 +4417,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4440,13 +4440,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4463,13 +4463,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4486,13 +4486,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4509,13 +4509,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4532,13 +4532,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4555,13 +4555,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>269</v>
+        <v>224</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="G111" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,13 +4601,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="G112" t="s">
         <v>274</v>
@@ -4624,13 +4624,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G113" t="s">
         <v>278</v>
@@ -4647,13 +4647,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G114" t="s">
         <v>278</v>
@@ -4670,13 +4670,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G115" t="s">
         <v>278</v>
@@ -4693,13 +4693,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G116" t="s">
         <v>278</v>
@@ -4716,13 +4716,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G117" t="s">
         <v>278</v>
@@ -4739,13 +4739,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G118" t="s">
         <v>278</v>
@@ -4762,13 +4762,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G119" t="s">
         <v>278</v>
@@ -4788,10 +4788,10 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
+        <v>294</v>
+      </c>
+      <c r="F120" t="s">
         <v>293</v>
-      </c>
-      <c r="F120" t="s">
-        <v>294</v>
       </c>
       <c r="G120" t="s">
         <v>294</v>
@@ -4811,10 +4811,10 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
+        <v>294</v>
+      </c>
+      <c r="F121" t="s">
         <v>293</v>
-      </c>
-      <c r="F121" t="s">
-        <v>294</v>
       </c>
       <c r="G121" t="s">
         <v>294</v>
@@ -4834,10 +4834,10 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
+        <v>294</v>
+      </c>
+      <c r="F122" t="s">
         <v>293</v>
-      </c>
-      <c r="F122" t="s">
-        <v>294</v>
       </c>
       <c r="G122" t="s">
         <v>294</v>
@@ -4857,10 +4857,10 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
+        <v>294</v>
+      </c>
+      <c r="F123" t="s">
         <v>293</v>
-      </c>
-      <c r="F123" t="s">
-        <v>294</v>
       </c>
       <c r="G123" t="s">
         <v>294</v>
@@ -4880,10 +4880,10 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
+        <v>294</v>
+      </c>
+      <c r="F124" t="s">
         <v>293</v>
-      </c>
-      <c r="F124" t="s">
-        <v>294</v>
       </c>
       <c r="G124" t="s">
         <v>294</v>
@@ -4903,10 +4903,10 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
+        <v>294</v>
+      </c>
+      <c r="F125" t="s">
         <v>293</v>
-      </c>
-      <c r="F125" t="s">
-        <v>294</v>
       </c>
       <c r="G125" t="s">
         <v>294</v>
@@ -4926,10 +4926,10 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
+        <v>308</v>
+      </c>
+      <c r="F126" t="s">
         <v>307</v>
-      </c>
-      <c r="F126" t="s">
-        <v>308</v>
       </c>
       <c r="G126" t="s">
         <v>308</v>
@@ -4949,10 +4949,10 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
+        <v>308</v>
+      </c>
+      <c r="F127" t="s">
         <v>307</v>
-      </c>
-      <c r="F127" t="s">
-        <v>308</v>
       </c>
       <c r="G127" t="s">
         <v>308</v>
@@ -4972,10 +4972,10 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
+        <v>308</v>
+      </c>
+      <c r="F128" t="s">
         <v>307</v>
-      </c>
-      <c r="F128" t="s">
-        <v>308</v>
       </c>
       <c r="G128" t="s">
         <v>308</v>
@@ -4995,10 +4995,10 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
+        <v>308</v>
+      </c>
+      <c r="F129" t="s">
         <v>307</v>
-      </c>
-      <c r="F129" t="s">
-        <v>308</v>
       </c>
       <c r="G129" t="s">
         <v>308</v>
@@ -5429,13 +5429,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E148" t="s">
         <v>318</v>
       </c>
       <c r="F148" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G148" t="s">
         <v>358</v>
@@ -5452,13 +5452,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E149" t="s">
         <v>318</v>
       </c>
       <c r="F149" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G149" t="s">
         <v>358</v>
@@ -5475,13 +5475,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E150" t="s">
         <v>318</v>
       </c>
       <c r="F150" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G150" t="s">
         <v>358</v>
@@ -5498,13 +5498,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E151" t="s">
         <v>318</v>
       </c>
       <c r="F151" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G151" t="s">
         <v>358</v>
@@ -5521,13 +5521,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E152" t="s">
         <v>318</v>
       </c>
       <c r="F152" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G152" t="s">
         <v>358</v>
@@ -5544,13 +5544,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E153" t="s">
         <v>318</v>
       </c>
       <c r="F153" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G153" t="s">
         <v>358</v>
@@ -5567,13 +5567,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E154" t="s">
         <v>318</v>
       </c>
       <c r="F154" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G154" t="s">
         <v>372</v>
@@ -5590,13 +5590,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E155" t="s">
         <v>318</v>
       </c>
       <c r="F155" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G155" t="s">
         <v>372</v>
@@ -5613,13 +5613,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E156" t="s">
         <v>318</v>
       </c>
       <c r="F156" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G156" t="s">
         <v>372</v>
@@ -5636,13 +5636,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E157" t="s">
         <v>318</v>
       </c>
       <c r="F157" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G157" t="s">
         <v>372</v>
@@ -5659,13 +5659,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E158" t="s">
         <v>318</v>
       </c>
       <c r="F158" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G158" t="s">
         <v>372</v>
@@ -6119,13 +6119,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E178" t="s">
         <v>384</v>
       </c>
       <c r="F178" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G178" t="s">
         <v>426</v>
@@ -6142,13 +6142,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E179" t="s">
         <v>384</v>
       </c>
       <c r="F179" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G179" t="s">
         <v>426</v>
@@ -6165,13 +6165,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E180" t="s">
         <v>384</v>
       </c>
       <c r="F180" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G180" t="s">
         <v>426</v>
@@ -6188,13 +6188,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E181" t="s">
         <v>384</v>
       </c>
       <c r="F181" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G181" t="s">
         <v>426</v>
@@ -6211,13 +6211,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E182" t="s">
         <v>384</v>
       </c>
       <c r="F182" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G182" t="s">
         <v>426</v>
@@ -6234,13 +6234,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E183" t="s">
         <v>384</v>
       </c>
       <c r="F183" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G183" t="s">
         <v>426</v>
@@ -6257,13 +6257,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E184" t="s">
         <v>384</v>
       </c>
       <c r="F184" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G184" t="s">
         <v>426</v>
@@ -6280,13 +6280,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E185" t="s">
         <v>384</v>
       </c>
       <c r="F185" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G185" t="s">
         <v>426</v>
@@ -6303,13 +6303,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E186" t="s">
         <v>384</v>
       </c>
       <c r="F186" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G186" t="s">
         <v>426</v>
@@ -6326,13 +6326,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E187" t="s">
         <v>384</v>
       </c>
       <c r="F187" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G187" t="s">
         <v>426</v>
@@ -6349,13 +6349,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>447</v>
+        <v>383</v>
       </c>
       <c r="E188" t="s">
         <v>384</v>
       </c>
       <c r="F188" t="s">
-        <v>385</v>
+        <v>447</v>
       </c>
       <c r="G188" t="s">
         <v>448</v>
@@ -6375,10 +6375,10 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
+        <v>452</v>
+      </c>
+      <c r="F189" t="s">
         <v>451</v>
-      </c>
-      <c r="F189" t="s">
-        <v>452</v>
       </c>
       <c r="G189" t="s">
         <v>452</v>
@@ -6398,10 +6398,10 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
+        <v>452</v>
+      </c>
+      <c r="F190" t="s">
         <v>451</v>
-      </c>
-      <c r="F190" t="s">
-        <v>452</v>
       </c>
       <c r="G190" t="s">
         <v>452</v>
@@ -6421,10 +6421,10 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
+        <v>452</v>
+      </c>
+      <c r="F191" t="s">
         <v>451</v>
-      </c>
-      <c r="F191" t="s">
-        <v>452</v>
       </c>
       <c r="G191" t="s">
         <v>452</v>
@@ -6444,10 +6444,10 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
+        <v>452</v>
+      </c>
+      <c r="F192" t="s">
         <v>451</v>
-      </c>
-      <c r="F192" t="s">
-        <v>452</v>
       </c>
       <c r="G192" t="s">
         <v>452</v>
@@ -6467,10 +6467,10 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
+        <v>452</v>
+      </c>
+      <c r="F193" t="s">
         <v>451</v>
-      </c>
-      <c r="F193" t="s">
-        <v>452</v>
       </c>
       <c r="G193" t="s">
         <v>452</v>
@@ -6490,10 +6490,10 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
+        <v>452</v>
+      </c>
+      <c r="F194" t="s">
         <v>451</v>
-      </c>
-      <c r="F194" t="s">
-        <v>452</v>
       </c>
       <c r="G194" t="s">
         <v>452</v>
@@ -6513,10 +6513,10 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
+        <v>466</v>
+      </c>
+      <c r="F195" t="s">
         <v>465</v>
-      </c>
-      <c r="F195" t="s">
-        <v>466</v>
       </c>
       <c r="G195" t="s">
         <v>466</v>
@@ -6536,10 +6536,10 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
+        <v>470</v>
+      </c>
+      <c r="F196" t="s">
         <v>469</v>
-      </c>
-      <c r="F196" t="s">
-        <v>470</v>
       </c>
       <c r="G196" t="s">
         <v>470</v>
@@ -6559,10 +6559,10 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
+        <v>470</v>
+      </c>
+      <c r="F197" t="s">
         <v>469</v>
-      </c>
-      <c r="F197" t="s">
-        <v>470</v>
       </c>
       <c r="G197" t="s">
         <v>470</v>
@@ -6582,10 +6582,10 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
+        <v>470</v>
+      </c>
+      <c r="F198" t="s">
         <v>469</v>
-      </c>
-      <c r="F198" t="s">
-        <v>470</v>
       </c>
       <c r="G198" t="s">
         <v>470</v>
@@ -6605,10 +6605,10 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
+        <v>470</v>
+      </c>
+      <c r="F199" t="s">
         <v>469</v>
-      </c>
-      <c r="F199" t="s">
-        <v>470</v>
       </c>
       <c r="G199" t="s">
         <v>470</v>
@@ -6628,10 +6628,10 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
+        <v>470</v>
+      </c>
+      <c r="F200" t="s">
         <v>469</v>
-      </c>
-      <c r="F200" t="s">
-        <v>470</v>
       </c>
       <c r="G200" t="s">
         <v>470</v>
@@ -6651,10 +6651,10 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
+        <v>470</v>
+      </c>
+      <c r="F201" t="s">
         <v>469</v>
-      </c>
-      <c r="F201" t="s">
-        <v>470</v>
       </c>
       <c r="G201" t="s">
         <v>470</v>
@@ -6674,10 +6674,10 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
+        <v>484</v>
+      </c>
+      <c r="F202" t="s">
         <v>483</v>
-      </c>
-      <c r="F202" t="s">
-        <v>484</v>
       </c>
       <c r="G202" t="s">
         <v>484</v>
@@ -6697,10 +6697,10 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
+        <v>484</v>
+      </c>
+      <c r="F203" t="s">
         <v>483</v>
-      </c>
-      <c r="F203" t="s">
-        <v>484</v>
       </c>
       <c r="G203" t="s">
         <v>484</v>
@@ -6720,10 +6720,10 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
+        <v>484</v>
+      </c>
+      <c r="F204" t="s">
         <v>483</v>
-      </c>
-      <c r="F204" t="s">
-        <v>484</v>
       </c>
       <c r="G204" t="s">
         <v>484</v>
@@ -6743,10 +6743,10 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
+        <v>484</v>
+      </c>
+      <c r="F205" t="s">
         <v>483</v>
-      </c>
-      <c r="F205" t="s">
-        <v>484</v>
       </c>
       <c r="G205" t="s">
         <v>484</v>
@@ -6766,10 +6766,10 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
+        <v>484</v>
+      </c>
+      <c r="F206" t="s">
         <v>483</v>
-      </c>
-      <c r="F206" t="s">
-        <v>484</v>
       </c>
       <c r="G206" t="s">
         <v>484</v>
@@ -6789,10 +6789,10 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
+        <v>484</v>
+      </c>
+      <c r="F207" t="s">
         <v>483</v>
-      </c>
-      <c r="F207" t="s">
-        <v>484</v>
       </c>
       <c r="G207" t="s">
         <v>484</v>
@@ -6812,10 +6812,10 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
+        <v>484</v>
+      </c>
+      <c r="F208" t="s">
         <v>483</v>
-      </c>
-      <c r="F208" t="s">
-        <v>484</v>
       </c>
       <c r="G208" t="s">
         <v>484</v>
@@ -6835,10 +6835,10 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
+        <v>484</v>
+      </c>
+      <c r="F209" t="s">
         <v>483</v>
-      </c>
-      <c r="F209" t="s">
-        <v>484</v>
       </c>
       <c r="G209" t="s">
         <v>484</v>
@@ -6858,10 +6858,10 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
+        <v>484</v>
+      </c>
+      <c r="F210" t="s">
         <v>483</v>
-      </c>
-      <c r="F210" t="s">
-        <v>484</v>
       </c>
       <c r="G210" t="s">
         <v>484</v>
@@ -6881,10 +6881,10 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
+        <v>484</v>
+      </c>
+      <c r="F211" t="s">
         <v>483</v>
-      </c>
-      <c r="F211" t="s">
-        <v>484</v>
       </c>
       <c r="G211" t="s">
         <v>484</v>
@@ -6904,10 +6904,10 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
+        <v>506</v>
+      </c>
+      <c r="F212" t="s">
         <v>505</v>
-      </c>
-      <c r="F212" t="s">
-        <v>506</v>
       </c>
       <c r="G212" t="s">
         <v>506</v>
@@ -6927,10 +6927,10 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
+        <v>510</v>
+      </c>
+      <c r="F213" t="s">
         <v>509</v>
-      </c>
-      <c r="F213" t="s">
-        <v>510</v>
       </c>
       <c r="G213" t="s">
         <v>510</v>
@@ -6950,10 +6950,10 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
+        <v>514</v>
+      </c>
+      <c r="F214" t="s">
         <v>513</v>
-      </c>
-      <c r="F214" t="s">
-        <v>514</v>
       </c>
       <c r="G214" t="s">
         <v>514</v>
@@ -6973,10 +6973,10 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
+        <v>514</v>
+      </c>
+      <c r="F215" t="s">
         <v>513</v>
-      </c>
-      <c r="F215" t="s">
-        <v>514</v>
       </c>
       <c r="G215" t="s">
         <v>514</v>
@@ -6996,10 +6996,10 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
+        <v>520</v>
+      </c>
+      <c r="F216" t="s">
         <v>519</v>
-      </c>
-      <c r="F216" t="s">
-        <v>520</v>
       </c>
       <c r="G216" t="s">
         <v>520</v>
@@ -7019,10 +7019,10 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
+        <v>520</v>
+      </c>
+      <c r="F217" t="s">
         <v>519</v>
-      </c>
-      <c r="F217" t="s">
-        <v>520</v>
       </c>
       <c r="G217" t="s">
         <v>520</v>
@@ -7042,10 +7042,10 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
+        <v>520</v>
+      </c>
+      <c r="F218" t="s">
         <v>519</v>
-      </c>
-      <c r="F218" t="s">
-        <v>520</v>
       </c>
       <c r="G218" t="s">
         <v>520</v>
@@ -7065,10 +7065,10 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
+        <v>520</v>
+      </c>
+      <c r="F219" t="s">
         <v>519</v>
-      </c>
-      <c r="F219" t="s">
-        <v>520</v>
       </c>
       <c r="G219" t="s">
         <v>520</v>
@@ -7088,10 +7088,10 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
+        <v>520</v>
+      </c>
+      <c r="F220" t="s">
         <v>519</v>
-      </c>
-      <c r="F220" t="s">
-        <v>520</v>
       </c>
       <c r="G220" t="s">
         <v>520</v>
@@ -7111,10 +7111,10 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
+        <v>520</v>
+      </c>
+      <c r="F221" t="s">
         <v>519</v>
-      </c>
-      <c r="F221" t="s">
-        <v>520</v>
       </c>
       <c r="G221" t="s">
         <v>520</v>
@@ -7134,10 +7134,10 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
+        <v>520</v>
+      </c>
+      <c r="F222" t="s">
         <v>519</v>
-      </c>
-      <c r="F222" t="s">
-        <v>520</v>
       </c>
       <c r="G222" t="s">
         <v>520</v>
@@ -7157,10 +7157,10 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
+        <v>536</v>
+      </c>
+      <c r="F223" t="s">
         <v>535</v>
-      </c>
-      <c r="F223" t="s">
-        <v>536</v>
       </c>
       <c r="G223" t="s">
         <v>536</v>
@@ -7180,10 +7180,10 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
+        <v>536</v>
+      </c>
+      <c r="F224" t="s">
         <v>535</v>
-      </c>
-      <c r="F224" t="s">
-        <v>536</v>
       </c>
       <c r="G224" t="s">
         <v>536</v>
@@ -7203,10 +7203,10 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
+        <v>536</v>
+      </c>
+      <c r="F225" t="s">
         <v>535</v>
-      </c>
-      <c r="F225" t="s">
-        <v>536</v>
       </c>
       <c r="G225" t="s">
         <v>536</v>
@@ -7226,10 +7226,10 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
+        <v>544</v>
+      </c>
+      <c r="F226" t="s">
         <v>543</v>
-      </c>
-      <c r="F226" t="s">
-        <v>544</v>
       </c>
       <c r="G226" t="s">
         <v>544</v>
@@ -7249,10 +7249,10 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
+        <v>548</v>
+      </c>
+      <c r="F227" t="s">
         <v>547</v>
-      </c>
-      <c r="F227" t="s">
-        <v>548</v>
       </c>
       <c r="G227" t="s">
         <v>548</v>
@@ -7272,10 +7272,10 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
+        <v>552</v>
+      </c>
+      <c r="F228" t="s">
         <v>551</v>
-      </c>
-      <c r="F228" t="s">
-        <v>552</v>
       </c>
       <c r="G228" t="s">
         <v>552</v>
@@ -7295,10 +7295,10 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
+        <v>556</v>
+      </c>
+      <c r="F229" t="s">
         <v>555</v>
-      </c>
-      <c r="F229" t="s">
-        <v>556</v>
       </c>
       <c r="G229" t="s">
         <v>556</v>
@@ -7318,10 +7318,10 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
+        <v>560</v>
+      </c>
+      <c r="F230" t="s">
         <v>559</v>
-      </c>
-      <c r="F230" t="s">
-        <v>560</v>
       </c>
       <c r="G230" t="s">
         <v>560</v>
@@ -7341,10 +7341,10 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
+        <v>560</v>
+      </c>
+      <c r="F231" t="s">
         <v>559</v>
-      </c>
-      <c r="F231" t="s">
-        <v>560</v>
       </c>
       <c r="G231" t="s">
         <v>560</v>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>110</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>Education de Base</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Education de Base</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>Education Secondaire</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Education Secondaire</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>Education Post Secondaire</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Education Post Secondaire</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>120</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
     <t>Santé</t>
   </si>
   <si>
     <t>121</t>
   </si>
   <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>Santé de Base</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Santé de Base</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>Maladies non-transmissibles (MNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Maladies non-transmissibles (MNT)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>150</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
     <t>151</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>Conflits, Paix et Sécurité</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflits, Paix et Sécurité</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>230</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
     <t>Energie</t>
   </si>
   <si>
     <t>231</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>Production d'électricité, sources renouvelables</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Production d'électricité, sources renouvelables</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>Production d'électricité, sources non renouvelables</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Production d'électricité, sources non renouvelables</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>Centrales nucléaires</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrales nucléaires</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>Distribution de l'énergie</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribution de l'énergie</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>310</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>Sylviculture</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Sylviculture</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>Pêche</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pêche</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,15 +1168,15 @@
     <t>320</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Extractives</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Industries Extractives</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,10 +1357,10 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>33110</t>
@@ -2166,10 +2166,10 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2189,10 +2189,10 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2212,10 +2212,10 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2235,10 +2235,10 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2258,10 +2258,10 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2281,10 +2281,10 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2304,10 +2304,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2327,10 +2327,10 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2442,10 +2442,10 @@
         <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2465,10 +2465,10 @@
         <v>44</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2488,10 +2488,10 @@
         <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2511,10 +2511,10 @@
         <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2534,10 +2534,10 @@
         <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2557,10 +2557,10 @@
         <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2580,10 +2580,10 @@
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2603,10 +2603,10 @@
         <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2626,10 +2626,10 @@
         <v>44</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2649,10 +2649,10 @@
         <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2672,10 +2672,10 @@
         <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2695,10 +2695,10 @@
         <v>44</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2718,10 +2718,10 @@
         <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2741,10 +2741,10 @@
         <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>124</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3523,10 +3523,10 @@
         <v>124</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3546,10 +3546,10 @@
         <v>124</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3569,10 +3569,10 @@
         <v>124</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3592,10 +3592,10 @@
         <v>124</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3615,10 +3615,10 @@
         <v>124</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,10 +4236,10 @@
         <v>224</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4259,10 +4259,10 @@
         <v>224</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4282,10 +4282,10 @@
         <v>224</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4305,10 +4305,10 @@
         <v>224</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4328,10 +4328,10 @@
         <v>224</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4351,10 +4351,10 @@
         <v>224</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4374,10 +4374,10 @@
         <v>224</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4397,10 +4397,10 @@
         <v>224</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4420,10 +4420,10 @@
         <v>224</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4443,10 +4443,10 @@
         <v>224</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4466,10 +4466,10 @@
         <v>224</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4489,10 +4489,10 @@
         <v>224</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4512,10 +4512,10 @@
         <v>224</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4535,10 +4535,10 @@
         <v>224</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4558,10 +4558,10 @@
         <v>224</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4581,13 +4581,13 @@
         <v>224</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="F111" t="s">
+        <v>226</v>
+      </c>
+      <c r="G111" t="s">
         <v>270</v>
-      </c>
-      <c r="G111" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,10 +4604,10 @@
         <v>224</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>273</v>
       </c>
       <c r="F112" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>274</v>
@@ -4627,10 +4627,10 @@
         <v>224</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F113" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>278</v>
@@ -4650,10 +4650,10 @@
         <v>224</v>
       </c>
       <c r="E114" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F114" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>278</v>
@@ -4673,10 +4673,10 @@
         <v>224</v>
       </c>
       <c r="E115" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F115" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>278</v>
@@ -4696,10 +4696,10 @@
         <v>224</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F116" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>278</v>
@@ -4719,10 +4719,10 @@
         <v>224</v>
       </c>
       <c r="E117" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F117" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>278</v>
@@ -4742,10 +4742,10 @@
         <v>224</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F118" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>278</v>
@@ -4765,10 +4765,10 @@
         <v>224</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F119" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>278</v>
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>293</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>293</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>293</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>293</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>293</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>293</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>307</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>307</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>307</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>307</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,10 +5432,10 @@
         <v>317</v>
       </c>
       <c r="E148" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F148" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G148" t="s">
         <v>358</v>
@@ -5455,10 +5455,10 @@
         <v>317</v>
       </c>
       <c r="E149" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F149" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G149" t="s">
         <v>358</v>
@@ -5478,10 +5478,10 @@
         <v>317</v>
       </c>
       <c r="E150" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F150" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G150" t="s">
         <v>358</v>
@@ -5501,10 +5501,10 @@
         <v>317</v>
       </c>
       <c r="E151" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F151" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G151" t="s">
         <v>358</v>
@@ -5524,10 +5524,10 @@
         <v>317</v>
       </c>
       <c r="E152" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F152" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G152" t="s">
         <v>358</v>
@@ -5547,10 +5547,10 @@
         <v>317</v>
       </c>
       <c r="E153" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F153" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G153" t="s">
         <v>358</v>
@@ -5570,10 +5570,10 @@
         <v>317</v>
       </c>
       <c r="E154" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="F154" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G154" t="s">
         <v>372</v>
@@ -5593,10 +5593,10 @@
         <v>317</v>
       </c>
       <c r="E155" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="F155" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G155" t="s">
         <v>372</v>
@@ -5616,10 +5616,10 @@
         <v>317</v>
       </c>
       <c r="E156" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="F156" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G156" t="s">
         <v>372</v>
@@ -5639,10 +5639,10 @@
         <v>317</v>
       </c>
       <c r="E157" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="F157" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G157" t="s">
         <v>372</v>
@@ -5662,10 +5662,10 @@
         <v>317</v>
       </c>
       <c r="E158" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="F158" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G158" t="s">
         <v>372</v>
@@ -6122,10 +6122,10 @@
         <v>383</v>
       </c>
       <c r="E178" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F178" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G178" t="s">
         <v>426</v>
@@ -6145,10 +6145,10 @@
         <v>383</v>
       </c>
       <c r="E179" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F179" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G179" t="s">
         <v>426</v>
@@ -6168,10 +6168,10 @@
         <v>383</v>
       </c>
       <c r="E180" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F180" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G180" t="s">
         <v>426</v>
@@ -6191,10 +6191,10 @@
         <v>383</v>
       </c>
       <c r="E181" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F181" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G181" t="s">
         <v>426</v>
@@ -6214,10 +6214,10 @@
         <v>383</v>
       </c>
       <c r="E182" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F182" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G182" t="s">
         <v>426</v>
@@ -6237,10 +6237,10 @@
         <v>383</v>
       </c>
       <c r="E183" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F183" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G183" t="s">
         <v>426</v>
@@ -6260,10 +6260,10 @@
         <v>383</v>
       </c>
       <c r="E184" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F184" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G184" t="s">
         <v>426</v>
@@ -6283,10 +6283,10 @@
         <v>383</v>
       </c>
       <c r="E185" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F185" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G185" t="s">
         <v>426</v>
@@ -6306,10 +6306,10 @@
         <v>383</v>
       </c>
       <c r="E186" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F186" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G186" t="s">
         <v>426</v>
@@ -6329,10 +6329,10 @@
         <v>383</v>
       </c>
       <c r="E187" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F187" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G187" t="s">
         <v>426</v>
@@ -6352,10 +6352,10 @@
         <v>383</v>
       </c>
       <c r="E188" t="s">
-        <v>384</v>
+        <v>447</v>
       </c>
       <c r="F188" t="s">
-        <v>447</v>
+        <v>385</v>
       </c>
       <c r="G188" t="s">
         <v>448</v>
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>451</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>451</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>451</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>451</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>451</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>451</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>465</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>469</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>469</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>469</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>469</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>469</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>469</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>483</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>483</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>483</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>483</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>483</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>483</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>483</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>483</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>483</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>483</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>505</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>509</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>513</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>513</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>519</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>519</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>519</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>519</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>519</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>519</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>519</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>535</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>535</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>535</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>543</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>547</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>551</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>555</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>559</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>559</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>Santé, Général</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>Santé</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>Politique de l'énergie</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>Energie</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Agriculture</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1171,10 +1171,10 @@
     <t>Industries Manufacturières</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>32120</t>
@@ -2169,10 +2169,10 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2192,10 +2192,10 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2215,10 +2215,10 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2238,10 +2238,10 @@
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2261,10 +2261,10 @@
         <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2284,10 +2284,10 @@
         <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2307,10 +2307,10 @@
         <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2330,10 +2330,10 @@
         <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2445,10 +2445,10 @@
         <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2468,10 +2468,10 @@
         <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2491,10 +2491,10 @@
         <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2514,10 +2514,10 @@
         <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2537,10 +2537,10 @@
         <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2560,10 +2560,10 @@
         <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2583,10 +2583,10 @@
         <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2606,10 +2606,10 @@
         <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2629,10 +2629,10 @@
         <v>74</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2652,10 +2652,10 @@
         <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2675,10 +2675,10 @@
         <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2698,10 +2698,10 @@
         <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2721,10 +2721,10 @@
         <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2744,10 +2744,10 @@
         <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3503,10 +3503,10 @@
         <v>160</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3526,10 +3526,10 @@
         <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3549,10 +3549,10 @@
         <v>160</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3572,10 +3572,10 @@
         <v>160</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3595,10 +3595,10 @@
         <v>160</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3618,10 +3618,10 @@
         <v>160</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4239,10 +4239,10 @@
         <v>236</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4262,10 +4262,10 @@
         <v>236</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4285,10 +4285,10 @@
         <v>236</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4308,10 +4308,10 @@
         <v>236</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4331,10 +4331,10 @@
         <v>236</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4354,10 +4354,10 @@
         <v>236</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4377,10 +4377,10 @@
         <v>236</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4400,10 +4400,10 @@
         <v>236</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4423,10 +4423,10 @@
         <v>236</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4446,10 +4446,10 @@
         <v>256</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4469,10 +4469,10 @@
         <v>256</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4492,10 +4492,10 @@
         <v>256</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4515,10 +4515,10 @@
         <v>256</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4538,10 +4538,10 @@
         <v>256</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4561,10 +4561,10 @@
         <v>256</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4584,10 +4584,10 @@
         <v>269</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="G111" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4607,10 +4607,10 @@
         <v>273</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4630,10 +4630,10 @@
         <v>277</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4653,10 +4653,10 @@
         <v>277</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4676,10 +4676,10 @@
         <v>277</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4699,10 +4699,10 @@
         <v>277</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G116" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4722,10 +4722,10 @@
         <v>277</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4745,10 +4745,10 @@
         <v>277</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G118" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4768,10 +4768,10 @@
         <v>277</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G119" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>293</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>293</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>293</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>293</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>293</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>293</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>307</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>307</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>307</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>307</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5435,10 +5435,10 @@
         <v>357</v>
       </c>
       <c r="F148" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5458,10 +5458,10 @@
         <v>357</v>
       </c>
       <c r="F149" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5481,10 +5481,10 @@
         <v>357</v>
       </c>
       <c r="F150" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5504,10 +5504,10 @@
         <v>357</v>
       </c>
       <c r="F151" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5527,10 +5527,10 @@
         <v>357</v>
       </c>
       <c r="F152" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5550,10 +5550,10 @@
         <v>357</v>
       </c>
       <c r="F153" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5573,10 +5573,10 @@
         <v>371</v>
       </c>
       <c r="F154" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5596,10 +5596,10 @@
         <v>371</v>
       </c>
       <c r="F155" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5619,10 +5619,10 @@
         <v>371</v>
       </c>
       <c r="F156" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5642,10 +5642,10 @@
         <v>371</v>
       </c>
       <c r="F157" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5665,10 +5665,10 @@
         <v>371</v>
       </c>
       <c r="F158" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6125,10 +6125,10 @@
         <v>425</v>
       </c>
       <c r="F178" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6148,10 +6148,10 @@
         <v>425</v>
       </c>
       <c r="F179" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6171,10 +6171,10 @@
         <v>425</v>
       </c>
       <c r="F180" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6194,10 +6194,10 @@
         <v>425</v>
       </c>
       <c r="F181" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6217,10 +6217,10 @@
         <v>425</v>
       </c>
       <c r="F182" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6240,10 +6240,10 @@
         <v>425</v>
       </c>
       <c r="F183" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6263,10 +6263,10 @@
         <v>425</v>
       </c>
       <c r="F184" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6286,10 +6286,10 @@
         <v>425</v>
       </c>
       <c r="F185" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6309,10 +6309,10 @@
         <v>425</v>
       </c>
       <c r="F186" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6332,10 +6332,10 @@
         <v>425</v>
       </c>
       <c r="F187" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6355,10 +6355,10 @@
         <v>447</v>
       </c>
       <c r="F188" t="s">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="G188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>451</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>451</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>451</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>451</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>451</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>451</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>465</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>469</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>469</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>469</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>469</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>469</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>469</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>483</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>483</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>483</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>483</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>483</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>483</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>483</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>483</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>483</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>483</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>505</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>509</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>513</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>513</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>519</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>519</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>519</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>519</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>519</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>519</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>519</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>535</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>535</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>535</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>543</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>547</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>551</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>555</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>559</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>559</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -28,12 +28,12 @@
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
@@ -49,12 +49,12 @@
     <t>110</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>Education</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Education de Base</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Education Secondaire</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Education Post Secondaire</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -151,12 +151,12 @@
     <t>120</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>Santé</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Santé de Base</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Maladies non-transmissibles (MNT)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>150</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflits, Paix et Sécurité</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>230</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>Energie</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources renouvelables</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources non renouvelables</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Centrales nucléaires</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Distribution de l'énergie</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -970,12 +970,12 @@
     <t>310</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Sylviculture</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Pêche</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,12 +1168,12 @@
     <t>320</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Industries Extractives</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,10 +1357,10 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
-  </si>
-  <si>
-    <t>323</t>
   </si>
   <si>
     <t>33110</t>
@@ -2764,10 +2764,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" t="s">
         <v>89</v>
-      </c>
-      <c r="F32" t="s">
-        <v>88</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2787,10 +2787,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" t="s">
         <v>89</v>
-      </c>
-      <c r="F33" t="s">
-        <v>88</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2810,10 +2810,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" t="s">
         <v>89</v>
-      </c>
-      <c r="F34" t="s">
-        <v>88</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2833,10 +2833,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" t="s">
         <v>89</v>
-      </c>
-      <c r="F35" t="s">
-        <v>88</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2856,10 +2856,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>88</v>
+      </c>
+      <c r="F36" t="s">
         <v>89</v>
-      </c>
-      <c r="F36" t="s">
-        <v>88</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2879,10 +2879,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" t="s">
         <v>101</v>
-      </c>
-      <c r="F37" t="s">
-        <v>100</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2902,10 +2902,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" t="s">
         <v>101</v>
-      </c>
-      <c r="F38" t="s">
-        <v>100</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2925,10 +2925,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>100</v>
+      </c>
+      <c r="F39" t="s">
         <v>101</v>
-      </c>
-      <c r="F39" t="s">
-        <v>100</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2948,10 +2948,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" t="s">
         <v>101</v>
-      </c>
-      <c r="F40" t="s">
-        <v>100</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2971,10 +2971,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" t="s">
         <v>101</v>
-      </c>
-      <c r="F41" t="s">
-        <v>100</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2994,10 +2994,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>100</v>
+      </c>
+      <c r="F42" t="s">
         <v>101</v>
-      </c>
-      <c r="F42" t="s">
-        <v>100</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3017,10 +3017,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>100</v>
+      </c>
+      <c r="F43" t="s">
         <v>101</v>
-      </c>
-      <c r="F43" t="s">
-        <v>100</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3040,10 +3040,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>100</v>
+      </c>
+      <c r="F44" t="s">
         <v>101</v>
-      </c>
-      <c r="F44" t="s">
-        <v>100</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3063,10 +3063,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>100</v>
+      </c>
+      <c r="F45" t="s">
         <v>101</v>
-      </c>
-      <c r="F45" t="s">
-        <v>100</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3086,10 +3086,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>100</v>
+      </c>
+      <c r="F46" t="s">
         <v>101</v>
-      </c>
-      <c r="F46" t="s">
-        <v>100</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3109,10 +3109,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>100</v>
+      </c>
+      <c r="F47" t="s">
         <v>101</v>
-      </c>
-      <c r="F47" t="s">
-        <v>100</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3638,10 +3638,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>174</v>
+      </c>
+      <c r="F70" t="s">
         <v>175</v>
-      </c>
-      <c r="F70" t="s">
-        <v>174</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3661,10 +3661,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>174</v>
+      </c>
+      <c r="F71" t="s">
         <v>175</v>
-      </c>
-      <c r="F71" t="s">
-        <v>174</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3684,10 +3684,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>174</v>
+      </c>
+      <c r="F72" t="s">
         <v>175</v>
-      </c>
-      <c r="F72" t="s">
-        <v>174</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3707,10 +3707,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73" t="s">
         <v>175</v>
-      </c>
-      <c r="F73" t="s">
-        <v>174</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3730,10 +3730,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>174</v>
+      </c>
+      <c r="F74" t="s">
         <v>175</v>
-      </c>
-      <c r="F74" t="s">
-        <v>174</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3753,10 +3753,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>174</v>
+      </c>
+      <c r="F75" t="s">
         <v>175</v>
-      </c>
-      <c r="F75" t="s">
-        <v>174</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3776,10 +3776,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>174</v>
+      </c>
+      <c r="F76" t="s">
         <v>175</v>
-      </c>
-      <c r="F76" t="s">
-        <v>174</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3799,10 +3799,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>174</v>
+      </c>
+      <c r="F77" t="s">
         <v>175</v>
-      </c>
-      <c r="F77" t="s">
-        <v>174</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3822,10 +3822,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>174</v>
+      </c>
+      <c r="F78" t="s">
         <v>175</v>
-      </c>
-      <c r="F78" t="s">
-        <v>174</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3845,10 +3845,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>174</v>
+      </c>
+      <c r="F79" t="s">
         <v>175</v>
-      </c>
-      <c r="F79" t="s">
-        <v>174</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3868,10 +3868,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>174</v>
+      </c>
+      <c r="F80" t="s">
         <v>175</v>
-      </c>
-      <c r="F80" t="s">
-        <v>174</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3891,10 +3891,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>198</v>
+      </c>
+      <c r="F81" t="s">
         <v>199</v>
-      </c>
-      <c r="F81" t="s">
-        <v>198</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3914,10 +3914,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>198</v>
+      </c>
+      <c r="F82" t="s">
         <v>199</v>
-      </c>
-      <c r="F82" t="s">
-        <v>198</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3937,10 +3937,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>198</v>
+      </c>
+      <c r="F83" t="s">
         <v>199</v>
-      </c>
-      <c r="F83" t="s">
-        <v>198</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3960,10 +3960,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>198</v>
+      </c>
+      <c r="F84" t="s">
         <v>199</v>
-      </c>
-      <c r="F84" t="s">
-        <v>198</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3983,10 +3983,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>198</v>
+      </c>
+      <c r="F85" t="s">
         <v>199</v>
-      </c>
-      <c r="F85" t="s">
-        <v>198</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4006,10 +4006,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>198</v>
+      </c>
+      <c r="F86" t="s">
         <v>199</v>
-      </c>
-      <c r="F86" t="s">
-        <v>198</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4029,10 +4029,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>198</v>
+      </c>
+      <c r="F87" t="s">
         <v>199</v>
-      </c>
-      <c r="F87" t="s">
-        <v>198</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4052,10 +4052,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>214</v>
+      </c>
+      <c r="F88" t="s">
         <v>215</v>
-      </c>
-      <c r="F88" t="s">
-        <v>214</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4075,10 +4075,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>214</v>
+      </c>
+      <c r="F89" t="s">
         <v>215</v>
-      </c>
-      <c r="F89" t="s">
-        <v>214</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4098,10 +4098,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>214</v>
+      </c>
+      <c r="F90" t="s">
         <v>215</v>
-      </c>
-      <c r="F90" t="s">
-        <v>214</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4121,10 +4121,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>214</v>
+      </c>
+      <c r="F91" t="s">
         <v>215</v>
-      </c>
-      <c r="F91" t="s">
-        <v>214</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4581,10 +4581,10 @@
         <v>224</v>
       </c>
       <c r="E111" t="s">
+        <v>270</v>
+      </c>
+      <c r="F111" t="s">
         <v>269</v>
-      </c>
-      <c r="F111" t="s">
-        <v>270</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4788,10 +4788,10 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
+        <v>293</v>
+      </c>
+      <c r="F120" t="s">
         <v>294</v>
-      </c>
-      <c r="F120" t="s">
-        <v>293</v>
       </c>
       <c r="G120" t="s">
         <v>294</v>
@@ -4811,10 +4811,10 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
+        <v>293</v>
+      </c>
+      <c r="F121" t="s">
         <v>294</v>
-      </c>
-      <c r="F121" t="s">
-        <v>293</v>
       </c>
       <c r="G121" t="s">
         <v>294</v>
@@ -4834,10 +4834,10 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
+        <v>293</v>
+      </c>
+      <c r="F122" t="s">
         <v>294</v>
-      </c>
-      <c r="F122" t="s">
-        <v>293</v>
       </c>
       <c r="G122" t="s">
         <v>294</v>
@@ -4857,10 +4857,10 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
+        <v>293</v>
+      </c>
+      <c r="F123" t="s">
         <v>294</v>
-      </c>
-      <c r="F123" t="s">
-        <v>293</v>
       </c>
       <c r="G123" t="s">
         <v>294</v>
@@ -4880,10 +4880,10 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
+        <v>293</v>
+      </c>
+      <c r="F124" t="s">
         <v>294</v>
-      </c>
-      <c r="F124" t="s">
-        <v>293</v>
       </c>
       <c r="G124" t="s">
         <v>294</v>
@@ -4903,10 +4903,10 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
+        <v>293</v>
+      </c>
+      <c r="F125" t="s">
         <v>294</v>
-      </c>
-      <c r="F125" t="s">
-        <v>293</v>
       </c>
       <c r="G125" t="s">
         <v>294</v>
@@ -4926,10 +4926,10 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
+        <v>307</v>
+      </c>
+      <c r="F126" t="s">
         <v>308</v>
-      </c>
-      <c r="F126" t="s">
-        <v>307</v>
       </c>
       <c r="G126" t="s">
         <v>308</v>
@@ -4949,10 +4949,10 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
+        <v>307</v>
+      </c>
+      <c r="F127" t="s">
         <v>308</v>
-      </c>
-      <c r="F127" t="s">
-        <v>307</v>
       </c>
       <c r="G127" t="s">
         <v>308</v>
@@ -4972,10 +4972,10 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
+        <v>307</v>
+      </c>
+      <c r="F128" t="s">
         <v>308</v>
-      </c>
-      <c r="F128" t="s">
-        <v>307</v>
       </c>
       <c r="G128" t="s">
         <v>308</v>
@@ -4995,10 +4995,10 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
+        <v>307</v>
+      </c>
+      <c r="F129" t="s">
         <v>308</v>
-      </c>
-      <c r="F129" t="s">
-        <v>307</v>
       </c>
       <c r="G129" t="s">
         <v>308</v>
@@ -6375,10 +6375,10 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
+        <v>451</v>
+      </c>
+      <c r="F189" t="s">
         <v>452</v>
-      </c>
-      <c r="F189" t="s">
-        <v>451</v>
       </c>
       <c r="G189" t="s">
         <v>452</v>
@@ -6398,10 +6398,10 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
+        <v>451</v>
+      </c>
+      <c r="F190" t="s">
         <v>452</v>
-      </c>
-      <c r="F190" t="s">
-        <v>451</v>
       </c>
       <c r="G190" t="s">
         <v>452</v>
@@ -6421,10 +6421,10 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
+        <v>451</v>
+      </c>
+      <c r="F191" t="s">
         <v>452</v>
-      </c>
-      <c r="F191" t="s">
-        <v>451</v>
       </c>
       <c r="G191" t="s">
         <v>452</v>
@@ -6444,10 +6444,10 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
+        <v>451</v>
+      </c>
+      <c r="F192" t="s">
         <v>452</v>
-      </c>
-      <c r="F192" t="s">
-        <v>451</v>
       </c>
       <c r="G192" t="s">
         <v>452</v>
@@ -6467,10 +6467,10 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
+        <v>451</v>
+      </c>
+      <c r="F193" t="s">
         <v>452</v>
-      </c>
-      <c r="F193" t="s">
-        <v>451</v>
       </c>
       <c r="G193" t="s">
         <v>452</v>
@@ -6490,10 +6490,10 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
+        <v>451</v>
+      </c>
+      <c r="F194" t="s">
         <v>452</v>
-      </c>
-      <c r="F194" t="s">
-        <v>451</v>
       </c>
       <c r="G194" t="s">
         <v>452</v>
@@ -6513,10 +6513,10 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
+        <v>465</v>
+      </c>
+      <c r="F195" t="s">
         <v>466</v>
-      </c>
-      <c r="F195" t="s">
-        <v>465</v>
       </c>
       <c r="G195" t="s">
         <v>466</v>
@@ -6536,10 +6536,10 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
+        <v>469</v>
+      </c>
+      <c r="F196" t="s">
         <v>470</v>
-      </c>
-      <c r="F196" t="s">
-        <v>469</v>
       </c>
       <c r="G196" t="s">
         <v>470</v>
@@ -6559,10 +6559,10 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
+        <v>469</v>
+      </c>
+      <c r="F197" t="s">
         <v>470</v>
-      </c>
-      <c r="F197" t="s">
-        <v>469</v>
       </c>
       <c r="G197" t="s">
         <v>470</v>
@@ -6582,10 +6582,10 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
+        <v>469</v>
+      </c>
+      <c r="F198" t="s">
         <v>470</v>
-      </c>
-      <c r="F198" t="s">
-        <v>469</v>
       </c>
       <c r="G198" t="s">
         <v>470</v>
@@ -6605,10 +6605,10 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
+        <v>469</v>
+      </c>
+      <c r="F199" t="s">
         <v>470</v>
-      </c>
-      <c r="F199" t="s">
-        <v>469</v>
       </c>
       <c r="G199" t="s">
         <v>470</v>
@@ -6628,10 +6628,10 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
+        <v>469</v>
+      </c>
+      <c r="F200" t="s">
         <v>470</v>
-      </c>
-      <c r="F200" t="s">
-        <v>469</v>
       </c>
       <c r="G200" t="s">
         <v>470</v>
@@ -6651,10 +6651,10 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
+        <v>469</v>
+      </c>
+      <c r="F201" t="s">
         <v>470</v>
-      </c>
-      <c r="F201" t="s">
-        <v>469</v>
       </c>
       <c r="G201" t="s">
         <v>470</v>
@@ -6674,10 +6674,10 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
+        <v>483</v>
+      </c>
+      <c r="F202" t="s">
         <v>484</v>
-      </c>
-      <c r="F202" t="s">
-        <v>483</v>
       </c>
       <c r="G202" t="s">
         <v>484</v>
@@ -6697,10 +6697,10 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
+        <v>483</v>
+      </c>
+      <c r="F203" t="s">
         <v>484</v>
-      </c>
-      <c r="F203" t="s">
-        <v>483</v>
       </c>
       <c r="G203" t="s">
         <v>484</v>
@@ -6720,10 +6720,10 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
+        <v>483</v>
+      </c>
+      <c r="F204" t="s">
         <v>484</v>
-      </c>
-      <c r="F204" t="s">
-        <v>483</v>
       </c>
       <c r="G204" t="s">
         <v>484</v>
@@ -6743,10 +6743,10 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
+        <v>483</v>
+      </c>
+      <c r="F205" t="s">
         <v>484</v>
-      </c>
-      <c r="F205" t="s">
-        <v>483</v>
       </c>
       <c r="G205" t="s">
         <v>484</v>
@@ -6766,10 +6766,10 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
+        <v>483</v>
+      </c>
+      <c r="F206" t="s">
         <v>484</v>
-      </c>
-      <c r="F206" t="s">
-        <v>483</v>
       </c>
       <c r="G206" t="s">
         <v>484</v>
@@ -6789,10 +6789,10 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
+        <v>483</v>
+      </c>
+      <c r="F207" t="s">
         <v>484</v>
-      </c>
-      <c r="F207" t="s">
-        <v>483</v>
       </c>
       <c r="G207" t="s">
         <v>484</v>
@@ -6812,10 +6812,10 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
+        <v>483</v>
+      </c>
+      <c r="F208" t="s">
         <v>484</v>
-      </c>
-      <c r="F208" t="s">
-        <v>483</v>
       </c>
       <c r="G208" t="s">
         <v>484</v>
@@ -6835,10 +6835,10 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
+        <v>483</v>
+      </c>
+      <c r="F209" t="s">
         <v>484</v>
-      </c>
-      <c r="F209" t="s">
-        <v>483</v>
       </c>
       <c r="G209" t="s">
         <v>484</v>
@@ -6858,10 +6858,10 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
+        <v>483</v>
+      </c>
+      <c r="F210" t="s">
         <v>484</v>
-      </c>
-      <c r="F210" t="s">
-        <v>483</v>
       </c>
       <c r="G210" t="s">
         <v>484</v>
@@ -6881,10 +6881,10 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
+        <v>483</v>
+      </c>
+      <c r="F211" t="s">
         <v>484</v>
-      </c>
-      <c r="F211" t="s">
-        <v>483</v>
       </c>
       <c r="G211" t="s">
         <v>484</v>
@@ -6904,10 +6904,10 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
+        <v>505</v>
+      </c>
+      <c r="F212" t="s">
         <v>506</v>
-      </c>
-      <c r="F212" t="s">
-        <v>505</v>
       </c>
       <c r="G212" t="s">
         <v>506</v>
@@ -6927,10 +6927,10 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
+        <v>509</v>
+      </c>
+      <c r="F213" t="s">
         <v>510</v>
-      </c>
-      <c r="F213" t="s">
-        <v>509</v>
       </c>
       <c r="G213" t="s">
         <v>510</v>
@@ -6950,10 +6950,10 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
+        <v>513</v>
+      </c>
+      <c r="F214" t="s">
         <v>514</v>
-      </c>
-      <c r="F214" t="s">
-        <v>513</v>
       </c>
       <c r="G214" t="s">
         <v>514</v>
@@ -6973,10 +6973,10 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
+        <v>513</v>
+      </c>
+      <c r="F215" t="s">
         <v>514</v>
-      </c>
-      <c r="F215" t="s">
-        <v>513</v>
       </c>
       <c r="G215" t="s">
         <v>514</v>
@@ -6996,10 +6996,10 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
+        <v>519</v>
+      </c>
+      <c r="F216" t="s">
         <v>520</v>
-      </c>
-      <c r="F216" t="s">
-        <v>519</v>
       </c>
       <c r="G216" t="s">
         <v>520</v>
@@ -7019,10 +7019,10 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
+        <v>519</v>
+      </c>
+      <c r="F217" t="s">
         <v>520</v>
-      </c>
-      <c r="F217" t="s">
-        <v>519</v>
       </c>
       <c r="G217" t="s">
         <v>520</v>
@@ -7042,10 +7042,10 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
+        <v>519</v>
+      </c>
+      <c r="F218" t="s">
         <v>520</v>
-      </c>
-      <c r="F218" t="s">
-        <v>519</v>
       </c>
       <c r="G218" t="s">
         <v>520</v>
@@ -7065,10 +7065,10 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
+        <v>519</v>
+      </c>
+      <c r="F219" t="s">
         <v>520</v>
-      </c>
-      <c r="F219" t="s">
-        <v>519</v>
       </c>
       <c r="G219" t="s">
         <v>520</v>
@@ -7088,10 +7088,10 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
+        <v>519</v>
+      </c>
+      <c r="F220" t="s">
         <v>520</v>
-      </c>
-      <c r="F220" t="s">
-        <v>519</v>
       </c>
       <c r="G220" t="s">
         <v>520</v>
@@ -7111,10 +7111,10 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
+        <v>519</v>
+      </c>
+      <c r="F221" t="s">
         <v>520</v>
-      </c>
-      <c r="F221" t="s">
-        <v>519</v>
       </c>
       <c r="G221" t="s">
         <v>520</v>
@@ -7134,10 +7134,10 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
+        <v>519</v>
+      </c>
+      <c r="F222" t="s">
         <v>520</v>
-      </c>
-      <c r="F222" t="s">
-        <v>519</v>
       </c>
       <c r="G222" t="s">
         <v>520</v>
@@ -7157,10 +7157,10 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
+        <v>535</v>
+      </c>
+      <c r="F223" t="s">
         <v>536</v>
-      </c>
-      <c r="F223" t="s">
-        <v>535</v>
       </c>
       <c r="G223" t="s">
         <v>536</v>
@@ -7180,10 +7180,10 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
+        <v>535</v>
+      </c>
+      <c r="F224" t="s">
         <v>536</v>
-      </c>
-      <c r="F224" t="s">
-        <v>535</v>
       </c>
       <c r="G224" t="s">
         <v>536</v>
@@ -7203,10 +7203,10 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
+        <v>535</v>
+      </c>
+      <c r="F225" t="s">
         <v>536</v>
-      </c>
-      <c r="F225" t="s">
-        <v>535</v>
       </c>
       <c r="G225" t="s">
         <v>536</v>
@@ -7226,10 +7226,10 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
+        <v>543</v>
+      </c>
+      <c r="F226" t="s">
         <v>544</v>
-      </c>
-      <c r="F226" t="s">
-        <v>543</v>
       </c>
       <c r="G226" t="s">
         <v>544</v>
@@ -7249,10 +7249,10 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
+        <v>547</v>
+      </c>
+      <c r="F227" t="s">
         <v>548</v>
-      </c>
-      <c r="F227" t="s">
-        <v>547</v>
       </c>
       <c r="G227" t="s">
         <v>548</v>
@@ -7272,10 +7272,10 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
+        <v>551</v>
+      </c>
+      <c r="F228" t="s">
         <v>552</v>
-      </c>
-      <c r="F228" t="s">
-        <v>551</v>
       </c>
       <c r="G228" t="s">
         <v>552</v>
@@ -7295,10 +7295,10 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
+        <v>555</v>
+      </c>
+      <c r="F229" t="s">
         <v>556</v>
-      </c>
-      <c r="F229" t="s">
-        <v>555</v>
       </c>
       <c r="G229" t="s">
         <v>556</v>
@@ -7318,10 +7318,10 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
+        <v>559</v>
+      </c>
+      <c r="F230" t="s">
         <v>560</v>
-      </c>
-      <c r="F230" t="s">
-        <v>559</v>
       </c>
       <c r="G230" t="s">
         <v>560</v>
@@ -7341,10 +7341,10 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
+        <v>559</v>
+      </c>
+      <c r="F231" t="s">
         <v>560</v>
-      </c>
-      <c r="F231" t="s">
-        <v>559</v>
       </c>
       <c r="G231" t="s">
         <v>560</v>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>Santé, Général</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
@@ -967,12 +967,12 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
@@ -1165,10 +1165,10 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>Industries Manufacturières</t>
@@ -2163,10 +2163,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>23</v>
@@ -2186,10 +2186,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>23</v>
@@ -2209,10 +2209,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -2232,10 +2232,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>23</v>
@@ -2255,10 +2255,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>33</v>
@@ -2278,10 +2278,10 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2301,10 +2301,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -2324,10 +2324,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -2439,10 +2439,10 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -2462,10 +2462,10 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>57</v>
@@ -2485,10 +2485,10 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>57</v>
@@ -2508,10 +2508,10 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2531,10 +2531,10 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>57</v>
@@ -2554,10 +2554,10 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>57</v>
@@ -2577,10 +2577,10 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>57</v>
@@ -2600,10 +2600,10 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>57</v>
@@ -2623,10 +2623,10 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>75</v>
@@ -2646,10 +2646,10 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>75</v>
@@ -2669,10 +2669,10 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>75</v>
@@ -2692,10 +2692,10 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>75</v>
@@ -2715,10 +2715,10 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>75</v>
@@ -2738,10 +2738,10 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>75</v>
@@ -3497,10 +3497,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
         <v>161</v>
@@ -3520,10 +3520,10 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
         <v>161</v>
@@ -3543,10 +3543,10 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
         <v>161</v>
@@ -3566,10 +3566,10 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
         <v>161</v>
@@ -3589,10 +3589,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
         <v>161</v>
@@ -3612,10 +3612,10 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
         <v>161</v>
@@ -4233,10 +4233,10 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
         <v>237</v>
@@ -4256,10 +4256,10 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
         <v>237</v>
@@ -4279,10 +4279,10 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F98" t="s">
         <v>237</v>
@@ -4302,10 +4302,10 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>237</v>
@@ -4325,10 +4325,10 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
         <v>237</v>
@@ -4348,10 +4348,10 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>237</v>
@@ -4371,10 +4371,10 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F102" t="s">
         <v>237</v>
@@ -4394,10 +4394,10 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F103" t="s">
         <v>237</v>
@@ -4417,10 +4417,10 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>237</v>
@@ -4440,10 +4440,10 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>257</v>
@@ -4463,10 +4463,10 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>257</v>
@@ -4486,10 +4486,10 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F107" t="s">
         <v>257</v>
@@ -4509,10 +4509,10 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
         <v>257</v>
@@ -4532,10 +4532,10 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F109" t="s">
         <v>257</v>
@@ -4555,10 +4555,10 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>257</v>
@@ -4578,10 +4578,10 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
         <v>269</v>
@@ -4601,10 +4601,10 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>273</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
         <v>274</v>
@@ -4624,10 +4624,10 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F113" t="s">
         <v>278</v>
@@ -4647,10 +4647,10 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F114" t="s">
         <v>278</v>
@@ -4670,10 +4670,10 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F115" t="s">
         <v>278</v>
@@ -4693,10 +4693,10 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
         <v>278</v>
@@ -4716,10 +4716,10 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
         <v>278</v>
@@ -4739,10 +4739,10 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E118" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F118" t="s">
         <v>278</v>
@@ -4762,10 +4762,10 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E119" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F119" t="s">
         <v>278</v>
@@ -5429,10 +5429,10 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E148" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F148" t="s">
         <v>358</v>
@@ -5452,10 +5452,10 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F149" t="s">
         <v>358</v>
@@ -5475,10 +5475,10 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E150" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F150" t="s">
         <v>358</v>
@@ -5498,10 +5498,10 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F151" t="s">
         <v>358</v>
@@ -5521,10 +5521,10 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E152" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F152" t="s">
         <v>358</v>
@@ -5544,10 +5544,10 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F153" t="s">
         <v>358</v>
@@ -5567,10 +5567,10 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E154" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F154" t="s">
         <v>372</v>
@@ -5590,10 +5590,10 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E155" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F155" t="s">
         <v>372</v>
@@ -5613,10 +5613,10 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F156" t="s">
         <v>372</v>
@@ -5636,10 +5636,10 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F157" t="s">
         <v>372</v>
@@ -5659,10 +5659,10 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E158" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F158" t="s">
         <v>372</v>
@@ -6119,10 +6119,10 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E178" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F178" t="s">
         <v>426</v>
@@ -6142,10 +6142,10 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E179" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F179" t="s">
         <v>426</v>
@@ -6165,10 +6165,10 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E180" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F180" t="s">
         <v>426</v>
@@ -6188,10 +6188,10 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E181" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F181" t="s">
         <v>426</v>
@@ -6211,10 +6211,10 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E182" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F182" t="s">
         <v>426</v>
@@ -6234,10 +6234,10 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E183" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F183" t="s">
         <v>426</v>
@@ -6257,10 +6257,10 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E184" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F184" t="s">
         <v>426</v>
@@ -6280,10 +6280,10 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E185" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F185" t="s">
         <v>426</v>
@@ -6303,10 +6303,10 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E186" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F186" t="s">
         <v>426</v>
@@ -6326,10 +6326,10 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E187" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F187" t="s">
         <v>426</v>
@@ -6349,10 +6349,10 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>447</v>
+        <v>384</v>
       </c>
       <c r="F188" t="s">
         <v>448</v>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>Education de Base</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Education de Base</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>Education Secondaire</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Education Secondaire</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>Education Post Secondaire</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Education Post Secondaire</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>Santé de Base</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Santé de Base</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>Maladies non-transmissibles (MNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Maladies non-transmissibles (MNT)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>Conflits, Paix et Sécurité</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflits, Paix et Sécurité</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>Production d'électricité, sources renouvelables</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Production d'électricité, sources renouvelables</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>Production d'électricité, sources non renouvelables</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Production d'électricité, sources non renouvelables</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>Centrales nucléaires</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrales nucléaires</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>Distribution de l'énergie</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribution de l'énergie</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>Sylviculture</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Sylviculture</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>Pêche</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pêche</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Extractives</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Industries Extractives</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,10 +1357,10 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>33110</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2764,13 +2764,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2787,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2810,13 +2810,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2833,13 +2833,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2856,13 +2856,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2879,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2902,13 +2902,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2925,13 +2925,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2971,13 +2971,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2994,13 +2994,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3017,13 +3017,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3040,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3063,13 +3063,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3086,13 +3086,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3109,13 +3109,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
+        <v>160</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
+        <v>160</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
+        <v>160</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
+        <v>160</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
+        <v>160</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
+        <v>160</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3638,13 +3638,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3661,13 +3661,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3684,13 +3684,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3707,13 +3707,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3730,13 +3730,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3753,13 +3753,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3776,13 +3776,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3799,13 +3799,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3822,13 +3822,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3845,13 +3845,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3868,13 +3868,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3891,13 +3891,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3914,13 +3914,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3937,13 +3937,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3960,13 +3960,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3983,13 +3983,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4006,13 +4006,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4029,13 +4029,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4052,13 +4052,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4075,13 +4075,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4098,13 +4098,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4121,13 +4121,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
+        <v>236</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
+        <v>236</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
+        <v>236</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
+        <v>236</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
+        <v>236</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
+        <v>236</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
+        <v>236</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
+        <v>236</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
+        <v>236</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
+        <v>256</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
+        <v>256</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
+        <v>256</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
+        <v>256</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
+        <v>256</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
+        <v>256</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,7 +4578,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
@@ -4587,7 +4587,7 @@
         <v>269</v>
       </c>
       <c r="G111" t="s">
-        <v>227</v>
+        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
+        <v>273</v>
+      </c>
+      <c r="G112" t="s">
         <v>274</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
+        <v>277</v>
+      </c>
+      <c r="G113" t="s">
         <v>278</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
+        <v>277</v>
+      </c>
+      <c r="G114" t="s">
         <v>278</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
+        <v>277</v>
+      </c>
+      <c r="G115" t="s">
         <v>278</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
+        <v>277</v>
+      </c>
+      <c r="G116" t="s">
         <v>278</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
+        <v>277</v>
+      </c>
+      <c r="G117" t="s">
         <v>278</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
+        <v>277</v>
+      </c>
+      <c r="G118" t="s">
         <v>278</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
+        <v>277</v>
+      </c>
+      <c r="G119" t="s">
         <v>278</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4788,13 +4788,13 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F120" t="s">
         <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4811,13 +4811,13 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F121" t="s">
         <v>294</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4834,13 +4834,13 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
         <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4857,13 +4857,13 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F123" t="s">
         <v>294</v>
       </c>
       <c r="G123" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4880,13 +4880,13 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F124" t="s">
         <v>294</v>
       </c>
       <c r="G124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4903,13 +4903,13 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F125" t="s">
         <v>294</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4926,13 +4926,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F126" t="s">
         <v>308</v>
       </c>
       <c r="G126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4949,13 +4949,13 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4972,13 +4972,13 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
         <v>308</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4995,13 +4995,13 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F129" t="s">
         <v>308</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E148" t="s">
         <v>318</v>
       </c>
       <c r="F148" t="s">
+        <v>357</v>
+      </c>
+      <c r="G148" t="s">
         <v>358</v>
-      </c>
-      <c r="G148" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E149" t="s">
         <v>318</v>
       </c>
       <c r="F149" t="s">
+        <v>357</v>
+      </c>
+      <c r="G149" t="s">
         <v>358</v>
-      </c>
-      <c r="G149" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E150" t="s">
         <v>318</v>
       </c>
       <c r="F150" t="s">
+        <v>357</v>
+      </c>
+      <c r="G150" t="s">
         <v>358</v>
-      </c>
-      <c r="G150" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E151" t="s">
         <v>318</v>
       </c>
       <c r="F151" t="s">
+        <v>357</v>
+      </c>
+      <c r="G151" t="s">
         <v>358</v>
-      </c>
-      <c r="G151" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E152" t="s">
         <v>318</v>
       </c>
       <c r="F152" t="s">
+        <v>357</v>
+      </c>
+      <c r="G152" t="s">
         <v>358</v>
-      </c>
-      <c r="G152" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E153" t="s">
         <v>318</v>
       </c>
       <c r="F153" t="s">
+        <v>357</v>
+      </c>
+      <c r="G153" t="s">
         <v>358</v>
-      </c>
-      <c r="G153" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E154" t="s">
         <v>318</v>
       </c>
       <c r="F154" t="s">
+        <v>371</v>
+      </c>
+      <c r="G154" t="s">
         <v>372</v>
-      </c>
-      <c r="G154" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E155" t="s">
         <v>318</v>
       </c>
       <c r="F155" t="s">
+        <v>371</v>
+      </c>
+      <c r="G155" t="s">
         <v>372</v>
-      </c>
-      <c r="G155" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E156" t="s">
         <v>318</v>
       </c>
       <c r="F156" t="s">
+        <v>371</v>
+      </c>
+      <c r="G156" t="s">
         <v>372</v>
-      </c>
-      <c r="G156" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E157" t="s">
         <v>318</v>
       </c>
       <c r="F157" t="s">
+        <v>371</v>
+      </c>
+      <c r="G157" t="s">
         <v>372</v>
-      </c>
-      <c r="G157" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E158" t="s">
         <v>318</v>
       </c>
       <c r="F158" t="s">
+        <v>371</v>
+      </c>
+      <c r="G158" t="s">
         <v>372</v>
-      </c>
-      <c r="G158" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E178" t="s">
         <v>384</v>
       </c>
       <c r="F178" t="s">
+        <v>425</v>
+      </c>
+      <c r="G178" t="s">
         <v>426</v>
-      </c>
-      <c r="G178" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E179" t="s">
         <v>384</v>
       </c>
       <c r="F179" t="s">
+        <v>425</v>
+      </c>
+      <c r="G179" t="s">
         <v>426</v>
-      </c>
-      <c r="G179" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E180" t="s">
         <v>384</v>
       </c>
       <c r="F180" t="s">
+        <v>425</v>
+      </c>
+      <c r="G180" t="s">
         <v>426</v>
-      </c>
-      <c r="G180" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E181" t="s">
         <v>384</v>
       </c>
       <c r="F181" t="s">
+        <v>425</v>
+      </c>
+      <c r="G181" t="s">
         <v>426</v>
-      </c>
-      <c r="G181" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E182" t="s">
         <v>384</v>
       </c>
       <c r="F182" t="s">
+        <v>425</v>
+      </c>
+      <c r="G182" t="s">
         <v>426</v>
-      </c>
-      <c r="G182" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6234,16 +6234,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E183" t="s">
         <v>384</v>
       </c>
       <c r="F183" t="s">
+        <v>425</v>
+      </c>
+      <c r="G183" t="s">
         <v>426</v>
-      </c>
-      <c r="G183" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6257,16 +6257,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E184" t="s">
         <v>384</v>
       </c>
       <c r="F184" t="s">
+        <v>425</v>
+      </c>
+      <c r="G184" t="s">
         <v>426</v>
-      </c>
-      <c r="G184" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6280,16 +6280,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E185" t="s">
         <v>384</v>
       </c>
       <c r="F185" t="s">
+        <v>425</v>
+      </c>
+      <c r="G185" t="s">
         <v>426</v>
-      </c>
-      <c r="G185" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6303,16 +6303,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E186" t="s">
         <v>384</v>
       </c>
       <c r="F186" t="s">
+        <v>425</v>
+      </c>
+      <c r="G186" t="s">
         <v>426</v>
-      </c>
-      <c r="G186" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6326,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E187" t="s">
         <v>384</v>
       </c>
       <c r="F187" t="s">
+        <v>425</v>
+      </c>
+      <c r="G187" t="s">
         <v>426</v>
-      </c>
-      <c r="G187" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6349,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>447</v>
+        <v>383</v>
       </c>
       <c r="E188" t="s">
         <v>384</v>
       </c>
       <c r="F188" t="s">
+        <v>447</v>
+      </c>
+      <c r="G188" t="s">
         <v>448</v>
-      </c>
-      <c r="G188" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6375,13 +6375,13 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s">
         <v>452</v>
       </c>
       <c r="G189" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6398,13 +6398,13 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F190" t="s">
         <v>452</v>
       </c>
       <c r="G190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6421,13 +6421,13 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F191" t="s">
         <v>452</v>
       </c>
       <c r="G191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6444,13 +6444,13 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F192" t="s">
         <v>452</v>
       </c>
       <c r="G192" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6467,13 +6467,13 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>452</v>
       </c>
       <c r="G193" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6490,13 +6490,13 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F194" t="s">
         <v>452</v>
       </c>
       <c r="G194" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6513,13 +6513,13 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F195" t="s">
         <v>466</v>
       </c>
       <c r="G195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6536,13 +6536,13 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F196" t="s">
         <v>470</v>
       </c>
       <c r="G196" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6559,13 +6559,13 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F197" t="s">
         <v>470</v>
       </c>
       <c r="G197" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6582,13 +6582,13 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F198" t="s">
         <v>470</v>
       </c>
       <c r="G198" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6605,13 +6605,13 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F199" t="s">
         <v>470</v>
       </c>
       <c r="G199" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6628,13 +6628,13 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F200" t="s">
         <v>470</v>
       </c>
       <c r="G200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6651,13 +6651,13 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
         <v>470</v>
       </c>
       <c r="G201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6674,13 +6674,13 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F202" t="s">
         <v>484</v>
       </c>
       <c r="G202" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6697,13 +6697,13 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F203" t="s">
         <v>484</v>
       </c>
       <c r="G203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6720,13 +6720,13 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F204" t="s">
         <v>484</v>
       </c>
       <c r="G204" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6743,13 +6743,13 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F205" t="s">
         <v>484</v>
       </c>
       <c r="G205" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6766,13 +6766,13 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F206" t="s">
         <v>484</v>
       </c>
       <c r="G206" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6789,13 +6789,13 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F207" t="s">
         <v>484</v>
       </c>
       <c r="G207" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6812,13 +6812,13 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F208" t="s">
         <v>484</v>
       </c>
       <c r="G208" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6835,13 +6835,13 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F209" t="s">
         <v>484</v>
       </c>
       <c r="G209" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6858,13 +6858,13 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F210" t="s">
         <v>484</v>
       </c>
       <c r="G210" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6881,13 +6881,13 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F211" t="s">
         <v>484</v>
       </c>
       <c r="G211" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6904,13 +6904,13 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F212" t="s">
         <v>506</v>
       </c>
       <c r="G212" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6927,13 +6927,13 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F213" t="s">
         <v>510</v>
       </c>
       <c r="G213" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6950,13 +6950,13 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F214" t="s">
         <v>514</v>
       </c>
       <c r="G214" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6973,13 +6973,13 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F215" t="s">
         <v>514</v>
       </c>
       <c r="G215" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6996,13 +6996,13 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F216" t="s">
         <v>520</v>
       </c>
       <c r="G216" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7019,13 +7019,13 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F217" t="s">
         <v>520</v>
       </c>
       <c r="G217" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7042,13 +7042,13 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F218" t="s">
         <v>520</v>
       </c>
       <c r="G218" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7065,13 +7065,13 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
         <v>520</v>
       </c>
       <c r="G219" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7088,13 +7088,13 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F220" t="s">
         <v>520</v>
       </c>
       <c r="G220" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7111,13 +7111,13 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F221" t="s">
         <v>520</v>
       </c>
       <c r="G221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7134,13 +7134,13 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F222" t="s">
         <v>520</v>
       </c>
       <c r="G222" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7157,13 +7157,13 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F223" t="s">
         <v>536</v>
       </c>
       <c r="G223" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7180,13 +7180,13 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F224" t="s">
         <v>536</v>
       </c>
       <c r="G224" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7203,13 +7203,13 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F225" t="s">
         <v>536</v>
       </c>
       <c r="G225" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7226,13 +7226,13 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F226" t="s">
         <v>544</v>
       </c>
       <c r="G226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7249,13 +7249,13 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F227" t="s">
         <v>548</v>
       </c>
       <c r="G227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7272,13 +7272,13 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F228" t="s">
         <v>552</v>
       </c>
       <c r="G228" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7295,13 +7295,13 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F229" t="s">
         <v>556</v>
       </c>
       <c r="G229" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7318,13 +7318,13 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F230" t="s">
         <v>560</v>
       </c>
       <c r="G230" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7341,13 +7341,13 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F231" t="s">
         <v>560</v>
       </c>
       <c r="G231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Education de Base</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Education Secondaire</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Education Post Secondaire</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>Santé, Général</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Santé de Base</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Maladies non-transmissibles (MNT)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflits, Paix et Sécurité</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources renouvelables</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources non renouvelables</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Centrales nucléaires</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Distribution de l'énergie</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Sylviculture</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Pêche</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Industries Extractives</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,10 +1357,10 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
-  </si>
-  <si>
-    <t>323</t>
   </si>
   <si>
     <t>33110</t>
@@ -2163,13 +2163,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2209,13 +2209,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2232,13 +2232,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2255,13 +2255,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2278,13 +2278,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2301,13 +2301,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2324,13 +2324,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2439,13 +2439,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2462,13 +2462,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2485,13 +2485,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2508,13 +2508,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2531,13 +2531,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2554,13 +2554,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2577,13 +2577,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2600,13 +2600,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2623,13 +2623,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2646,13 +2646,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2669,13 +2669,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2692,13 +2692,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2715,13 +2715,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2738,13 +2738,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3497,13 +3497,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3520,13 +3520,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3543,13 +3543,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3566,13 +3566,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3589,13 +3589,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3612,13 +3612,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4233,13 +4233,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4256,13 +4256,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4279,13 +4279,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4302,13 +4302,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4325,13 +4325,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4348,13 +4348,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4371,13 +4371,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4394,13 +4394,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4417,13 +4417,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4440,13 +4440,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4463,13 +4463,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4486,13 +4486,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4509,13 +4509,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4532,13 +4532,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4555,13 +4555,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
+        <v>226</v>
+      </c>
+      <c r="G111" t="s">
         <v>269</v>
-      </c>
-      <c r="G111" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,13 +4601,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>274</v>
@@ -4624,13 +4624,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>278</v>
@@ -4647,13 +4647,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>278</v>
@@ -4670,13 +4670,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>278</v>
@@ -4693,13 +4693,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>278</v>
@@ -4716,13 +4716,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>278</v>
@@ -4739,13 +4739,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>278</v>
@@ -4762,13 +4762,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>278</v>
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>293</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>293</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>293</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>293</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>293</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>293</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>307</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>307</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>307</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>307</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5429,13 +5429,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E148" t="s">
         <v>318</v>
       </c>
       <c r="F148" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G148" t="s">
         <v>358</v>
@@ -5452,13 +5452,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
         <v>318</v>
       </c>
       <c r="F149" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G149" t="s">
         <v>358</v>
@@ -5475,13 +5475,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E150" t="s">
         <v>318</v>
       </c>
       <c r="F150" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G150" t="s">
         <v>358</v>
@@ -5498,13 +5498,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E151" t="s">
         <v>318</v>
       </c>
       <c r="F151" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G151" t="s">
         <v>358</v>
@@ -5521,13 +5521,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E152" t="s">
         <v>318</v>
       </c>
       <c r="F152" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G152" t="s">
         <v>358</v>
@@ -5544,13 +5544,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
         <v>318</v>
       </c>
       <c r="F153" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G153" t="s">
         <v>358</v>
@@ -5567,13 +5567,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E154" t="s">
         <v>318</v>
       </c>
       <c r="F154" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G154" t="s">
         <v>372</v>
@@ -5590,13 +5590,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E155" t="s">
         <v>318</v>
       </c>
       <c r="F155" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G155" t="s">
         <v>372</v>
@@ -5613,13 +5613,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
         <v>318</v>
       </c>
       <c r="F156" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G156" t="s">
         <v>372</v>
@@ -5636,13 +5636,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
         <v>318</v>
       </c>
       <c r="F157" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G157" t="s">
         <v>372</v>
@@ -5659,13 +5659,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E158" t="s">
         <v>318</v>
       </c>
       <c r="F158" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G158" t="s">
         <v>372</v>
@@ -6119,13 +6119,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E178" t="s">
         <v>384</v>
       </c>
       <c r="F178" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G178" t="s">
         <v>426</v>
@@ -6142,13 +6142,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E179" t="s">
         <v>384</v>
       </c>
       <c r="F179" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G179" t="s">
         <v>426</v>
@@ -6165,13 +6165,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E180" t="s">
         <v>384</v>
       </c>
       <c r="F180" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G180" t="s">
         <v>426</v>
@@ -6188,13 +6188,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E181" t="s">
         <v>384</v>
       </c>
       <c r="F181" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G181" t="s">
         <v>426</v>
@@ -6211,13 +6211,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E182" t="s">
         <v>384</v>
       </c>
       <c r="F182" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G182" t="s">
         <v>426</v>
@@ -6234,13 +6234,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E183" t="s">
         <v>384</v>
       </c>
       <c r="F183" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G183" t="s">
         <v>426</v>
@@ -6257,13 +6257,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E184" t="s">
         <v>384</v>
       </c>
       <c r="F184" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G184" t="s">
         <v>426</v>
@@ -6280,13 +6280,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E185" t="s">
         <v>384</v>
       </c>
       <c r="F185" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G185" t="s">
         <v>426</v>
@@ -6303,13 +6303,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E186" t="s">
         <v>384</v>
       </c>
       <c r="F186" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G186" t="s">
         <v>426</v>
@@ -6326,13 +6326,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E187" t="s">
         <v>384</v>
       </c>
       <c r="F187" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G187" t="s">
         <v>426</v>
@@ -6349,13 +6349,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="E188" t="s">
         <v>384</v>
       </c>
       <c r="F188" t="s">
-        <v>447</v>
+        <v>385</v>
       </c>
       <c r="G188" t="s">
         <v>448</v>
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>451</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>451</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>451</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>451</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>451</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>451</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>465</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>469</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>469</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>469</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>469</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>469</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>469</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>483</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>483</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>483</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>483</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>483</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>483</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>483</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>483</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>483</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>483</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>505</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>509</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>513</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>513</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>519</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>519</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>519</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>519</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>519</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>519</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>519</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>535</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>535</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>535</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>543</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>547</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>551</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>555</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>559</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>559</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>Santé, Général</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
@@ -967,15 +967,15 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
@@ -1165,13 +1165,13 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>321</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>320</t>
   </si>
   <si>
     <t>Industries Manufacturières</t>
@@ -2163,13 +2163,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2209,13 +2209,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2232,13 +2232,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2255,13 +2255,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2278,13 +2278,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2301,13 +2301,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2324,13 +2324,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2439,13 +2439,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2462,13 +2462,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2485,13 +2485,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2508,13 +2508,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2531,13 +2531,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2554,13 +2554,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2577,13 +2577,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2600,13 +2600,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2623,13 +2623,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2646,13 +2646,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2669,13 +2669,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2692,13 +2692,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2715,13 +2715,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2738,13 +2738,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -3497,13 +3497,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3520,13 +3520,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3543,13 +3543,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3566,13 +3566,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3589,13 +3589,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3612,13 +3612,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -4233,13 +4233,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4256,13 +4256,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4279,13 +4279,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4302,13 +4302,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4325,13 +4325,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4348,13 +4348,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4371,13 +4371,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4394,13 +4394,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4417,13 +4417,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4440,13 +4440,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4463,13 +4463,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4486,13 +4486,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4509,13 +4509,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4532,13 +4532,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4555,13 +4555,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4578,13 +4578,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="G111" t="s">
         <v>269</v>
@@ -4601,13 +4601,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="G112" t="s">
         <v>274</v>
@@ -4624,13 +4624,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G113" t="s">
         <v>278</v>
@@ -4647,13 +4647,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G114" t="s">
         <v>278</v>
@@ -4670,13 +4670,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G115" t="s">
         <v>278</v>
@@ -4693,13 +4693,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G116" t="s">
         <v>278</v>
@@ -4716,13 +4716,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G117" t="s">
         <v>278</v>
@@ -4739,13 +4739,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G118" t="s">
         <v>278</v>
@@ -4762,13 +4762,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G119" t="s">
         <v>278</v>
@@ -5429,13 +5429,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E148" t="s">
         <v>318</v>
       </c>
       <c r="F148" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G148" t="s">
         <v>358</v>
@@ -5452,13 +5452,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E149" t="s">
         <v>318</v>
       </c>
       <c r="F149" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G149" t="s">
         <v>358</v>
@@ -5475,13 +5475,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E150" t="s">
         <v>318</v>
       </c>
       <c r="F150" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G150" t="s">
         <v>358</v>
@@ -5498,13 +5498,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E151" t="s">
         <v>318</v>
       </c>
       <c r="F151" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G151" t="s">
         <v>358</v>
@@ -5521,13 +5521,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E152" t="s">
         <v>318</v>
       </c>
       <c r="F152" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G152" t="s">
         <v>358</v>
@@ -5544,13 +5544,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E153" t="s">
         <v>318</v>
       </c>
       <c r="F153" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="G153" t="s">
         <v>358</v>
@@ -5567,13 +5567,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E154" t="s">
         <v>318</v>
       </c>
       <c r="F154" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G154" t="s">
         <v>372</v>
@@ -5590,13 +5590,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E155" t="s">
         <v>318</v>
       </c>
       <c r="F155" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G155" t="s">
         <v>372</v>
@@ -5613,13 +5613,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E156" t="s">
         <v>318</v>
       </c>
       <c r="F156" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G156" t="s">
         <v>372</v>
@@ -5636,13 +5636,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E157" t="s">
         <v>318</v>
       </c>
       <c r="F157" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G157" t="s">
         <v>372</v>
@@ -5659,13 +5659,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E158" t="s">
         <v>318</v>
       </c>
       <c r="F158" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G158" t="s">
         <v>372</v>
@@ -6119,13 +6119,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E178" t="s">
         <v>384</v>
       </c>
       <c r="F178" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G178" t="s">
         <v>426</v>
@@ -6142,13 +6142,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E179" t="s">
         <v>384</v>
       </c>
       <c r="F179" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G179" t="s">
         <v>426</v>
@@ -6165,13 +6165,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E180" t="s">
         <v>384</v>
       </c>
       <c r="F180" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G180" t="s">
         <v>426</v>
@@ -6188,13 +6188,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E181" t="s">
         <v>384</v>
       </c>
       <c r="F181" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G181" t="s">
         <v>426</v>
@@ -6211,13 +6211,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E182" t="s">
         <v>384</v>
       </c>
       <c r="F182" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G182" t="s">
         <v>426</v>
@@ -6234,13 +6234,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E183" t="s">
         <v>384</v>
       </c>
       <c r="F183" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G183" t="s">
         <v>426</v>
@@ -6257,13 +6257,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E184" t="s">
         <v>384</v>
       </c>
       <c r="F184" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G184" t="s">
         <v>426</v>
@@ -6280,13 +6280,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E185" t="s">
         <v>384</v>
       </c>
       <c r="F185" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G185" t="s">
         <v>426</v>
@@ -6303,13 +6303,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E186" t="s">
         <v>384</v>
       </c>
       <c r="F186" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G186" t="s">
         <v>426</v>
@@ -6326,13 +6326,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E187" t="s">
         <v>384</v>
       </c>
       <c r="F187" t="s">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="G187" t="s">
         <v>426</v>
@@ -6349,13 +6349,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>447</v>
+        <v>383</v>
       </c>
       <c r="E188" t="s">
         <v>384</v>
       </c>
       <c r="F188" t="s">
-        <v>385</v>
+        <v>447</v>
       </c>
       <c r="G188" t="s">
         <v>448</v>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>Distribution d'Eau et Assainissement</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Distribution d'Eau et Assainissement</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>Infrastructure et Services Sociaux Divers</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Infrastructure et Services Sociaux Divers</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>Transports et Entreposage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transports et Entreposage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>Banques et Services Financiers</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banques et Services Financiers</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>Entreprises et Autres Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Entreprises et Autres Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,12 +967,12 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1165,12 +1165,12 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>Politique Commerciale et Réglementations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Politique Commerciale et Réglementations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>Tourisme</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourisme</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>Protection de l'Environnement Général</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protection de l'Environnement Général</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>Autres Multisecteurs</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Autres Multisecteurs</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>Soutien Budgétaire</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Soutien Budgétaire</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>Aide Alimentaire Dévelopmentale</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Aide Alimentaire Dévelopmentale</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>Aide sous forme de Produits, Autre</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Aide sous forme de Produits, Autre</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>Actions se Rapportant a la Dette</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actions se Rapportant a la Dette</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>Intervention d'Urgence</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Intervention d'Urgence</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>Reconstruction &amp; Réhabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction &amp; Réhabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>Prévention catastrophes/Préparation à leur survenue</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prévention catastrophes/Préparation à leur survenue</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>Frais Administratifs des Donneurs</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Frais Administratifs des Donneurs</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>Refugiés dans les Pays Donneurs</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiés dans les Pays Donneurs</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>Non Affecté / Non Specifié</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Non Affecté / Non Specifié</t>
   </si>
   <si>
     <t>99820</t>
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>293</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>293</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>293</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>293</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>293</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>293</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>307</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>307</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>307</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>307</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>451</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>451</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>451</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>451</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>451</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>451</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>465</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>469</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>469</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>469</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>469</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>469</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>469</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>483</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>483</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>483</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>483</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>483</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>483</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>483</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>483</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>483</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>483</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>505</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>509</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>513</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>513</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>519</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>519</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>519</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>519</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>519</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>519</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>519</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>535</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>535</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>535</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>543</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>547</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>551</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>555</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>559</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>559</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:group-name</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Education</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>Education de Base</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Education de Base</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>Education Secondaire</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Education Secondaire</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>Education Post Secondaire</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Education Post Secondaire</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>Santé</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
     <t>121</t>
   </si>
   <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>Santé de Base</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Santé de Base</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>Maladies non-transmissibles (MNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Maladies non-transmissibles (MNT)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
     <t>151</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>Conflits, Paix et Sécurité</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflits, Paix et Sécurité</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>Energie</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
     <t>231</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>Production d'électricité, sources renouvelables</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Production d'électricité, sources renouvelables</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>Production d'électricité, sources non renouvelables</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Production d'électricité, sources non renouvelables</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>Centrales nucléaires</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrales nucléaires</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>Distribution de l'énergie</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribution de l'énergie</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>Sylviculture</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Sylviculture</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>Pêche</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pêche</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1168,15 +1168,15 @@
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Extractives</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Industries Extractives</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,10 +1357,10 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>33110</t>
@@ -2166,10 +2166,10 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2189,10 +2189,10 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2212,10 +2212,10 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2235,10 +2235,10 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2258,10 +2258,10 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2281,10 +2281,10 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2304,10 +2304,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2327,10 +2327,10 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2442,10 +2442,10 @@
         <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2465,10 +2465,10 @@
         <v>44</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2488,10 +2488,10 @@
         <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2511,10 +2511,10 @@
         <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2534,10 +2534,10 @@
         <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2557,10 +2557,10 @@
         <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2580,10 +2580,10 @@
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2603,10 +2603,10 @@
         <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2626,10 +2626,10 @@
         <v>44</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2649,10 +2649,10 @@
         <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2672,10 +2672,10 @@
         <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2695,10 +2695,10 @@
         <v>44</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2718,10 +2718,10 @@
         <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2741,10 +2741,10 @@
         <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -2764,13 +2764,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2787,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2810,13 +2810,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2833,13 +2833,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2856,13 +2856,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2879,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2902,13 +2902,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2925,13 +2925,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2971,13 +2971,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2994,13 +2994,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3017,13 +3017,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3040,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3063,13 +3063,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3086,13 +3086,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3109,13 +3109,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>124</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3523,10 +3523,10 @@
         <v>124</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3546,10 +3546,10 @@
         <v>124</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3569,10 +3569,10 @@
         <v>124</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3592,10 +3592,10 @@
         <v>124</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3615,10 +3615,10 @@
         <v>124</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -3638,13 +3638,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3661,13 +3661,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3684,13 +3684,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3707,13 +3707,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3730,13 +3730,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3753,13 +3753,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3776,13 +3776,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3799,13 +3799,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3822,13 +3822,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3845,13 +3845,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3868,13 +3868,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3891,13 +3891,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3914,13 +3914,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3937,13 +3937,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3960,13 +3960,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3983,13 +3983,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4006,13 +4006,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4029,13 +4029,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4052,13 +4052,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4075,13 +4075,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4098,13 +4098,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4121,13 +4121,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,10 +4236,10 @@
         <v>224</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4259,10 +4259,10 @@
         <v>224</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4282,10 +4282,10 @@
         <v>224</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4305,10 +4305,10 @@
         <v>224</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4328,10 +4328,10 @@
         <v>224</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4351,10 +4351,10 @@
         <v>224</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4374,10 +4374,10 @@
         <v>224</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4397,10 +4397,10 @@
         <v>224</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4420,10 +4420,10 @@
         <v>224</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4443,10 +4443,10 @@
         <v>224</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4466,10 +4466,10 @@
         <v>224</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4489,10 +4489,10 @@
         <v>224</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4512,10 +4512,10 @@
         <v>224</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4535,10 +4535,10 @@
         <v>224</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4558,10 +4558,10 @@
         <v>224</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4581,13 +4581,13 @@
         <v>224</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="F111" t="s">
+        <v>226</v>
+      </c>
+      <c r="G111" t="s">
         <v>270</v>
-      </c>
-      <c r="G111" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,10 +4604,10 @@
         <v>224</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>273</v>
       </c>
       <c r="F112" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>274</v>
@@ -4627,10 +4627,10 @@
         <v>224</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F113" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>278</v>
@@ -4650,10 +4650,10 @@
         <v>224</v>
       </c>
       <c r="E114" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F114" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>278</v>
@@ -4673,10 +4673,10 @@
         <v>224</v>
       </c>
       <c r="E115" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F115" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>278</v>
@@ -4696,10 +4696,10 @@
         <v>224</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F116" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>278</v>
@@ -4719,10 +4719,10 @@
         <v>224</v>
       </c>
       <c r="E117" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F117" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>278</v>
@@ -4742,10 +4742,10 @@
         <v>224</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F118" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>278</v>
@@ -4765,10 +4765,10 @@
         <v>224</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F119" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>278</v>
@@ -4788,13 +4788,13 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F120" t="s">
         <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4811,13 +4811,13 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F121" t="s">
         <v>294</v>
       </c>
       <c r="G121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4834,13 +4834,13 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F122" t="s">
         <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4857,13 +4857,13 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F123" t="s">
         <v>294</v>
       </c>
       <c r="G123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4880,13 +4880,13 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F124" t="s">
         <v>294</v>
       </c>
       <c r="G124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4903,13 +4903,13 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F125" t="s">
         <v>294</v>
       </c>
       <c r="G125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4926,13 +4926,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F126" t="s">
         <v>308</v>
       </c>
       <c r="G126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4949,13 +4949,13 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F127" t="s">
         <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4972,13 +4972,13 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F128" t="s">
         <v>308</v>
       </c>
       <c r="G128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4995,13 +4995,13 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F129" t="s">
         <v>308</v>
       </c>
       <c r="G129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,10 +5432,10 @@
         <v>317</v>
       </c>
       <c r="E148" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F148" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G148" t="s">
         <v>358</v>
@@ -5455,10 +5455,10 @@
         <v>317</v>
       </c>
       <c r="E149" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F149" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G149" t="s">
         <v>358</v>
@@ -5478,10 +5478,10 @@
         <v>317</v>
       </c>
       <c r="E150" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F150" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G150" t="s">
         <v>358</v>
@@ -5501,10 +5501,10 @@
         <v>317</v>
       </c>
       <c r="E151" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F151" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G151" t="s">
         <v>358</v>
@@ -5524,10 +5524,10 @@
         <v>317</v>
       </c>
       <c r="E152" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F152" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G152" t="s">
         <v>358</v>
@@ -5547,10 +5547,10 @@
         <v>317</v>
       </c>
       <c r="E153" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F153" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G153" t="s">
         <v>358</v>
@@ -5570,10 +5570,10 @@
         <v>317</v>
       </c>
       <c r="E154" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="F154" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G154" t="s">
         <v>372</v>
@@ -5593,10 +5593,10 @@
         <v>317</v>
       </c>
       <c r="E155" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="F155" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G155" t="s">
         <v>372</v>
@@ -5616,10 +5616,10 @@
         <v>317</v>
       </c>
       <c r="E156" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="F156" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G156" t="s">
         <v>372</v>
@@ -5639,10 +5639,10 @@
         <v>317</v>
       </c>
       <c r="E157" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="F157" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G157" t="s">
         <v>372</v>
@@ -5662,10 +5662,10 @@
         <v>317</v>
       </c>
       <c r="E158" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="F158" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G158" t="s">
         <v>372</v>
@@ -6122,10 +6122,10 @@
         <v>383</v>
       </c>
       <c r="E178" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F178" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G178" t="s">
         <v>426</v>
@@ -6145,10 +6145,10 @@
         <v>383</v>
       </c>
       <c r="E179" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F179" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G179" t="s">
         <v>426</v>
@@ -6168,10 +6168,10 @@
         <v>383</v>
       </c>
       <c r="E180" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F180" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G180" t="s">
         <v>426</v>
@@ -6191,10 +6191,10 @@
         <v>383</v>
       </c>
       <c r="E181" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F181" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G181" t="s">
         <v>426</v>
@@ -6214,10 +6214,10 @@
         <v>383</v>
       </c>
       <c r="E182" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F182" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G182" t="s">
         <v>426</v>
@@ -6237,10 +6237,10 @@
         <v>383</v>
       </c>
       <c r="E183" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F183" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G183" t="s">
         <v>426</v>
@@ -6260,10 +6260,10 @@
         <v>383</v>
       </c>
       <c r="E184" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F184" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G184" t="s">
         <v>426</v>
@@ -6283,10 +6283,10 @@
         <v>383</v>
       </c>
       <c r="E185" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F185" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G185" t="s">
         <v>426</v>
@@ -6306,10 +6306,10 @@
         <v>383</v>
       </c>
       <c r="E186" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F186" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G186" t="s">
         <v>426</v>
@@ -6329,10 +6329,10 @@
         <v>383</v>
       </c>
       <c r="E187" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F187" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G187" t="s">
         <v>426</v>
@@ -6352,10 +6352,10 @@
         <v>383</v>
       </c>
       <c r="E188" t="s">
-        <v>384</v>
+        <v>447</v>
       </c>
       <c r="F188" t="s">
-        <v>447</v>
+        <v>385</v>
       </c>
       <c r="G188" t="s">
         <v>448</v>
@@ -6375,13 +6375,13 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F189" t="s">
         <v>452</v>
       </c>
       <c r="G189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6398,13 +6398,13 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F190" t="s">
         <v>452</v>
       </c>
       <c r="G190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6421,13 +6421,13 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F191" t="s">
         <v>452</v>
       </c>
       <c r="G191" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6444,13 +6444,13 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F192" t="s">
         <v>452</v>
       </c>
       <c r="G192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6467,13 +6467,13 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F193" t="s">
         <v>452</v>
       </c>
       <c r="G193" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6490,13 +6490,13 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F194" t="s">
         <v>452</v>
       </c>
       <c r="G194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6513,13 +6513,13 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F195" t="s">
         <v>466</v>
       </c>
       <c r="G195" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6536,13 +6536,13 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F196" t="s">
         <v>470</v>
       </c>
       <c r="G196" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6559,13 +6559,13 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F197" t="s">
         <v>470</v>
       </c>
       <c r="G197" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6582,13 +6582,13 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F198" t="s">
         <v>470</v>
       </c>
       <c r="G198" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6605,13 +6605,13 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F199" t="s">
         <v>470</v>
       </c>
       <c r="G199" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6628,13 +6628,13 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F200" t="s">
         <v>470</v>
       </c>
       <c r="G200" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6651,13 +6651,13 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F201" t="s">
         <v>470</v>
       </c>
       <c r="G201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6674,13 +6674,13 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F202" t="s">
         <v>484</v>
       </c>
       <c r="G202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6697,13 +6697,13 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F203" t="s">
         <v>484</v>
       </c>
       <c r="G203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6720,13 +6720,13 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F204" t="s">
         <v>484</v>
       </c>
       <c r="G204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6743,13 +6743,13 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F205" t="s">
         <v>484</v>
       </c>
       <c r="G205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6766,13 +6766,13 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F206" t="s">
         <v>484</v>
       </c>
       <c r="G206" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6789,13 +6789,13 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F207" t="s">
         <v>484</v>
       </c>
       <c r="G207" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6812,13 +6812,13 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F208" t="s">
         <v>484</v>
       </c>
       <c r="G208" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6835,13 +6835,13 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F209" t="s">
         <v>484</v>
       </c>
       <c r="G209" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6858,13 +6858,13 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F210" t="s">
         <v>484</v>
       </c>
       <c r="G210" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6881,13 +6881,13 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F211" t="s">
         <v>484</v>
       </c>
       <c r="G211" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6904,13 +6904,13 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F212" t="s">
         <v>506</v>
       </c>
       <c r="G212" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6927,13 +6927,13 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F213" t="s">
         <v>510</v>
       </c>
       <c r="G213" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6950,13 +6950,13 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F214" t="s">
         <v>514</v>
       </c>
       <c r="G214" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6973,13 +6973,13 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F215" t="s">
         <v>514</v>
       </c>
       <c r="G215" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6996,13 +6996,13 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F216" t="s">
         <v>520</v>
       </c>
       <c r="G216" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7019,13 +7019,13 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F217" t="s">
         <v>520</v>
       </c>
       <c r="G217" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7042,13 +7042,13 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F218" t="s">
         <v>520</v>
       </c>
       <c r="G218" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7065,13 +7065,13 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F219" t="s">
         <v>520</v>
       </c>
       <c r="G219" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7088,13 +7088,13 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F220" t="s">
         <v>520</v>
       </c>
       <c r="G220" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7111,13 +7111,13 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F221" t="s">
         <v>520</v>
       </c>
       <c r="G221" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7134,13 +7134,13 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F222" t="s">
         <v>520</v>
       </c>
       <c r="G222" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7157,13 +7157,13 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F223" t="s">
         <v>536</v>
       </c>
       <c r="G223" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7180,13 +7180,13 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F224" t="s">
         <v>536</v>
       </c>
       <c r="G224" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7203,13 +7203,13 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F225" t="s">
         <v>536</v>
       </c>
       <c r="G225" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7226,13 +7226,13 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F226" t="s">
         <v>544</v>
       </c>
       <c r="G226" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7249,13 +7249,13 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F227" t="s">
         <v>548</v>
       </c>
       <c r="G227" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7272,13 +7272,13 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F228" t="s">
         <v>552</v>
       </c>
       <c r="G228" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7295,13 +7295,13 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F229" t="s">
         <v>556</v>
       </c>
       <c r="G229" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7318,13 +7318,13 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F230" t="s">
         <v>560</v>
       </c>
       <c r="G230" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7341,13 +7341,13 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F231" t="s">
         <v>560</v>
       </c>
       <c r="G231" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Santé</t>
   </si>
   <si>
     <t>Santé, Général</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Distribution d'Eau et Assainissement</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Infrastructure et Services Sociaux Divers</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transports et Entreposage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energie</t>
   </si>
   <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banques et Services Financiers</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Entreprises et Autres Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,15 +967,15 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1165,15 +1165,15 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Politique Commerciale et Réglementations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourisme</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>Protection de l'Environnement Général</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Autres Multisecteurs</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>Soutien Budgétaire</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Aide Alimentaire Dévelopmentale</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Aide sous forme de Produits, Autre</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Actions se Rapportant a la Dette</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Intervention d'Urgence</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction &amp; Réhabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Prévention catastrophes/Préparation à leur survenue</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Frais Administratifs des Donneurs</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugiés dans les Pays Donneurs</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Non Affecté / Non Specifié</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2166,10 +2166,10 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -2189,10 +2189,10 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -2212,10 +2212,10 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -2235,10 +2235,10 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -2258,10 +2258,10 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>32</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2281,10 +2281,10 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2304,10 +2304,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>39</v>
@@ -2327,10 +2327,10 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>38</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2442,10 +2442,10 @@
         <v>44</v>
       </c>
       <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s">
         <v>56</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>57</v>
@@ -2465,10 +2465,10 @@
         <v>44</v>
       </c>
       <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -2488,10 +2488,10 @@
         <v>44</v>
       </c>
       <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
         <v>56</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>57</v>
@@ -2511,10 +2511,10 @@
         <v>44</v>
       </c>
       <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
         <v>56</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>57</v>
@@ -2534,10 +2534,10 @@
         <v>44</v>
       </c>
       <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
         <v>56</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>57</v>
@@ -2557,10 +2557,10 @@
         <v>44</v>
       </c>
       <c r="E23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" t="s">
         <v>56</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>57</v>
@@ -2580,10 +2580,10 @@
         <v>44</v>
       </c>
       <c r="E24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" t="s">
         <v>56</v>
-      </c>
-      <c r="F24" t="s">
-        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>57</v>
@@ -2603,10 +2603,10 @@
         <v>44</v>
       </c>
       <c r="E25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
         <v>56</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
@@ -2626,10 +2626,10 @@
         <v>44</v>
       </c>
       <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
         <v>74</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2649,10 +2649,10 @@
         <v>44</v>
       </c>
       <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
         <v>74</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
@@ -2672,10 +2672,10 @@
         <v>44</v>
       </c>
       <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
         <v>74</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2695,10 +2695,10 @@
         <v>44</v>
       </c>
       <c r="E29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s">
         <v>74</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>75</v>
@@ -2718,10 +2718,10 @@
         <v>44</v>
       </c>
       <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
         <v>74</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
@@ -2741,10 +2741,10 @@
         <v>44</v>
       </c>
       <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" t="s">
         <v>74</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
@@ -2764,13 +2764,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2787,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2810,13 +2810,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2833,13 +2833,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2856,13 +2856,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2879,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2902,13 +2902,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2925,13 +2925,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2971,13 +2971,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2994,13 +2994,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3017,13 +3017,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3040,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3063,13 +3063,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3086,13 +3086,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3109,13 +3109,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>124</v>
       </c>
       <c r="E64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" t="s">
         <v>160</v>
-      </c>
-      <c r="F64" t="s">
-        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -3523,10 +3523,10 @@
         <v>124</v>
       </c>
       <c r="E65" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" t="s">
         <v>160</v>
-      </c>
-      <c r="F65" t="s">
-        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>161</v>
@@ -3546,10 +3546,10 @@
         <v>124</v>
       </c>
       <c r="E66" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" t="s">
         <v>160</v>
-      </c>
-      <c r="F66" t="s">
-        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -3569,10 +3569,10 @@
         <v>124</v>
       </c>
       <c r="E67" t="s">
+        <v>125</v>
+      </c>
+      <c r="F67" t="s">
         <v>160</v>
-      </c>
-      <c r="F67" t="s">
-        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>161</v>
@@ -3592,10 +3592,10 @@
         <v>124</v>
       </c>
       <c r="E68" t="s">
+        <v>125</v>
+      </c>
+      <c r="F68" t="s">
         <v>160</v>
-      </c>
-      <c r="F68" t="s">
-        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>161</v>
@@ -3615,10 +3615,10 @@
         <v>124</v>
       </c>
       <c r="E69" t="s">
+        <v>125</v>
+      </c>
+      <c r="F69" t="s">
         <v>160</v>
-      </c>
-      <c r="F69" t="s">
-        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>161</v>
@@ -3638,13 +3638,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3661,13 +3661,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3684,13 +3684,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3707,13 +3707,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3730,13 +3730,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3753,13 +3753,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3776,13 +3776,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3799,13 +3799,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3822,13 +3822,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3845,13 +3845,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3868,13 +3868,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3891,13 +3891,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3914,13 +3914,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3937,13 +3937,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3960,13 +3960,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3983,13 +3983,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4006,13 +4006,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4029,13 +4029,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4052,13 +4052,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4075,13 +4075,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4098,13 +4098,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4121,13 +4121,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,10 +4236,10 @@
         <v>224</v>
       </c>
       <c r="E96" t="s">
+        <v>225</v>
+      </c>
+      <c r="F96" t="s">
         <v>236</v>
-      </c>
-      <c r="F96" t="s">
-        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>237</v>
@@ -4259,10 +4259,10 @@
         <v>224</v>
       </c>
       <c r="E97" t="s">
+        <v>225</v>
+      </c>
+      <c r="F97" t="s">
         <v>236</v>
-      </c>
-      <c r="F97" t="s">
-        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>237</v>
@@ -4282,10 +4282,10 @@
         <v>224</v>
       </c>
       <c r="E98" t="s">
+        <v>225</v>
+      </c>
+      <c r="F98" t="s">
         <v>236</v>
-      </c>
-      <c r="F98" t="s">
-        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>237</v>
@@ -4305,10 +4305,10 @@
         <v>224</v>
       </c>
       <c r="E99" t="s">
+        <v>225</v>
+      </c>
+      <c r="F99" t="s">
         <v>236</v>
-      </c>
-      <c r="F99" t="s">
-        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>237</v>
@@ -4328,10 +4328,10 @@
         <v>224</v>
       </c>
       <c r="E100" t="s">
+        <v>225</v>
+      </c>
+      <c r="F100" t="s">
         <v>236</v>
-      </c>
-      <c r="F100" t="s">
-        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>237</v>
@@ -4351,10 +4351,10 @@
         <v>224</v>
       </c>
       <c r="E101" t="s">
+        <v>225</v>
+      </c>
+      <c r="F101" t="s">
         <v>236</v>
-      </c>
-      <c r="F101" t="s">
-        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>237</v>
@@ -4374,10 +4374,10 @@
         <v>224</v>
       </c>
       <c r="E102" t="s">
+        <v>225</v>
+      </c>
+      <c r="F102" t="s">
         <v>236</v>
-      </c>
-      <c r="F102" t="s">
-        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>237</v>
@@ -4397,10 +4397,10 @@
         <v>224</v>
       </c>
       <c r="E103" t="s">
+        <v>225</v>
+      </c>
+      <c r="F103" t="s">
         <v>236</v>
-      </c>
-      <c r="F103" t="s">
-        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>237</v>
@@ -4420,10 +4420,10 @@
         <v>224</v>
       </c>
       <c r="E104" t="s">
+        <v>225</v>
+      </c>
+      <c r="F104" t="s">
         <v>236</v>
-      </c>
-      <c r="F104" t="s">
-        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
@@ -4443,10 +4443,10 @@
         <v>224</v>
       </c>
       <c r="E105" t="s">
+        <v>225</v>
+      </c>
+      <c r="F105" t="s">
         <v>256</v>
-      </c>
-      <c r="F105" t="s">
-        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>257</v>
@@ -4466,10 +4466,10 @@
         <v>224</v>
       </c>
       <c r="E106" t="s">
+        <v>225</v>
+      </c>
+      <c r="F106" t="s">
         <v>256</v>
-      </c>
-      <c r="F106" t="s">
-        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>257</v>
@@ -4489,10 +4489,10 @@
         <v>224</v>
       </c>
       <c r="E107" t="s">
+        <v>225</v>
+      </c>
+      <c r="F107" t="s">
         <v>256</v>
-      </c>
-      <c r="F107" t="s">
-        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>257</v>
@@ -4512,10 +4512,10 @@
         <v>224</v>
       </c>
       <c r="E108" t="s">
+        <v>225</v>
+      </c>
+      <c r="F108" t="s">
         <v>256</v>
-      </c>
-      <c r="F108" t="s">
-        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>257</v>
@@ -4535,10 +4535,10 @@
         <v>224</v>
       </c>
       <c r="E109" t="s">
+        <v>225</v>
+      </c>
+      <c r="F109" t="s">
         <v>256</v>
-      </c>
-      <c r="F109" t="s">
-        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>257</v>
@@ -4558,10 +4558,10 @@
         <v>224</v>
       </c>
       <c r="E110" t="s">
+        <v>225</v>
+      </c>
+      <c r="F110" t="s">
         <v>256</v>
-      </c>
-      <c r="F110" t="s">
-        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>257</v>
@@ -4581,10 +4581,10 @@
         <v>224</v>
       </c>
       <c r="E111" t="s">
+        <v>225</v>
+      </c>
+      <c r="F111" t="s">
         <v>269</v>
-      </c>
-      <c r="F111" t="s">
-        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>270</v>
@@ -4604,10 +4604,10 @@
         <v>224</v>
       </c>
       <c r="E112" t="s">
+        <v>225</v>
+      </c>
+      <c r="F112" t="s">
         <v>273</v>
-      </c>
-      <c r="F112" t="s">
-        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>274</v>
@@ -4627,10 +4627,10 @@
         <v>224</v>
       </c>
       <c r="E113" t="s">
+        <v>225</v>
+      </c>
+      <c r="F113" t="s">
         <v>277</v>
-      </c>
-      <c r="F113" t="s">
-        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>278</v>
@@ -4650,10 +4650,10 @@
         <v>224</v>
       </c>
       <c r="E114" t="s">
+        <v>225</v>
+      </c>
+      <c r="F114" t="s">
         <v>277</v>
-      </c>
-      <c r="F114" t="s">
-        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>278</v>
@@ -4673,10 +4673,10 @@
         <v>224</v>
       </c>
       <c r="E115" t="s">
+        <v>225</v>
+      </c>
+      <c r="F115" t="s">
         <v>277</v>
-      </c>
-      <c r="F115" t="s">
-        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>278</v>
@@ -4696,10 +4696,10 @@
         <v>224</v>
       </c>
       <c r="E116" t="s">
+        <v>225</v>
+      </c>
+      <c r="F116" t="s">
         <v>277</v>
-      </c>
-      <c r="F116" t="s">
-        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>278</v>
@@ -4719,10 +4719,10 @@
         <v>224</v>
       </c>
       <c r="E117" t="s">
+        <v>225</v>
+      </c>
+      <c r="F117" t="s">
         <v>277</v>
-      </c>
-      <c r="F117" t="s">
-        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>278</v>
@@ -4742,10 +4742,10 @@
         <v>224</v>
       </c>
       <c r="E118" t="s">
+        <v>225</v>
+      </c>
+      <c r="F118" t="s">
         <v>277</v>
-      </c>
-      <c r="F118" t="s">
-        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>278</v>
@@ -4765,10 +4765,10 @@
         <v>224</v>
       </c>
       <c r="E119" t="s">
+        <v>225</v>
+      </c>
+      <c r="F119" t="s">
         <v>277</v>
-      </c>
-      <c r="F119" t="s">
-        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>278</v>
@@ -4788,13 +4788,13 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F120" t="s">
         <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4811,13 +4811,13 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F121" t="s">
         <v>294</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4834,13 +4834,13 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
         <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4857,13 +4857,13 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F123" t="s">
         <v>294</v>
       </c>
       <c r="G123" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4880,13 +4880,13 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F124" t="s">
         <v>294</v>
       </c>
       <c r="G124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4903,13 +4903,13 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F125" t="s">
         <v>294</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4926,13 +4926,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F126" t="s">
         <v>308</v>
       </c>
       <c r="G126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4949,13 +4949,13 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4972,13 +4972,13 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
         <v>308</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4995,13 +4995,13 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F129" t="s">
         <v>308</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,10 +5432,10 @@
         <v>317</v>
       </c>
       <c r="E148" t="s">
+        <v>318</v>
+      </c>
+      <c r="F148" t="s">
         <v>357</v>
-      </c>
-      <c r="F148" t="s">
-        <v>319</v>
       </c>
       <c r="G148" t="s">
         <v>358</v>
@@ -5455,10 +5455,10 @@
         <v>317</v>
       </c>
       <c r="E149" t="s">
+        <v>318</v>
+      </c>
+      <c r="F149" t="s">
         <v>357</v>
-      </c>
-      <c r="F149" t="s">
-        <v>319</v>
       </c>
       <c r="G149" t="s">
         <v>358</v>
@@ -5478,10 +5478,10 @@
         <v>317</v>
       </c>
       <c r="E150" t="s">
+        <v>318</v>
+      </c>
+      <c r="F150" t="s">
         <v>357</v>
-      </c>
-      <c r="F150" t="s">
-        <v>319</v>
       </c>
       <c r="G150" t="s">
         <v>358</v>
@@ -5501,10 +5501,10 @@
         <v>317</v>
       </c>
       <c r="E151" t="s">
+        <v>318</v>
+      </c>
+      <c r="F151" t="s">
         <v>357</v>
-      </c>
-      <c r="F151" t="s">
-        <v>319</v>
       </c>
       <c r="G151" t="s">
         <v>358</v>
@@ -5524,10 +5524,10 @@
         <v>317</v>
       </c>
       <c r="E152" t="s">
+        <v>318</v>
+      </c>
+      <c r="F152" t="s">
         <v>357</v>
-      </c>
-      <c r="F152" t="s">
-        <v>319</v>
       </c>
       <c r="G152" t="s">
         <v>358</v>
@@ -5547,10 +5547,10 @@
         <v>317</v>
       </c>
       <c r="E153" t="s">
+        <v>318</v>
+      </c>
+      <c r="F153" t="s">
         <v>357</v>
-      </c>
-      <c r="F153" t="s">
-        <v>319</v>
       </c>
       <c r="G153" t="s">
         <v>358</v>
@@ -5570,10 +5570,10 @@
         <v>317</v>
       </c>
       <c r="E154" t="s">
+        <v>318</v>
+      </c>
+      <c r="F154" t="s">
         <v>371</v>
-      </c>
-      <c r="F154" t="s">
-        <v>319</v>
       </c>
       <c r="G154" t="s">
         <v>372</v>
@@ -5593,10 +5593,10 @@
         <v>317</v>
       </c>
       <c r="E155" t="s">
+        <v>318</v>
+      </c>
+      <c r="F155" t="s">
         <v>371</v>
-      </c>
-      <c r="F155" t="s">
-        <v>319</v>
       </c>
       <c r="G155" t="s">
         <v>372</v>
@@ -5616,10 +5616,10 @@
         <v>317</v>
       </c>
       <c r="E156" t="s">
+        <v>318</v>
+      </c>
+      <c r="F156" t="s">
         <v>371</v>
-      </c>
-      <c r="F156" t="s">
-        <v>319</v>
       </c>
       <c r="G156" t="s">
         <v>372</v>
@@ -5639,10 +5639,10 @@
         <v>317</v>
       </c>
       <c r="E157" t="s">
+        <v>318</v>
+      </c>
+      <c r="F157" t="s">
         <v>371</v>
-      </c>
-      <c r="F157" t="s">
-        <v>319</v>
       </c>
       <c r="G157" t="s">
         <v>372</v>
@@ -5662,10 +5662,10 @@
         <v>317</v>
       </c>
       <c r="E158" t="s">
+        <v>318</v>
+      </c>
+      <c r="F158" t="s">
         <v>371</v>
-      </c>
-      <c r="F158" t="s">
-        <v>319</v>
       </c>
       <c r="G158" t="s">
         <v>372</v>
@@ -6122,10 +6122,10 @@
         <v>383</v>
       </c>
       <c r="E178" t="s">
+        <v>384</v>
+      </c>
+      <c r="F178" t="s">
         <v>425</v>
-      </c>
-      <c r="F178" t="s">
-        <v>385</v>
       </c>
       <c r="G178" t="s">
         <v>426</v>
@@ -6145,10 +6145,10 @@
         <v>383</v>
       </c>
       <c r="E179" t="s">
+        <v>384</v>
+      </c>
+      <c r="F179" t="s">
         <v>425</v>
-      </c>
-      <c r="F179" t="s">
-        <v>385</v>
       </c>
       <c r="G179" t="s">
         <v>426</v>
@@ -6168,10 +6168,10 @@
         <v>383</v>
       </c>
       <c r="E180" t="s">
+        <v>384</v>
+      </c>
+      <c r="F180" t="s">
         <v>425</v>
-      </c>
-      <c r="F180" t="s">
-        <v>385</v>
       </c>
       <c r="G180" t="s">
         <v>426</v>
@@ -6191,10 +6191,10 @@
         <v>383</v>
       </c>
       <c r="E181" t="s">
+        <v>384</v>
+      </c>
+      <c r="F181" t="s">
         <v>425</v>
-      </c>
-      <c r="F181" t="s">
-        <v>385</v>
       </c>
       <c r="G181" t="s">
         <v>426</v>
@@ -6214,10 +6214,10 @@
         <v>383</v>
       </c>
       <c r="E182" t="s">
+        <v>384</v>
+      </c>
+      <c r="F182" t="s">
         <v>425</v>
-      </c>
-      <c r="F182" t="s">
-        <v>385</v>
       </c>
       <c r="G182" t="s">
         <v>426</v>
@@ -6237,10 +6237,10 @@
         <v>383</v>
       </c>
       <c r="E183" t="s">
+        <v>384</v>
+      </c>
+      <c r="F183" t="s">
         <v>425</v>
-      </c>
-      <c r="F183" t="s">
-        <v>385</v>
       </c>
       <c r="G183" t="s">
         <v>426</v>
@@ -6260,10 +6260,10 @@
         <v>383</v>
       </c>
       <c r="E184" t="s">
+        <v>384</v>
+      </c>
+      <c r="F184" t="s">
         <v>425</v>
-      </c>
-      <c r="F184" t="s">
-        <v>385</v>
       </c>
       <c r="G184" t="s">
         <v>426</v>
@@ -6283,10 +6283,10 @@
         <v>383</v>
       </c>
       <c r="E185" t="s">
+        <v>384</v>
+      </c>
+      <c r="F185" t="s">
         <v>425</v>
-      </c>
-      <c r="F185" t="s">
-        <v>385</v>
       </c>
       <c r="G185" t="s">
         <v>426</v>
@@ -6306,10 +6306,10 @@
         <v>383</v>
       </c>
       <c r="E186" t="s">
+        <v>384</v>
+      </c>
+      <c r="F186" t="s">
         <v>425</v>
-      </c>
-      <c r="F186" t="s">
-        <v>385</v>
       </c>
       <c r="G186" t="s">
         <v>426</v>
@@ -6329,10 +6329,10 @@
         <v>383</v>
       </c>
       <c r="E187" t="s">
+        <v>384</v>
+      </c>
+      <c r="F187" t="s">
         <v>425</v>
-      </c>
-      <c r="F187" t="s">
-        <v>385</v>
       </c>
       <c r="G187" t="s">
         <v>426</v>
@@ -6352,10 +6352,10 @@
         <v>383</v>
       </c>
       <c r="E188" t="s">
+        <v>384</v>
+      </c>
+      <c r="F188" t="s">
         <v>447</v>
-      </c>
-      <c r="F188" t="s">
-        <v>385</v>
       </c>
       <c r="G188" t="s">
         <v>448</v>
@@ -6375,13 +6375,13 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s">
         <v>452</v>
       </c>
       <c r="G189" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6398,13 +6398,13 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F190" t="s">
         <v>452</v>
       </c>
       <c r="G190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6421,13 +6421,13 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F191" t="s">
         <v>452</v>
       </c>
       <c r="G191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6444,13 +6444,13 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F192" t="s">
         <v>452</v>
       </c>
       <c r="G192" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6467,13 +6467,13 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>452</v>
       </c>
       <c r="G193" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6490,13 +6490,13 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F194" t="s">
         <v>452</v>
       </c>
       <c r="G194" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6513,13 +6513,13 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F195" t="s">
         <v>466</v>
       </c>
       <c r="G195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6536,13 +6536,13 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F196" t="s">
         <v>470</v>
       </c>
       <c r="G196" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6559,13 +6559,13 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F197" t="s">
         <v>470</v>
       </c>
       <c r="G197" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6582,13 +6582,13 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F198" t="s">
         <v>470</v>
       </c>
       <c r="G198" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6605,13 +6605,13 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F199" t="s">
         <v>470</v>
       </c>
       <c r="G199" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6628,13 +6628,13 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F200" t="s">
         <v>470</v>
       </c>
       <c r="G200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6651,13 +6651,13 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
         <v>470</v>
       </c>
       <c r="G201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6674,13 +6674,13 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F202" t="s">
         <v>484</v>
       </c>
       <c r="G202" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6697,13 +6697,13 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F203" t="s">
         <v>484</v>
       </c>
       <c r="G203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6720,13 +6720,13 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F204" t="s">
         <v>484</v>
       </c>
       <c r="G204" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6743,13 +6743,13 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F205" t="s">
         <v>484</v>
       </c>
       <c r="G205" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6766,13 +6766,13 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F206" t="s">
         <v>484</v>
       </c>
       <c r="G206" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6789,13 +6789,13 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F207" t="s">
         <v>484</v>
       </c>
       <c r="G207" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6812,13 +6812,13 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F208" t="s">
         <v>484</v>
       </c>
       <c r="G208" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6835,13 +6835,13 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F209" t="s">
         <v>484</v>
       </c>
       <c r="G209" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6858,13 +6858,13 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F210" t="s">
         <v>484</v>
       </c>
       <c r="G210" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6881,13 +6881,13 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F211" t="s">
         <v>484</v>
       </c>
       <c r="G211" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6904,13 +6904,13 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F212" t="s">
         <v>506</v>
       </c>
       <c r="G212" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6927,13 +6927,13 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F213" t="s">
         <v>510</v>
       </c>
       <c r="G213" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6950,13 +6950,13 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F214" t="s">
         <v>514</v>
       </c>
       <c r="G214" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6973,13 +6973,13 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F215" t="s">
         <v>514</v>
       </c>
       <c r="G215" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6996,13 +6996,13 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F216" t="s">
         <v>520</v>
       </c>
       <c r="G216" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7019,13 +7019,13 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F217" t="s">
         <v>520</v>
       </c>
       <c r="G217" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7042,13 +7042,13 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F218" t="s">
         <v>520</v>
       </c>
       <c r="G218" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7065,13 +7065,13 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
         <v>520</v>
       </c>
       <c r="G219" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7088,13 +7088,13 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F220" t="s">
         <v>520</v>
       </c>
       <c r="G220" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7111,13 +7111,13 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F221" t="s">
         <v>520</v>
       </c>
       <c r="G221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7134,13 +7134,13 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F222" t="s">
         <v>520</v>
       </c>
       <c r="G222" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7157,13 +7157,13 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F223" t="s">
         <v>536</v>
       </c>
       <c r="G223" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7180,13 +7180,13 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F224" t="s">
         <v>536</v>
       </c>
       <c r="G224" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7203,13 +7203,13 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F225" t="s">
         <v>536</v>
       </c>
       <c r="G225" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7226,13 +7226,13 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F226" t="s">
         <v>544</v>
       </c>
       <c r="G226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7249,13 +7249,13 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F227" t="s">
         <v>548</v>
       </c>
       <c r="G227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7272,13 +7272,13 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F228" t="s">
         <v>552</v>
       </c>
       <c r="G228" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7295,13 +7295,13 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F229" t="s">
         <v>556</v>
       </c>
       <c r="G229" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7318,13 +7318,13 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F230" t="s">
         <v>560</v>
       </c>
       <c r="G230" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7341,13 +7341,13 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F231" t="s">
         <v>560</v>
       </c>
       <c r="G231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:group-name</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>Education</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Education de Base</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Education Secondaire</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Education Post Secondaire</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>Santé</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Santé de Base</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Maladies non-transmissibles (MNT)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflits, Paix et Sécurité</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>Energie</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources renouvelables</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources non renouvelables</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Centrales nucléaires</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Distribution de l'énergie</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Sylviculture</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Pêche</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1171,12 +1171,12 @@
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Industries Extractives</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,10 +1357,10 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
-  </si>
-  <si>
-    <t>323</t>
   </si>
   <si>
     <t>33110</t>
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4584,10 +4584,10 @@
         <v>225</v>
       </c>
       <c r="F111" t="s">
+        <v>270</v>
+      </c>
+      <c r="G111" t="s">
         <v>269</v>
-      </c>
-      <c r="G111" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>293</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>293</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>293</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>293</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>293</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>293</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>307</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>307</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>307</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>307</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>451</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>451</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>451</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>451</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>451</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>451</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>465</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>469</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>469</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>469</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>469</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>469</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>469</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>483</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>483</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>483</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>483</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>483</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>483</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>483</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>483</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>483</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>483</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>505</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>509</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>513</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>513</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>519</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>519</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>519</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>519</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>519</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>519</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>519</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>535</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>535</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>535</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>543</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>547</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>551</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>555</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>559</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>559</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>Education de Base</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Education de Base</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>Education Secondaire</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Education Secondaire</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>Education Post Secondaire</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Education Post Secondaire</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>Santé</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>Santé de Base</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Santé de Base</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>Maladies non-transmissibles (MNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Maladies non-transmissibles (MNT)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>Distribution d'Eau et Assainissement</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Distribution d'Eau et Assainissement</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>Conflits, Paix et Sécurité</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflits, Paix et Sécurité</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>Infrastructure et Services Sociaux Divers</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Infrastructure et Services Sociaux Divers</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>Transports et Entreposage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transports et Entreposage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>Energie</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>Production d'électricité, sources renouvelables</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Production d'électricité, sources renouvelables</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>Production d'électricité, sources non renouvelables</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Production d'électricité, sources non renouvelables</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>Centrales nucléaires</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrales nucléaires</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>Distribution de l'énergie</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribution de l'énergie</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>Banques et Services Financiers</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banques et Services Financiers</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>Entreprises et Autres Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Entreprises et Autres Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>Sylviculture</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Sylviculture</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>Pêche</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pêche</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Extractives</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Industries Extractives</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,24 +1357,24 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>Politique Commerciale et Réglementations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Politique Commerciale et Réglementations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>Tourisme</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourisme</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>Protection de l'Environnement Général</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protection de l'Environnement Général</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>Autres Multisecteurs</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Autres Multisecteurs</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>Soutien Budgétaire</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Soutien Budgétaire</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>Aide Alimentaire Dévelopmentale</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Aide Alimentaire Dévelopmentale</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>Aide sous forme de Produits, Autre</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Aide sous forme de Produits, Autre</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>Actions se Rapportant a la Dette</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actions se Rapportant a la Dette</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>Intervention d'Urgence</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Intervention d'Urgence</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>Reconstruction &amp; Réhabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction &amp; Réhabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>Prévention catastrophes/Préparation à leur survenue</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prévention catastrophes/Préparation à leur survenue</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>Frais Administratifs des Donneurs</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Frais Administratifs des Donneurs</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>Refugiés dans les Pays Donneurs</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiés dans les Pays Donneurs</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>Non Affecté / Non Specifié</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Non Affecté / Non Specifié</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,7 +4578,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
@@ -4587,7 +4587,7 @@
         <v>270</v>
       </c>
       <c r="G111" t="s">
-        <v>269</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G116" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G118" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G119" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>293</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>293</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>293</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>293</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>293</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>293</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>307</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>307</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>307</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>307</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E148" t="s">
         <v>318</v>
       </c>
       <c r="F148" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
         <v>318</v>
       </c>
       <c r="F149" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E150" t="s">
         <v>318</v>
       </c>
       <c r="F150" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E151" t="s">
         <v>318</v>
       </c>
       <c r="F151" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E152" t="s">
         <v>318</v>
       </c>
       <c r="F152" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
         <v>318</v>
       </c>
       <c r="F153" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E154" t="s">
         <v>318</v>
       </c>
       <c r="F154" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E155" t="s">
         <v>318</v>
       </c>
       <c r="F155" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
         <v>318</v>
       </c>
       <c r="F156" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
         <v>318</v>
       </c>
       <c r="F157" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E158" t="s">
         <v>318</v>
       </c>
       <c r="F158" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E178" t="s">
         <v>384</v>
       </c>
       <c r="F178" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E179" t="s">
         <v>384</v>
       </c>
       <c r="F179" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E180" t="s">
         <v>384</v>
       </c>
       <c r="F180" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E181" t="s">
         <v>384</v>
       </c>
       <c r="F181" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E182" t="s">
         <v>384</v>
       </c>
       <c r="F182" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6234,16 +6234,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E183" t="s">
         <v>384</v>
       </c>
       <c r="F183" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6257,16 +6257,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E184" t="s">
         <v>384</v>
       </c>
       <c r="F184" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6280,16 +6280,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E185" t="s">
         <v>384</v>
       </c>
       <c r="F185" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6303,16 +6303,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E186" t="s">
         <v>384</v>
       </c>
       <c r="F186" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6326,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E187" t="s">
         <v>384</v>
       </c>
       <c r="F187" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6349,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="E188" t="s">
         <v>384</v>
       </c>
       <c r="F188" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>451</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>451</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>451</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>451</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>451</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>451</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>465</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>469</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>469</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>469</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>469</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>469</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>469</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>483</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>483</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>483</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>483</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>483</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>483</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>483</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>483</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>483</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>483</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>505</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>509</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>513</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>513</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>519</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>519</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>519</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>519</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>519</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>519</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>519</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>535</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>535</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>535</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>543</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>547</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>551</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>555</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>559</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>559</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Distribution d'Eau et Assainissement</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Infrastructure et Services Sociaux Divers</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transports et Entreposage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banques et Services Financiers</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Entreprises et Autres Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,12 +967,12 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1165,12 +1165,12 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Politique Commerciale et Réglementations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourisme</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>Protection de l'Environnement Général</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Autres Multisecteurs</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>Soutien Budgétaire</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Aide Alimentaire Dévelopmentale</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Aide sous forme de Produits, Autre</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Actions se Rapportant a la Dette</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Intervention d'Urgence</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction &amp; Réhabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Prévention catastrophes/Préparation à leur survenue</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Frais Administratifs des Donneurs</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugiés dans les Pays Donneurs</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Non Affecté / Non Specifié</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,10 +2163,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>23</v>
@@ -2186,10 +2186,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>23</v>
@@ -2209,10 +2209,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -2232,10 +2232,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>23</v>
@@ -2255,10 +2255,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>33</v>
@@ -2278,10 +2278,10 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2301,10 +2301,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -2324,10 +2324,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -2439,10 +2439,10 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
-      </c>
-      <c r="E18" t="s">
-        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -2462,10 +2462,10 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>57</v>
@@ -2485,10 +2485,10 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>57</v>
@@ -2508,10 +2508,10 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
-      </c>
-      <c r="E21" t="s">
-        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2531,10 +2531,10 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
-      </c>
-      <c r="E22" t="s">
-        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>57</v>
@@ -2554,10 +2554,10 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
-      </c>
-      <c r="E23" t="s">
-        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>57</v>
@@ -2577,10 +2577,10 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
-      </c>
-      <c r="E24" t="s">
-        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>57</v>
@@ -2600,10 +2600,10 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
-      </c>
-      <c r="E25" t="s">
-        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>57</v>
@@ -2623,10 +2623,10 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
-      </c>
-      <c r="E26" t="s">
-        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>75</v>
@@ -2646,10 +2646,10 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
-      </c>
-      <c r="E27" t="s">
-        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>75</v>
@@ -2669,10 +2669,10 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
-      </c>
-      <c r="E28" t="s">
-        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>75</v>
@@ -2692,10 +2692,10 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
-      </c>
-      <c r="E29" t="s">
-        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>75</v>
@@ -2715,10 +2715,10 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
-      </c>
-      <c r="E30" t="s">
-        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>75</v>
@@ -2738,10 +2738,10 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
-      </c>
-      <c r="E31" t="s">
-        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>75</v>
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3497,10 +3497,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
-      </c>
-      <c r="E64" t="s">
-        <v>125</v>
       </c>
       <c r="F64" t="s">
         <v>161</v>
@@ -3520,10 +3520,10 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
-      </c>
-      <c r="E65" t="s">
-        <v>125</v>
       </c>
       <c r="F65" t="s">
         <v>161</v>
@@ -3543,10 +3543,10 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
-      </c>
-      <c r="E66" t="s">
-        <v>125</v>
       </c>
       <c r="F66" t="s">
         <v>161</v>
@@ -3566,10 +3566,10 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
-      </c>
-      <c r="E67" t="s">
-        <v>125</v>
       </c>
       <c r="F67" t="s">
         <v>161</v>
@@ -3589,10 +3589,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
-      </c>
-      <c r="E68" t="s">
-        <v>125</v>
       </c>
       <c r="F68" t="s">
         <v>161</v>
@@ -3612,10 +3612,10 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
-      </c>
-      <c r="E69" t="s">
-        <v>125</v>
       </c>
       <c r="F69" t="s">
         <v>161</v>
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4233,10 +4233,10 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
-      </c>
-      <c r="E96" t="s">
-        <v>225</v>
       </c>
       <c r="F96" t="s">
         <v>237</v>
@@ -4256,10 +4256,10 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
-      </c>
-      <c r="E97" t="s">
-        <v>225</v>
       </c>
       <c r="F97" t="s">
         <v>237</v>
@@ -4279,10 +4279,10 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
-      </c>
-      <c r="E98" t="s">
-        <v>225</v>
       </c>
       <c r="F98" t="s">
         <v>237</v>
@@ -4302,10 +4302,10 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
-      </c>
-      <c r="E99" t="s">
-        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>237</v>
@@ -4325,10 +4325,10 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
-      </c>
-      <c r="E100" t="s">
-        <v>225</v>
       </c>
       <c r="F100" t="s">
         <v>237</v>
@@ -4348,10 +4348,10 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
-      </c>
-      <c r="E101" t="s">
-        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>237</v>
@@ -4371,10 +4371,10 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
-      </c>
-      <c r="E102" t="s">
-        <v>225</v>
       </c>
       <c r="F102" t="s">
         <v>237</v>
@@ -4394,10 +4394,10 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
-      </c>
-      <c r="E103" t="s">
-        <v>225</v>
       </c>
       <c r="F103" t="s">
         <v>237</v>
@@ -4417,10 +4417,10 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
-      </c>
-      <c r="E104" t="s">
-        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>237</v>
@@ -4440,10 +4440,10 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
-      </c>
-      <c r="E105" t="s">
-        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>257</v>
@@ -4463,10 +4463,10 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
-      </c>
-      <c r="E106" t="s">
-        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>257</v>
@@ -4486,10 +4486,10 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
-      </c>
-      <c r="E107" t="s">
-        <v>225</v>
       </c>
       <c r="F107" t="s">
         <v>257</v>
@@ -4509,10 +4509,10 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
-      </c>
-      <c r="E108" t="s">
-        <v>225</v>
       </c>
       <c r="F108" t="s">
         <v>257</v>
@@ -4532,10 +4532,10 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
-      </c>
-      <c r="E109" t="s">
-        <v>225</v>
       </c>
       <c r="F109" t="s">
         <v>257</v>
@@ -4555,10 +4555,10 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
-      </c>
-      <c r="E110" t="s">
-        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>257</v>
@@ -4578,10 +4578,10 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
         <v>269</v>
-      </c>
-      <c r="E111" t="s">
-        <v>225</v>
       </c>
       <c r="F111" t="s">
         <v>270</v>
@@ -4601,10 +4601,10 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>273</v>
-      </c>
-      <c r="E112" t="s">
-        <v>225</v>
       </c>
       <c r="F112" t="s">
         <v>274</v>
@@ -4624,10 +4624,10 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>277</v>
-      </c>
-      <c r="E113" t="s">
-        <v>225</v>
       </c>
       <c r="F113" t="s">
         <v>278</v>
@@ -4647,10 +4647,10 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>277</v>
-      </c>
-      <c r="E114" t="s">
-        <v>225</v>
       </c>
       <c r="F114" t="s">
         <v>278</v>
@@ -4670,10 +4670,10 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>277</v>
-      </c>
-      <c r="E115" t="s">
-        <v>225</v>
       </c>
       <c r="F115" t="s">
         <v>278</v>
@@ -4693,10 +4693,10 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>277</v>
-      </c>
-      <c r="E116" t="s">
-        <v>225</v>
       </c>
       <c r="F116" t="s">
         <v>278</v>
@@ -4716,10 +4716,10 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>277</v>
-      </c>
-      <c r="E117" t="s">
-        <v>225</v>
       </c>
       <c r="F117" t="s">
         <v>278</v>
@@ -4739,10 +4739,10 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>277</v>
-      </c>
-      <c r="E118" t="s">
-        <v>225</v>
       </c>
       <c r="F118" t="s">
         <v>278</v>
@@ -4762,10 +4762,10 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>277</v>
-      </c>
-      <c r="E119" t="s">
-        <v>225</v>
       </c>
       <c r="F119" t="s">
         <v>278</v>
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>293</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>293</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>293</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>293</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>293</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>293</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>307</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>307</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>307</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>307</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5429,10 +5429,10 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>317</v>
+      </c>
+      <c r="E148" t="s">
         <v>357</v>
-      </c>
-      <c r="E148" t="s">
-        <v>318</v>
       </c>
       <c r="F148" t="s">
         <v>358</v>
@@ -5452,10 +5452,10 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>317</v>
+      </c>
+      <c r="E149" t="s">
         <v>357</v>
-      </c>
-      <c r="E149" t="s">
-        <v>318</v>
       </c>
       <c r="F149" t="s">
         <v>358</v>
@@ -5475,10 +5475,10 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>317</v>
+      </c>
+      <c r="E150" t="s">
         <v>357</v>
-      </c>
-      <c r="E150" t="s">
-        <v>318</v>
       </c>
       <c r="F150" t="s">
         <v>358</v>
@@ -5498,10 +5498,10 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>317</v>
+      </c>
+      <c r="E151" t="s">
         <v>357</v>
-      </c>
-      <c r="E151" t="s">
-        <v>318</v>
       </c>
       <c r="F151" t="s">
         <v>358</v>
@@ -5521,10 +5521,10 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>317</v>
+      </c>
+      <c r="E152" t="s">
         <v>357</v>
-      </c>
-      <c r="E152" t="s">
-        <v>318</v>
       </c>
       <c r="F152" t="s">
         <v>358</v>
@@ -5544,10 +5544,10 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>317</v>
+      </c>
+      <c r="E153" t="s">
         <v>357</v>
-      </c>
-      <c r="E153" t="s">
-        <v>318</v>
       </c>
       <c r="F153" t="s">
         <v>358</v>
@@ -5567,10 +5567,10 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>317</v>
+      </c>
+      <c r="E154" t="s">
         <v>371</v>
-      </c>
-      <c r="E154" t="s">
-        <v>318</v>
       </c>
       <c r="F154" t="s">
         <v>372</v>
@@ -5590,10 +5590,10 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>317</v>
+      </c>
+      <c r="E155" t="s">
         <v>371</v>
-      </c>
-      <c r="E155" t="s">
-        <v>318</v>
       </c>
       <c r="F155" t="s">
         <v>372</v>
@@ -5613,10 +5613,10 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>317</v>
+      </c>
+      <c r="E156" t="s">
         <v>371</v>
-      </c>
-      <c r="E156" t="s">
-        <v>318</v>
       </c>
       <c r="F156" t="s">
         <v>372</v>
@@ -5636,10 +5636,10 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>317</v>
+      </c>
+      <c r="E157" t="s">
         <v>371</v>
-      </c>
-      <c r="E157" t="s">
-        <v>318</v>
       </c>
       <c r="F157" t="s">
         <v>372</v>
@@ -5659,10 +5659,10 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>317</v>
+      </c>
+      <c r="E158" t="s">
         <v>371</v>
-      </c>
-      <c r="E158" t="s">
-        <v>318</v>
       </c>
       <c r="F158" t="s">
         <v>372</v>
@@ -6119,10 +6119,10 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>383</v>
+      </c>
+      <c r="E178" t="s">
         <v>425</v>
-      </c>
-      <c r="E178" t="s">
-        <v>384</v>
       </c>
       <c r="F178" t="s">
         <v>426</v>
@@ -6142,10 +6142,10 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>383</v>
+      </c>
+      <c r="E179" t="s">
         <v>425</v>
-      </c>
-      <c r="E179" t="s">
-        <v>384</v>
       </c>
       <c r="F179" t="s">
         <v>426</v>
@@ -6165,10 +6165,10 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>383</v>
+      </c>
+      <c r="E180" t="s">
         <v>425</v>
-      </c>
-      <c r="E180" t="s">
-        <v>384</v>
       </c>
       <c r="F180" t="s">
         <v>426</v>
@@ -6188,10 +6188,10 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>383</v>
+      </c>
+      <c r="E181" t="s">
         <v>425</v>
-      </c>
-      <c r="E181" t="s">
-        <v>384</v>
       </c>
       <c r="F181" t="s">
         <v>426</v>
@@ -6211,10 +6211,10 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>383</v>
+      </c>
+      <c r="E182" t="s">
         <v>425</v>
-      </c>
-      <c r="E182" t="s">
-        <v>384</v>
       </c>
       <c r="F182" t="s">
         <v>426</v>
@@ -6234,10 +6234,10 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>383</v>
+      </c>
+      <c r="E183" t="s">
         <v>425</v>
-      </c>
-      <c r="E183" t="s">
-        <v>384</v>
       </c>
       <c r="F183" t="s">
         <v>426</v>
@@ -6257,10 +6257,10 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>383</v>
+      </c>
+      <c r="E184" t="s">
         <v>425</v>
-      </c>
-      <c r="E184" t="s">
-        <v>384</v>
       </c>
       <c r="F184" t="s">
         <v>426</v>
@@ -6280,10 +6280,10 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>383</v>
+      </c>
+      <c r="E185" t="s">
         <v>425</v>
-      </c>
-      <c r="E185" t="s">
-        <v>384</v>
       </c>
       <c r="F185" t="s">
         <v>426</v>
@@ -6303,10 +6303,10 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>383</v>
+      </c>
+      <c r="E186" t="s">
         <v>425</v>
-      </c>
-      <c r="E186" t="s">
-        <v>384</v>
       </c>
       <c r="F186" t="s">
         <v>426</v>
@@ -6326,10 +6326,10 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>383</v>
+      </c>
+      <c r="E187" t="s">
         <v>425</v>
-      </c>
-      <c r="E187" t="s">
-        <v>384</v>
       </c>
       <c r="F187" t="s">
         <v>426</v>
@@ -6349,10 +6349,10 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>383</v>
+      </c>
+      <c r="E188" t="s">
         <v>447</v>
-      </c>
-      <c r="E188" t="s">
-        <v>384</v>
       </c>
       <c r="F188" t="s">
         <v>448</v>
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>451</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>451</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>451</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>451</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>451</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>451</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>465</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>469</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>469</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>469</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>469</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>469</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>469</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>483</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>483</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>483</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>483</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>483</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>483</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>483</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>483</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>483</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>483</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>505</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>509</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>513</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>513</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>519</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>519</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>519</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>519</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>519</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>519</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>519</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>535</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>535</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>535</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>543</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>547</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>551</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>555</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>559</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>559</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>Distribution d'Eau et Assainissement</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Distribution d'Eau et Assainissement</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>Infrastructure et Services Sociaux Divers</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Infrastructure et Services Sociaux Divers</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>Transports et Entreposage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transports et Entreposage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>Banques et Services Financiers</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banques et Services Financiers</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>Entreprises et Autres Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Entreprises et Autres Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>Politique Commerciale et Réglementations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Politique Commerciale et Réglementations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>Tourisme</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourisme</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>Protection de l'Environnement Général</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protection de l'Environnement Général</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>Autres Multisecteurs</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Autres Multisecteurs</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>Soutien Budgétaire</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Soutien Budgétaire</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>Aide Alimentaire Dévelopmentale</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Aide Alimentaire Dévelopmentale</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>Aide sous forme de Produits, Autre</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Aide sous forme de Produits, Autre</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>Actions se Rapportant a la Dette</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actions se Rapportant a la Dette</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>Intervention d'Urgence</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Intervention d'Urgence</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>Reconstruction &amp; Réhabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction &amp; Réhabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>Prévention catastrophes/Préparation à leur survenue</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prévention catastrophes/Préparation à leur survenue</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>Frais Administratifs des Donneurs</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Frais Administratifs des Donneurs</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>Refugiés dans les Pays Donneurs</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiés dans les Pays Donneurs</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>Non Affecté / Non Specifié</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Non Affecté / Non Specifié</t>
   </si>
   <si>
     <t>99820</t>
@@ -2764,10 +2764,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" t="s">
         <v>89</v>
-      </c>
-      <c r="F32" t="s">
-        <v>88</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2787,10 +2787,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" t="s">
         <v>89</v>
-      </c>
-      <c r="F33" t="s">
-        <v>88</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2810,10 +2810,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" t="s">
         <v>89</v>
-      </c>
-      <c r="F34" t="s">
-        <v>88</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2833,10 +2833,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" t="s">
         <v>89</v>
-      </c>
-      <c r="F35" t="s">
-        <v>88</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2856,10 +2856,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>88</v>
+      </c>
+      <c r="F36" t="s">
         <v>89</v>
-      </c>
-      <c r="F36" t="s">
-        <v>88</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2879,10 +2879,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" t="s">
         <v>101</v>
-      </c>
-      <c r="F37" t="s">
-        <v>100</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2902,10 +2902,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" t="s">
         <v>101</v>
-      </c>
-      <c r="F38" t="s">
-        <v>100</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2925,10 +2925,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>100</v>
+      </c>
+      <c r="F39" t="s">
         <v>101</v>
-      </c>
-      <c r="F39" t="s">
-        <v>100</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2948,10 +2948,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" t="s">
         <v>101</v>
-      </c>
-      <c r="F40" t="s">
-        <v>100</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2971,10 +2971,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" t="s">
         <v>101</v>
-      </c>
-      <c r="F41" t="s">
-        <v>100</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2994,10 +2994,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>100</v>
+      </c>
+      <c r="F42" t="s">
         <v>101</v>
-      </c>
-      <c r="F42" t="s">
-        <v>100</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3017,10 +3017,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>100</v>
+      </c>
+      <c r="F43" t="s">
         <v>101</v>
-      </c>
-      <c r="F43" t="s">
-        <v>100</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3040,10 +3040,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>100</v>
+      </c>
+      <c r="F44" t="s">
         <v>101</v>
-      </c>
-      <c r="F44" t="s">
-        <v>100</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3063,10 +3063,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>100</v>
+      </c>
+      <c r="F45" t="s">
         <v>101</v>
-      </c>
-      <c r="F45" t="s">
-        <v>100</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3086,10 +3086,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>100</v>
+      </c>
+      <c r="F46" t="s">
         <v>101</v>
-      </c>
-      <c r="F46" t="s">
-        <v>100</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3109,10 +3109,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>100</v>
+      </c>
+      <c r="F47" t="s">
         <v>101</v>
-      </c>
-      <c r="F47" t="s">
-        <v>100</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3638,10 +3638,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>174</v>
+      </c>
+      <c r="F70" t="s">
         <v>175</v>
-      </c>
-      <c r="F70" t="s">
-        <v>174</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3661,10 +3661,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>174</v>
+      </c>
+      <c r="F71" t="s">
         <v>175</v>
-      </c>
-      <c r="F71" t="s">
-        <v>174</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3684,10 +3684,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>174</v>
+      </c>
+      <c r="F72" t="s">
         <v>175</v>
-      </c>
-      <c r="F72" t="s">
-        <v>174</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3707,10 +3707,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73" t="s">
         <v>175</v>
-      </c>
-      <c r="F73" t="s">
-        <v>174</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3730,10 +3730,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>174</v>
+      </c>
+      <c r="F74" t="s">
         <v>175</v>
-      </c>
-      <c r="F74" t="s">
-        <v>174</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3753,10 +3753,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>174</v>
+      </c>
+      <c r="F75" t="s">
         <v>175</v>
-      </c>
-      <c r="F75" t="s">
-        <v>174</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3776,10 +3776,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>174</v>
+      </c>
+      <c r="F76" t="s">
         <v>175</v>
-      </c>
-      <c r="F76" t="s">
-        <v>174</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3799,10 +3799,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>174</v>
+      </c>
+      <c r="F77" t="s">
         <v>175</v>
-      </c>
-      <c r="F77" t="s">
-        <v>174</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3822,10 +3822,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>174</v>
+      </c>
+      <c r="F78" t="s">
         <v>175</v>
-      </c>
-      <c r="F78" t="s">
-        <v>174</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3845,10 +3845,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>174</v>
+      </c>
+      <c r="F79" t="s">
         <v>175</v>
-      </c>
-      <c r="F79" t="s">
-        <v>174</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3868,10 +3868,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>174</v>
+      </c>
+      <c r="F80" t="s">
         <v>175</v>
-      </c>
-      <c r="F80" t="s">
-        <v>174</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3891,10 +3891,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>198</v>
+      </c>
+      <c r="F81" t="s">
         <v>199</v>
-      </c>
-      <c r="F81" t="s">
-        <v>198</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3914,10 +3914,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>198</v>
+      </c>
+      <c r="F82" t="s">
         <v>199</v>
-      </c>
-      <c r="F82" t="s">
-        <v>198</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3937,10 +3937,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>198</v>
+      </c>
+      <c r="F83" t="s">
         <v>199</v>
-      </c>
-      <c r="F83" t="s">
-        <v>198</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3960,10 +3960,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>198</v>
+      </c>
+      <c r="F84" t="s">
         <v>199</v>
-      </c>
-      <c r="F84" t="s">
-        <v>198</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3983,10 +3983,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>198</v>
+      </c>
+      <c r="F85" t="s">
         <v>199</v>
-      </c>
-      <c r="F85" t="s">
-        <v>198</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4006,10 +4006,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>198</v>
+      </c>
+      <c r="F86" t="s">
         <v>199</v>
-      </c>
-      <c r="F86" t="s">
-        <v>198</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4029,10 +4029,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>198</v>
+      </c>
+      <c r="F87" t="s">
         <v>199</v>
-      </c>
-      <c r="F87" t="s">
-        <v>198</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4052,10 +4052,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>214</v>
+      </c>
+      <c r="F88" t="s">
         <v>215</v>
-      </c>
-      <c r="F88" t="s">
-        <v>214</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4075,10 +4075,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>214</v>
+      </c>
+      <c r="F89" t="s">
         <v>215</v>
-      </c>
-      <c r="F89" t="s">
-        <v>214</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4098,10 +4098,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>214</v>
+      </c>
+      <c r="F90" t="s">
         <v>215</v>
-      </c>
-      <c r="F90" t="s">
-        <v>214</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4121,10 +4121,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>214</v>
+      </c>
+      <c r="F91" t="s">
         <v>215</v>
-      </c>
-      <c r="F91" t="s">
-        <v>214</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4788,10 +4788,10 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
+        <v>293</v>
+      </c>
+      <c r="F120" t="s">
         <v>294</v>
-      </c>
-      <c r="F120" t="s">
-        <v>293</v>
       </c>
       <c r="G120" t="s">
         <v>294</v>
@@ -4811,10 +4811,10 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
+        <v>293</v>
+      </c>
+      <c r="F121" t="s">
         <v>294</v>
-      </c>
-      <c r="F121" t="s">
-        <v>293</v>
       </c>
       <c r="G121" t="s">
         <v>294</v>
@@ -4834,10 +4834,10 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
+        <v>293</v>
+      </c>
+      <c r="F122" t="s">
         <v>294</v>
-      </c>
-      <c r="F122" t="s">
-        <v>293</v>
       </c>
       <c r="G122" t="s">
         <v>294</v>
@@ -4857,10 +4857,10 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
+        <v>293</v>
+      </c>
+      <c r="F123" t="s">
         <v>294</v>
-      </c>
-      <c r="F123" t="s">
-        <v>293</v>
       </c>
       <c r="G123" t="s">
         <v>294</v>
@@ -4880,10 +4880,10 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
+        <v>293</v>
+      </c>
+      <c r="F124" t="s">
         <v>294</v>
-      </c>
-      <c r="F124" t="s">
-        <v>293</v>
       </c>
       <c r="G124" t="s">
         <v>294</v>
@@ -4903,10 +4903,10 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
+        <v>293</v>
+      </c>
+      <c r="F125" t="s">
         <v>294</v>
-      </c>
-      <c r="F125" t="s">
-        <v>293</v>
       </c>
       <c r="G125" t="s">
         <v>294</v>
@@ -4926,10 +4926,10 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
+        <v>307</v>
+      </c>
+      <c r="F126" t="s">
         <v>308</v>
-      </c>
-      <c r="F126" t="s">
-        <v>307</v>
       </c>
       <c r="G126" t="s">
         <v>308</v>
@@ -4949,10 +4949,10 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
+        <v>307</v>
+      </c>
+      <c r="F127" t="s">
         <v>308</v>
-      </c>
-      <c r="F127" t="s">
-        <v>307</v>
       </c>
       <c r="G127" t="s">
         <v>308</v>
@@ -4972,10 +4972,10 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
+        <v>307</v>
+      </c>
+      <c r="F128" t="s">
         <v>308</v>
-      </c>
-      <c r="F128" t="s">
-        <v>307</v>
       </c>
       <c r="G128" t="s">
         <v>308</v>
@@ -4995,10 +4995,10 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
+        <v>307</v>
+      </c>
+      <c r="F129" t="s">
         <v>308</v>
-      </c>
-      <c r="F129" t="s">
-        <v>307</v>
       </c>
       <c r="G129" t="s">
         <v>308</v>
@@ -6375,10 +6375,10 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
+        <v>451</v>
+      </c>
+      <c r="F189" t="s">
         <v>452</v>
-      </c>
-      <c r="F189" t="s">
-        <v>451</v>
       </c>
       <c r="G189" t="s">
         <v>452</v>
@@ -6398,10 +6398,10 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
+        <v>451</v>
+      </c>
+      <c r="F190" t="s">
         <v>452</v>
-      </c>
-      <c r="F190" t="s">
-        <v>451</v>
       </c>
       <c r="G190" t="s">
         <v>452</v>
@@ -6421,10 +6421,10 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
+        <v>451</v>
+      </c>
+      <c r="F191" t="s">
         <v>452</v>
-      </c>
-      <c r="F191" t="s">
-        <v>451</v>
       </c>
       <c r="G191" t="s">
         <v>452</v>
@@ -6444,10 +6444,10 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
+        <v>451</v>
+      </c>
+      <c r="F192" t="s">
         <v>452</v>
-      </c>
-      <c r="F192" t="s">
-        <v>451</v>
       </c>
       <c r="G192" t="s">
         <v>452</v>
@@ -6467,10 +6467,10 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
+        <v>451</v>
+      </c>
+      <c r="F193" t="s">
         <v>452</v>
-      </c>
-      <c r="F193" t="s">
-        <v>451</v>
       </c>
       <c r="G193" t="s">
         <v>452</v>
@@ -6490,10 +6490,10 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
+        <v>451</v>
+      </c>
+      <c r="F194" t="s">
         <v>452</v>
-      </c>
-      <c r="F194" t="s">
-        <v>451</v>
       </c>
       <c r="G194" t="s">
         <v>452</v>
@@ -6513,10 +6513,10 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
+        <v>465</v>
+      </c>
+      <c r="F195" t="s">
         <v>466</v>
-      </c>
-      <c r="F195" t="s">
-        <v>465</v>
       </c>
       <c r="G195" t="s">
         <v>466</v>
@@ -6536,10 +6536,10 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
+        <v>469</v>
+      </c>
+      <c r="F196" t="s">
         <v>470</v>
-      </c>
-      <c r="F196" t="s">
-        <v>469</v>
       </c>
       <c r="G196" t="s">
         <v>470</v>
@@ -6559,10 +6559,10 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
+        <v>469</v>
+      </c>
+      <c r="F197" t="s">
         <v>470</v>
-      </c>
-      <c r="F197" t="s">
-        <v>469</v>
       </c>
       <c r="G197" t="s">
         <v>470</v>
@@ -6582,10 +6582,10 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
+        <v>469</v>
+      </c>
+      <c r="F198" t="s">
         <v>470</v>
-      </c>
-      <c r="F198" t="s">
-        <v>469</v>
       </c>
       <c r="G198" t="s">
         <v>470</v>
@@ -6605,10 +6605,10 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
+        <v>469</v>
+      </c>
+      <c r="F199" t="s">
         <v>470</v>
-      </c>
-      <c r="F199" t="s">
-        <v>469</v>
       </c>
       <c r="G199" t="s">
         <v>470</v>
@@ -6628,10 +6628,10 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
+        <v>469</v>
+      </c>
+      <c r="F200" t="s">
         <v>470</v>
-      </c>
-      <c r="F200" t="s">
-        <v>469</v>
       </c>
       <c r="G200" t="s">
         <v>470</v>
@@ -6651,10 +6651,10 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
+        <v>469</v>
+      </c>
+      <c r="F201" t="s">
         <v>470</v>
-      </c>
-      <c r="F201" t="s">
-        <v>469</v>
       </c>
       <c r="G201" t="s">
         <v>470</v>
@@ -6674,10 +6674,10 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
+        <v>483</v>
+      </c>
+      <c r="F202" t="s">
         <v>484</v>
-      </c>
-      <c r="F202" t="s">
-        <v>483</v>
       </c>
       <c r="G202" t="s">
         <v>484</v>
@@ -6697,10 +6697,10 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
+        <v>483</v>
+      </c>
+      <c r="F203" t="s">
         <v>484</v>
-      </c>
-      <c r="F203" t="s">
-        <v>483</v>
       </c>
       <c r="G203" t="s">
         <v>484</v>
@@ -6720,10 +6720,10 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
+        <v>483</v>
+      </c>
+      <c r="F204" t="s">
         <v>484</v>
-      </c>
-      <c r="F204" t="s">
-        <v>483</v>
       </c>
       <c r="G204" t="s">
         <v>484</v>
@@ -6743,10 +6743,10 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
+        <v>483</v>
+      </c>
+      <c r="F205" t="s">
         <v>484</v>
-      </c>
-      <c r="F205" t="s">
-        <v>483</v>
       </c>
       <c r="G205" t="s">
         <v>484</v>
@@ -6766,10 +6766,10 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
+        <v>483</v>
+      </c>
+      <c r="F206" t="s">
         <v>484</v>
-      </c>
-      <c r="F206" t="s">
-        <v>483</v>
       </c>
       <c r="G206" t="s">
         <v>484</v>
@@ -6789,10 +6789,10 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
+        <v>483</v>
+      </c>
+      <c r="F207" t="s">
         <v>484</v>
-      </c>
-      <c r="F207" t="s">
-        <v>483</v>
       </c>
       <c r="G207" t="s">
         <v>484</v>
@@ -6812,10 +6812,10 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
+        <v>483</v>
+      </c>
+      <c r="F208" t="s">
         <v>484</v>
-      </c>
-      <c r="F208" t="s">
-        <v>483</v>
       </c>
       <c r="G208" t="s">
         <v>484</v>
@@ -6835,10 +6835,10 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
+        <v>483</v>
+      </c>
+      <c r="F209" t="s">
         <v>484</v>
-      </c>
-      <c r="F209" t="s">
-        <v>483</v>
       </c>
       <c r="G209" t="s">
         <v>484</v>
@@ -6858,10 +6858,10 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
+        <v>483</v>
+      </c>
+      <c r="F210" t="s">
         <v>484</v>
-      </c>
-      <c r="F210" t="s">
-        <v>483</v>
       </c>
       <c r="G210" t="s">
         <v>484</v>
@@ -6881,10 +6881,10 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
+        <v>483</v>
+      </c>
+      <c r="F211" t="s">
         <v>484</v>
-      </c>
-      <c r="F211" t="s">
-        <v>483</v>
       </c>
       <c r="G211" t="s">
         <v>484</v>
@@ -6904,10 +6904,10 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
+        <v>505</v>
+      </c>
+      <c r="F212" t="s">
         <v>506</v>
-      </c>
-      <c r="F212" t="s">
-        <v>505</v>
       </c>
       <c r="G212" t="s">
         <v>506</v>
@@ -6927,10 +6927,10 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
+        <v>509</v>
+      </c>
+      <c r="F213" t="s">
         <v>510</v>
-      </c>
-      <c r="F213" t="s">
-        <v>509</v>
       </c>
       <c r="G213" t="s">
         <v>510</v>
@@ -6950,10 +6950,10 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
+        <v>513</v>
+      </c>
+      <c r="F214" t="s">
         <v>514</v>
-      </c>
-      <c r="F214" t="s">
-        <v>513</v>
       </c>
       <c r="G214" t="s">
         <v>514</v>
@@ -6973,10 +6973,10 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
+        <v>513</v>
+      </c>
+      <c r="F215" t="s">
         <v>514</v>
-      </c>
-      <c r="F215" t="s">
-        <v>513</v>
       </c>
       <c r="G215" t="s">
         <v>514</v>
@@ -6996,10 +6996,10 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
+        <v>519</v>
+      </c>
+      <c r="F216" t="s">
         <v>520</v>
-      </c>
-      <c r="F216" t="s">
-        <v>519</v>
       </c>
       <c r="G216" t="s">
         <v>520</v>
@@ -7019,10 +7019,10 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
+        <v>519</v>
+      </c>
+      <c r="F217" t="s">
         <v>520</v>
-      </c>
-      <c r="F217" t="s">
-        <v>519</v>
       </c>
       <c r="G217" t="s">
         <v>520</v>
@@ -7042,10 +7042,10 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
+        <v>519</v>
+      </c>
+      <c r="F218" t="s">
         <v>520</v>
-      </c>
-      <c r="F218" t="s">
-        <v>519</v>
       </c>
       <c r="G218" t="s">
         <v>520</v>
@@ -7065,10 +7065,10 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
+        <v>519</v>
+      </c>
+      <c r="F219" t="s">
         <v>520</v>
-      </c>
-      <c r="F219" t="s">
-        <v>519</v>
       </c>
       <c r="G219" t="s">
         <v>520</v>
@@ -7088,10 +7088,10 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
+        <v>519</v>
+      </c>
+      <c r="F220" t="s">
         <v>520</v>
-      </c>
-      <c r="F220" t="s">
-        <v>519</v>
       </c>
       <c r="G220" t="s">
         <v>520</v>
@@ -7111,10 +7111,10 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
+        <v>519</v>
+      </c>
+      <c r="F221" t="s">
         <v>520</v>
-      </c>
-      <c r="F221" t="s">
-        <v>519</v>
       </c>
       <c r="G221" t="s">
         <v>520</v>
@@ -7134,10 +7134,10 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
+        <v>519</v>
+      </c>
+      <c r="F222" t="s">
         <v>520</v>
-      </c>
-      <c r="F222" t="s">
-        <v>519</v>
       </c>
       <c r="G222" t="s">
         <v>520</v>
@@ -7157,10 +7157,10 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
+        <v>535</v>
+      </c>
+      <c r="F223" t="s">
         <v>536</v>
-      </c>
-      <c r="F223" t="s">
-        <v>535</v>
       </c>
       <c r="G223" t="s">
         <v>536</v>
@@ -7180,10 +7180,10 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
+        <v>535</v>
+      </c>
+      <c r="F224" t="s">
         <v>536</v>
-      </c>
-      <c r="F224" t="s">
-        <v>535</v>
       </c>
       <c r="G224" t="s">
         <v>536</v>
@@ -7203,10 +7203,10 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
+        <v>535</v>
+      </c>
+      <c r="F225" t="s">
         <v>536</v>
-      </c>
-      <c r="F225" t="s">
-        <v>535</v>
       </c>
       <c r="G225" t="s">
         <v>536</v>
@@ -7226,10 +7226,10 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
+        <v>543</v>
+      </c>
+      <c r="F226" t="s">
         <v>544</v>
-      </c>
-      <c r="F226" t="s">
-        <v>543</v>
       </c>
       <c r="G226" t="s">
         <v>544</v>
@@ -7249,10 +7249,10 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
+        <v>547</v>
+      </c>
+      <c r="F227" t="s">
         <v>548</v>
-      </c>
-      <c r="F227" t="s">
-        <v>547</v>
       </c>
       <c r="G227" t="s">
         <v>548</v>
@@ -7272,10 +7272,10 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
+        <v>551</v>
+      </c>
+      <c r="F228" t="s">
         <v>552</v>
-      </c>
-      <c r="F228" t="s">
-        <v>551</v>
       </c>
       <c r="G228" t="s">
         <v>552</v>
@@ -7295,10 +7295,10 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
+        <v>555</v>
+      </c>
+      <c r="F229" t="s">
         <v>556</v>
-      </c>
-      <c r="F229" t="s">
-        <v>555</v>
       </c>
       <c r="G229" t="s">
         <v>556</v>
@@ -7318,10 +7318,10 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
+        <v>559</v>
+      </c>
+      <c r="F230" t="s">
         <v>560</v>
-      </c>
-      <c r="F230" t="s">
-        <v>559</v>
       </c>
       <c r="G230" t="s">
         <v>560</v>
@@ -7341,10 +7341,10 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
+        <v>559</v>
+      </c>
+      <c r="F231" t="s">
         <v>560</v>
-      </c>
-      <c r="F231" t="s">
-        <v>559</v>
       </c>
       <c r="G231" t="s">
         <v>560</v>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Santé</t>
   </si>
   <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energie</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1165,16 +1165,16 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>320</t>
   </si>
   <si>
     <t>32120</t>
@@ -2163,13 +2163,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2209,13 +2209,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2232,13 +2232,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2255,13 +2255,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2278,13 +2278,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2301,13 +2301,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2324,13 +2324,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2439,13 +2439,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2462,13 +2462,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2485,13 +2485,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2508,13 +2508,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2531,13 +2531,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2554,13 +2554,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2577,13 +2577,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2600,13 +2600,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2623,13 +2623,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2646,13 +2646,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2669,13 +2669,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2692,13 +2692,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2715,13 +2715,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2738,13 +2738,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -2764,13 +2764,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2787,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2810,13 +2810,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2833,13 +2833,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2856,13 +2856,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2879,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2902,13 +2902,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2925,13 +2925,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2971,13 +2971,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2994,13 +2994,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3017,13 +3017,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3040,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3063,13 +3063,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3086,13 +3086,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3109,13 +3109,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3497,13 +3497,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3520,13 +3520,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3543,13 +3543,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3566,13 +3566,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3589,13 +3589,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3612,13 +3612,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -3638,13 +3638,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3661,13 +3661,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3684,13 +3684,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3707,13 +3707,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3730,13 +3730,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3753,13 +3753,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3776,13 +3776,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3799,13 +3799,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3822,13 +3822,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3845,13 +3845,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3868,13 +3868,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3891,13 +3891,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3914,13 +3914,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3937,13 +3937,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3960,13 +3960,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3983,13 +3983,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4006,13 +4006,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4029,13 +4029,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4052,13 +4052,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4075,13 +4075,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4098,13 +4098,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4121,13 +4121,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4233,13 +4233,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4256,13 +4256,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4279,13 +4279,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4302,13 +4302,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4325,13 +4325,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4348,13 +4348,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4371,13 +4371,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4394,13 +4394,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4417,13 +4417,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4440,13 +4440,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4463,13 +4463,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4486,13 +4486,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4509,13 +4509,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4532,13 +4532,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4555,13 +4555,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4578,13 +4578,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="E111" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F111" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4601,13 +4601,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F112" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4624,13 +4624,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4647,13 +4647,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F114" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4670,13 +4670,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F115" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4693,13 +4693,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F116" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4716,13 +4716,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4739,13 +4739,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4762,13 +4762,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E119" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F119" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -4788,13 +4788,13 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F120" t="s">
         <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4811,13 +4811,13 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F121" t="s">
         <v>294</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4834,13 +4834,13 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
         <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4857,13 +4857,13 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F123" t="s">
         <v>294</v>
       </c>
       <c r="G123" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4880,13 +4880,13 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F124" t="s">
         <v>294</v>
       </c>
       <c r="G124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4903,13 +4903,13 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F125" t="s">
         <v>294</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4926,13 +4926,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F126" t="s">
         <v>308</v>
       </c>
       <c r="G126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4949,13 +4949,13 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4972,13 +4972,13 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
         <v>308</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4995,13 +4995,13 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F129" t="s">
         <v>308</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5429,13 +5429,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E148" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F148" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G148" t="s">
         <v>320</v>
@@ -5452,13 +5452,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F149" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G149" t="s">
         <v>320</v>
@@ -5475,13 +5475,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E150" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F150" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G150" t="s">
         <v>320</v>
@@ -5498,13 +5498,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F151" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G151" t="s">
         <v>320</v>
@@ -5521,13 +5521,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E152" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F152" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G152" t="s">
         <v>320</v>
@@ -5544,13 +5544,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F153" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G153" t="s">
         <v>320</v>
@@ -5567,13 +5567,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E154" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F154" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G154" t="s">
         <v>320</v>
@@ -5590,13 +5590,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E155" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F155" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G155" t="s">
         <v>320</v>
@@ -5613,13 +5613,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F156" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G156" t="s">
         <v>320</v>
@@ -5636,13 +5636,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G157" t="s">
         <v>320</v>
@@ -5659,13 +5659,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E158" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F158" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G158" t="s">
         <v>320</v>
@@ -6119,13 +6119,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E178" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F178" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G178" t="s">
         <v>386</v>
@@ -6142,13 +6142,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E179" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F179" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G179" t="s">
         <v>386</v>
@@ -6165,13 +6165,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E180" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F180" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G180" t="s">
         <v>386</v>
@@ -6188,13 +6188,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E181" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F181" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G181" t="s">
         <v>386</v>
@@ -6211,13 +6211,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E182" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F182" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G182" t="s">
         <v>386</v>
@@ -6234,13 +6234,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E183" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F183" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G183" t="s">
         <v>386</v>
@@ -6257,13 +6257,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E184" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F184" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G184" t="s">
         <v>386</v>
@@ -6280,13 +6280,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E185" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F185" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G185" t="s">
         <v>386</v>
@@ -6303,13 +6303,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E186" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F186" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G186" t="s">
         <v>386</v>
@@ -6326,13 +6326,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E187" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F187" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G187" t="s">
         <v>386</v>
@@ -6349,13 +6349,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F188" t="s">
-        <v>448</v>
+        <v>385</v>
       </c>
       <c r="G188" t="s">
         <v>386</v>
@@ -6375,13 +6375,13 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s">
         <v>452</v>
       </c>
       <c r="G189" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6398,13 +6398,13 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F190" t="s">
         <v>452</v>
       </c>
       <c r="G190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6421,13 +6421,13 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F191" t="s">
         <v>452</v>
       </c>
       <c r="G191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6444,13 +6444,13 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F192" t="s">
         <v>452</v>
       </c>
       <c r="G192" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6467,13 +6467,13 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>452</v>
       </c>
       <c r="G193" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6490,13 +6490,13 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F194" t="s">
         <v>452</v>
       </c>
       <c r="G194" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6513,13 +6513,13 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F195" t="s">
         <v>466</v>
       </c>
       <c r="G195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6536,13 +6536,13 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F196" t="s">
         <v>470</v>
       </c>
       <c r="G196" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6559,13 +6559,13 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F197" t="s">
         <v>470</v>
       </c>
       <c r="G197" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6582,13 +6582,13 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F198" t="s">
         <v>470</v>
       </c>
       <c r="G198" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6605,13 +6605,13 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F199" t="s">
         <v>470</v>
       </c>
       <c r="G199" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6628,13 +6628,13 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F200" t="s">
         <v>470</v>
       </c>
       <c r="G200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6651,13 +6651,13 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
         <v>470</v>
       </c>
       <c r="G201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6674,13 +6674,13 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F202" t="s">
         <v>484</v>
       </c>
       <c r="G202" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6697,13 +6697,13 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F203" t="s">
         <v>484</v>
       </c>
       <c r="G203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6720,13 +6720,13 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F204" t="s">
         <v>484</v>
       </c>
       <c r="G204" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6743,13 +6743,13 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F205" t="s">
         <v>484</v>
       </c>
       <c r="G205" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6766,13 +6766,13 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F206" t="s">
         <v>484</v>
       </c>
       <c r="G206" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6789,13 +6789,13 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F207" t="s">
         <v>484</v>
       </c>
       <c r="G207" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6812,13 +6812,13 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F208" t="s">
         <v>484</v>
       </c>
       <c r="G208" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6835,13 +6835,13 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F209" t="s">
         <v>484</v>
       </c>
       <c r="G209" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6858,13 +6858,13 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F210" t="s">
         <v>484</v>
       </c>
       <c r="G210" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6881,13 +6881,13 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F211" t="s">
         <v>484</v>
       </c>
       <c r="G211" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6904,13 +6904,13 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F212" t="s">
         <v>506</v>
       </c>
       <c r="G212" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6927,13 +6927,13 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F213" t="s">
         <v>510</v>
       </c>
       <c r="G213" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6950,13 +6950,13 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F214" t="s">
         <v>514</v>
       </c>
       <c r="G214" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6973,13 +6973,13 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F215" t="s">
         <v>514</v>
       </c>
       <c r="G215" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6996,13 +6996,13 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F216" t="s">
         <v>520</v>
       </c>
       <c r="G216" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7019,13 +7019,13 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F217" t="s">
         <v>520</v>
       </c>
       <c r="G217" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7042,13 +7042,13 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F218" t="s">
         <v>520</v>
       </c>
       <c r="G218" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7065,13 +7065,13 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
         <v>520</v>
       </c>
       <c r="G219" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7088,13 +7088,13 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F220" t="s">
         <v>520</v>
       </c>
       <c r="G220" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7111,13 +7111,13 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F221" t="s">
         <v>520</v>
       </c>
       <c r="G221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7134,13 +7134,13 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F222" t="s">
         <v>520</v>
       </c>
       <c r="G222" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7157,13 +7157,13 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F223" t="s">
         <v>536</v>
       </c>
       <c r="G223" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7180,13 +7180,13 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F224" t="s">
         <v>536</v>
       </c>
       <c r="G224" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7203,13 +7203,13 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F225" t="s">
         <v>536</v>
       </c>
       <c r="G225" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7226,13 +7226,13 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F226" t="s">
         <v>544</v>
       </c>
       <c r="G226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7249,13 +7249,13 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F227" t="s">
         <v>548</v>
       </c>
       <c r="G227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7272,13 +7272,13 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F228" t="s">
         <v>552</v>
       </c>
       <c r="G228" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7295,13 +7295,13 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F229" t="s">
         <v>556</v>
       </c>
       <c r="G229" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7318,13 +7318,13 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F230" t="s">
         <v>560</v>
       </c>
       <c r="G230" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7341,13 +7341,13 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F231" t="s">
         <v>560</v>
       </c>
       <c r="G231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Distribution d'Eau et Assainissement</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Infrastructure et Services Sociaux Divers</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transports et Entreposage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banques et Services Financiers</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Entreprises et Autres Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Politique Commerciale et Réglementations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourisme</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>Protection de l'Environnement Général</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Autres Multisecteurs</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>Soutien Budgétaire</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Aide Alimentaire Dévelopmentale</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Aide sous forme de Produits, Autre</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Actions se Rapportant a la Dette</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Intervention d'Urgence</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction &amp; Réhabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Prévention catastrophes/Préparation à leur survenue</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Frais Administratifs des Donneurs</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugiés dans les Pays Donneurs</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Non Affecté / Non Specifié</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s">
         <v>56</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
         <v>56</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
         <v>56</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
         <v>56</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
         <v>56</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" t="s">
         <v>56</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" t="s">
         <v>56</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="F24" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
         <v>56</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
         <v>74</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
         <v>74</v>
       </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
         <v>74</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s">
         <v>74</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
         <v>74</v>
       </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" t="s">
         <v>74</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" t="s">
         <v>160</v>
       </c>
-      <c r="E64" t="s">
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="F64" t="s">
-        <v>126</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" t="s">
         <v>160</v>
       </c>
-      <c r="E65" t="s">
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="F65" t="s">
-        <v>126</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" t="s">
         <v>160</v>
       </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="F66" t="s">
-        <v>126</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
+        <v>125</v>
+      </c>
+      <c r="F67" t="s">
         <v>160</v>
       </c>
-      <c r="E67" t="s">
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="F67" t="s">
-        <v>126</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
+        <v>125</v>
+      </c>
+      <c r="F68" t="s">
         <v>160</v>
       </c>
-      <c r="E68" t="s">
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="F68" t="s">
-        <v>126</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
+        <v>125</v>
+      </c>
+      <c r="F69" t="s">
         <v>160</v>
       </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="F69" t="s">
-        <v>126</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
+        <v>225</v>
+      </c>
+      <c r="F96" t="s">
         <v>236</v>
       </c>
-      <c r="E96" t="s">
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="F96" t="s">
-        <v>226</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
+        <v>225</v>
+      </c>
+      <c r="F97" t="s">
         <v>236</v>
       </c>
-      <c r="E97" t="s">
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="F97" t="s">
-        <v>226</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
+        <v>225</v>
+      </c>
+      <c r="F98" t="s">
         <v>236</v>
       </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="F98" t="s">
-        <v>226</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
+        <v>225</v>
+      </c>
+      <c r="F99" t="s">
         <v>236</v>
       </c>
-      <c r="E99" t="s">
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="F99" t="s">
-        <v>226</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
+        <v>225</v>
+      </c>
+      <c r="F100" t="s">
         <v>236</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="F100" t="s">
-        <v>226</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
+        <v>225</v>
+      </c>
+      <c r="F101" t="s">
         <v>236</v>
       </c>
-      <c r="E101" t="s">
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="F101" t="s">
-        <v>226</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
+        <v>225</v>
+      </c>
+      <c r="F102" t="s">
         <v>236</v>
       </c>
-      <c r="E102" t="s">
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="F102" t="s">
-        <v>226</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
+        <v>225</v>
+      </c>
+      <c r="F103" t="s">
         <v>236</v>
       </c>
-      <c r="E103" t="s">
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="F103" t="s">
-        <v>226</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
+        <v>225</v>
+      </c>
+      <c r="F104" t="s">
         <v>236</v>
       </c>
-      <c r="E104" t="s">
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="F104" t="s">
-        <v>226</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
+        <v>225</v>
+      </c>
+      <c r="F105" t="s">
         <v>256</v>
       </c>
-      <c r="E105" t="s">
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="F105" t="s">
-        <v>226</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
+        <v>225</v>
+      </c>
+      <c r="F106" t="s">
         <v>256</v>
       </c>
-      <c r="E106" t="s">
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="F106" t="s">
-        <v>226</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
+        <v>225</v>
+      </c>
+      <c r="F107" t="s">
         <v>256</v>
       </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="F107" t="s">
-        <v>226</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
+        <v>225</v>
+      </c>
+      <c r="F108" t="s">
         <v>256</v>
       </c>
-      <c r="E108" t="s">
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="F108" t="s">
-        <v>226</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
+        <v>225</v>
+      </c>
+      <c r="F109" t="s">
         <v>256</v>
       </c>
-      <c r="E109" t="s">
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="F109" t="s">
-        <v>226</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
+        <v>225</v>
+      </c>
+      <c r="F110" t="s">
         <v>256</v>
       </c>
-      <c r="E110" t="s">
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="F110" t="s">
-        <v>226</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
+        <v>225</v>
+      </c>
+      <c r="F111" t="s">
         <v>269</v>
       </c>
-      <c r="E111" t="s">
+      <c r="G111" t="s">
         <v>270</v>
-      </c>
-      <c r="F111" t="s">
-        <v>226</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
+        <v>225</v>
+      </c>
+      <c r="F112" t="s">
         <v>273</v>
       </c>
-      <c r="E112" t="s">
+      <c r="G112" t="s">
         <v>274</v>
-      </c>
-      <c r="F112" t="s">
-        <v>226</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
+        <v>225</v>
+      </c>
+      <c r="F113" t="s">
         <v>277</v>
       </c>
-      <c r="E113" t="s">
+      <c r="G113" t="s">
         <v>278</v>
-      </c>
-      <c r="F113" t="s">
-        <v>226</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
+        <v>225</v>
+      </c>
+      <c r="F114" t="s">
         <v>277</v>
       </c>
-      <c r="E114" t="s">
+      <c r="G114" t="s">
         <v>278</v>
-      </c>
-      <c r="F114" t="s">
-        <v>226</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
+        <v>225</v>
+      </c>
+      <c r="F115" t="s">
         <v>277</v>
       </c>
-      <c r="E115" t="s">
+      <c r="G115" t="s">
         <v>278</v>
-      </c>
-      <c r="F115" t="s">
-        <v>226</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
+        <v>225</v>
+      </c>
+      <c r="F116" t="s">
         <v>277</v>
       </c>
-      <c r="E116" t="s">
+      <c r="G116" t="s">
         <v>278</v>
-      </c>
-      <c r="F116" t="s">
-        <v>226</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
+        <v>225</v>
+      </c>
+      <c r="F117" t="s">
         <v>277</v>
       </c>
-      <c r="E117" t="s">
+      <c r="G117" t="s">
         <v>278</v>
-      </c>
-      <c r="F117" t="s">
-        <v>226</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
+        <v>225</v>
+      </c>
+      <c r="F118" t="s">
         <v>277</v>
       </c>
-      <c r="E118" t="s">
+      <c r="G118" t="s">
         <v>278</v>
-      </c>
-      <c r="F118" t="s">
-        <v>226</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
+        <v>225</v>
+      </c>
+      <c r="F119" t="s">
         <v>277</v>
       </c>
-      <c r="E119" t="s">
+      <c r="G119" t="s">
         <v>278</v>
-      </c>
-      <c r="F119" t="s">
-        <v>226</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>317</v>
+      </c>
+      <c r="E148" t="s">
+        <v>318</v>
+      </c>
+      <c r="F148" t="s">
         <v>357</v>
       </c>
-      <c r="E148" t="s">
+      <c r="G148" t="s">
         <v>358</v>
-      </c>
-      <c r="F148" t="s">
-        <v>319</v>
-      </c>
-      <c r="G148" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>317</v>
+      </c>
+      <c r="E149" t="s">
+        <v>318</v>
+      </c>
+      <c r="F149" t="s">
         <v>357</v>
       </c>
-      <c r="E149" t="s">
+      <c r="G149" t="s">
         <v>358</v>
-      </c>
-      <c r="F149" t="s">
-        <v>319</v>
-      </c>
-      <c r="G149" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>317</v>
+      </c>
+      <c r="E150" t="s">
+        <v>318</v>
+      </c>
+      <c r="F150" t="s">
         <v>357</v>
       </c>
-      <c r="E150" t="s">
+      <c r="G150" t="s">
         <v>358</v>
-      </c>
-      <c r="F150" t="s">
-        <v>319</v>
-      </c>
-      <c r="G150" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>317</v>
+      </c>
+      <c r="E151" t="s">
+        <v>318</v>
+      </c>
+      <c r="F151" t="s">
         <v>357</v>
       </c>
-      <c r="E151" t="s">
+      <c r="G151" t="s">
         <v>358</v>
-      </c>
-      <c r="F151" t="s">
-        <v>319</v>
-      </c>
-      <c r="G151" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>317</v>
+      </c>
+      <c r="E152" t="s">
+        <v>318</v>
+      </c>
+      <c r="F152" t="s">
         <v>357</v>
       </c>
-      <c r="E152" t="s">
+      <c r="G152" t="s">
         <v>358</v>
-      </c>
-      <c r="F152" t="s">
-        <v>319</v>
-      </c>
-      <c r="G152" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>317</v>
+      </c>
+      <c r="E153" t="s">
+        <v>318</v>
+      </c>
+      <c r="F153" t="s">
         <v>357</v>
       </c>
-      <c r="E153" t="s">
+      <c r="G153" t="s">
         <v>358</v>
-      </c>
-      <c r="F153" t="s">
-        <v>319</v>
-      </c>
-      <c r="G153" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>317</v>
+      </c>
+      <c r="E154" t="s">
+        <v>318</v>
+      </c>
+      <c r="F154" t="s">
         <v>371</v>
       </c>
-      <c r="E154" t="s">
+      <c r="G154" t="s">
         <v>372</v>
-      </c>
-      <c r="F154" t="s">
-        <v>319</v>
-      </c>
-      <c r="G154" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>317</v>
+      </c>
+      <c r="E155" t="s">
+        <v>318</v>
+      </c>
+      <c r="F155" t="s">
         <v>371</v>
       </c>
-      <c r="E155" t="s">
+      <c r="G155" t="s">
         <v>372</v>
-      </c>
-      <c r="F155" t="s">
-        <v>319</v>
-      </c>
-      <c r="G155" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>317</v>
+      </c>
+      <c r="E156" t="s">
+        <v>318</v>
+      </c>
+      <c r="F156" t="s">
         <v>371</v>
       </c>
-      <c r="E156" t="s">
+      <c r="G156" t="s">
         <v>372</v>
-      </c>
-      <c r="F156" t="s">
-        <v>319</v>
-      </c>
-      <c r="G156" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>317</v>
+      </c>
+      <c r="E157" t="s">
+        <v>318</v>
+      </c>
+      <c r="F157" t="s">
         <v>371</v>
       </c>
-      <c r="E157" t="s">
+      <c r="G157" t="s">
         <v>372</v>
-      </c>
-      <c r="F157" t="s">
-        <v>319</v>
-      </c>
-      <c r="G157" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>317</v>
+      </c>
+      <c r="E158" t="s">
+        <v>318</v>
+      </c>
+      <c r="F158" t="s">
         <v>371</v>
       </c>
-      <c r="E158" t="s">
+      <c r="G158" t="s">
         <v>372</v>
-      </c>
-      <c r="F158" t="s">
-        <v>319</v>
-      </c>
-      <c r="G158" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>383</v>
+      </c>
+      <c r="E178" t="s">
+        <v>384</v>
+      </c>
+      <c r="F178" t="s">
         <v>425</v>
       </c>
-      <c r="E178" t="s">
+      <c r="G178" t="s">
         <v>426</v>
-      </c>
-      <c r="F178" t="s">
-        <v>385</v>
-      </c>
-      <c r="G178" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>383</v>
+      </c>
+      <c r="E179" t="s">
+        <v>384</v>
+      </c>
+      <c r="F179" t="s">
         <v>425</v>
       </c>
-      <c r="E179" t="s">
+      <c r="G179" t="s">
         <v>426</v>
-      </c>
-      <c r="F179" t="s">
-        <v>385</v>
-      </c>
-      <c r="G179" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>383</v>
+      </c>
+      <c r="E180" t="s">
+        <v>384</v>
+      </c>
+      <c r="F180" t="s">
         <v>425</v>
       </c>
-      <c r="E180" t="s">
+      <c r="G180" t="s">
         <v>426</v>
-      </c>
-      <c r="F180" t="s">
-        <v>385</v>
-      </c>
-      <c r="G180" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>383</v>
+      </c>
+      <c r="E181" t="s">
+        <v>384</v>
+      </c>
+      <c r="F181" t="s">
         <v>425</v>
       </c>
-      <c r="E181" t="s">
+      <c r="G181" t="s">
         <v>426</v>
-      </c>
-      <c r="F181" t="s">
-        <v>385</v>
-      </c>
-      <c r="G181" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>383</v>
+      </c>
+      <c r="E182" t="s">
+        <v>384</v>
+      </c>
+      <c r="F182" t="s">
         <v>425</v>
       </c>
-      <c r="E182" t="s">
+      <c r="G182" t="s">
         <v>426</v>
-      </c>
-      <c r="F182" t="s">
-        <v>385</v>
-      </c>
-      <c r="G182" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6234,16 +6234,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>383</v>
+      </c>
+      <c r="E183" t="s">
+        <v>384</v>
+      </c>
+      <c r="F183" t="s">
         <v>425</v>
       </c>
-      <c r="E183" t="s">
+      <c r="G183" t="s">
         <v>426</v>
-      </c>
-      <c r="F183" t="s">
-        <v>385</v>
-      </c>
-      <c r="G183" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6257,16 +6257,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>383</v>
+      </c>
+      <c r="E184" t="s">
+        <v>384</v>
+      </c>
+      <c r="F184" t="s">
         <v>425</v>
       </c>
-      <c r="E184" t="s">
+      <c r="G184" t="s">
         <v>426</v>
-      </c>
-      <c r="F184" t="s">
-        <v>385</v>
-      </c>
-      <c r="G184" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6280,16 +6280,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>383</v>
+      </c>
+      <c r="E185" t="s">
+        <v>384</v>
+      </c>
+      <c r="F185" t="s">
         <v>425</v>
       </c>
-      <c r="E185" t="s">
+      <c r="G185" t="s">
         <v>426</v>
-      </c>
-      <c r="F185" t="s">
-        <v>385</v>
-      </c>
-      <c r="G185" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6303,16 +6303,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>383</v>
+      </c>
+      <c r="E186" t="s">
+        <v>384</v>
+      </c>
+      <c r="F186" t="s">
         <v>425</v>
       </c>
-      <c r="E186" t="s">
+      <c r="G186" t="s">
         <v>426</v>
-      </c>
-      <c r="F186" t="s">
-        <v>385</v>
-      </c>
-      <c r="G186" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6326,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>383</v>
+      </c>
+      <c r="E187" t="s">
+        <v>384</v>
+      </c>
+      <c r="F187" t="s">
         <v>425</v>
       </c>
-      <c r="E187" t="s">
+      <c r="G187" t="s">
         <v>426</v>
-      </c>
-      <c r="F187" t="s">
-        <v>385</v>
-      </c>
-      <c r="G187" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6349,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>383</v>
+      </c>
+      <c r="E188" t="s">
+        <v>384</v>
+      </c>
+      <c r="F188" t="s">
         <v>447</v>
       </c>
-      <c r="E188" t="s">
+      <c r="G188" t="s">
         <v>448</v>
-      </c>
-      <c r="F188" t="s">
-        <v>385</v>
-      </c>
-      <c r="G188" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Education de Base</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Education Secondaire</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Education Post Secondaire</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Santé de Base</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Maladies non-transmissibles (MNT)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflits, Paix et Sécurité</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources renouvelables</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources non renouvelables</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Centrales nucléaires</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Distribution de l'énergie</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Sylviculture</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Pêche</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Industries Extractives</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,10 +1357,10 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
-  </si>
-  <si>
-    <t>323</t>
   </si>
   <si>
     <t>33110</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="F111" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="F112" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F113" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F114" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F115" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F116" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F117" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F118" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F119" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F148" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F149" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F150" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F151" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F152" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F153" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="G153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F154" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F155" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F156" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F157" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F158" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="G158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F178" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F179" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F180" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F181" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F182" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6234,16 +6234,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F183" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6257,16 +6257,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F184" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6280,16 +6280,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F185" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6303,16 +6303,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F186" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6326,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F187" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="G187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6349,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="F188" t="s">
-        <v>447</v>
+        <v>385</v>
       </c>
       <c r="G188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>111</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
     <t>Education</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>121</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
     <t>Santé</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>151</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>231</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
     <t>Energie</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>311</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,13 +1168,13 @@
     <t>321</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>320</t>
   </si>
   <si>
     <t>32120</t>
@@ -2166,10 +2166,10 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2189,10 +2189,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2212,10 +2212,10 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2235,10 +2235,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2258,10 +2258,10 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2281,10 +2281,10 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2304,10 +2304,10 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>39</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2327,10 +2327,10 @@
         <v>38</v>
       </c>
       <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2442,10 +2442,10 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s">
         <v>57</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2465,10 +2465,10 @@
         <v>56</v>
       </c>
       <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
         <v>57</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2488,10 +2488,10 @@
         <v>56</v>
       </c>
       <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
         <v>57</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2511,10 +2511,10 @@
         <v>56</v>
       </c>
       <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
         <v>57</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2534,10 +2534,10 @@
         <v>56</v>
       </c>
       <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
         <v>57</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2557,10 +2557,10 @@
         <v>56</v>
       </c>
       <c r="E23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" t="s">
         <v>57</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2580,10 +2580,10 @@
         <v>56</v>
       </c>
       <c r="E24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" t="s">
         <v>57</v>
-      </c>
-      <c r="F24" t="s">
-        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2603,10 +2603,10 @@
         <v>56</v>
       </c>
       <c r="E25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
         <v>57</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2626,10 +2626,10 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
         <v>75</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2649,10 +2649,10 @@
         <v>74</v>
       </c>
       <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
         <v>75</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2672,10 +2672,10 @@
         <v>74</v>
       </c>
       <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
         <v>75</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2695,10 +2695,10 @@
         <v>74</v>
       </c>
       <c r="E29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s">
         <v>75</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2718,10 +2718,10 @@
         <v>74</v>
       </c>
       <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
         <v>75</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2741,10 +2741,10 @@
         <v>74</v>
       </c>
       <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" t="s">
         <v>75</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -2764,13 +2764,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2787,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2810,13 +2810,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2833,13 +2833,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2856,13 +2856,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2879,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2902,13 +2902,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2925,13 +2925,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2971,13 +2971,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2994,13 +2994,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3017,13 +3017,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3040,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3063,13 +3063,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3086,13 +3086,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3109,13 +3109,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" t="s">
         <v>161</v>
-      </c>
-      <c r="F64" t="s">
-        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3523,10 +3523,10 @@
         <v>160</v>
       </c>
       <c r="E65" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" t="s">
         <v>161</v>
-      </c>
-      <c r="F65" t="s">
-        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3546,10 +3546,10 @@
         <v>160</v>
       </c>
       <c r="E66" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" t="s">
         <v>161</v>
-      </c>
-      <c r="F66" t="s">
-        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3569,10 +3569,10 @@
         <v>160</v>
       </c>
       <c r="E67" t="s">
+        <v>125</v>
+      </c>
+      <c r="F67" t="s">
         <v>161</v>
-      </c>
-      <c r="F67" t="s">
-        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3592,10 +3592,10 @@
         <v>160</v>
       </c>
       <c r="E68" t="s">
+        <v>125</v>
+      </c>
+      <c r="F68" t="s">
         <v>161</v>
-      </c>
-      <c r="F68" t="s">
-        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3615,10 +3615,10 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
+        <v>125</v>
+      </c>
+      <c r="F69" t="s">
         <v>161</v>
-      </c>
-      <c r="F69" t="s">
-        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -3638,13 +3638,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3661,13 +3661,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3684,13 +3684,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3707,13 +3707,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3730,13 +3730,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3753,13 +3753,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3776,13 +3776,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3799,13 +3799,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3822,13 +3822,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3845,13 +3845,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3868,13 +3868,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3891,13 +3891,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3914,13 +3914,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3937,13 +3937,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3960,13 +3960,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3983,13 +3983,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4006,13 +4006,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4029,13 +4029,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4052,13 +4052,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4075,13 +4075,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4098,13 +4098,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4121,13 +4121,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,10 +4236,10 @@
         <v>236</v>
       </c>
       <c r="E96" t="s">
+        <v>225</v>
+      </c>
+      <c r="F96" t="s">
         <v>237</v>
-      </c>
-      <c r="F96" t="s">
-        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4259,10 +4259,10 @@
         <v>236</v>
       </c>
       <c r="E97" t="s">
+        <v>225</v>
+      </c>
+      <c r="F97" t="s">
         <v>237</v>
-      </c>
-      <c r="F97" t="s">
-        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4282,10 +4282,10 @@
         <v>236</v>
       </c>
       <c r="E98" t="s">
+        <v>225</v>
+      </c>
+      <c r="F98" t="s">
         <v>237</v>
-      </c>
-      <c r="F98" t="s">
-        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4305,10 +4305,10 @@
         <v>236</v>
       </c>
       <c r="E99" t="s">
+        <v>225</v>
+      </c>
+      <c r="F99" t="s">
         <v>237</v>
-      </c>
-      <c r="F99" t="s">
-        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4328,10 +4328,10 @@
         <v>236</v>
       </c>
       <c r="E100" t="s">
+        <v>225</v>
+      </c>
+      <c r="F100" t="s">
         <v>237</v>
-      </c>
-      <c r="F100" t="s">
-        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4351,10 +4351,10 @@
         <v>236</v>
       </c>
       <c r="E101" t="s">
+        <v>225</v>
+      </c>
+      <c r="F101" t="s">
         <v>237</v>
-      </c>
-      <c r="F101" t="s">
-        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4374,10 +4374,10 @@
         <v>236</v>
       </c>
       <c r="E102" t="s">
+        <v>225</v>
+      </c>
+      <c r="F102" t="s">
         <v>237</v>
-      </c>
-      <c r="F102" t="s">
-        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4397,10 +4397,10 @@
         <v>236</v>
       </c>
       <c r="E103" t="s">
+        <v>225</v>
+      </c>
+      <c r="F103" t="s">
         <v>237</v>
-      </c>
-      <c r="F103" t="s">
-        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4420,10 +4420,10 @@
         <v>236</v>
       </c>
       <c r="E104" t="s">
+        <v>225</v>
+      </c>
+      <c r="F104" t="s">
         <v>237</v>
-      </c>
-      <c r="F104" t="s">
-        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4443,10 +4443,10 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
+        <v>225</v>
+      </c>
+      <c r="F105" t="s">
         <v>257</v>
-      </c>
-      <c r="F105" t="s">
-        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4466,10 +4466,10 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
+        <v>225</v>
+      </c>
+      <c r="F106" t="s">
         <v>257</v>
-      </c>
-      <c r="F106" t="s">
-        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4489,10 +4489,10 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
+        <v>225</v>
+      </c>
+      <c r="F107" t="s">
         <v>257</v>
-      </c>
-      <c r="F107" t="s">
-        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4512,10 +4512,10 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
+        <v>225</v>
+      </c>
+      <c r="F108" t="s">
         <v>257</v>
-      </c>
-      <c r="F108" t="s">
-        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4535,10 +4535,10 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
+        <v>225</v>
+      </c>
+      <c r="F109" t="s">
         <v>257</v>
-      </c>
-      <c r="F109" t="s">
-        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4558,10 +4558,10 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
+        <v>225</v>
+      </c>
+      <c r="F110" t="s">
         <v>257</v>
-      </c>
-      <c r="F110" t="s">
-        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4581,10 +4581,10 @@
         <v>270</v>
       </c>
       <c r="E111" t="s">
+        <v>225</v>
+      </c>
+      <c r="F111" t="s">
         <v>269</v>
-      </c>
-      <c r="F111" t="s">
-        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4604,10 +4604,10 @@
         <v>273</v>
       </c>
       <c r="E112" t="s">
+        <v>225</v>
+      </c>
+      <c r="F112" t="s">
         <v>274</v>
-      </c>
-      <c r="F112" t="s">
-        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4627,10 +4627,10 @@
         <v>277</v>
       </c>
       <c r="E113" t="s">
+        <v>225</v>
+      </c>
+      <c r="F113" t="s">
         <v>278</v>
-      </c>
-      <c r="F113" t="s">
-        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4650,10 +4650,10 @@
         <v>277</v>
       </c>
       <c r="E114" t="s">
+        <v>225</v>
+      </c>
+      <c r="F114" t="s">
         <v>278</v>
-      </c>
-      <c r="F114" t="s">
-        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4673,10 +4673,10 @@
         <v>277</v>
       </c>
       <c r="E115" t="s">
+        <v>225</v>
+      </c>
+      <c r="F115" t="s">
         <v>278</v>
-      </c>
-      <c r="F115" t="s">
-        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4696,10 +4696,10 @@
         <v>277</v>
       </c>
       <c r="E116" t="s">
+        <v>225</v>
+      </c>
+      <c r="F116" t="s">
         <v>278</v>
-      </c>
-      <c r="F116" t="s">
-        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4719,10 +4719,10 @@
         <v>277</v>
       </c>
       <c r="E117" t="s">
+        <v>225</v>
+      </c>
+      <c r="F117" t="s">
         <v>278</v>
-      </c>
-      <c r="F117" t="s">
-        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4742,10 +4742,10 @@
         <v>277</v>
       </c>
       <c r="E118" t="s">
+        <v>225</v>
+      </c>
+      <c r="F118" t="s">
         <v>278</v>
-      </c>
-      <c r="F118" t="s">
-        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4765,10 +4765,10 @@
         <v>277</v>
       </c>
       <c r="E119" t="s">
+        <v>225</v>
+      </c>
+      <c r="F119" t="s">
         <v>278</v>
-      </c>
-      <c r="F119" t="s">
-        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -4788,13 +4788,13 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F120" t="s">
         <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4811,13 +4811,13 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F121" t="s">
         <v>294</v>
       </c>
       <c r="G121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4834,13 +4834,13 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F122" t="s">
         <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4857,13 +4857,13 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F123" t="s">
         <v>294</v>
       </c>
       <c r="G123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4880,13 +4880,13 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F124" t="s">
         <v>294</v>
       </c>
       <c r="G124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4903,13 +4903,13 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F125" t="s">
         <v>294</v>
       </c>
       <c r="G125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4926,13 +4926,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F126" t="s">
         <v>308</v>
       </c>
       <c r="G126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4949,13 +4949,13 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F127" t="s">
         <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4972,13 +4972,13 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F128" t="s">
         <v>308</v>
       </c>
       <c r="G128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4995,13 +4995,13 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F129" t="s">
         <v>308</v>
       </c>
       <c r="G129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,10 +5432,10 @@
         <v>357</v>
       </c>
       <c r="E148" t="s">
+        <v>318</v>
+      </c>
+      <c r="F148" t="s">
         <v>358</v>
-      </c>
-      <c r="F148" t="s">
-        <v>319</v>
       </c>
       <c r="G148" t="s">
         <v>320</v>
@@ -5455,10 +5455,10 @@
         <v>357</v>
       </c>
       <c r="E149" t="s">
+        <v>318</v>
+      </c>
+      <c r="F149" t="s">
         <v>358</v>
-      </c>
-      <c r="F149" t="s">
-        <v>319</v>
       </c>
       <c r="G149" t="s">
         <v>320</v>
@@ -5478,10 +5478,10 @@
         <v>357</v>
       </c>
       <c r="E150" t="s">
+        <v>318</v>
+      </c>
+      <c r="F150" t="s">
         <v>358</v>
-      </c>
-      <c r="F150" t="s">
-        <v>319</v>
       </c>
       <c r="G150" t="s">
         <v>320</v>
@@ -5501,10 +5501,10 @@
         <v>357</v>
       </c>
       <c r="E151" t="s">
+        <v>318</v>
+      </c>
+      <c r="F151" t="s">
         <v>358</v>
-      </c>
-      <c r="F151" t="s">
-        <v>319</v>
       </c>
       <c r="G151" t="s">
         <v>320</v>
@@ -5524,10 +5524,10 @@
         <v>357</v>
       </c>
       <c r="E152" t="s">
+        <v>318</v>
+      </c>
+      <c r="F152" t="s">
         <v>358</v>
-      </c>
-      <c r="F152" t="s">
-        <v>319</v>
       </c>
       <c r="G152" t="s">
         <v>320</v>
@@ -5547,10 +5547,10 @@
         <v>357</v>
       </c>
       <c r="E153" t="s">
+        <v>318</v>
+      </c>
+      <c r="F153" t="s">
         <v>358</v>
-      </c>
-      <c r="F153" t="s">
-        <v>319</v>
       </c>
       <c r="G153" t="s">
         <v>320</v>
@@ -5570,10 +5570,10 @@
         <v>371</v>
       </c>
       <c r="E154" t="s">
+        <v>318</v>
+      </c>
+      <c r="F154" t="s">
         <v>372</v>
-      </c>
-      <c r="F154" t="s">
-        <v>319</v>
       </c>
       <c r="G154" t="s">
         <v>320</v>
@@ -5593,10 +5593,10 @@
         <v>371</v>
       </c>
       <c r="E155" t="s">
+        <v>318</v>
+      </c>
+      <c r="F155" t="s">
         <v>372</v>
-      </c>
-      <c r="F155" t="s">
-        <v>319</v>
       </c>
       <c r="G155" t="s">
         <v>320</v>
@@ -5616,10 +5616,10 @@
         <v>371</v>
       </c>
       <c r="E156" t="s">
+        <v>318</v>
+      </c>
+      <c r="F156" t="s">
         <v>372</v>
-      </c>
-      <c r="F156" t="s">
-        <v>319</v>
       </c>
       <c r="G156" t="s">
         <v>320</v>
@@ -5639,10 +5639,10 @@
         <v>371</v>
       </c>
       <c r="E157" t="s">
+        <v>318</v>
+      </c>
+      <c r="F157" t="s">
         <v>372</v>
-      </c>
-      <c r="F157" t="s">
-        <v>319</v>
       </c>
       <c r="G157" t="s">
         <v>320</v>
@@ -5662,10 +5662,10 @@
         <v>371</v>
       </c>
       <c r="E158" t="s">
+        <v>318</v>
+      </c>
+      <c r="F158" t="s">
         <v>372</v>
-      </c>
-      <c r="F158" t="s">
-        <v>319</v>
       </c>
       <c r="G158" t="s">
         <v>320</v>
@@ -6122,10 +6122,10 @@
         <v>425</v>
       </c>
       <c r="E178" t="s">
+        <v>384</v>
+      </c>
+      <c r="F178" t="s">
         <v>426</v>
-      </c>
-      <c r="F178" t="s">
-        <v>385</v>
       </c>
       <c r="G178" t="s">
         <v>386</v>
@@ -6145,10 +6145,10 @@
         <v>425</v>
       </c>
       <c r="E179" t="s">
+        <v>384</v>
+      </c>
+      <c r="F179" t="s">
         <v>426</v>
-      </c>
-      <c r="F179" t="s">
-        <v>385</v>
       </c>
       <c r="G179" t="s">
         <v>386</v>
@@ -6168,10 +6168,10 @@
         <v>425</v>
       </c>
       <c r="E180" t="s">
+        <v>384</v>
+      </c>
+      <c r="F180" t="s">
         <v>426</v>
-      </c>
-      <c r="F180" t="s">
-        <v>385</v>
       </c>
       <c r="G180" t="s">
         <v>386</v>
@@ -6191,10 +6191,10 @@
         <v>425</v>
       </c>
       <c r="E181" t="s">
+        <v>384</v>
+      </c>
+      <c r="F181" t="s">
         <v>426</v>
-      </c>
-      <c r="F181" t="s">
-        <v>385</v>
       </c>
       <c r="G181" t="s">
         <v>386</v>
@@ -6214,10 +6214,10 @@
         <v>425</v>
       </c>
       <c r="E182" t="s">
+        <v>384</v>
+      </c>
+      <c r="F182" t="s">
         <v>426</v>
-      </c>
-      <c r="F182" t="s">
-        <v>385</v>
       </c>
       <c r="G182" t="s">
         <v>386</v>
@@ -6237,10 +6237,10 @@
         <v>425</v>
       </c>
       <c r="E183" t="s">
+        <v>384</v>
+      </c>
+      <c r="F183" t="s">
         <v>426</v>
-      </c>
-      <c r="F183" t="s">
-        <v>385</v>
       </c>
       <c r="G183" t="s">
         <v>386</v>
@@ -6260,10 +6260,10 @@
         <v>425</v>
       </c>
       <c r="E184" t="s">
+        <v>384</v>
+      </c>
+      <c r="F184" t="s">
         <v>426</v>
-      </c>
-      <c r="F184" t="s">
-        <v>385</v>
       </c>
       <c r="G184" t="s">
         <v>386</v>
@@ -6283,10 +6283,10 @@
         <v>425</v>
       </c>
       <c r="E185" t="s">
+        <v>384</v>
+      </c>
+      <c r="F185" t="s">
         <v>426</v>
-      </c>
-      <c r="F185" t="s">
-        <v>385</v>
       </c>
       <c r="G185" t="s">
         <v>386</v>
@@ -6306,10 +6306,10 @@
         <v>425</v>
       </c>
       <c r="E186" t="s">
+        <v>384</v>
+      </c>
+      <c r="F186" t="s">
         <v>426</v>
-      </c>
-      <c r="F186" t="s">
-        <v>385</v>
       </c>
       <c r="G186" t="s">
         <v>386</v>
@@ -6329,10 +6329,10 @@
         <v>425</v>
       </c>
       <c r="E187" t="s">
+        <v>384</v>
+      </c>
+      <c r="F187" t="s">
         <v>426</v>
-      </c>
-      <c r="F187" t="s">
-        <v>385</v>
       </c>
       <c r="G187" t="s">
         <v>386</v>
@@ -6352,10 +6352,10 @@
         <v>447</v>
       </c>
       <c r="E188" t="s">
+        <v>384</v>
+      </c>
+      <c r="F188" t="s">
         <v>448</v>
-      </c>
-      <c r="F188" t="s">
-        <v>385</v>
       </c>
       <c r="G188" t="s">
         <v>386</v>
@@ -6375,13 +6375,13 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F189" t="s">
         <v>452</v>
       </c>
       <c r="G189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6398,13 +6398,13 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F190" t="s">
         <v>452</v>
       </c>
       <c r="G190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6421,13 +6421,13 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F191" t="s">
         <v>452</v>
       </c>
       <c r="G191" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6444,13 +6444,13 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F192" t="s">
         <v>452</v>
       </c>
       <c r="G192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6467,13 +6467,13 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F193" t="s">
         <v>452</v>
       </c>
       <c r="G193" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6490,13 +6490,13 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F194" t="s">
         <v>452</v>
       </c>
       <c r="G194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6513,13 +6513,13 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F195" t="s">
         <v>466</v>
       </c>
       <c r="G195" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6536,13 +6536,13 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F196" t="s">
         <v>470</v>
       </c>
       <c r="G196" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6559,13 +6559,13 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F197" t="s">
         <v>470</v>
       </c>
       <c r="G197" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6582,13 +6582,13 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F198" t="s">
         <v>470</v>
       </c>
       <c r="G198" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6605,13 +6605,13 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F199" t="s">
         <v>470</v>
       </c>
       <c r="G199" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6628,13 +6628,13 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F200" t="s">
         <v>470</v>
       </c>
       <c r="G200" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6651,13 +6651,13 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F201" t="s">
         <v>470</v>
       </c>
       <c r="G201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6674,13 +6674,13 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F202" t="s">
         <v>484</v>
       </c>
       <c r="G202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6697,13 +6697,13 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F203" t="s">
         <v>484</v>
       </c>
       <c r="G203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6720,13 +6720,13 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F204" t="s">
         <v>484</v>
       </c>
       <c r="G204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6743,13 +6743,13 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F205" t="s">
         <v>484</v>
       </c>
       <c r="G205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6766,13 +6766,13 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F206" t="s">
         <v>484</v>
       </c>
       <c r="G206" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6789,13 +6789,13 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F207" t="s">
         <v>484</v>
       </c>
       <c r="G207" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6812,13 +6812,13 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F208" t="s">
         <v>484</v>
       </c>
       <c r="G208" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6835,13 +6835,13 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F209" t="s">
         <v>484</v>
       </c>
       <c r="G209" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6858,13 +6858,13 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F210" t="s">
         <v>484</v>
       </c>
       <c r="G210" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6881,13 +6881,13 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F211" t="s">
         <v>484</v>
       </c>
       <c r="G211" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6904,13 +6904,13 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F212" t="s">
         <v>506</v>
       </c>
       <c r="G212" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6927,13 +6927,13 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F213" t="s">
         <v>510</v>
       </c>
       <c r="G213" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6950,13 +6950,13 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F214" t="s">
         <v>514</v>
       </c>
       <c r="G214" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6973,13 +6973,13 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F215" t="s">
         <v>514</v>
       </c>
       <c r="G215" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6996,13 +6996,13 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F216" t="s">
         <v>520</v>
       </c>
       <c r="G216" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7019,13 +7019,13 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F217" t="s">
         <v>520</v>
       </c>
       <c r="G217" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7042,13 +7042,13 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F218" t="s">
         <v>520</v>
       </c>
       <c r="G218" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7065,13 +7065,13 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F219" t="s">
         <v>520</v>
       </c>
       <c r="G219" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7088,13 +7088,13 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F220" t="s">
         <v>520</v>
       </c>
       <c r="G220" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7111,13 +7111,13 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F221" t="s">
         <v>520</v>
       </c>
       <c r="G221" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7134,13 +7134,13 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F222" t="s">
         <v>520</v>
       </c>
       <c r="G222" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7157,13 +7157,13 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F223" t="s">
         <v>536</v>
       </c>
       <c r="G223" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7180,13 +7180,13 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F224" t="s">
         <v>536</v>
       </c>
       <c r="G224" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7203,13 +7203,13 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F225" t="s">
         <v>536</v>
       </c>
       <c r="G225" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7226,13 +7226,13 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F226" t="s">
         <v>544</v>
       </c>
       <c r="G226" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7249,13 +7249,13 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F227" t="s">
         <v>548</v>
       </c>
       <c r="G227" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7272,13 +7272,13 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F228" t="s">
         <v>552</v>
       </c>
       <c r="G228" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7295,13 +7295,13 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F229" t="s">
         <v>556</v>
       </c>
       <c r="G229" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7318,13 +7318,13 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F230" t="s">
         <v>560</v>
       </c>
       <c r="G230" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7341,13 +7341,13 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F231" t="s">
         <v>560</v>
       </c>
       <c r="G231" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>111</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>121</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
     <t>Santé, Général</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>151</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>231</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,13 +1168,13 @@
     <t>321</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
     <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
     <t>32120</t>
@@ -2169,10 +2169,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2192,10 +2192,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2215,10 +2215,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2238,10 +2238,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2261,10 +2261,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2284,10 +2284,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2307,10 +2307,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2330,10 +2330,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2445,10 +2445,10 @@
         <v>45</v>
       </c>
       <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2468,10 +2468,10 @@
         <v>45</v>
       </c>
       <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2491,10 +2491,10 @@
         <v>45</v>
       </c>
       <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2514,10 +2514,10 @@
         <v>45</v>
       </c>
       <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2537,10 +2537,10 @@
         <v>45</v>
       </c>
       <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2560,10 +2560,10 @@
         <v>45</v>
       </c>
       <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2583,10 +2583,10 @@
         <v>45</v>
       </c>
       <c r="F24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2606,10 +2606,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2629,10 +2629,10 @@
         <v>45</v>
       </c>
       <c r="F26" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2652,10 +2652,10 @@
         <v>45</v>
       </c>
       <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2675,10 +2675,10 @@
         <v>45</v>
       </c>
       <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2698,10 +2698,10 @@
         <v>45</v>
       </c>
       <c r="F29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2721,10 +2721,10 @@
         <v>45</v>
       </c>
       <c r="F30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2744,10 +2744,10 @@
         <v>45</v>
       </c>
       <c r="F31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2764,10 +2764,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" t="s">
-        <v>89</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2787,10 +2787,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" t="s">
         <v>88</v>
-      </c>
-      <c r="F33" t="s">
-        <v>89</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2810,10 +2810,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" t="s">
         <v>88</v>
-      </c>
-      <c r="F34" t="s">
-        <v>89</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2833,10 +2833,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" t="s">
         <v>88</v>
-      </c>
-      <c r="F35" t="s">
-        <v>89</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2856,10 +2856,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" t="s">
         <v>88</v>
-      </c>
-      <c r="F36" t="s">
-        <v>89</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2879,10 +2879,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
         <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>101</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2902,10 +2902,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" t="s">
         <v>100</v>
-      </c>
-      <c r="F38" t="s">
-        <v>101</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2925,10 +2925,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
         <v>100</v>
-      </c>
-      <c r="F39" t="s">
-        <v>101</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2948,10 +2948,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
         <v>100</v>
-      </c>
-      <c r="F40" t="s">
-        <v>101</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2971,10 +2971,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
         <v>100</v>
-      </c>
-      <c r="F41" t="s">
-        <v>101</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2994,10 +2994,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
         <v>100</v>
-      </c>
-      <c r="F42" t="s">
-        <v>101</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3017,10 +3017,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
         <v>100</v>
-      </c>
-      <c r="F43" t="s">
-        <v>101</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3040,10 +3040,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
         <v>100</v>
-      </c>
-      <c r="F44" t="s">
-        <v>101</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3063,10 +3063,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" t="s">
         <v>100</v>
-      </c>
-      <c r="F45" t="s">
-        <v>101</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3086,10 +3086,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
         <v>100</v>
-      </c>
-      <c r="F46" t="s">
-        <v>101</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3109,10 +3109,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
         <v>100</v>
-      </c>
-      <c r="F47" t="s">
-        <v>101</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3503,10 +3503,10 @@
         <v>125</v>
       </c>
       <c r="F64" t="s">
+        <v>126</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3526,10 +3526,10 @@
         <v>125</v>
       </c>
       <c r="F65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3549,10 +3549,10 @@
         <v>125</v>
       </c>
       <c r="F66" t="s">
+        <v>126</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3572,10 +3572,10 @@
         <v>125</v>
       </c>
       <c r="F67" t="s">
+        <v>126</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3595,10 +3595,10 @@
         <v>125</v>
       </c>
       <c r="F68" t="s">
+        <v>126</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3618,10 +3618,10 @@
         <v>125</v>
       </c>
       <c r="F69" t="s">
+        <v>126</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3638,10 +3638,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s">
         <v>174</v>
-      </c>
-      <c r="F70" t="s">
-        <v>175</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3661,10 +3661,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71" t="s">
         <v>174</v>
-      </c>
-      <c r="F71" t="s">
-        <v>175</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3684,10 +3684,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>175</v>
+      </c>
+      <c r="F72" t="s">
         <v>174</v>
-      </c>
-      <c r="F72" t="s">
-        <v>175</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3707,10 +3707,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" t="s">
         <v>174</v>
-      </c>
-      <c r="F73" t="s">
-        <v>175</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3730,10 +3730,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" t="s">
         <v>174</v>
-      </c>
-      <c r="F74" t="s">
-        <v>175</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3753,10 +3753,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>175</v>
+      </c>
+      <c r="F75" t="s">
         <v>174</v>
-      </c>
-      <c r="F75" t="s">
-        <v>175</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3776,10 +3776,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>175</v>
+      </c>
+      <c r="F76" t="s">
         <v>174</v>
-      </c>
-      <c r="F76" t="s">
-        <v>175</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3799,10 +3799,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>175</v>
+      </c>
+      <c r="F77" t="s">
         <v>174</v>
-      </c>
-      <c r="F77" t="s">
-        <v>175</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3822,10 +3822,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>175</v>
+      </c>
+      <c r="F78" t="s">
         <v>174</v>
-      </c>
-      <c r="F78" t="s">
-        <v>175</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3845,10 +3845,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>175</v>
+      </c>
+      <c r="F79" t="s">
         <v>174</v>
-      </c>
-      <c r="F79" t="s">
-        <v>175</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3868,10 +3868,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>175</v>
+      </c>
+      <c r="F80" t="s">
         <v>174</v>
-      </c>
-      <c r="F80" t="s">
-        <v>175</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3891,10 +3891,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" t="s">
         <v>198</v>
-      </c>
-      <c r="F81" t="s">
-        <v>199</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3914,10 +3914,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>199</v>
+      </c>
+      <c r="F82" t="s">
         <v>198</v>
-      </c>
-      <c r="F82" t="s">
-        <v>199</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3937,10 +3937,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>199</v>
+      </c>
+      <c r="F83" t="s">
         <v>198</v>
-      </c>
-      <c r="F83" t="s">
-        <v>199</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3960,10 +3960,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>199</v>
+      </c>
+      <c r="F84" t="s">
         <v>198</v>
-      </c>
-      <c r="F84" t="s">
-        <v>199</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3983,10 +3983,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>199</v>
+      </c>
+      <c r="F85" t="s">
         <v>198</v>
-      </c>
-      <c r="F85" t="s">
-        <v>199</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4006,10 +4006,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" t="s">
         <v>198</v>
-      </c>
-      <c r="F86" t="s">
-        <v>199</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4029,10 +4029,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>199</v>
+      </c>
+      <c r="F87" t="s">
         <v>198</v>
-      </c>
-      <c r="F87" t="s">
-        <v>199</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4052,10 +4052,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>215</v>
+      </c>
+      <c r="F88" t="s">
         <v>214</v>
-      </c>
-      <c r="F88" t="s">
-        <v>215</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4075,10 +4075,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>215</v>
+      </c>
+      <c r="F89" t="s">
         <v>214</v>
-      </c>
-      <c r="F89" t="s">
-        <v>215</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4098,10 +4098,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>215</v>
+      </c>
+      <c r="F90" t="s">
         <v>214</v>
-      </c>
-      <c r="F90" t="s">
-        <v>215</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4121,10 +4121,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>215</v>
+      </c>
+      <c r="F91" t="s">
         <v>214</v>
-      </c>
-      <c r="F91" t="s">
-        <v>215</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4239,10 +4239,10 @@
         <v>225</v>
       </c>
       <c r="F96" t="s">
+        <v>226</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4262,10 +4262,10 @@
         <v>225</v>
       </c>
       <c r="F97" t="s">
+        <v>226</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4285,10 +4285,10 @@
         <v>225</v>
       </c>
       <c r="F98" t="s">
+        <v>226</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4308,10 +4308,10 @@
         <v>225</v>
       </c>
       <c r="F99" t="s">
+        <v>226</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4331,10 +4331,10 @@
         <v>225</v>
       </c>
       <c r="F100" t="s">
+        <v>226</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4354,10 +4354,10 @@
         <v>225</v>
       </c>
       <c r="F101" t="s">
+        <v>226</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4377,10 +4377,10 @@
         <v>225</v>
       </c>
       <c r="F102" t="s">
+        <v>226</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4400,10 +4400,10 @@
         <v>225</v>
       </c>
       <c r="F103" t="s">
+        <v>226</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4423,10 +4423,10 @@
         <v>225</v>
       </c>
       <c r="F104" t="s">
+        <v>226</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4446,10 +4446,10 @@
         <v>225</v>
       </c>
       <c r="F105" t="s">
+        <v>226</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4469,10 +4469,10 @@
         <v>225</v>
       </c>
       <c r="F106" t="s">
+        <v>226</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4492,10 +4492,10 @@
         <v>225</v>
       </c>
       <c r="F107" t="s">
+        <v>226</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4515,10 +4515,10 @@
         <v>225</v>
       </c>
       <c r="F108" t="s">
+        <v>226</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4538,10 +4538,10 @@
         <v>225</v>
       </c>
       <c r="F109" t="s">
+        <v>226</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4561,10 +4561,10 @@
         <v>225</v>
       </c>
       <c r="F110" t="s">
+        <v>226</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4584,10 +4584,10 @@
         <v>225</v>
       </c>
       <c r="F111" t="s">
+        <v>226</v>
+      </c>
+      <c r="G111" t="s">
         <v>269</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4607,10 +4607,10 @@
         <v>225</v>
       </c>
       <c r="F112" t="s">
+        <v>226</v>
+      </c>
+      <c r="G112" t="s">
         <v>274</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4630,10 +4630,10 @@
         <v>225</v>
       </c>
       <c r="F113" t="s">
+        <v>226</v>
+      </c>
+      <c r="G113" t="s">
         <v>278</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4653,10 +4653,10 @@
         <v>225</v>
       </c>
       <c r="F114" t="s">
+        <v>226</v>
+      </c>
+      <c r="G114" t="s">
         <v>278</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4676,10 +4676,10 @@
         <v>225</v>
       </c>
       <c r="F115" t="s">
+        <v>226</v>
+      </c>
+      <c r="G115" t="s">
         <v>278</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4699,10 +4699,10 @@
         <v>225</v>
       </c>
       <c r="F116" t="s">
+        <v>226</v>
+      </c>
+      <c r="G116" t="s">
         <v>278</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4722,10 +4722,10 @@
         <v>225</v>
       </c>
       <c r="F117" t="s">
+        <v>226</v>
+      </c>
+      <c r="G117" t="s">
         <v>278</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4745,10 +4745,10 @@
         <v>225</v>
       </c>
       <c r="F118" t="s">
+        <v>226</v>
+      </c>
+      <c r="G118" t="s">
         <v>278</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4768,10 +4768,10 @@
         <v>225</v>
       </c>
       <c r="F119" t="s">
+        <v>226</v>
+      </c>
+      <c r="G119" t="s">
         <v>278</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4788,10 +4788,10 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
+        <v>294</v>
+      </c>
+      <c r="F120" t="s">
         <v>293</v>
-      </c>
-      <c r="F120" t="s">
-        <v>294</v>
       </c>
       <c r="G120" t="s">
         <v>294</v>
@@ -4811,10 +4811,10 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
+        <v>294</v>
+      </c>
+      <c r="F121" t="s">
         <v>293</v>
-      </c>
-      <c r="F121" t="s">
-        <v>294</v>
       </c>
       <c r="G121" t="s">
         <v>294</v>
@@ -4834,10 +4834,10 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
+        <v>294</v>
+      </c>
+      <c r="F122" t="s">
         <v>293</v>
-      </c>
-      <c r="F122" t="s">
-        <v>294</v>
       </c>
       <c r="G122" t="s">
         <v>294</v>
@@ -4857,10 +4857,10 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
+        <v>294</v>
+      </c>
+      <c r="F123" t="s">
         <v>293</v>
-      </c>
-      <c r="F123" t="s">
-        <v>294</v>
       </c>
       <c r="G123" t="s">
         <v>294</v>
@@ -4880,10 +4880,10 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
+        <v>294</v>
+      </c>
+      <c r="F124" t="s">
         <v>293</v>
-      </c>
-      <c r="F124" t="s">
-        <v>294</v>
       </c>
       <c r="G124" t="s">
         <v>294</v>
@@ -4903,10 +4903,10 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
+        <v>294</v>
+      </c>
+      <c r="F125" t="s">
         <v>293</v>
-      </c>
-      <c r="F125" t="s">
-        <v>294</v>
       </c>
       <c r="G125" t="s">
         <v>294</v>
@@ -4926,10 +4926,10 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
+        <v>308</v>
+      </c>
+      <c r="F126" t="s">
         <v>307</v>
-      </c>
-      <c r="F126" t="s">
-        <v>308</v>
       </c>
       <c r="G126" t="s">
         <v>308</v>
@@ -4949,10 +4949,10 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
+        <v>308</v>
+      </c>
+      <c r="F127" t="s">
         <v>307</v>
-      </c>
-      <c r="F127" t="s">
-        <v>308</v>
       </c>
       <c r="G127" t="s">
         <v>308</v>
@@ -4972,10 +4972,10 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
+        <v>308</v>
+      </c>
+      <c r="F128" t="s">
         <v>307</v>
-      </c>
-      <c r="F128" t="s">
-        <v>308</v>
       </c>
       <c r="G128" t="s">
         <v>308</v>
@@ -4995,10 +4995,10 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
+        <v>308</v>
+      </c>
+      <c r="F129" t="s">
         <v>307</v>
-      </c>
-      <c r="F129" t="s">
-        <v>308</v>
       </c>
       <c r="G129" t="s">
         <v>308</v>
@@ -5435,10 +5435,10 @@
         <v>318</v>
       </c>
       <c r="F148" t="s">
+        <v>319</v>
+      </c>
+      <c r="G148" t="s">
         <v>358</v>
-      </c>
-      <c r="G148" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5458,10 +5458,10 @@
         <v>318</v>
       </c>
       <c r="F149" t="s">
+        <v>319</v>
+      </c>
+      <c r="G149" t="s">
         <v>358</v>
-      </c>
-      <c r="G149" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5481,10 +5481,10 @@
         <v>318</v>
       </c>
       <c r="F150" t="s">
+        <v>319</v>
+      </c>
+      <c r="G150" t="s">
         <v>358</v>
-      </c>
-      <c r="G150" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5504,10 +5504,10 @@
         <v>318</v>
       </c>
       <c r="F151" t="s">
+        <v>319</v>
+      </c>
+      <c r="G151" t="s">
         <v>358</v>
-      </c>
-      <c r="G151" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5527,10 +5527,10 @@
         <v>318</v>
       </c>
       <c r="F152" t="s">
+        <v>319</v>
+      </c>
+      <c r="G152" t="s">
         <v>358</v>
-      </c>
-      <c r="G152" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5550,10 +5550,10 @@
         <v>318</v>
       </c>
       <c r="F153" t="s">
+        <v>319</v>
+      </c>
+      <c r="G153" t="s">
         <v>358</v>
-      </c>
-      <c r="G153" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5573,10 +5573,10 @@
         <v>318</v>
       </c>
       <c r="F154" t="s">
+        <v>319</v>
+      </c>
+      <c r="G154" t="s">
         <v>372</v>
-      </c>
-      <c r="G154" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5596,10 +5596,10 @@
         <v>318</v>
       </c>
       <c r="F155" t="s">
+        <v>319</v>
+      </c>
+      <c r="G155" t="s">
         <v>372</v>
-      </c>
-      <c r="G155" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5619,10 +5619,10 @@
         <v>318</v>
       </c>
       <c r="F156" t="s">
+        <v>319</v>
+      </c>
+      <c r="G156" t="s">
         <v>372</v>
-      </c>
-      <c r="G156" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5642,10 +5642,10 @@
         <v>318</v>
       </c>
       <c r="F157" t="s">
+        <v>319</v>
+      </c>
+      <c r="G157" t="s">
         <v>372</v>
-      </c>
-      <c r="G157" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5665,10 +5665,10 @@
         <v>318</v>
       </c>
       <c r="F158" t="s">
+        <v>319</v>
+      </c>
+      <c r="G158" t="s">
         <v>372</v>
-      </c>
-      <c r="G158" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6125,10 +6125,10 @@
         <v>384</v>
       </c>
       <c r="F178" t="s">
+        <v>385</v>
+      </c>
+      <c r="G178" t="s">
         <v>426</v>
-      </c>
-      <c r="G178" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6148,10 +6148,10 @@
         <v>384</v>
       </c>
       <c r="F179" t="s">
+        <v>385</v>
+      </c>
+      <c r="G179" t="s">
         <v>426</v>
-      </c>
-      <c r="G179" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6171,10 +6171,10 @@
         <v>384</v>
       </c>
       <c r="F180" t="s">
+        <v>385</v>
+      </c>
+      <c r="G180" t="s">
         <v>426</v>
-      </c>
-      <c r="G180" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6194,10 +6194,10 @@
         <v>384</v>
       </c>
       <c r="F181" t="s">
+        <v>385</v>
+      </c>
+      <c r="G181" t="s">
         <v>426</v>
-      </c>
-      <c r="G181" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6217,10 +6217,10 @@
         <v>384</v>
       </c>
       <c r="F182" t="s">
+        <v>385</v>
+      </c>
+      <c r="G182" t="s">
         <v>426</v>
-      </c>
-      <c r="G182" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6240,10 +6240,10 @@
         <v>384</v>
       </c>
       <c r="F183" t="s">
+        <v>385</v>
+      </c>
+      <c r="G183" t="s">
         <v>426</v>
-      </c>
-      <c r="G183" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6263,10 +6263,10 @@
         <v>384</v>
       </c>
       <c r="F184" t="s">
+        <v>385</v>
+      </c>
+      <c r="G184" t="s">
         <v>426</v>
-      </c>
-      <c r="G184" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6286,10 +6286,10 @@
         <v>384</v>
       </c>
       <c r="F185" t="s">
+        <v>385</v>
+      </c>
+      <c r="G185" t="s">
         <v>426</v>
-      </c>
-      <c r="G185" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6309,10 +6309,10 @@
         <v>384</v>
       </c>
       <c r="F186" t="s">
+        <v>385</v>
+      </c>
+      <c r="G186" t="s">
         <v>426</v>
-      </c>
-      <c r="G186" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6332,10 +6332,10 @@
         <v>384</v>
       </c>
       <c r="F187" t="s">
+        <v>385</v>
+      </c>
+      <c r="G187" t="s">
         <v>426</v>
-      </c>
-      <c r="G187" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6355,10 +6355,10 @@
         <v>384</v>
       </c>
       <c r="F188" t="s">
+        <v>385</v>
+      </c>
+      <c r="G188" t="s">
         <v>448</v>
-      </c>
-      <c r="G188" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6375,10 +6375,10 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
+        <v>452</v>
+      </c>
+      <c r="F189" t="s">
         <v>451</v>
-      </c>
-      <c r="F189" t="s">
-        <v>452</v>
       </c>
       <c r="G189" t="s">
         <v>452</v>
@@ -6398,10 +6398,10 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
+        <v>452</v>
+      </c>
+      <c r="F190" t="s">
         <v>451</v>
-      </c>
-      <c r="F190" t="s">
-        <v>452</v>
       </c>
       <c r="G190" t="s">
         <v>452</v>
@@ -6421,10 +6421,10 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
+        <v>452</v>
+      </c>
+      <c r="F191" t="s">
         <v>451</v>
-      </c>
-      <c r="F191" t="s">
-        <v>452</v>
       </c>
       <c r="G191" t="s">
         <v>452</v>
@@ -6444,10 +6444,10 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
+        <v>452</v>
+      </c>
+      <c r="F192" t="s">
         <v>451</v>
-      </c>
-      <c r="F192" t="s">
-        <v>452</v>
       </c>
       <c r="G192" t="s">
         <v>452</v>
@@ -6467,10 +6467,10 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
+        <v>452</v>
+      </c>
+      <c r="F193" t="s">
         <v>451</v>
-      </c>
-      <c r="F193" t="s">
-        <v>452</v>
       </c>
       <c r="G193" t="s">
         <v>452</v>
@@ -6490,10 +6490,10 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
+        <v>452</v>
+      </c>
+      <c r="F194" t="s">
         <v>451</v>
-      </c>
-      <c r="F194" t="s">
-        <v>452</v>
       </c>
       <c r="G194" t="s">
         <v>452</v>
@@ -6513,10 +6513,10 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
+        <v>466</v>
+      </c>
+      <c r="F195" t="s">
         <v>465</v>
-      </c>
-      <c r="F195" t="s">
-        <v>466</v>
       </c>
       <c r="G195" t="s">
         <v>466</v>
@@ -6536,10 +6536,10 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
+        <v>470</v>
+      </c>
+      <c r="F196" t="s">
         <v>469</v>
-      </c>
-      <c r="F196" t="s">
-        <v>470</v>
       </c>
       <c r="G196" t="s">
         <v>470</v>
@@ -6559,10 +6559,10 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
+        <v>470</v>
+      </c>
+      <c r="F197" t="s">
         <v>469</v>
-      </c>
-      <c r="F197" t="s">
-        <v>470</v>
       </c>
       <c r="G197" t="s">
         <v>470</v>
@@ -6582,10 +6582,10 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
+        <v>470</v>
+      </c>
+      <c r="F198" t="s">
         <v>469</v>
-      </c>
-      <c r="F198" t="s">
-        <v>470</v>
       </c>
       <c r="G198" t="s">
         <v>470</v>
@@ -6605,10 +6605,10 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
+        <v>470</v>
+      </c>
+      <c r="F199" t="s">
         <v>469</v>
-      </c>
-      <c r="F199" t="s">
-        <v>470</v>
       </c>
       <c r="G199" t="s">
         <v>470</v>
@@ -6628,10 +6628,10 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
+        <v>470</v>
+      </c>
+      <c r="F200" t="s">
         <v>469</v>
-      </c>
-      <c r="F200" t="s">
-        <v>470</v>
       </c>
       <c r="G200" t="s">
         <v>470</v>
@@ -6651,10 +6651,10 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
+        <v>470</v>
+      </c>
+      <c r="F201" t="s">
         <v>469</v>
-      </c>
-      <c r="F201" t="s">
-        <v>470</v>
       </c>
       <c r="G201" t="s">
         <v>470</v>
@@ -6674,10 +6674,10 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
+        <v>484</v>
+      </c>
+      <c r="F202" t="s">
         <v>483</v>
-      </c>
-      <c r="F202" t="s">
-        <v>484</v>
       </c>
       <c r="G202" t="s">
         <v>484</v>
@@ -6697,10 +6697,10 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
+        <v>484</v>
+      </c>
+      <c r="F203" t="s">
         <v>483</v>
-      </c>
-      <c r="F203" t="s">
-        <v>484</v>
       </c>
       <c r="G203" t="s">
         <v>484</v>
@@ -6720,10 +6720,10 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
+        <v>484</v>
+      </c>
+      <c r="F204" t="s">
         <v>483</v>
-      </c>
-      <c r="F204" t="s">
-        <v>484</v>
       </c>
       <c r="G204" t="s">
         <v>484</v>
@@ -6743,10 +6743,10 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
+        <v>484</v>
+      </c>
+      <c r="F205" t="s">
         <v>483</v>
-      </c>
-      <c r="F205" t="s">
-        <v>484</v>
       </c>
       <c r="G205" t="s">
         <v>484</v>
@@ -6766,10 +6766,10 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
+        <v>484</v>
+      </c>
+      <c r="F206" t="s">
         <v>483</v>
-      </c>
-      <c r="F206" t="s">
-        <v>484</v>
       </c>
       <c r="G206" t="s">
         <v>484</v>
@@ -6789,10 +6789,10 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
+        <v>484</v>
+      </c>
+      <c r="F207" t="s">
         <v>483</v>
-      </c>
-      <c r="F207" t="s">
-        <v>484</v>
       </c>
       <c r="G207" t="s">
         <v>484</v>
@@ -6812,10 +6812,10 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
+        <v>484</v>
+      </c>
+      <c r="F208" t="s">
         <v>483</v>
-      </c>
-      <c r="F208" t="s">
-        <v>484</v>
       </c>
       <c r="G208" t="s">
         <v>484</v>
@@ -6835,10 +6835,10 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
+        <v>484</v>
+      </c>
+      <c r="F209" t="s">
         <v>483</v>
-      </c>
-      <c r="F209" t="s">
-        <v>484</v>
       </c>
       <c r="G209" t="s">
         <v>484</v>
@@ -6858,10 +6858,10 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
+        <v>484</v>
+      </c>
+      <c r="F210" t="s">
         <v>483</v>
-      </c>
-      <c r="F210" t="s">
-        <v>484</v>
       </c>
       <c r="G210" t="s">
         <v>484</v>
@@ -6881,10 +6881,10 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
+        <v>484</v>
+      </c>
+      <c r="F211" t="s">
         <v>483</v>
-      </c>
-      <c r="F211" t="s">
-        <v>484</v>
       </c>
       <c r="G211" t="s">
         <v>484</v>
@@ -6904,10 +6904,10 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
+        <v>506</v>
+      </c>
+      <c r="F212" t="s">
         <v>505</v>
-      </c>
-      <c r="F212" t="s">
-        <v>506</v>
       </c>
       <c r="G212" t="s">
         <v>506</v>
@@ -6927,10 +6927,10 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
+        <v>510</v>
+      </c>
+      <c r="F213" t="s">
         <v>509</v>
-      </c>
-      <c r="F213" t="s">
-        <v>510</v>
       </c>
       <c r="G213" t="s">
         <v>510</v>
@@ -6950,10 +6950,10 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
+        <v>514</v>
+      </c>
+      <c r="F214" t="s">
         <v>513</v>
-      </c>
-      <c r="F214" t="s">
-        <v>514</v>
       </c>
       <c r="G214" t="s">
         <v>514</v>
@@ -6973,10 +6973,10 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
+        <v>514</v>
+      </c>
+      <c r="F215" t="s">
         <v>513</v>
-      </c>
-      <c r="F215" t="s">
-        <v>514</v>
       </c>
       <c r="G215" t="s">
         <v>514</v>
@@ -6996,10 +6996,10 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
+        <v>520</v>
+      </c>
+      <c r="F216" t="s">
         <v>519</v>
-      </c>
-      <c r="F216" t="s">
-        <v>520</v>
       </c>
       <c r="G216" t="s">
         <v>520</v>
@@ -7019,10 +7019,10 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
+        <v>520</v>
+      </c>
+      <c r="F217" t="s">
         <v>519</v>
-      </c>
-      <c r="F217" t="s">
-        <v>520</v>
       </c>
       <c r="G217" t="s">
         <v>520</v>
@@ -7042,10 +7042,10 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
+        <v>520</v>
+      </c>
+      <c r="F218" t="s">
         <v>519</v>
-      </c>
-      <c r="F218" t="s">
-        <v>520</v>
       </c>
       <c r="G218" t="s">
         <v>520</v>
@@ -7065,10 +7065,10 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
+        <v>520</v>
+      </c>
+      <c r="F219" t="s">
         <v>519</v>
-      </c>
-      <c r="F219" t="s">
-        <v>520</v>
       </c>
       <c r="G219" t="s">
         <v>520</v>
@@ -7088,10 +7088,10 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
+        <v>520</v>
+      </c>
+      <c r="F220" t="s">
         <v>519</v>
-      </c>
-      <c r="F220" t="s">
-        <v>520</v>
       </c>
       <c r="G220" t="s">
         <v>520</v>
@@ -7111,10 +7111,10 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
+        <v>520</v>
+      </c>
+      <c r="F221" t="s">
         <v>519</v>
-      </c>
-      <c r="F221" t="s">
-        <v>520</v>
       </c>
       <c r="G221" t="s">
         <v>520</v>
@@ -7134,10 +7134,10 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
+        <v>520</v>
+      </c>
+      <c r="F222" t="s">
         <v>519</v>
-      </c>
-      <c r="F222" t="s">
-        <v>520</v>
       </c>
       <c r="G222" t="s">
         <v>520</v>
@@ -7157,10 +7157,10 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
+        <v>536</v>
+      </c>
+      <c r="F223" t="s">
         <v>535</v>
-      </c>
-      <c r="F223" t="s">
-        <v>536</v>
       </c>
       <c r="G223" t="s">
         <v>536</v>
@@ -7180,10 +7180,10 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
+        <v>536</v>
+      </c>
+      <c r="F224" t="s">
         <v>535</v>
-      </c>
-      <c r="F224" t="s">
-        <v>536</v>
       </c>
       <c r="G224" t="s">
         <v>536</v>
@@ -7203,10 +7203,10 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
+        <v>536</v>
+      </c>
+      <c r="F225" t="s">
         <v>535</v>
-      </c>
-      <c r="F225" t="s">
-        <v>536</v>
       </c>
       <c r="G225" t="s">
         <v>536</v>
@@ -7226,10 +7226,10 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
+        <v>544</v>
+      </c>
+      <c r="F226" t="s">
         <v>543</v>
-      </c>
-      <c r="F226" t="s">
-        <v>544</v>
       </c>
       <c r="G226" t="s">
         <v>544</v>
@@ -7249,10 +7249,10 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
+        <v>548</v>
+      </c>
+      <c r="F227" t="s">
         <v>547</v>
-      </c>
-      <c r="F227" t="s">
-        <v>548</v>
       </c>
       <c r="G227" t="s">
         <v>548</v>
@@ -7272,10 +7272,10 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
+        <v>552</v>
+      </c>
+      <c r="F228" t="s">
         <v>551</v>
-      </c>
-      <c r="F228" t="s">
-        <v>552</v>
       </c>
       <c r="G228" t="s">
         <v>552</v>
@@ -7295,10 +7295,10 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
+        <v>556</v>
+      </c>
+      <c r="F229" t="s">
         <v>555</v>
-      </c>
-      <c r="F229" t="s">
-        <v>556</v>
       </c>
       <c r="G229" t="s">
         <v>556</v>
@@ -7318,10 +7318,10 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
+        <v>560</v>
+      </c>
+      <c r="F230" t="s">
         <v>559</v>
-      </c>
-      <c r="F230" t="s">
-        <v>560</v>
       </c>
       <c r="G230" t="s">
         <v>560</v>
@@ -7341,10 +7341,10 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
+        <v>560</v>
+      </c>
+      <c r="F231" t="s">
         <v>559</v>
-      </c>
-      <c r="F231" t="s">
-        <v>560</v>
       </c>
       <c r="G231" t="s">
         <v>560</v>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
+    <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
+    <t>Education, Niveau non spécifié</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Santé</t>
+    <t>Santé, Général</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>Distribution d'Eau et Assainissement</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Distribution d'Eau et Assainissement</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
+    <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>Infrastructure et Services Sociaux Divers</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Infrastructure et Services Sociaux Divers</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>Transports et Entreposage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transports et Entreposage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energie</t>
+    <t>Politique de l'énergie</t>
   </si>
   <si>
     <t>230</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>Banques et Services Financiers</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banques et Services Financiers</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>Entreprises et Autres Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Entreprises et Autres Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
+    <t>Agriculture</t>
   </si>
   <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
+    <t>Industries Manufacturières</t>
   </si>
   <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>Politique Commerciale et Réglementations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Politique Commerciale et Réglementations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>Tourisme</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourisme</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>Protection de l'Environnement Général</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protection de l'Environnement Général</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>Autres Multisecteurs</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Autres Multisecteurs</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>Soutien Budgétaire</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Soutien Budgétaire</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>Aide Alimentaire Dévelopmentale</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Aide Alimentaire Dévelopmentale</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>Aide sous forme de Produits, Autre</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Aide sous forme de Produits, Autre</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>Actions se Rapportant a la Dette</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actions se Rapportant a la Dette</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>Intervention d'Urgence</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Intervention d'Urgence</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>Reconstruction &amp; Réhabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction &amp; Réhabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>Prévention catastrophes/Préparation à leur survenue</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prévention catastrophes/Préparation à leur survenue</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>Frais Administratifs des Donneurs</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Frais Administratifs des Donneurs</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>Refugiés dans les Pays Donneurs</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiés dans les Pays Donneurs</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>Non Affecté / Non Specifié</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Non Affecté / Non Specifié</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
       </c>
-      <c r="E18" t="s">
-        <v>45</v>
-      </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
       </c>
-      <c r="E19" t="s">
-        <v>45</v>
-      </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="E20" t="s">
-        <v>45</v>
-      </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
       </c>
-      <c r="E21" t="s">
-        <v>45</v>
-      </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
       </c>
-      <c r="E22" t="s">
-        <v>45</v>
-      </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
       </c>
-      <c r="E23" t="s">
-        <v>45</v>
-      </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
       </c>
-      <c r="E24" t="s">
-        <v>45</v>
-      </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
       </c>
-      <c r="E25" t="s">
-        <v>45</v>
-      </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
       </c>
-      <c r="E26" t="s">
-        <v>45</v>
-      </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
       </c>
-      <c r="E27" t="s">
-        <v>45</v>
-      </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
       </c>
-      <c r="E28" t="s">
-        <v>45</v>
-      </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
       </c>
-      <c r="E29" t="s">
-        <v>45</v>
-      </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
       </c>
-      <c r="E30" t="s">
-        <v>45</v>
-      </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
       </c>
-      <c r="E31" t="s">
-        <v>45</v>
-      </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
       </c>
-      <c r="E64" t="s">
-        <v>125</v>
-      </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
       </c>
-      <c r="E65" t="s">
-        <v>125</v>
-      </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
       </c>
-      <c r="E66" t="s">
-        <v>125</v>
-      </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
       </c>
-      <c r="E67" t="s">
-        <v>125</v>
-      </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
       </c>
-      <c r="E68" t="s">
-        <v>125</v>
-      </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
       </c>
-      <c r="E69" t="s">
-        <v>125</v>
-      </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
       </c>
-      <c r="E96" t="s">
-        <v>225</v>
-      </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
       </c>
-      <c r="E97" t="s">
-        <v>225</v>
-      </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
       </c>
-      <c r="E98" t="s">
-        <v>225</v>
-      </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
       </c>
-      <c r="E99" t="s">
-        <v>225</v>
-      </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
       </c>
-      <c r="E100" t="s">
-        <v>225</v>
-      </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
       </c>
-      <c r="E101" t="s">
-        <v>225</v>
-      </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
       </c>
-      <c r="E102" t="s">
-        <v>225</v>
-      </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
       </c>
-      <c r="E103" t="s">
-        <v>225</v>
-      </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
       </c>
-      <c r="E104" t="s">
-        <v>225</v>
-      </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
       </c>
-      <c r="E105" t="s">
-        <v>225</v>
-      </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
       </c>
-      <c r="E106" t="s">
-        <v>225</v>
-      </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
       </c>
-      <c r="E107" t="s">
-        <v>225</v>
-      </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
       </c>
-      <c r="E108" t="s">
-        <v>225</v>
-      </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
       </c>
-      <c r="E109" t="s">
-        <v>225</v>
-      </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
       </c>
-      <c r="E110" t="s">
-        <v>225</v>
-      </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
         <v>270</v>
       </c>
-      <c r="E111" t="s">
-        <v>225</v>
-      </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="G111" t="s">
-        <v>269</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>273</v>
       </c>
-      <c r="E112" t="s">
-        <v>225</v>
-      </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>277</v>
       </c>
-      <c r="E113" t="s">
-        <v>225</v>
-      </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>277</v>
       </c>
-      <c r="E114" t="s">
-        <v>225</v>
-      </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>277</v>
       </c>
-      <c r="E115" t="s">
-        <v>225</v>
-      </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>277</v>
       </c>
-      <c r="E116" t="s">
-        <v>225</v>
-      </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G116" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>277</v>
       </c>
-      <c r="E117" t="s">
-        <v>225</v>
-      </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>277</v>
       </c>
-      <c r="E118" t="s">
-        <v>225</v>
-      </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G118" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>277</v>
       </c>
-      <c r="E119" t="s">
-        <v>225</v>
-      </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G119" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>317</v>
+      </c>
+      <c r="E148" t="s">
         <v>357</v>
       </c>
-      <c r="E148" t="s">
-        <v>318</v>
-      </c>
       <c r="F148" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>317</v>
+      </c>
+      <c r="E149" t="s">
         <v>357</v>
       </c>
-      <c r="E149" t="s">
-        <v>318</v>
-      </c>
       <c r="F149" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>317</v>
+      </c>
+      <c r="E150" t="s">
         <v>357</v>
       </c>
-      <c r="E150" t="s">
-        <v>318</v>
-      </c>
       <c r="F150" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>317</v>
+      </c>
+      <c r="E151" t="s">
         <v>357</v>
       </c>
-      <c r="E151" t="s">
-        <v>318</v>
-      </c>
       <c r="F151" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>317</v>
+      </c>
+      <c r="E152" t="s">
         <v>357</v>
       </c>
-      <c r="E152" t="s">
-        <v>318</v>
-      </c>
       <c r="F152" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>317</v>
+      </c>
+      <c r="E153" t="s">
         <v>357</v>
       </c>
-      <c r="E153" t="s">
-        <v>318</v>
-      </c>
       <c r="F153" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>317</v>
+      </c>
+      <c r="E154" t="s">
         <v>371</v>
       </c>
-      <c r="E154" t="s">
-        <v>318</v>
-      </c>
       <c r="F154" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>317</v>
+      </c>
+      <c r="E155" t="s">
         <v>371</v>
       </c>
-      <c r="E155" t="s">
-        <v>318</v>
-      </c>
       <c r="F155" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>317</v>
+      </c>
+      <c r="E156" t="s">
         <v>371</v>
       </c>
-      <c r="E156" t="s">
-        <v>318</v>
-      </c>
       <c r="F156" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>317</v>
+      </c>
+      <c r="E157" t="s">
         <v>371</v>
       </c>
-      <c r="E157" t="s">
-        <v>318</v>
-      </c>
       <c r="F157" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>317</v>
+      </c>
+      <c r="E158" t="s">
         <v>371</v>
       </c>
-      <c r="E158" t="s">
-        <v>318</v>
-      </c>
       <c r="F158" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>383</v>
+      </c>
+      <c r="E178" t="s">
         <v>425</v>
       </c>
-      <c r="E178" t="s">
-        <v>384</v>
-      </c>
       <c r="F178" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>383</v>
+      </c>
+      <c r="E179" t="s">
         <v>425</v>
       </c>
-      <c r="E179" t="s">
-        <v>384</v>
-      </c>
       <c r="F179" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>383</v>
+      </c>
+      <c r="E180" t="s">
         <v>425</v>
       </c>
-      <c r="E180" t="s">
-        <v>384</v>
-      </c>
       <c r="F180" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>383</v>
+      </c>
+      <c r="E181" t="s">
         <v>425</v>
       </c>
-      <c r="E181" t="s">
-        <v>384</v>
-      </c>
       <c r="F181" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>383</v>
+      </c>
+      <c r="E182" t="s">
         <v>425</v>
       </c>
-      <c r="E182" t="s">
-        <v>384</v>
-      </c>
       <c r="F182" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6234,16 +6234,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>383</v>
+      </c>
+      <c r="E183" t="s">
         <v>425</v>
       </c>
-      <c r="E183" t="s">
-        <v>384</v>
-      </c>
       <c r="F183" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6257,16 +6257,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>383</v>
+      </c>
+      <c r="E184" t="s">
         <v>425</v>
       </c>
-      <c r="E184" t="s">
-        <v>384</v>
-      </c>
       <c r="F184" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6280,16 +6280,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>383</v>
+      </c>
+      <c r="E185" t="s">
         <v>425</v>
       </c>
-      <c r="E185" t="s">
-        <v>384</v>
-      </c>
       <c r="F185" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6303,16 +6303,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>383</v>
+      </c>
+      <c r="E186" t="s">
         <v>425</v>
       </c>
-      <c r="E186" t="s">
-        <v>384</v>
-      </c>
       <c r="F186" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6326,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>383</v>
+      </c>
+      <c r="E187" t="s">
         <v>425</v>
       </c>
-      <c r="E187" t="s">
-        <v>384</v>
-      </c>
       <c r="F187" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6349,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>383</v>
+      </c>
+      <c r="E188" t="s">
         <v>447</v>
       </c>
-      <c r="E188" t="s">
-        <v>384</v>
-      </c>
       <c r="F188" t="s">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="G188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>111</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>121</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>151</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>231</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>311</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1171,10 +1171,10 @@
     <t>321</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>320</t>
   </si>
   <si>
     <t>32120</t>
@@ -2169,10 +2169,10 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2192,10 +2192,10 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2215,10 +2215,10 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2238,10 +2238,10 @@
         <v>22</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2261,10 +2261,10 @@
         <v>32</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2284,10 +2284,10 @@
         <v>32</v>
       </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2307,10 +2307,10 @@
         <v>38</v>
       </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2330,10 +2330,10 @@
         <v>38</v>
       </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2445,10 +2445,10 @@
         <v>56</v>
       </c>
       <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2468,10 +2468,10 @@
         <v>56</v>
       </c>
       <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2491,10 +2491,10 @@
         <v>56</v>
       </c>
       <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2514,10 +2514,10 @@
         <v>56</v>
       </c>
       <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2537,10 +2537,10 @@
         <v>56</v>
       </c>
       <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2560,10 +2560,10 @@
         <v>56</v>
       </c>
       <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2583,10 +2583,10 @@
         <v>56</v>
       </c>
       <c r="F24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2606,10 +2606,10 @@
         <v>56</v>
       </c>
       <c r="F25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2629,10 +2629,10 @@
         <v>74</v>
       </c>
       <c r="F26" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2652,10 +2652,10 @@
         <v>74</v>
       </c>
       <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2675,10 +2675,10 @@
         <v>74</v>
       </c>
       <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2698,10 +2698,10 @@
         <v>74</v>
       </c>
       <c r="F29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2721,10 +2721,10 @@
         <v>74</v>
       </c>
       <c r="F30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2744,10 +2744,10 @@
         <v>74</v>
       </c>
       <c r="F31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3503,10 +3503,10 @@
         <v>160</v>
       </c>
       <c r="F64" t="s">
+        <v>126</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3526,10 +3526,10 @@
         <v>160</v>
       </c>
       <c r="F65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3549,10 +3549,10 @@
         <v>160</v>
       </c>
       <c r="F66" t="s">
+        <v>126</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3572,10 +3572,10 @@
         <v>160</v>
       </c>
       <c r="F67" t="s">
+        <v>126</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3595,10 +3595,10 @@
         <v>160</v>
       </c>
       <c r="F68" t="s">
+        <v>126</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3618,10 +3618,10 @@
         <v>160</v>
       </c>
       <c r="F69" t="s">
+        <v>126</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4239,10 +4239,10 @@
         <v>236</v>
       </c>
       <c r="F96" t="s">
+        <v>226</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4262,10 +4262,10 @@
         <v>236</v>
       </c>
       <c r="F97" t="s">
+        <v>226</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4285,10 +4285,10 @@
         <v>236</v>
       </c>
       <c r="F98" t="s">
+        <v>226</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4308,10 +4308,10 @@
         <v>236</v>
       </c>
       <c r="F99" t="s">
+        <v>226</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4331,10 +4331,10 @@
         <v>236</v>
       </c>
       <c r="F100" t="s">
+        <v>226</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4354,10 +4354,10 @@
         <v>236</v>
       </c>
       <c r="F101" t="s">
+        <v>226</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4377,10 +4377,10 @@
         <v>236</v>
       </c>
       <c r="F102" t="s">
+        <v>226</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4400,10 +4400,10 @@
         <v>236</v>
       </c>
       <c r="F103" t="s">
+        <v>226</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4423,10 +4423,10 @@
         <v>236</v>
       </c>
       <c r="F104" t="s">
+        <v>226</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4446,10 +4446,10 @@
         <v>256</v>
       </c>
       <c r="F105" t="s">
+        <v>226</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4469,10 +4469,10 @@
         <v>256</v>
       </c>
       <c r="F106" t="s">
+        <v>226</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4492,10 +4492,10 @@
         <v>256</v>
       </c>
       <c r="F107" t="s">
+        <v>226</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4515,10 +4515,10 @@
         <v>256</v>
       </c>
       <c r="F108" t="s">
+        <v>226</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4538,10 +4538,10 @@
         <v>256</v>
       </c>
       <c r="F109" t="s">
+        <v>226</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4561,10 +4561,10 @@
         <v>256</v>
       </c>
       <c r="F110" t="s">
+        <v>226</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4584,10 +4584,10 @@
         <v>270</v>
       </c>
       <c r="F111" t="s">
+        <v>226</v>
+      </c>
+      <c r="G111" t="s">
         <v>269</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4607,10 +4607,10 @@
         <v>273</v>
       </c>
       <c r="F112" t="s">
+        <v>226</v>
+      </c>
+      <c r="G112" t="s">
         <v>274</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4630,10 +4630,10 @@
         <v>277</v>
       </c>
       <c r="F113" t="s">
+        <v>226</v>
+      </c>
+      <c r="G113" t="s">
         <v>278</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4653,10 +4653,10 @@
         <v>277</v>
       </c>
       <c r="F114" t="s">
+        <v>226</v>
+      </c>
+      <c r="G114" t="s">
         <v>278</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4676,10 +4676,10 @@
         <v>277</v>
       </c>
       <c r="F115" t="s">
+        <v>226</v>
+      </c>
+      <c r="G115" t="s">
         <v>278</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4699,10 +4699,10 @@
         <v>277</v>
       </c>
       <c r="F116" t="s">
+        <v>226</v>
+      </c>
+      <c r="G116" t="s">
         <v>278</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4722,10 +4722,10 @@
         <v>277</v>
       </c>
       <c r="F117" t="s">
+        <v>226</v>
+      </c>
+      <c r="G117" t="s">
         <v>278</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4745,10 +4745,10 @@
         <v>277</v>
       </c>
       <c r="F118" t="s">
+        <v>226</v>
+      </c>
+      <c r="G118" t="s">
         <v>278</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4768,10 +4768,10 @@
         <v>277</v>
       </c>
       <c r="F119" t="s">
+        <v>226</v>
+      </c>
+      <c r="G119" t="s">
         <v>278</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>293</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>293</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>293</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>293</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>293</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>293</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>307</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>307</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>307</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>307</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5435,10 +5435,10 @@
         <v>357</v>
       </c>
       <c r="F148" t="s">
+        <v>319</v>
+      </c>
+      <c r="G148" t="s">
         <v>358</v>
-      </c>
-      <c r="G148" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5458,10 +5458,10 @@
         <v>357</v>
       </c>
       <c r="F149" t="s">
+        <v>319</v>
+      </c>
+      <c r="G149" t="s">
         <v>358</v>
-      </c>
-      <c r="G149" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5481,10 +5481,10 @@
         <v>357</v>
       </c>
       <c r="F150" t="s">
+        <v>319</v>
+      </c>
+      <c r="G150" t="s">
         <v>358</v>
-      </c>
-      <c r="G150" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5504,10 +5504,10 @@
         <v>357</v>
       </c>
       <c r="F151" t="s">
+        <v>319</v>
+      </c>
+      <c r="G151" t="s">
         <v>358</v>
-      </c>
-      <c r="G151" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5527,10 +5527,10 @@
         <v>357</v>
       </c>
       <c r="F152" t="s">
+        <v>319</v>
+      </c>
+      <c r="G152" t="s">
         <v>358</v>
-      </c>
-      <c r="G152" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5550,10 +5550,10 @@
         <v>357</v>
       </c>
       <c r="F153" t="s">
+        <v>319</v>
+      </c>
+      <c r="G153" t="s">
         <v>358</v>
-      </c>
-      <c r="G153" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5573,10 +5573,10 @@
         <v>371</v>
       </c>
       <c r="F154" t="s">
+        <v>319</v>
+      </c>
+      <c r="G154" t="s">
         <v>372</v>
-      </c>
-      <c r="G154" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5596,10 +5596,10 @@
         <v>371</v>
       </c>
       <c r="F155" t="s">
+        <v>319</v>
+      </c>
+      <c r="G155" t="s">
         <v>372</v>
-      </c>
-      <c r="G155" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5619,10 +5619,10 @@
         <v>371</v>
       </c>
       <c r="F156" t="s">
+        <v>319</v>
+      </c>
+      <c r="G156" t="s">
         <v>372</v>
-      </c>
-      <c r="G156" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5642,10 +5642,10 @@
         <v>371</v>
       </c>
       <c r="F157" t="s">
+        <v>319</v>
+      </c>
+      <c r="G157" t="s">
         <v>372</v>
-      </c>
-      <c r="G157" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5665,10 +5665,10 @@
         <v>371</v>
       </c>
       <c r="F158" t="s">
+        <v>319</v>
+      </c>
+      <c r="G158" t="s">
         <v>372</v>
-      </c>
-      <c r="G158" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6125,10 +6125,10 @@
         <v>425</v>
       </c>
       <c r="F178" t="s">
+        <v>385</v>
+      </c>
+      <c r="G178" t="s">
         <v>426</v>
-      </c>
-      <c r="G178" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6148,10 +6148,10 @@
         <v>425</v>
       </c>
       <c r="F179" t="s">
+        <v>385</v>
+      </c>
+      <c r="G179" t="s">
         <v>426</v>
-      </c>
-      <c r="G179" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6171,10 +6171,10 @@
         <v>425</v>
       </c>
       <c r="F180" t="s">
+        <v>385</v>
+      </c>
+      <c r="G180" t="s">
         <v>426</v>
-      </c>
-      <c r="G180" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6194,10 +6194,10 @@
         <v>425</v>
       </c>
       <c r="F181" t="s">
+        <v>385</v>
+      </c>
+      <c r="G181" t="s">
         <v>426</v>
-      </c>
-      <c r="G181" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6217,10 +6217,10 @@
         <v>425</v>
       </c>
       <c r="F182" t="s">
+        <v>385</v>
+      </c>
+      <c r="G182" t="s">
         <v>426</v>
-      </c>
-      <c r="G182" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6240,10 +6240,10 @@
         <v>425</v>
       </c>
       <c r="F183" t="s">
+        <v>385</v>
+      </c>
+      <c r="G183" t="s">
         <v>426</v>
-      </c>
-      <c r="G183" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6263,10 +6263,10 @@
         <v>425</v>
       </c>
       <c r="F184" t="s">
+        <v>385</v>
+      </c>
+      <c r="G184" t="s">
         <v>426</v>
-      </c>
-      <c r="G184" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6286,10 +6286,10 @@
         <v>425</v>
       </c>
       <c r="F185" t="s">
+        <v>385</v>
+      </c>
+      <c r="G185" t="s">
         <v>426</v>
-      </c>
-      <c r="G185" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6309,10 +6309,10 @@
         <v>425</v>
       </c>
       <c r="F186" t="s">
+        <v>385</v>
+      </c>
+      <c r="G186" t="s">
         <v>426</v>
-      </c>
-      <c r="G186" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6332,10 +6332,10 @@
         <v>425</v>
       </c>
       <c r="F187" t="s">
+        <v>385</v>
+      </c>
+      <c r="G187" t="s">
         <v>426</v>
-      </c>
-      <c r="G187" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6355,10 +6355,10 @@
         <v>447</v>
       </c>
       <c r="F188" t="s">
+        <v>385</v>
+      </c>
+      <c r="G188" t="s">
         <v>448</v>
-      </c>
-      <c r="G188" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>451</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>451</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>451</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>451</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>451</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>451</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>465</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>469</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>469</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>469</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>469</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>469</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>469</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>483</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>483</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>483</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>483</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>483</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>483</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>483</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>483</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>483</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>483</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>505</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>509</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>513</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>513</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>519</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>519</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>519</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>519</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>519</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>519</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>519</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>535</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>535</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>535</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>543</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>547</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>551</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>555</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>559</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>559</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>111</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>121</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>151</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>231</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1171,10 +1171,10 @@
     <t>321</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
   </si>
   <si>
     <t>32120</t>
@@ -2169,10 +2169,10 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2192,10 +2192,10 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2215,10 +2215,10 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2238,10 +2238,10 @@
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2261,10 +2261,10 @@
         <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2284,10 +2284,10 @@
         <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2307,10 +2307,10 @@
         <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2330,10 +2330,10 @@
         <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2445,10 +2445,10 @@
         <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2468,10 +2468,10 @@
         <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2491,10 +2491,10 @@
         <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2514,10 +2514,10 @@
         <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2537,10 +2537,10 @@
         <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2560,10 +2560,10 @@
         <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2583,10 +2583,10 @@
         <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2606,10 +2606,10 @@
         <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2629,10 +2629,10 @@
         <v>74</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2652,10 +2652,10 @@
         <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2675,10 +2675,10 @@
         <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2698,10 +2698,10 @@
         <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2721,10 +2721,10 @@
         <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2744,10 +2744,10 @@
         <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3503,10 +3503,10 @@
         <v>160</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3526,10 +3526,10 @@
         <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3549,10 +3549,10 @@
         <v>160</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3572,10 +3572,10 @@
         <v>160</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3595,10 +3595,10 @@
         <v>160</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3618,10 +3618,10 @@
         <v>160</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4239,10 +4239,10 @@
         <v>236</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4262,10 +4262,10 @@
         <v>236</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4285,10 +4285,10 @@
         <v>236</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4308,10 +4308,10 @@
         <v>236</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4331,10 +4331,10 @@
         <v>236</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4354,10 +4354,10 @@
         <v>236</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4377,10 +4377,10 @@
         <v>236</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4400,10 +4400,10 @@
         <v>236</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4423,10 +4423,10 @@
         <v>236</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4446,10 +4446,10 @@
         <v>256</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4469,10 +4469,10 @@
         <v>256</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4492,10 +4492,10 @@
         <v>256</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4515,10 +4515,10 @@
         <v>256</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4538,10 +4538,10 @@
         <v>256</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4561,10 +4561,10 @@
         <v>256</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4584,10 +4584,10 @@
         <v>270</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="G111" t="s">
-        <v>269</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4607,10 +4607,10 @@
         <v>273</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4630,10 +4630,10 @@
         <v>277</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4653,10 +4653,10 @@
         <v>277</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4676,10 +4676,10 @@
         <v>277</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4699,10 +4699,10 @@
         <v>277</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G116" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4722,10 +4722,10 @@
         <v>277</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4745,10 +4745,10 @@
         <v>277</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G118" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4768,10 +4768,10 @@
         <v>277</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G119" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>293</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>293</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>293</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>293</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>293</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>293</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>307</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>307</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>307</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>307</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5435,10 +5435,10 @@
         <v>357</v>
       </c>
       <c r="F148" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5458,10 +5458,10 @@
         <v>357</v>
       </c>
       <c r="F149" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5481,10 +5481,10 @@
         <v>357</v>
       </c>
       <c r="F150" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5504,10 +5504,10 @@
         <v>357</v>
       </c>
       <c r="F151" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5527,10 +5527,10 @@
         <v>357</v>
       </c>
       <c r="F152" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5550,10 +5550,10 @@
         <v>357</v>
       </c>
       <c r="F153" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5573,10 +5573,10 @@
         <v>371</v>
       </c>
       <c r="F154" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5596,10 +5596,10 @@
         <v>371</v>
       </c>
       <c r="F155" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5619,10 +5619,10 @@
         <v>371</v>
       </c>
       <c r="F156" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5642,10 +5642,10 @@
         <v>371</v>
       </c>
       <c r="F157" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5665,10 +5665,10 @@
         <v>371</v>
       </c>
       <c r="F158" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6125,10 +6125,10 @@
         <v>425</v>
       </c>
       <c r="F178" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6148,10 +6148,10 @@
         <v>425</v>
       </c>
       <c r="F179" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6171,10 +6171,10 @@
         <v>425</v>
       </c>
       <c r="F180" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6194,10 +6194,10 @@
         <v>425</v>
       </c>
       <c r="F181" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6217,10 +6217,10 @@
         <v>425</v>
       </c>
       <c r="F182" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6240,10 +6240,10 @@
         <v>425</v>
       </c>
       <c r="F183" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6263,10 +6263,10 @@
         <v>425</v>
       </c>
       <c r="F184" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6286,10 +6286,10 @@
         <v>425</v>
       </c>
       <c r="F185" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6309,10 +6309,10 @@
         <v>425</v>
       </c>
       <c r="F186" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6332,10 +6332,10 @@
         <v>425</v>
       </c>
       <c r="F187" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6355,10 +6355,10 @@
         <v>447</v>
       </c>
       <c r="F188" t="s">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="G188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>451</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>451</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>451</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>451</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>451</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>451</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>465</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>469</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>469</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>469</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>469</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>469</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>469</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>483</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>483</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>483</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>483</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>483</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>483</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>483</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>483</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>483</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>483</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>505</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>509</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>513</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>513</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>519</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>519</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>519</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>519</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>519</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>519</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>519</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>535</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>535</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>535</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>543</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>547</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>551</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>555</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>559</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>559</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Santé</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Distribution d'Eau et Assainissement</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Infrastructure et Services Sociaux Divers</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transports et Entreposage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Energie</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banques et Services Financiers</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Entreprises et Autres Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Politique Commerciale et Réglementations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourisme</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>Protection de l'Environnement Général</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Autres Multisecteurs</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>Soutien Budgétaire</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Aide Alimentaire Dévelopmentale</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Aide sous forme de Produits, Autre</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Actions se Rapportant a la Dette</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Intervention d'Urgence</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction &amp; Réhabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Prévention catastrophes/Préparation à leur survenue</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Frais Administratifs des Donneurs</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugiés dans les Pays Donneurs</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Non Affecté / Non Specifié</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,13 +2163,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2209,13 +2209,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2232,13 +2232,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2255,13 +2255,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2278,13 +2278,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2301,13 +2301,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2324,13 +2324,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2439,13 +2439,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2462,13 +2462,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2485,13 +2485,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2508,13 +2508,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2531,13 +2531,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2554,13 +2554,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2577,13 +2577,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2600,13 +2600,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2623,13 +2623,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2646,13 +2646,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2669,13 +2669,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2692,13 +2692,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2715,13 +2715,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2738,13 +2738,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -3497,13 +3497,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3520,13 +3520,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3543,13 +3543,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3566,13 +3566,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3589,13 +3589,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3612,13 +3612,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -4233,13 +4233,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4256,13 +4256,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4279,13 +4279,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4302,13 +4302,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4325,13 +4325,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4348,13 +4348,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4371,13 +4371,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4394,13 +4394,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4417,13 +4417,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4440,13 +4440,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4463,13 +4463,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4486,13 +4486,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4509,13 +4509,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4532,13 +4532,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4555,13 +4555,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4578,13 +4578,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F111" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4601,13 +4601,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F112" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4624,13 +4624,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4647,13 +4647,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F114" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4670,13 +4670,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F115" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4693,13 +4693,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F116" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4716,13 +4716,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4739,13 +4739,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4762,13 +4762,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E119" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F119" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -5429,13 +5429,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E148" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F148" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G148" t="s">
         <v>320</v>
@@ -5452,13 +5452,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F149" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G149" t="s">
         <v>320</v>
@@ -5475,13 +5475,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E150" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F150" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G150" t="s">
         <v>320</v>
@@ -5498,13 +5498,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F151" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G151" t="s">
         <v>320</v>
@@ -5521,13 +5521,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E152" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F152" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G152" t="s">
         <v>320</v>
@@ -5544,13 +5544,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F153" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G153" t="s">
         <v>320</v>
@@ -5567,13 +5567,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E154" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F154" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G154" t="s">
         <v>320</v>
@@ -5590,13 +5590,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E155" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F155" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G155" t="s">
         <v>320</v>
@@ -5613,13 +5613,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F156" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G156" t="s">
         <v>320</v>
@@ -5636,13 +5636,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G157" t="s">
         <v>320</v>
@@ -5659,13 +5659,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E158" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F158" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G158" t="s">
         <v>320</v>
@@ -6119,13 +6119,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E178" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F178" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G178" t="s">
         <v>386</v>
@@ -6142,13 +6142,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E179" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F179" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G179" t="s">
         <v>386</v>
@@ -6165,13 +6165,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E180" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F180" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G180" t="s">
         <v>386</v>
@@ -6188,13 +6188,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E181" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F181" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G181" t="s">
         <v>386</v>
@@ -6211,13 +6211,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E182" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F182" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G182" t="s">
         <v>386</v>
@@ -6234,13 +6234,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E183" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F183" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G183" t="s">
         <v>386</v>
@@ -6257,13 +6257,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E184" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F184" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G184" t="s">
         <v>386</v>
@@ -6280,13 +6280,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E185" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F185" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G185" t="s">
         <v>386</v>
@@ -6303,13 +6303,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E186" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F186" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G186" t="s">
         <v>386</v>
@@ -6326,13 +6326,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E187" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F187" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G187" t="s">
         <v>386</v>
@@ -6349,13 +6349,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F188" t="s">
-        <v>448</v>
+        <v>385</v>
       </c>
       <c r="G188" t="s">
         <v>386</v>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>111</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>121</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>151</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>231</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,13 +1168,13 @@
     <t>321</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
     <t>32120</t>
@@ -2166,10 +2166,10 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2189,10 +2189,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2212,10 +2212,10 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2235,10 +2235,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2258,10 +2258,10 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2281,10 +2281,10 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2304,10 +2304,10 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>39</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2327,10 +2327,10 @@
         <v>38</v>
       </c>
       <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2442,10 +2442,10 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s">
         <v>57</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2465,10 +2465,10 @@
         <v>56</v>
       </c>
       <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
         <v>57</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2488,10 +2488,10 @@
         <v>56</v>
       </c>
       <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
         <v>57</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2511,10 +2511,10 @@
         <v>56</v>
       </c>
       <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
         <v>57</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2534,10 +2534,10 @@
         <v>56</v>
       </c>
       <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
         <v>57</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2557,10 +2557,10 @@
         <v>56</v>
       </c>
       <c r="E23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" t="s">
         <v>57</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2580,10 +2580,10 @@
         <v>56</v>
       </c>
       <c r="E24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" t="s">
         <v>57</v>
-      </c>
-      <c r="F24" t="s">
-        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2603,10 +2603,10 @@
         <v>56</v>
       </c>
       <c r="E25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
         <v>57</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2626,10 +2626,10 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
         <v>75</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2649,10 +2649,10 @@
         <v>74</v>
       </c>
       <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
         <v>75</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2672,10 +2672,10 @@
         <v>74</v>
       </c>
       <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
         <v>75</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2695,10 +2695,10 @@
         <v>74</v>
       </c>
       <c r="E29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s">
         <v>75</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2718,10 +2718,10 @@
         <v>74</v>
       </c>
       <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
         <v>75</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2741,10 +2741,10 @@
         <v>74</v>
       </c>
       <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" t="s">
         <v>75</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" t="s">
         <v>161</v>
-      </c>
-      <c r="F64" t="s">
-        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3523,10 +3523,10 @@
         <v>160</v>
       </c>
       <c r="E65" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" t="s">
         <v>161</v>
-      </c>
-      <c r="F65" t="s">
-        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3546,10 +3546,10 @@
         <v>160</v>
       </c>
       <c r="E66" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" t="s">
         <v>161</v>
-      </c>
-      <c r="F66" t="s">
-        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3569,10 +3569,10 @@
         <v>160</v>
       </c>
       <c r="E67" t="s">
+        <v>125</v>
+      </c>
+      <c r="F67" t="s">
         <v>161</v>
-      </c>
-      <c r="F67" t="s">
-        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3592,10 +3592,10 @@
         <v>160</v>
       </c>
       <c r="E68" t="s">
+        <v>125</v>
+      </c>
+      <c r="F68" t="s">
         <v>161</v>
-      </c>
-      <c r="F68" t="s">
-        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3615,10 +3615,10 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
+        <v>125</v>
+      </c>
+      <c r="F69" t="s">
         <v>161</v>
-      </c>
-      <c r="F69" t="s">
-        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,10 +4236,10 @@
         <v>236</v>
       </c>
       <c r="E96" t="s">
+        <v>225</v>
+      </c>
+      <c r="F96" t="s">
         <v>237</v>
-      </c>
-      <c r="F96" t="s">
-        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4259,10 +4259,10 @@
         <v>236</v>
       </c>
       <c r="E97" t="s">
+        <v>225</v>
+      </c>
+      <c r="F97" t="s">
         <v>237</v>
-      </c>
-      <c r="F97" t="s">
-        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4282,10 +4282,10 @@
         <v>236</v>
       </c>
       <c r="E98" t="s">
+        <v>225</v>
+      </c>
+      <c r="F98" t="s">
         <v>237</v>
-      </c>
-      <c r="F98" t="s">
-        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4305,10 +4305,10 @@
         <v>236</v>
       </c>
       <c r="E99" t="s">
+        <v>225</v>
+      </c>
+      <c r="F99" t="s">
         <v>237</v>
-      </c>
-      <c r="F99" t="s">
-        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4328,10 +4328,10 @@
         <v>236</v>
       </c>
       <c r="E100" t="s">
+        <v>225</v>
+      </c>
+      <c r="F100" t="s">
         <v>237</v>
-      </c>
-      <c r="F100" t="s">
-        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4351,10 +4351,10 @@
         <v>236</v>
       </c>
       <c r="E101" t="s">
+        <v>225</v>
+      </c>
+      <c r="F101" t="s">
         <v>237</v>
-      </c>
-      <c r="F101" t="s">
-        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4374,10 +4374,10 @@
         <v>236</v>
       </c>
       <c r="E102" t="s">
+        <v>225</v>
+      </c>
+      <c r="F102" t="s">
         <v>237</v>
-      </c>
-      <c r="F102" t="s">
-        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4397,10 +4397,10 @@
         <v>236</v>
       </c>
       <c r="E103" t="s">
+        <v>225</v>
+      </c>
+      <c r="F103" t="s">
         <v>237</v>
-      </c>
-      <c r="F103" t="s">
-        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4420,10 +4420,10 @@
         <v>236</v>
       </c>
       <c r="E104" t="s">
+        <v>225</v>
+      </c>
+      <c r="F104" t="s">
         <v>237</v>
-      </c>
-      <c r="F104" t="s">
-        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4443,10 +4443,10 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
+        <v>225</v>
+      </c>
+      <c r="F105" t="s">
         <v>257</v>
-      </c>
-      <c r="F105" t="s">
-        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4466,10 +4466,10 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
+        <v>225</v>
+      </c>
+      <c r="F106" t="s">
         <v>257</v>
-      </c>
-      <c r="F106" t="s">
-        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4489,10 +4489,10 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
+        <v>225</v>
+      </c>
+      <c r="F107" t="s">
         <v>257</v>
-      </c>
-      <c r="F107" t="s">
-        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4512,10 +4512,10 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
+        <v>225</v>
+      </c>
+      <c r="F108" t="s">
         <v>257</v>
-      </c>
-      <c r="F108" t="s">
-        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4535,10 +4535,10 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
+        <v>225</v>
+      </c>
+      <c r="F109" t="s">
         <v>257</v>
-      </c>
-      <c r="F109" t="s">
-        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4558,10 +4558,10 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
+        <v>225</v>
+      </c>
+      <c r="F110" t="s">
         <v>257</v>
-      </c>
-      <c r="F110" t="s">
-        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4581,10 +4581,10 @@
         <v>270</v>
       </c>
       <c r="E111" t="s">
+        <v>225</v>
+      </c>
+      <c r="F111" t="s">
         <v>269</v>
-      </c>
-      <c r="F111" t="s">
-        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4604,10 +4604,10 @@
         <v>273</v>
       </c>
       <c r="E112" t="s">
+        <v>225</v>
+      </c>
+      <c r="F112" t="s">
         <v>274</v>
-      </c>
-      <c r="F112" t="s">
-        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4627,10 +4627,10 @@
         <v>277</v>
       </c>
       <c r="E113" t="s">
+        <v>225</v>
+      </c>
+      <c r="F113" t="s">
         <v>278</v>
-      </c>
-      <c r="F113" t="s">
-        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4650,10 +4650,10 @@
         <v>277</v>
       </c>
       <c r="E114" t="s">
+        <v>225</v>
+      </c>
+      <c r="F114" t="s">
         <v>278</v>
-      </c>
-      <c r="F114" t="s">
-        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4673,10 +4673,10 @@
         <v>277</v>
       </c>
       <c r="E115" t="s">
+        <v>225</v>
+      </c>
+      <c r="F115" t="s">
         <v>278</v>
-      </c>
-      <c r="F115" t="s">
-        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4696,10 +4696,10 @@
         <v>277</v>
       </c>
       <c r="E116" t="s">
+        <v>225</v>
+      </c>
+      <c r="F116" t="s">
         <v>278</v>
-      </c>
-      <c r="F116" t="s">
-        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4719,10 +4719,10 @@
         <v>277</v>
       </c>
       <c r="E117" t="s">
+        <v>225</v>
+      </c>
+      <c r="F117" t="s">
         <v>278</v>
-      </c>
-      <c r="F117" t="s">
-        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4742,10 +4742,10 @@
         <v>277</v>
       </c>
       <c r="E118" t="s">
+        <v>225</v>
+      </c>
+      <c r="F118" t="s">
         <v>278</v>
-      </c>
-      <c r="F118" t="s">
-        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4765,10 +4765,10 @@
         <v>277</v>
       </c>
       <c r="E119" t="s">
+        <v>225</v>
+      </c>
+      <c r="F119" t="s">
         <v>278</v>
-      </c>
-      <c r="F119" t="s">
-        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>293</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>293</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>293</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>293</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>293</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>293</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>307</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>307</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>307</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>307</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,10 +5432,10 @@
         <v>357</v>
       </c>
       <c r="E148" t="s">
+        <v>318</v>
+      </c>
+      <c r="F148" t="s">
         <v>358</v>
-      </c>
-      <c r="F148" t="s">
-        <v>319</v>
       </c>
       <c r="G148" t="s">
         <v>320</v>
@@ -5455,10 +5455,10 @@
         <v>357</v>
       </c>
       <c r="E149" t="s">
+        <v>318</v>
+      </c>
+      <c r="F149" t="s">
         <v>358</v>
-      </c>
-      <c r="F149" t="s">
-        <v>319</v>
       </c>
       <c r="G149" t="s">
         <v>320</v>
@@ -5478,10 +5478,10 @@
         <v>357</v>
       </c>
       <c r="E150" t="s">
+        <v>318</v>
+      </c>
+      <c r="F150" t="s">
         <v>358</v>
-      </c>
-      <c r="F150" t="s">
-        <v>319</v>
       </c>
       <c r="G150" t="s">
         <v>320</v>
@@ -5501,10 +5501,10 @@
         <v>357</v>
       </c>
       <c r="E151" t="s">
+        <v>318</v>
+      </c>
+      <c r="F151" t="s">
         <v>358</v>
-      </c>
-      <c r="F151" t="s">
-        <v>319</v>
       </c>
       <c r="G151" t="s">
         <v>320</v>
@@ -5524,10 +5524,10 @@
         <v>357</v>
       </c>
       <c r="E152" t="s">
+        <v>318</v>
+      </c>
+      <c r="F152" t="s">
         <v>358</v>
-      </c>
-      <c r="F152" t="s">
-        <v>319</v>
       </c>
       <c r="G152" t="s">
         <v>320</v>
@@ -5547,10 +5547,10 @@
         <v>357</v>
       </c>
       <c r="E153" t="s">
+        <v>318</v>
+      </c>
+      <c r="F153" t="s">
         <v>358</v>
-      </c>
-      <c r="F153" t="s">
-        <v>319</v>
       </c>
       <c r="G153" t="s">
         <v>320</v>
@@ -5570,10 +5570,10 @@
         <v>371</v>
       </c>
       <c r="E154" t="s">
+        <v>318</v>
+      </c>
+      <c r="F154" t="s">
         <v>372</v>
-      </c>
-      <c r="F154" t="s">
-        <v>319</v>
       </c>
       <c r="G154" t="s">
         <v>320</v>
@@ -5593,10 +5593,10 @@
         <v>371</v>
       </c>
       <c r="E155" t="s">
+        <v>318</v>
+      </c>
+      <c r="F155" t="s">
         <v>372</v>
-      </c>
-      <c r="F155" t="s">
-        <v>319</v>
       </c>
       <c r="G155" t="s">
         <v>320</v>
@@ -5616,10 +5616,10 @@
         <v>371</v>
       </c>
       <c r="E156" t="s">
+        <v>318</v>
+      </c>
+      <c r="F156" t="s">
         <v>372</v>
-      </c>
-      <c r="F156" t="s">
-        <v>319</v>
       </c>
       <c r="G156" t="s">
         <v>320</v>
@@ -5639,10 +5639,10 @@
         <v>371</v>
       </c>
       <c r="E157" t="s">
+        <v>318</v>
+      </c>
+      <c r="F157" t="s">
         <v>372</v>
-      </c>
-      <c r="F157" t="s">
-        <v>319</v>
       </c>
       <c r="G157" t="s">
         <v>320</v>
@@ -5662,10 +5662,10 @@
         <v>371</v>
       </c>
       <c r="E158" t="s">
+        <v>318</v>
+      </c>
+      <c r="F158" t="s">
         <v>372</v>
-      </c>
-      <c r="F158" t="s">
-        <v>319</v>
       </c>
       <c r="G158" t="s">
         <v>320</v>
@@ -6122,10 +6122,10 @@
         <v>425</v>
       </c>
       <c r="E178" t="s">
+        <v>384</v>
+      </c>
+      <c r="F178" t="s">
         <v>426</v>
-      </c>
-      <c r="F178" t="s">
-        <v>385</v>
       </c>
       <c r="G178" t="s">
         <v>386</v>
@@ -6145,10 +6145,10 @@
         <v>425</v>
       </c>
       <c r="E179" t="s">
+        <v>384</v>
+      </c>
+      <c r="F179" t="s">
         <v>426</v>
-      </c>
-      <c r="F179" t="s">
-        <v>385</v>
       </c>
       <c r="G179" t="s">
         <v>386</v>
@@ -6168,10 +6168,10 @@
         <v>425</v>
       </c>
       <c r="E180" t="s">
+        <v>384</v>
+      </c>
+      <c r="F180" t="s">
         <v>426</v>
-      </c>
-      <c r="F180" t="s">
-        <v>385</v>
       </c>
       <c r="G180" t="s">
         <v>386</v>
@@ -6191,10 +6191,10 @@
         <v>425</v>
       </c>
       <c r="E181" t="s">
+        <v>384</v>
+      </c>
+      <c r="F181" t="s">
         <v>426</v>
-      </c>
-      <c r="F181" t="s">
-        <v>385</v>
       </c>
       <c r="G181" t="s">
         <v>386</v>
@@ -6214,10 +6214,10 @@
         <v>425</v>
       </c>
       <c r="E182" t="s">
+        <v>384</v>
+      </c>
+      <c r="F182" t="s">
         <v>426</v>
-      </c>
-      <c r="F182" t="s">
-        <v>385</v>
       </c>
       <c r="G182" t="s">
         <v>386</v>
@@ -6237,10 +6237,10 @@
         <v>425</v>
       </c>
       <c r="E183" t="s">
+        <v>384</v>
+      </c>
+      <c r="F183" t="s">
         <v>426</v>
-      </c>
-      <c r="F183" t="s">
-        <v>385</v>
       </c>
       <c r="G183" t="s">
         <v>386</v>
@@ -6260,10 +6260,10 @@
         <v>425</v>
       </c>
       <c r="E184" t="s">
+        <v>384</v>
+      </c>
+      <c r="F184" t="s">
         <v>426</v>
-      </c>
-      <c r="F184" t="s">
-        <v>385</v>
       </c>
       <c r="G184" t="s">
         <v>386</v>
@@ -6283,10 +6283,10 @@
         <v>425</v>
       </c>
       <c r="E185" t="s">
+        <v>384</v>
+      </c>
+      <c r="F185" t="s">
         <v>426</v>
-      </c>
-      <c r="F185" t="s">
-        <v>385</v>
       </c>
       <c r="G185" t="s">
         <v>386</v>
@@ -6306,10 +6306,10 @@
         <v>425</v>
       </c>
       <c r="E186" t="s">
+        <v>384</v>
+      </c>
+      <c r="F186" t="s">
         <v>426</v>
-      </c>
-      <c r="F186" t="s">
-        <v>385</v>
       </c>
       <c r="G186" t="s">
         <v>386</v>
@@ -6329,10 +6329,10 @@
         <v>425</v>
       </c>
       <c r="E187" t="s">
+        <v>384</v>
+      </c>
+      <c r="F187" t="s">
         <v>426</v>
-      </c>
-      <c r="F187" t="s">
-        <v>385</v>
       </c>
       <c r="G187" t="s">
         <v>386</v>
@@ -6352,10 +6352,10 @@
         <v>447</v>
       </c>
       <c r="E188" t="s">
+        <v>384</v>
+      </c>
+      <c r="F188" t="s">
         <v>448</v>
-      </c>
-      <c r="F188" t="s">
-        <v>385</v>
       </c>
       <c r="G188" t="s">
         <v>386</v>
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>451</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>451</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>451</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>451</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>451</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>451</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>465</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>469</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>469</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>469</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>469</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>469</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>469</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>483</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>483</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>483</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>483</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>483</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>483</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>483</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>483</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>483</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>483</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>505</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>509</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>513</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>513</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>519</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>519</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>519</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>519</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>519</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>519</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>519</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>535</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>535</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>535</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>543</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>547</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>551</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>555</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>559</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>559</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>Santé, Général</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>Distribution d'Eau et Assainissement</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Distribution d'Eau et Assainissement</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>Infrastructure et Services Sociaux Divers</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Infrastructure et Services Sociaux Divers</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>Transports et Entreposage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transports et Entreposage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>Banques et Services Financiers</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banques et Services Financiers</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>Entreprises et Autres Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Entreprises et Autres Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,12 +967,12 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
@@ -1165,12 +1165,12 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>Politique Commerciale et Réglementations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Politique Commerciale et Réglementations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>Tourisme</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourisme</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>Protection de l'Environnement Général</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protection de l'Environnement Général</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>Autres Multisecteurs</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Autres Multisecteurs</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>Soutien Budgétaire</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Soutien Budgétaire</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>Aide Alimentaire Dévelopmentale</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Aide Alimentaire Dévelopmentale</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>Aide sous forme de Produits, Autre</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Aide sous forme de Produits, Autre</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>Actions se Rapportant a la Dette</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actions se Rapportant a la Dette</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>Intervention d'Urgence</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Intervention d'Urgence</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>Reconstruction &amp; Réhabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction &amp; Réhabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>Prévention catastrophes/Préparation à leur survenue</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prévention catastrophes/Préparation à leur survenue</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>Frais Administratifs des Donneurs</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Frais Administratifs des Donneurs</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>Refugiés dans les Pays Donneurs</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiés dans les Pays Donneurs</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>Non Affecté / Non Specifié</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Non Affecté / Non Specifié</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,10 +2163,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>23</v>
@@ -2186,10 +2186,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>23</v>
@@ -2209,10 +2209,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -2232,10 +2232,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>23</v>
@@ -2255,10 +2255,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>33</v>
@@ -2278,10 +2278,10 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2301,10 +2301,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -2324,10 +2324,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -2439,10 +2439,10 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
-      </c>
-      <c r="E18" t="s">
-        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -2462,10 +2462,10 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>57</v>
@@ -2485,10 +2485,10 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>57</v>
@@ -2508,10 +2508,10 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
-      </c>
-      <c r="E21" t="s">
-        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -2531,10 +2531,10 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
-      </c>
-      <c r="E22" t="s">
-        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>57</v>
@@ -2554,10 +2554,10 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
-      </c>
-      <c r="E23" t="s">
-        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>57</v>
@@ -2577,10 +2577,10 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
-      </c>
-      <c r="E24" t="s">
-        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>57</v>
@@ -2600,10 +2600,10 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
-      </c>
-      <c r="E25" t="s">
-        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>57</v>
@@ -2623,10 +2623,10 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
-      </c>
-      <c r="E26" t="s">
-        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>75</v>
@@ -2646,10 +2646,10 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
-      </c>
-      <c r="E27" t="s">
-        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>75</v>
@@ -2669,10 +2669,10 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
-      </c>
-      <c r="E28" t="s">
-        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>75</v>
@@ -2692,10 +2692,10 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
-      </c>
-      <c r="E29" t="s">
-        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>75</v>
@@ -2715,10 +2715,10 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
-      </c>
-      <c r="E30" t="s">
-        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>75</v>
@@ -2738,10 +2738,10 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
-      </c>
-      <c r="E31" t="s">
-        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>75</v>
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3497,10 +3497,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
-      </c>
-      <c r="E64" t="s">
-        <v>125</v>
       </c>
       <c r="F64" t="s">
         <v>161</v>
@@ -3520,10 +3520,10 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
-      </c>
-      <c r="E65" t="s">
-        <v>125</v>
       </c>
       <c r="F65" t="s">
         <v>161</v>
@@ -3543,10 +3543,10 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
-      </c>
-      <c r="E66" t="s">
-        <v>125</v>
       </c>
       <c r="F66" t="s">
         <v>161</v>
@@ -3566,10 +3566,10 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
-      </c>
-      <c r="E67" t="s">
-        <v>125</v>
       </c>
       <c r="F67" t="s">
         <v>161</v>
@@ -3589,10 +3589,10 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
-      </c>
-      <c r="E68" t="s">
-        <v>125</v>
       </c>
       <c r="F68" t="s">
         <v>161</v>
@@ -3612,10 +3612,10 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
-      </c>
-      <c r="E69" t="s">
-        <v>125</v>
       </c>
       <c r="F69" t="s">
         <v>161</v>
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4233,10 +4233,10 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
-      </c>
-      <c r="E96" t="s">
-        <v>225</v>
       </c>
       <c r="F96" t="s">
         <v>237</v>
@@ -4256,10 +4256,10 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
-      </c>
-      <c r="E97" t="s">
-        <v>225</v>
       </c>
       <c r="F97" t="s">
         <v>237</v>
@@ -4279,10 +4279,10 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
-      </c>
-      <c r="E98" t="s">
-        <v>225</v>
       </c>
       <c r="F98" t="s">
         <v>237</v>
@@ -4302,10 +4302,10 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
-      </c>
-      <c r="E99" t="s">
-        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>237</v>
@@ -4325,10 +4325,10 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
-      </c>
-      <c r="E100" t="s">
-        <v>225</v>
       </c>
       <c r="F100" t="s">
         <v>237</v>
@@ -4348,10 +4348,10 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
-      </c>
-      <c r="E101" t="s">
-        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>237</v>
@@ -4371,10 +4371,10 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
-      </c>
-      <c r="E102" t="s">
-        <v>225</v>
       </c>
       <c r="F102" t="s">
         <v>237</v>
@@ -4394,10 +4394,10 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
-      </c>
-      <c r="E103" t="s">
-        <v>225</v>
       </c>
       <c r="F103" t="s">
         <v>237</v>
@@ -4417,10 +4417,10 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
-      </c>
-      <c r="E104" t="s">
-        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>237</v>
@@ -4440,10 +4440,10 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
-      </c>
-      <c r="E105" t="s">
-        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>257</v>
@@ -4463,10 +4463,10 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
-      </c>
-      <c r="E106" t="s">
-        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>257</v>
@@ -4486,10 +4486,10 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
-      </c>
-      <c r="E107" t="s">
-        <v>225</v>
       </c>
       <c r="F107" t="s">
         <v>257</v>
@@ -4509,10 +4509,10 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
-      </c>
-      <c r="E108" t="s">
-        <v>225</v>
       </c>
       <c r="F108" t="s">
         <v>257</v>
@@ -4532,10 +4532,10 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
-      </c>
-      <c r="E109" t="s">
-        <v>225</v>
       </c>
       <c r="F109" t="s">
         <v>257</v>
@@ -4555,10 +4555,10 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
-      </c>
-      <c r="E110" t="s">
-        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>257</v>
@@ -4578,10 +4578,10 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
         <v>270</v>
-      </c>
-      <c r="E111" t="s">
-        <v>225</v>
       </c>
       <c r="F111" t="s">
         <v>269</v>
@@ -4601,10 +4601,10 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>273</v>
-      </c>
-      <c r="E112" t="s">
-        <v>225</v>
       </c>
       <c r="F112" t="s">
         <v>274</v>
@@ -4624,10 +4624,10 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>277</v>
-      </c>
-      <c r="E113" t="s">
-        <v>225</v>
       </c>
       <c r="F113" t="s">
         <v>278</v>
@@ -4647,10 +4647,10 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>277</v>
-      </c>
-      <c r="E114" t="s">
-        <v>225</v>
       </c>
       <c r="F114" t="s">
         <v>278</v>
@@ -4670,10 +4670,10 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>277</v>
-      </c>
-      <c r="E115" t="s">
-        <v>225</v>
       </c>
       <c r="F115" t="s">
         <v>278</v>
@@ -4693,10 +4693,10 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>277</v>
-      </c>
-      <c r="E116" t="s">
-        <v>225</v>
       </c>
       <c r="F116" t="s">
         <v>278</v>
@@ -4716,10 +4716,10 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>277</v>
-      </c>
-      <c r="E117" t="s">
-        <v>225</v>
       </c>
       <c r="F117" t="s">
         <v>278</v>
@@ -4739,10 +4739,10 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>277</v>
-      </c>
-      <c r="E118" t="s">
-        <v>225</v>
       </c>
       <c r="F118" t="s">
         <v>278</v>
@@ -4762,10 +4762,10 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>277</v>
-      </c>
-      <c r="E119" t="s">
-        <v>225</v>
       </c>
       <c r="F119" t="s">
         <v>278</v>
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>293</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>293</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>293</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>293</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>293</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>293</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>307</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>307</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>307</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>307</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5429,10 +5429,10 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>317</v>
+      </c>
+      <c r="E148" t="s">
         <v>357</v>
-      </c>
-      <c r="E148" t="s">
-        <v>318</v>
       </c>
       <c r="F148" t="s">
         <v>358</v>
@@ -5452,10 +5452,10 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>317</v>
+      </c>
+      <c r="E149" t="s">
         <v>357</v>
-      </c>
-      <c r="E149" t="s">
-        <v>318</v>
       </c>
       <c r="F149" t="s">
         <v>358</v>
@@ -5475,10 +5475,10 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>317</v>
+      </c>
+      <c r="E150" t="s">
         <v>357</v>
-      </c>
-      <c r="E150" t="s">
-        <v>318</v>
       </c>
       <c r="F150" t="s">
         <v>358</v>
@@ -5498,10 +5498,10 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>317</v>
+      </c>
+      <c r="E151" t="s">
         <v>357</v>
-      </c>
-      <c r="E151" t="s">
-        <v>318</v>
       </c>
       <c r="F151" t="s">
         <v>358</v>
@@ -5521,10 +5521,10 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>317</v>
+      </c>
+      <c r="E152" t="s">
         <v>357</v>
-      </c>
-      <c r="E152" t="s">
-        <v>318</v>
       </c>
       <c r="F152" t="s">
         <v>358</v>
@@ -5544,10 +5544,10 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>317</v>
+      </c>
+      <c r="E153" t="s">
         <v>357</v>
-      </c>
-      <c r="E153" t="s">
-        <v>318</v>
       </c>
       <c r="F153" t="s">
         <v>358</v>
@@ -5567,10 +5567,10 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>317</v>
+      </c>
+      <c r="E154" t="s">
         <v>371</v>
-      </c>
-      <c r="E154" t="s">
-        <v>318</v>
       </c>
       <c r="F154" t="s">
         <v>372</v>
@@ -5590,10 +5590,10 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>317</v>
+      </c>
+      <c r="E155" t="s">
         <v>371</v>
-      </c>
-      <c r="E155" t="s">
-        <v>318</v>
       </c>
       <c r="F155" t="s">
         <v>372</v>
@@ -5613,10 +5613,10 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>317</v>
+      </c>
+      <c r="E156" t="s">
         <v>371</v>
-      </c>
-      <c r="E156" t="s">
-        <v>318</v>
       </c>
       <c r="F156" t="s">
         <v>372</v>
@@ -5636,10 +5636,10 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>317</v>
+      </c>
+      <c r="E157" t="s">
         <v>371</v>
-      </c>
-      <c r="E157" t="s">
-        <v>318</v>
       </c>
       <c r="F157" t="s">
         <v>372</v>
@@ -5659,10 +5659,10 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>317</v>
+      </c>
+      <c r="E158" t="s">
         <v>371</v>
-      </c>
-      <c r="E158" t="s">
-        <v>318</v>
       </c>
       <c r="F158" t="s">
         <v>372</v>
@@ -6119,10 +6119,10 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>383</v>
+      </c>
+      <c r="E178" t="s">
         <v>425</v>
-      </c>
-      <c r="E178" t="s">
-        <v>384</v>
       </c>
       <c r="F178" t="s">
         <v>426</v>
@@ -6142,10 +6142,10 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>383</v>
+      </c>
+      <c r="E179" t="s">
         <v>425</v>
-      </c>
-      <c r="E179" t="s">
-        <v>384</v>
       </c>
       <c r="F179" t="s">
         <v>426</v>
@@ -6165,10 +6165,10 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>383</v>
+      </c>
+      <c r="E180" t="s">
         <v>425</v>
-      </c>
-      <c r="E180" t="s">
-        <v>384</v>
       </c>
       <c r="F180" t="s">
         <v>426</v>
@@ -6188,10 +6188,10 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>383</v>
+      </c>
+      <c r="E181" t="s">
         <v>425</v>
-      </c>
-      <c r="E181" t="s">
-        <v>384</v>
       </c>
       <c r="F181" t="s">
         <v>426</v>
@@ -6211,10 +6211,10 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>383</v>
+      </c>
+      <c r="E182" t="s">
         <v>425</v>
-      </c>
-      <c r="E182" t="s">
-        <v>384</v>
       </c>
       <c r="F182" t="s">
         <v>426</v>
@@ -6234,10 +6234,10 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>383</v>
+      </c>
+      <c r="E183" t="s">
         <v>425</v>
-      </c>
-      <c r="E183" t="s">
-        <v>384</v>
       </c>
       <c r="F183" t="s">
         <v>426</v>
@@ -6257,10 +6257,10 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>383</v>
+      </c>
+      <c r="E184" t="s">
         <v>425</v>
-      </c>
-      <c r="E184" t="s">
-        <v>384</v>
       </c>
       <c r="F184" t="s">
         <v>426</v>
@@ -6280,10 +6280,10 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>383</v>
+      </c>
+      <c r="E185" t="s">
         <v>425</v>
-      </c>
-      <c r="E185" t="s">
-        <v>384</v>
       </c>
       <c r="F185" t="s">
         <v>426</v>
@@ -6303,10 +6303,10 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>383</v>
+      </c>
+      <c r="E186" t="s">
         <v>425</v>
-      </c>
-      <c r="E186" t="s">
-        <v>384</v>
       </c>
       <c r="F186" t="s">
         <v>426</v>
@@ -6326,10 +6326,10 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>383</v>
+      </c>
+      <c r="E187" t="s">
         <v>425</v>
-      </c>
-      <c r="E187" t="s">
-        <v>384</v>
       </c>
       <c r="F187" t="s">
         <v>426</v>
@@ -6349,10 +6349,10 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>383</v>
+      </c>
+      <c r="E188" t="s">
         <v>447</v>
-      </c>
-      <c r="E188" t="s">
-        <v>384</v>
       </c>
       <c r="F188" t="s">
         <v>448</v>
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>451</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>451</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>451</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>451</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>451</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>451</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>465</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>469</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>469</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>469</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>469</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>469</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>469</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>483</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>483</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>483</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>483</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>483</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>483</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>483</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>483</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>483</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>483</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>505</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>509</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>513</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>513</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>519</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>519</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>519</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>519</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>519</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>519</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>519</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>535</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>535</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>535</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>543</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>547</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>551</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>555</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>559</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>559</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
     <t>Santé</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Distribution d'Eau et Assainissement</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Infrastructure et Services Sociaux Divers</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transports et Entreposage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
     <t>Energie</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
     <t>230</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banques et Services Financiers</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Entreprises et Autres Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,15 +967,15 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>310</t>
   </si>
   <si>
@@ -1165,15 +1165,15 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Politique Commerciale et Réglementations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourisme</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>Protection de l'Environnement Général</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Autres Multisecteurs</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>Soutien Budgétaire</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Aide Alimentaire Dévelopmentale</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Aide sous forme de Produits, Autre</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Actions se Rapportant a la Dette</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Intervention d'Urgence</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction &amp; Réhabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Prévention catastrophes/Préparation à leur survenue</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Frais Administratifs des Donneurs</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugiés dans les Pays Donneurs</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Non Affecté / Non Specifié</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,13 +2163,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2209,13 +2209,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2232,13 +2232,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2255,13 +2255,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2278,13 +2278,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2301,13 +2301,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2324,13 +2324,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2439,13 +2439,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
@@ -2462,13 +2462,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>47</v>
@@ -2485,13 +2485,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>47</v>
@@ -2508,13 +2508,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>47</v>
@@ -2531,13 +2531,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -2554,13 +2554,13 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>47</v>
@@ -2577,13 +2577,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
         <v>47</v>
@@ -2600,13 +2600,13 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
         <v>47</v>
@@ -2623,13 +2623,13 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>47</v>
@@ -2646,13 +2646,13 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>47</v>
@@ -2669,13 +2669,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
         <v>47</v>
@@ -2692,13 +2692,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
         <v>47</v>
@@ -2715,13 +2715,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>47</v>
@@ -2738,13 +2738,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
         <v>47</v>
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3497,13 +3497,13 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>127</v>
@@ -3520,13 +3520,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>127</v>
@@ -3543,13 +3543,13 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
         <v>127</v>
@@ -3566,13 +3566,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
         <v>127</v>
@@ -3589,13 +3589,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -3612,13 +3612,13 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G69" t="s">
         <v>127</v>
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4233,13 +4233,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G96" t="s">
         <v>227</v>
@@ -4256,13 +4256,13 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G97" t="s">
         <v>227</v>
@@ -4279,13 +4279,13 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G98" t="s">
         <v>227</v>
@@ -4302,13 +4302,13 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G99" t="s">
         <v>227</v>
@@ -4325,13 +4325,13 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G100" t="s">
         <v>227</v>
@@ -4348,13 +4348,13 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G101" t="s">
         <v>227</v>
@@ -4371,13 +4371,13 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G102" t="s">
         <v>227</v>
@@ -4394,13 +4394,13 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G103" t="s">
         <v>227</v>
@@ -4417,13 +4417,13 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s">
         <v>227</v>
@@ -4440,13 +4440,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G105" t="s">
         <v>227</v>
@@ -4463,13 +4463,13 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G106" t="s">
         <v>227</v>
@@ -4486,13 +4486,13 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G107" t="s">
         <v>227</v>
@@ -4509,13 +4509,13 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
         <v>227</v>
@@ -4532,13 +4532,13 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G109" t="s">
         <v>227</v>
@@ -4555,13 +4555,13 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="G110" t="s">
         <v>227</v>
@@ -4578,13 +4578,13 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F111" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
         <v>227</v>
@@ -4601,13 +4601,13 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F112" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="G112" t="s">
         <v>227</v>
@@ -4624,13 +4624,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G113" t="s">
         <v>227</v>
@@ -4647,13 +4647,13 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F114" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G114" t="s">
         <v>227</v>
@@ -4670,13 +4670,13 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F115" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G115" t="s">
         <v>227</v>
@@ -4693,13 +4693,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F116" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G116" t="s">
         <v>227</v>
@@ -4716,13 +4716,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G117" t="s">
         <v>227</v>
@@ -4739,13 +4739,13 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G118" t="s">
         <v>227</v>
@@ -4762,13 +4762,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E119" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F119" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>293</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>293</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>293</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>293</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>293</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>293</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>307</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>307</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>307</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>307</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5429,13 +5429,13 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E148" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F148" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G148" t="s">
         <v>320</v>
@@ -5452,13 +5452,13 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F149" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G149" t="s">
         <v>320</v>
@@ -5475,13 +5475,13 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E150" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F150" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G150" t="s">
         <v>320</v>
@@ -5498,13 +5498,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F151" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G151" t="s">
         <v>320</v>
@@ -5521,13 +5521,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E152" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F152" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G152" t="s">
         <v>320</v>
@@ -5544,13 +5544,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F153" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="G153" t="s">
         <v>320</v>
@@ -5567,13 +5567,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E154" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F154" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G154" t="s">
         <v>320</v>
@@ -5590,13 +5590,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E155" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F155" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G155" t="s">
         <v>320</v>
@@ -5613,13 +5613,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F156" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G156" t="s">
         <v>320</v>
@@ -5636,13 +5636,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G157" t="s">
         <v>320</v>
@@ -5659,13 +5659,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E158" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F158" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="G158" t="s">
         <v>320</v>
@@ -6119,13 +6119,13 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E178" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F178" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G178" t="s">
         <v>386</v>
@@ -6142,13 +6142,13 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E179" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F179" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G179" t="s">
         <v>386</v>
@@ -6165,13 +6165,13 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E180" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F180" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G180" t="s">
         <v>386</v>
@@ -6188,13 +6188,13 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E181" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F181" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G181" t="s">
         <v>386</v>
@@ -6211,13 +6211,13 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E182" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F182" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G182" t="s">
         <v>386</v>
@@ -6234,13 +6234,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E183" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F183" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G183" t="s">
         <v>386</v>
@@ -6257,13 +6257,13 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E184" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F184" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G184" t="s">
         <v>386</v>
@@ -6280,13 +6280,13 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E185" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F185" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G185" t="s">
         <v>386</v>
@@ -6303,13 +6303,13 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E186" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F186" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G186" t="s">
         <v>386</v>
@@ -6326,13 +6326,13 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E187" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F187" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="G187" t="s">
         <v>386</v>
@@ -6349,13 +6349,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F188" t="s">
-        <v>448</v>
+        <v>385</v>
       </c>
       <c r="G188" t="s">
         <v>386</v>
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>451</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>451</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>451</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>451</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>451</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>451</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>465</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>469</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>469</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>469</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>469</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>469</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>469</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>483</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>483</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>483</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>483</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>483</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>483</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>483</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>483</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>483</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>483</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>505</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>509</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>513</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>513</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>519</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>519</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>519</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>519</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>519</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>519</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>519</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>535</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>535</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>535</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>543</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>547</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>551</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>555</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>559</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>559</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>111</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>121</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>151</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>231</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,13 +1168,13 @@
     <t>321</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>320</t>
   </si>
   <si>
     <t>32120</t>
@@ -2166,13 +2166,13 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,13 +2189,13 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,13 +2212,13 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,13 +2235,13 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,13 +2258,13 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,13 +2281,13 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,13 +2304,13 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,13 +2327,13 @@
         <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,13 +2442,13 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,13 +2465,13 @@
         <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,13 +2488,13 @@
         <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,13 +2511,13 @@
         <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,13 +2534,13 @@
         <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,13 +2557,13 @@
         <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,13 +2580,13 @@
         <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,13 +2603,13 @@
         <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
       </c>
       <c r="G25" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,13 +2626,13 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
         <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,13 +2649,13 @@
         <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,13 +2672,13 @@
         <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,13 +2695,13 @@
         <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,13 +2718,13 @@
         <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,13 +2741,13 @@
         <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s">
         <v>89</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
         <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
         <v>101</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
         <v>101</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
         <v>101</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,13 +3500,13 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
         <v>126</v>
       </c>
       <c r="G64" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,13 +3523,13 @@
         <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
         <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,13 +3546,13 @@
         <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
         <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,13 +3569,13 @@
         <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
         <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,13 +3592,13 @@
         <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
         <v>126</v>
       </c>
       <c r="G68" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,13 +3615,13 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
         <v>126</v>
       </c>
       <c r="G69" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" t="s">
         <v>175</v>
-      </c>
-      <c r="G70" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
         <v>175</v>
-      </c>
-      <c r="G71" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>175</v>
-      </c>
-      <c r="G73" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>174</v>
+      </c>
+      <c r="G74" t="s">
         <v>175</v>
-      </c>
-      <c r="G74" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>174</v>
+      </c>
+      <c r="G75" t="s">
         <v>175</v>
-      </c>
-      <c r="G75" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
         <v>175</v>
-      </c>
-      <c r="G76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G77" t="s">
         <v>175</v>
-      </c>
-      <c r="G77" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>174</v>
+      </c>
+      <c r="G78" t="s">
         <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79" t="s">
         <v>175</v>
-      </c>
-      <c r="G79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>174</v>
+      </c>
+      <c r="G80" t="s">
         <v>175</v>
-      </c>
-      <c r="G80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>198</v>
+      </c>
+      <c r="G81" t="s">
         <v>199</v>
-      </c>
-      <c r="G81" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>198</v>
+      </c>
+      <c r="G82" t="s">
         <v>199</v>
-      </c>
-      <c r="G82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>198</v>
+      </c>
+      <c r="G83" t="s">
         <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" t="s">
         <v>199</v>
-      </c>
-      <c r="G85" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" t="s">
         <v>199</v>
-      </c>
-      <c r="G86" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>198</v>
+      </c>
+      <c r="G87" t="s">
         <v>199</v>
-      </c>
-      <c r="G87" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>214</v>
+      </c>
+      <c r="G88" t="s">
         <v>215</v>
-      </c>
-      <c r="G88" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" t="s">
         <v>215</v>
-      </c>
-      <c r="G89" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>214</v>
+      </c>
+      <c r="G90" t="s">
         <v>215</v>
-      </c>
-      <c r="G90" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>214</v>
+      </c>
+      <c r="G91" t="s">
         <v>215</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,13 +4236,13 @@
         <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
         <v>226</v>
       </c>
       <c r="G96" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,13 +4259,13 @@
         <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
         <v>226</v>
       </c>
       <c r="G97" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,13 +4282,13 @@
         <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F98" t="s">
         <v>226</v>
       </c>
       <c r="G98" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,13 +4305,13 @@
         <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>226</v>
       </c>
       <c r="G99" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,13 +4328,13 @@
         <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
         <v>226</v>
       </c>
       <c r="G100" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,13 +4351,13 @@
         <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>226</v>
       </c>
       <c r="G101" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,13 +4374,13 @@
         <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F102" t="s">
         <v>226</v>
       </c>
       <c r="G102" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,13 +4397,13 @@
         <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F103" t="s">
         <v>226</v>
       </c>
       <c r="G103" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,13 +4420,13 @@
         <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>226</v>
       </c>
       <c r="G104" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,13 +4443,13 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>226</v>
       </c>
       <c r="G105" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,13 +4466,13 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>226</v>
       </c>
       <c r="G106" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,13 +4489,13 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F107" t="s">
         <v>226</v>
       </c>
       <c r="G107" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,13 +4512,13 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
         <v>226</v>
       </c>
       <c r="G108" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,13 +4535,13 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F109" t="s">
         <v>226</v>
       </c>
       <c r="G109" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,13 +4558,13 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>226</v>
       </c>
       <c r="G110" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,13 +4581,13 @@
         <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
         <v>226</v>
       </c>
       <c r="G111" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,13 +4604,13 @@
         <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
         <v>226</v>
       </c>
       <c r="G112" t="s">
-        <v>227</v>
+        <v>274</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,13 +4627,13 @@
         <v>277</v>
       </c>
       <c r="E113" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F113" t="s">
         <v>226</v>
       </c>
       <c r="G113" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,13 +4650,13 @@
         <v>277</v>
       </c>
       <c r="E114" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F114" t="s">
         <v>226</v>
       </c>
       <c r="G114" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,13 +4673,13 @@
         <v>277</v>
       </c>
       <c r="E115" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F115" t="s">
         <v>226</v>
       </c>
       <c r="G115" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,13 +4696,13 @@
         <v>277</v>
       </c>
       <c r="E116" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
         <v>226</v>
       </c>
       <c r="G116" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,13 +4719,13 @@
         <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
         <v>226</v>
       </c>
       <c r="G117" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,13 +4742,13 @@
         <v>277</v>
       </c>
       <c r="E118" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F118" t="s">
         <v>226</v>
       </c>
       <c r="G118" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,13 +4765,13 @@
         <v>277</v>
       </c>
       <c r="E119" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F119" t="s">
         <v>226</v>
       </c>
       <c r="G119" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>293</v>
+      </c>
+      <c r="G120" t="s">
         <v>294</v>
-      </c>
-      <c r="G120" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>293</v>
+      </c>
+      <c r="G121" t="s">
         <v>294</v>
-      </c>
-      <c r="G121" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>293</v>
+      </c>
+      <c r="G122" t="s">
         <v>294</v>
-      </c>
-      <c r="G122" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>293</v>
+      </c>
+      <c r="G123" t="s">
         <v>294</v>
-      </c>
-      <c r="G123" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>293</v>
+      </c>
+      <c r="G124" t="s">
         <v>294</v>
-      </c>
-      <c r="G124" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>293</v>
+      </c>
+      <c r="G125" t="s">
         <v>294</v>
-      </c>
-      <c r="G125" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>307</v>
+      </c>
+      <c r="G126" t="s">
         <v>308</v>
-      </c>
-      <c r="G126" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>307</v>
+      </c>
+      <c r="G127" t="s">
         <v>308</v>
-      </c>
-      <c r="G127" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>307</v>
+      </c>
+      <c r="G128" t="s">
         <v>308</v>
-      </c>
-      <c r="G128" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>307</v>
+      </c>
+      <c r="G129" t="s">
         <v>308</v>
-      </c>
-      <c r="G129" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,13 +5432,13 @@
         <v>357</v>
       </c>
       <c r="E148" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="F148" t="s">
         <v>319</v>
       </c>
       <c r="G148" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,13 +5455,13 @@
         <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="F149" t="s">
         <v>319</v>
       </c>
       <c r="G149" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,13 +5478,13 @@
         <v>357</v>
       </c>
       <c r="E150" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="F150" t="s">
         <v>319</v>
       </c>
       <c r="G150" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,13 +5501,13 @@
         <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="F151" t="s">
         <v>319</v>
       </c>
       <c r="G151" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,13 +5524,13 @@
         <v>357</v>
       </c>
       <c r="E152" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="F152" t="s">
         <v>319</v>
       </c>
       <c r="G152" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,13 +5547,13 @@
         <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="F153" t="s">
         <v>319</v>
       </c>
       <c r="G153" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,13 +5570,13 @@
         <v>371</v>
       </c>
       <c r="E154" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="F154" t="s">
         <v>319</v>
       </c>
       <c r="G154" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,13 +5593,13 @@
         <v>371</v>
       </c>
       <c r="E155" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="F155" t="s">
         <v>319</v>
       </c>
       <c r="G155" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,13 +5616,13 @@
         <v>371</v>
       </c>
       <c r="E156" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="F156" t="s">
         <v>319</v>
       </c>
       <c r="G156" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,13 +5639,13 @@
         <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="F157" t="s">
         <v>319</v>
       </c>
       <c r="G157" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,13 +5662,13 @@
         <v>371</v>
       </c>
       <c r="E158" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="F158" t="s">
         <v>319</v>
       </c>
       <c r="G158" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,13 +6122,13 @@
         <v>425</v>
       </c>
       <c r="E178" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F178" t="s">
         <v>385</v>
       </c>
       <c r="G178" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,13 +6145,13 @@
         <v>425</v>
       </c>
       <c r="E179" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F179" t="s">
         <v>385</v>
       </c>
       <c r="G179" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,13 +6168,13 @@
         <v>425</v>
       </c>
       <c r="E180" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F180" t="s">
         <v>385</v>
       </c>
       <c r="G180" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,13 +6191,13 @@
         <v>425</v>
       </c>
       <c r="E181" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F181" t="s">
         <v>385</v>
       </c>
       <c r="G181" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,13 +6214,13 @@
         <v>425</v>
       </c>
       <c r="E182" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F182" t="s">
         <v>385</v>
       </c>
       <c r="G182" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,13 +6237,13 @@
         <v>425</v>
       </c>
       <c r="E183" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F183" t="s">
         <v>385</v>
       </c>
       <c r="G183" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,13 +6260,13 @@
         <v>425</v>
       </c>
       <c r="E184" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F184" t="s">
         <v>385</v>
       </c>
       <c r="G184" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,13 +6283,13 @@
         <v>425</v>
       </c>
       <c r="E185" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F185" t="s">
         <v>385</v>
       </c>
       <c r="G185" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,13 +6306,13 @@
         <v>425</v>
       </c>
       <c r="E186" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F186" t="s">
         <v>385</v>
       </c>
       <c r="G186" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,13 +6329,13 @@
         <v>425</v>
       </c>
       <c r="E187" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F187" t="s">
         <v>385</v>
       </c>
       <c r="G187" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,13 +6352,13 @@
         <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>448</v>
+        <v>384</v>
       </c>
       <c r="F188" t="s">
         <v>385</v>
       </c>
       <c r="G188" t="s">
-        <v>386</v>
+        <v>448</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>451</v>
+      </c>
+      <c r="G189" t="s">
         <v>452</v>
-      </c>
-      <c r="G189" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>451</v>
+      </c>
+      <c r="G190" t="s">
         <v>452</v>
-      </c>
-      <c r="G190" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>451</v>
+      </c>
+      <c r="G191" t="s">
         <v>452</v>
-      </c>
-      <c r="G191" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>451</v>
+      </c>
+      <c r="G192" t="s">
         <v>452</v>
-      </c>
-      <c r="G192" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>451</v>
+      </c>
+      <c r="G193" t="s">
         <v>452</v>
-      </c>
-      <c r="G193" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>451</v>
+      </c>
+      <c r="G194" t="s">
         <v>452</v>
-      </c>
-      <c r="G194" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>465</v>
+      </c>
+      <c r="G195" t="s">
         <v>466</v>
-      </c>
-      <c r="G195" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>469</v>
+      </c>
+      <c r="G196" t="s">
         <v>470</v>
-      </c>
-      <c r="G196" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>469</v>
+      </c>
+      <c r="G197" t="s">
         <v>470</v>
-      </c>
-      <c r="G197" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>469</v>
+      </c>
+      <c r="G198" t="s">
         <v>470</v>
-      </c>
-      <c r="G198" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>469</v>
+      </c>
+      <c r="G199" t="s">
         <v>470</v>
-      </c>
-      <c r="G199" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>469</v>
+      </c>
+      <c r="G200" t="s">
         <v>470</v>
-      </c>
-      <c r="G200" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>469</v>
+      </c>
+      <c r="G201" t="s">
         <v>470</v>
-      </c>
-      <c r="G201" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>483</v>
+      </c>
+      <c r="G202" t="s">
         <v>484</v>
-      </c>
-      <c r="G202" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>483</v>
+      </c>
+      <c r="G203" t="s">
         <v>484</v>
-      </c>
-      <c r="G203" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>483</v>
+      </c>
+      <c r="G204" t="s">
         <v>484</v>
-      </c>
-      <c r="G204" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>483</v>
+      </c>
+      <c r="G205" t="s">
         <v>484</v>
-      </c>
-      <c r="G205" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>483</v>
+      </c>
+      <c r="G206" t="s">
         <v>484</v>
-      </c>
-      <c r="G206" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>483</v>
+      </c>
+      <c r="G207" t="s">
         <v>484</v>
-      </c>
-      <c r="G207" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>483</v>
+      </c>
+      <c r="G208" t="s">
         <v>484</v>
-      </c>
-      <c r="G208" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>483</v>
+      </c>
+      <c r="G209" t="s">
         <v>484</v>
-      </c>
-      <c r="G209" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>483</v>
+      </c>
+      <c r="G210" t="s">
         <v>484</v>
-      </c>
-      <c r="G210" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>483</v>
+      </c>
+      <c r="G211" t="s">
         <v>484</v>
-      </c>
-      <c r="G211" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>505</v>
+      </c>
+      <c r="G212" t="s">
         <v>506</v>
-      </c>
-      <c r="G212" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>509</v>
+      </c>
+      <c r="G213" t="s">
         <v>510</v>
-      </c>
-      <c r="G213" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>513</v>
+      </c>
+      <c r="G214" t="s">
         <v>514</v>
-      </c>
-      <c r="G214" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>513</v>
+      </c>
+      <c r="G215" t="s">
         <v>514</v>
-      </c>
-      <c r="G215" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>519</v>
+      </c>
+      <c r="G216" t="s">
         <v>520</v>
-      </c>
-      <c r="G216" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>519</v>
+      </c>
+      <c r="G217" t="s">
         <v>520</v>
-      </c>
-      <c r="G217" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>519</v>
+      </c>
+      <c r="G218" t="s">
         <v>520</v>
-      </c>
-      <c r="G218" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>519</v>
+      </c>
+      <c r="G219" t="s">
         <v>520</v>
-      </c>
-      <c r="G219" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>519</v>
+      </c>
+      <c r="G220" t="s">
         <v>520</v>
-      </c>
-      <c r="G220" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>519</v>
+      </c>
+      <c r="G221" t="s">
         <v>520</v>
-      </c>
-      <c r="G221" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>519</v>
+      </c>
+      <c r="G222" t="s">
         <v>520</v>
-      </c>
-      <c r="G222" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>535</v>
+      </c>
+      <c r="G223" t="s">
         <v>536</v>
-      </c>
-      <c r="G223" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>535</v>
+      </c>
+      <c r="G224" t="s">
         <v>536</v>
-      </c>
-      <c r="G224" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>535</v>
+      </c>
+      <c r="G225" t="s">
         <v>536</v>
-      </c>
-      <c r="G225" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>543</v>
+      </c>
+      <c r="G226" t="s">
         <v>544</v>
-      </c>
-      <c r="G226" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>547</v>
+      </c>
+      <c r="G227" t="s">
         <v>548</v>
-      </c>
-      <c r="G227" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>551</v>
+      </c>
+      <c r="G228" t="s">
         <v>552</v>
-      </c>
-      <c r="G228" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>555</v>
+      </c>
+      <c r="G229" t="s">
         <v>556</v>
-      </c>
-      <c r="G229" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>559</v>
+      </c>
+      <c r="G230" t="s">
         <v>560</v>
-      </c>
-      <c r="G230" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>559</v>
+      </c>
+      <c r="G231" t="s">
         <v>560</v>
-      </c>
-      <c r="G231" t="s">
-        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:group-name</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>Education</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -154,12 +154,12 @@
     <t>Santé</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>Energie</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1171,10 +1171,10 @@
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
   </si>
   <si>
     <t>32120</t>
@@ -2169,10 +2169,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2192,10 +2192,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2215,10 +2215,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2238,10 +2238,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2261,10 +2261,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2284,10 +2284,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2307,10 +2307,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2330,10 +2330,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2445,10 +2445,10 @@
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2468,10 +2468,10 @@
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2491,10 +2491,10 @@
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2514,10 +2514,10 @@
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2537,10 +2537,10 @@
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2560,10 +2560,10 @@
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2583,10 +2583,10 @@
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2606,10 +2606,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2629,10 +2629,10 @@
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2652,10 +2652,10 @@
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2675,10 +2675,10 @@
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2698,10 +2698,10 @@
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2721,10 +2721,10 @@
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2744,10 +2744,10 @@
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3503,10 +3503,10 @@
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3526,10 +3526,10 @@
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3549,10 +3549,10 @@
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3572,10 +3572,10 @@
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3595,10 +3595,10 @@
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3618,10 +3618,10 @@
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4239,10 +4239,10 @@
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4262,10 +4262,10 @@
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4285,10 +4285,10 @@
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4308,10 +4308,10 @@
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4331,10 +4331,10 @@
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4354,10 +4354,10 @@
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4377,10 +4377,10 @@
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4400,10 +4400,10 @@
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4423,10 +4423,10 @@
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4446,10 +4446,10 @@
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4469,10 +4469,10 @@
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4492,10 +4492,10 @@
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4515,10 +4515,10 @@
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4538,10 +4538,10 @@
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4561,10 +4561,10 @@
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4584,10 +4584,10 @@
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="G111" t="s">
-        <v>269</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4607,10 +4607,10 @@
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4630,10 +4630,10 @@
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4653,10 +4653,10 @@
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4676,10 +4676,10 @@
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4699,10 +4699,10 @@
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G116" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4722,10 +4722,10 @@
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4745,10 +4745,10 @@
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G118" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4768,10 +4768,10 @@
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G119" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>293</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>293</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>293</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>293</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>293</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>293</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>307</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>307</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>307</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>307</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5435,10 +5435,10 @@
         <v>318</v>
       </c>
       <c r="F148" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5458,10 +5458,10 @@
         <v>318</v>
       </c>
       <c r="F149" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5481,10 +5481,10 @@
         <v>318</v>
       </c>
       <c r="F150" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5504,10 +5504,10 @@
         <v>318</v>
       </c>
       <c r="F151" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5527,10 +5527,10 @@
         <v>318</v>
       </c>
       <c r="F152" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5550,10 +5550,10 @@
         <v>318</v>
       </c>
       <c r="F153" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5573,10 +5573,10 @@
         <v>318</v>
       </c>
       <c r="F154" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5596,10 +5596,10 @@
         <v>318</v>
       </c>
       <c r="F155" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5619,10 +5619,10 @@
         <v>318</v>
       </c>
       <c r="F156" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5642,10 +5642,10 @@
         <v>318</v>
       </c>
       <c r="F157" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5665,10 +5665,10 @@
         <v>318</v>
       </c>
       <c r="F158" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6125,10 +6125,10 @@
         <v>384</v>
       </c>
       <c r="F178" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6148,10 +6148,10 @@
         <v>384</v>
       </c>
       <c r="F179" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6171,10 +6171,10 @@
         <v>384</v>
       </c>
       <c r="F180" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6194,10 +6194,10 @@
         <v>384</v>
       </c>
       <c r="F181" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6217,10 +6217,10 @@
         <v>384</v>
       </c>
       <c r="F182" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6240,10 +6240,10 @@
         <v>384</v>
       </c>
       <c r="F183" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6263,10 +6263,10 @@
         <v>384</v>
       </c>
       <c r="F184" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6286,10 +6286,10 @@
         <v>384</v>
       </c>
       <c r="F185" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6309,10 +6309,10 @@
         <v>384</v>
       </c>
       <c r="F186" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6332,10 +6332,10 @@
         <v>384</v>
       </c>
       <c r="F187" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6355,10 +6355,10 @@
         <v>384</v>
       </c>
       <c r="F188" t="s">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="G188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>451</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>451</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>451</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>451</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>451</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>451</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>465</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>469</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>469</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>469</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>469</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>469</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>469</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>483</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>483</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>483</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>483</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>483</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>483</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>483</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>483</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>483</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>483</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>505</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>509</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>513</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>513</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>519</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>519</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>519</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>519</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>519</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>519</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>519</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>535</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>535</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>535</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>543</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>547</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>551</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>555</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>559</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>559</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>Education de Base</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Education de Base</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>Education Secondaire</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Education Secondaire</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>Education Post Secondaire</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Education Post Secondaire</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>Santé de Base</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Santé de Base</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>Maladies non-transmissibles (MNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Maladies non-transmissibles (MNT)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>Conflits, Paix et Sécurité</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflits, Paix et Sécurité</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>Production d'électricité, sources renouvelables</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Production d'électricité, sources renouvelables</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>Production d'électricité, sources non renouvelables</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Production d'électricité, sources non renouvelables</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>Centrales nucléaires</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrales nucléaires</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>Distribution de l'énergie</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribution de l'énergie</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>Sylviculture</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Sylviculture</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>Pêche</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pêche</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Extractives</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Industries Extractives</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,10 +1357,10 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>Construction</t>
   </si>
   <si>
     <t>33110</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
       </c>
-      <c r="E18" t="s">
-        <v>45</v>
-      </c>
       <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
       </c>
-      <c r="E19" t="s">
-        <v>45</v>
-      </c>
       <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="E20" t="s">
-        <v>45</v>
-      </c>
       <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
       </c>
-      <c r="E21" t="s">
-        <v>45</v>
-      </c>
       <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
       </c>
-      <c r="E22" t="s">
-        <v>45</v>
-      </c>
       <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
       </c>
-      <c r="E23" t="s">
-        <v>45</v>
-      </c>
       <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
       </c>
-      <c r="E24" t="s">
-        <v>45</v>
-      </c>
       <c r="F24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
       </c>
-      <c r="E25" t="s">
-        <v>45</v>
-      </c>
       <c r="F25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
       </c>
-      <c r="E26" t="s">
-        <v>45</v>
-      </c>
       <c r="F26" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
       </c>
-      <c r="E27" t="s">
-        <v>45</v>
-      </c>
       <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
       </c>
-      <c r="E28" t="s">
-        <v>45</v>
-      </c>
       <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
       </c>
-      <c r="E29" t="s">
-        <v>45</v>
-      </c>
       <c r="F29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
       </c>
-      <c r="E30" t="s">
-        <v>45</v>
-      </c>
       <c r="F30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
       </c>
-      <c r="E31" t="s">
-        <v>45</v>
-      </c>
       <c r="F31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
       </c>
-      <c r="E64" t="s">
-        <v>125</v>
-      </c>
       <c r="F64" t="s">
+        <v>126</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
       </c>
-      <c r="E65" t="s">
-        <v>125</v>
-      </c>
       <c r="F65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
       </c>
-      <c r="E66" t="s">
-        <v>125</v>
-      </c>
       <c r="F66" t="s">
+        <v>126</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
       </c>
-      <c r="E67" t="s">
-        <v>125</v>
-      </c>
       <c r="F67" t="s">
+        <v>126</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
       </c>
-      <c r="E68" t="s">
-        <v>125</v>
-      </c>
       <c r="F68" t="s">
+        <v>126</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
       </c>
-      <c r="E69" t="s">
-        <v>125</v>
-      </c>
       <c r="F69" t="s">
+        <v>126</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
       </c>
-      <c r="E96" t="s">
-        <v>225</v>
-      </c>
       <c r="F96" t="s">
+        <v>226</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
       </c>
-      <c r="E97" t="s">
-        <v>225</v>
-      </c>
       <c r="F97" t="s">
+        <v>226</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
       </c>
-      <c r="E98" t="s">
-        <v>225</v>
-      </c>
       <c r="F98" t="s">
+        <v>226</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
       </c>
-      <c r="E99" t="s">
-        <v>225</v>
-      </c>
       <c r="F99" t="s">
+        <v>226</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
       </c>
-      <c r="E100" t="s">
-        <v>225</v>
-      </c>
       <c r="F100" t="s">
+        <v>226</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
       </c>
-      <c r="E101" t="s">
-        <v>225</v>
-      </c>
       <c r="F101" t="s">
+        <v>226</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
       </c>
-      <c r="E102" t="s">
-        <v>225</v>
-      </c>
       <c r="F102" t="s">
+        <v>226</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
       </c>
-      <c r="E103" t="s">
-        <v>225</v>
-      </c>
       <c r="F103" t="s">
+        <v>226</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
       </c>
-      <c r="E104" t="s">
-        <v>225</v>
-      </c>
       <c r="F104" t="s">
+        <v>226</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
       </c>
-      <c r="E105" t="s">
-        <v>225</v>
-      </c>
       <c r="F105" t="s">
+        <v>226</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
       </c>
-      <c r="E106" t="s">
-        <v>225</v>
-      </c>
       <c r="F106" t="s">
+        <v>226</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
       </c>
-      <c r="E107" t="s">
-        <v>225</v>
-      </c>
       <c r="F107" t="s">
+        <v>226</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
       </c>
-      <c r="E108" t="s">
-        <v>225</v>
-      </c>
       <c r="F108" t="s">
+        <v>226</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
       </c>
-      <c r="E109" t="s">
-        <v>225</v>
-      </c>
       <c r="F109" t="s">
+        <v>226</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
       </c>
-      <c r="E110" t="s">
-        <v>225</v>
-      </c>
       <c r="F110" t="s">
+        <v>226</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
+        <v>269</v>
+      </c>
+      <c r="F111" t="s">
+        <v>226</v>
+      </c>
+      <c r="G111" t="s">
         <v>270</v>
-      </c>
-      <c r="E111" t="s">
-        <v>225</v>
-      </c>
-      <c r="F111" t="s">
-        <v>269</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>273</v>
       </c>
-      <c r="E112" t="s">
-        <v>225</v>
-      </c>
       <c r="F112" t="s">
+        <v>226</v>
+      </c>
+      <c r="G112" t="s">
         <v>274</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>277</v>
       </c>
-      <c r="E113" t="s">
-        <v>225</v>
-      </c>
       <c r="F113" t="s">
+        <v>226</v>
+      </c>
+      <c r="G113" t="s">
         <v>278</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>277</v>
       </c>
-      <c r="E114" t="s">
-        <v>225</v>
-      </c>
       <c r="F114" t="s">
+        <v>226</v>
+      </c>
+      <c r="G114" t="s">
         <v>278</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>277</v>
       </c>
-      <c r="E115" t="s">
-        <v>225</v>
-      </c>
       <c r="F115" t="s">
+        <v>226</v>
+      </c>
+      <c r="G115" t="s">
         <v>278</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>277</v>
       </c>
-      <c r="E116" t="s">
-        <v>225</v>
-      </c>
       <c r="F116" t="s">
+        <v>226</v>
+      </c>
+      <c r="G116" t="s">
         <v>278</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>277</v>
       </c>
-      <c r="E117" t="s">
-        <v>225</v>
-      </c>
       <c r="F117" t="s">
+        <v>226</v>
+      </c>
+      <c r="G117" t="s">
         <v>278</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>277</v>
       </c>
-      <c r="E118" t="s">
-        <v>225</v>
-      </c>
       <c r="F118" t="s">
+        <v>226</v>
+      </c>
+      <c r="G118" t="s">
         <v>278</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>277</v>
       </c>
-      <c r="E119" t="s">
-        <v>225</v>
-      </c>
       <c r="F119" t="s">
+        <v>226</v>
+      </c>
+      <c r="G119" t="s">
         <v>278</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>317</v>
+      </c>
+      <c r="E148" t="s">
         <v>357</v>
       </c>
-      <c r="E148" t="s">
-        <v>318</v>
-      </c>
       <c r="F148" t="s">
+        <v>319</v>
+      </c>
+      <c r="G148" t="s">
         <v>358</v>
-      </c>
-      <c r="G148" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>317</v>
+      </c>
+      <c r="E149" t="s">
         <v>357</v>
       </c>
-      <c r="E149" t="s">
-        <v>318</v>
-      </c>
       <c r="F149" t="s">
+        <v>319</v>
+      </c>
+      <c r="G149" t="s">
         <v>358</v>
-      </c>
-      <c r="G149" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>317</v>
+      </c>
+      <c r="E150" t="s">
         <v>357</v>
       </c>
-      <c r="E150" t="s">
-        <v>318</v>
-      </c>
       <c r="F150" t="s">
+        <v>319</v>
+      </c>
+      <c r="G150" t="s">
         <v>358</v>
-      </c>
-      <c r="G150" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>317</v>
+      </c>
+      <c r="E151" t="s">
         <v>357</v>
       </c>
-      <c r="E151" t="s">
-        <v>318</v>
-      </c>
       <c r="F151" t="s">
+        <v>319</v>
+      </c>
+      <c r="G151" t="s">
         <v>358</v>
-      </c>
-      <c r="G151" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>317</v>
+      </c>
+      <c r="E152" t="s">
         <v>357</v>
       </c>
-      <c r="E152" t="s">
-        <v>318</v>
-      </c>
       <c r="F152" t="s">
+        <v>319</v>
+      </c>
+      <c r="G152" t="s">
         <v>358</v>
-      </c>
-      <c r="G152" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>317</v>
+      </c>
+      <c r="E153" t="s">
         <v>357</v>
       </c>
-      <c r="E153" t="s">
-        <v>318</v>
-      </c>
       <c r="F153" t="s">
+        <v>319</v>
+      </c>
+      <c r="G153" t="s">
         <v>358</v>
-      </c>
-      <c r="G153" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>317</v>
+      </c>
+      <c r="E154" t="s">
         <v>371</v>
       </c>
-      <c r="E154" t="s">
-        <v>318</v>
-      </c>
       <c r="F154" t="s">
+        <v>319</v>
+      </c>
+      <c r="G154" t="s">
         <v>372</v>
-      </c>
-      <c r="G154" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>317</v>
+      </c>
+      <c r="E155" t="s">
         <v>371</v>
       </c>
-      <c r="E155" t="s">
-        <v>318</v>
-      </c>
       <c r="F155" t="s">
+        <v>319</v>
+      </c>
+      <c r="G155" t="s">
         <v>372</v>
-      </c>
-      <c r="G155" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>317</v>
+      </c>
+      <c r="E156" t="s">
         <v>371</v>
       </c>
-      <c r="E156" t="s">
-        <v>318</v>
-      </c>
       <c r="F156" t="s">
+        <v>319</v>
+      </c>
+      <c r="G156" t="s">
         <v>372</v>
-      </c>
-      <c r="G156" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>317</v>
+      </c>
+      <c r="E157" t="s">
         <v>371</v>
       </c>
-      <c r="E157" t="s">
-        <v>318</v>
-      </c>
       <c r="F157" t="s">
+        <v>319</v>
+      </c>
+      <c r="G157" t="s">
         <v>372</v>
-      </c>
-      <c r="G157" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>317</v>
+      </c>
+      <c r="E158" t="s">
         <v>371</v>
       </c>
-      <c r="E158" t="s">
-        <v>318</v>
-      </c>
       <c r="F158" t="s">
+        <v>319</v>
+      </c>
+      <c r="G158" t="s">
         <v>372</v>
-      </c>
-      <c r="G158" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>383</v>
+      </c>
+      <c r="E178" t="s">
         <v>425</v>
       </c>
-      <c r="E178" t="s">
-        <v>384</v>
-      </c>
       <c r="F178" t="s">
+        <v>385</v>
+      </c>
+      <c r="G178" t="s">
         <v>426</v>
-      </c>
-      <c r="G178" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>383</v>
+      </c>
+      <c r="E179" t="s">
         <v>425</v>
       </c>
-      <c r="E179" t="s">
-        <v>384</v>
-      </c>
       <c r="F179" t="s">
+        <v>385</v>
+      </c>
+      <c r="G179" t="s">
         <v>426</v>
-      </c>
-      <c r="G179" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>383</v>
+      </c>
+      <c r="E180" t="s">
         <v>425</v>
       </c>
-      <c r="E180" t="s">
-        <v>384</v>
-      </c>
       <c r="F180" t="s">
+        <v>385</v>
+      </c>
+      <c r="G180" t="s">
         <v>426</v>
-      </c>
-      <c r="G180" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>383</v>
+      </c>
+      <c r="E181" t="s">
         <v>425</v>
       </c>
-      <c r="E181" t="s">
-        <v>384</v>
-      </c>
       <c r="F181" t="s">
+        <v>385</v>
+      </c>
+      <c r="G181" t="s">
         <v>426</v>
-      </c>
-      <c r="G181" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>383</v>
+      </c>
+      <c r="E182" t="s">
         <v>425</v>
       </c>
-      <c r="E182" t="s">
-        <v>384</v>
-      </c>
       <c r="F182" t="s">
+        <v>385</v>
+      </c>
+      <c r="G182" t="s">
         <v>426</v>
-      </c>
-      <c r="G182" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6234,16 +6234,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>383</v>
+      </c>
+      <c r="E183" t="s">
         <v>425</v>
       </c>
-      <c r="E183" t="s">
-        <v>384</v>
-      </c>
       <c r="F183" t="s">
+        <v>385</v>
+      </c>
+      <c r="G183" t="s">
         <v>426</v>
-      </c>
-      <c r="G183" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6257,16 +6257,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>383</v>
+      </c>
+      <c r="E184" t="s">
         <v>425</v>
       </c>
-      <c r="E184" t="s">
-        <v>384</v>
-      </c>
       <c r="F184" t="s">
+        <v>385</v>
+      </c>
+      <c r="G184" t="s">
         <v>426</v>
-      </c>
-      <c r="G184" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6280,16 +6280,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>383</v>
+      </c>
+      <c r="E185" t="s">
         <v>425</v>
       </c>
-      <c r="E185" t="s">
-        <v>384</v>
-      </c>
       <c r="F185" t="s">
+        <v>385</v>
+      </c>
+      <c r="G185" t="s">
         <v>426</v>
-      </c>
-      <c r="G185" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6303,16 +6303,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>383</v>
+      </c>
+      <c r="E186" t="s">
         <v>425</v>
       </c>
-      <c r="E186" t="s">
-        <v>384</v>
-      </c>
       <c r="F186" t="s">
+        <v>385</v>
+      </c>
+      <c r="G186" t="s">
         <v>426</v>
-      </c>
-      <c r="G186" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6326,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>383</v>
+      </c>
+      <c r="E187" t="s">
         <v>425</v>
       </c>
-      <c r="E187" t="s">
-        <v>384</v>
-      </c>
       <c r="F187" t="s">
+        <v>385</v>
+      </c>
+      <c r="G187" t="s">
         <v>426</v>
-      </c>
-      <c r="G187" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6349,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>383</v>
+      </c>
+      <c r="E188" t="s">
         <v>447</v>
       </c>
-      <c r="E188" t="s">
-        <v>384</v>
-      </c>
       <c r="F188" t="s">
+        <v>385</v>
+      </c>
+      <c r="G188" t="s">
         <v>448</v>
-      </c>
-      <c r="G188" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,6 +25,9 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
@@ -34,9 +37,6 @@
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,6 +46,9 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
@@ -55,9 +58,6 @@
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Education de Base</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Education Secondaire</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Education Post Secondaire</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,6 +148,9 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
@@ -157,9 +160,6 @@
     <t>Santé</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Santé de Base</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Maladies non-transmissibles (MNT)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -388,6 +388,9 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
@@ -397,9 +400,6 @@
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflits, Paix et Sécurité</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -688,6 +688,9 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
@@ -697,9 +700,6 @@
     <t>Energie</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources renouvelables</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources non renouvelables</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Centrales nucléaires</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Distribution de l'énergie</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -967,6 +967,9 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
@@ -976,9 +979,6 @@
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Sylviculture</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Pêche</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,6 +1165,9 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
@@ -1174,9 +1177,6 @@
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Industries Extractives</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,10 +1357,10 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
-  </si>
-  <si>
-    <t>323</t>
   </si>
   <si>
     <t>33110</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2764,13 +2764,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2787,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2810,13 +2810,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2833,13 +2833,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2856,13 +2856,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2879,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2902,13 +2902,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2925,13 +2925,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2971,13 +2971,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2994,13 +2994,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3017,13 +3017,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3040,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3063,13 +3063,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3086,13 +3086,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3109,13 +3109,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3638,13 +3638,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3661,13 +3661,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3684,13 +3684,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3707,13 +3707,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3730,13 +3730,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3753,13 +3753,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3776,13 +3776,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3799,13 +3799,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3822,13 +3822,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3845,13 +3845,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3868,13 +3868,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3891,13 +3891,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3914,13 +3914,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3937,13 +3937,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3960,13 +3960,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3983,13 +3983,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4006,13 +4006,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4029,13 +4029,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4052,13 +4052,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4075,13 +4075,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4098,13 +4098,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4121,13 +4121,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
+        <v>225</v>
+      </c>
+      <c r="F111" t="s">
         <v>269</v>
       </c>
-      <c r="F111" t="s">
-        <v>226</v>
-      </c>
       <c r="G111" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>273</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G116" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E118" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G118" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E119" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G119" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4788,13 +4788,13 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F120" t="s">
         <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4811,13 +4811,13 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F121" t="s">
         <v>294</v>
       </c>
       <c r="G121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4834,13 +4834,13 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F122" t="s">
         <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4857,13 +4857,13 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F123" t="s">
         <v>294</v>
       </c>
       <c r="G123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4880,13 +4880,13 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F124" t="s">
         <v>294</v>
       </c>
       <c r="G124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4903,13 +4903,13 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F125" t="s">
         <v>294</v>
       </c>
       <c r="G125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4926,13 +4926,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F126" t="s">
         <v>308</v>
       </c>
       <c r="G126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4949,13 +4949,13 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F127" t="s">
         <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4972,13 +4972,13 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F128" t="s">
         <v>308</v>
       </c>
       <c r="G128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4995,13 +4995,13 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F129" t="s">
         <v>308</v>
       </c>
       <c r="G129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E148" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F148" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F149" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E150" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F150" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F151" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E152" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F152" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F153" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E154" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F154" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E155" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F155" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F156" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F157" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E158" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F158" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E178" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F178" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E179" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F179" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E180" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F180" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E181" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F181" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E182" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F182" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6234,16 +6234,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E183" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F183" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6257,16 +6257,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E184" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F184" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6280,16 +6280,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E185" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F185" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6303,16 +6303,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E186" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F186" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6326,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E187" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F187" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6349,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>447</v>
+        <v>384</v>
       </c>
       <c r="F188" t="s">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="G188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6375,13 +6375,13 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F189" t="s">
         <v>452</v>
       </c>
       <c r="G189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6398,13 +6398,13 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F190" t="s">
         <v>452</v>
       </c>
       <c r="G190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6421,13 +6421,13 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F191" t="s">
         <v>452</v>
       </c>
       <c r="G191" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6444,13 +6444,13 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F192" t="s">
         <v>452</v>
       </c>
       <c r="G192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6467,13 +6467,13 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F193" t="s">
         <v>452</v>
       </c>
       <c r="G193" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6490,13 +6490,13 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F194" t="s">
         <v>452</v>
       </c>
       <c r="G194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6513,13 +6513,13 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F195" t="s">
         <v>466</v>
       </c>
       <c r="G195" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6536,13 +6536,13 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F196" t="s">
         <v>470</v>
       </c>
       <c r="G196" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6559,13 +6559,13 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F197" t="s">
         <v>470</v>
       </c>
       <c r="G197" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6582,13 +6582,13 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F198" t="s">
         <v>470</v>
       </c>
       <c r="G198" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6605,13 +6605,13 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F199" t="s">
         <v>470</v>
       </c>
       <c r="G199" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6628,13 +6628,13 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F200" t="s">
         <v>470</v>
       </c>
       <c r="G200" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6651,13 +6651,13 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F201" t="s">
         <v>470</v>
       </c>
       <c r="G201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6674,13 +6674,13 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F202" t="s">
         <v>484</v>
       </c>
       <c r="G202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6697,13 +6697,13 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F203" t="s">
         <v>484</v>
       </c>
       <c r="G203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6720,13 +6720,13 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F204" t="s">
         <v>484</v>
       </c>
       <c r="G204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6743,13 +6743,13 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F205" t="s">
         <v>484</v>
       </c>
       <c r="G205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6766,13 +6766,13 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F206" t="s">
         <v>484</v>
       </c>
       <c r="G206" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6789,13 +6789,13 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F207" t="s">
         <v>484</v>
       </c>
       <c r="G207" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6812,13 +6812,13 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F208" t="s">
         <v>484</v>
       </c>
       <c r="G208" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6835,13 +6835,13 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F209" t="s">
         <v>484</v>
       </c>
       <c r="G209" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6858,13 +6858,13 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F210" t="s">
         <v>484</v>
       </c>
       <c r="G210" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6881,13 +6881,13 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F211" t="s">
         <v>484</v>
       </c>
       <c r="G211" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6904,13 +6904,13 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F212" t="s">
         <v>506</v>
       </c>
       <c r="G212" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6927,13 +6927,13 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F213" t="s">
         <v>510</v>
       </c>
       <c r="G213" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6950,13 +6950,13 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F214" t="s">
         <v>514</v>
       </c>
       <c r="G214" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6973,13 +6973,13 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F215" t="s">
         <v>514</v>
       </c>
       <c r="G215" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6996,13 +6996,13 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F216" t="s">
         <v>520</v>
       </c>
       <c r="G216" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7019,13 +7019,13 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F217" t="s">
         <v>520</v>
       </c>
       <c r="G217" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7042,13 +7042,13 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F218" t="s">
         <v>520</v>
       </c>
       <c r="G218" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7065,13 +7065,13 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F219" t="s">
         <v>520</v>
       </c>
       <c r="G219" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7088,13 +7088,13 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F220" t="s">
         <v>520</v>
       </c>
       <c r="G220" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7111,13 +7111,13 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F221" t="s">
         <v>520</v>
       </c>
       <c r="G221" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7134,13 +7134,13 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F222" t="s">
         <v>520</v>
       </c>
       <c r="G222" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7157,13 +7157,13 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F223" t="s">
         <v>536</v>
       </c>
       <c r="G223" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7180,13 +7180,13 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F224" t="s">
         <v>536</v>
       </c>
       <c r="G224" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7203,13 +7203,13 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F225" t="s">
         <v>536</v>
       </c>
       <c r="G225" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7226,13 +7226,13 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F226" t="s">
         <v>544</v>
       </c>
       <c r="G226" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7249,13 +7249,13 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F227" t="s">
         <v>548</v>
       </c>
       <c r="G227" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7272,13 +7272,13 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F228" t="s">
         <v>552</v>
       </c>
       <c r="G228" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7295,13 +7295,13 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F229" t="s">
         <v>556</v>
       </c>
       <c r="G229" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7318,13 +7318,13 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F230" t="s">
         <v>560</v>
       </c>
       <c r="G230" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7341,13 +7341,13 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F231" t="s">
         <v>560</v>
       </c>
       <c r="G231" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>Education de Base</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Education de Base</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>Education Secondaire</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Education Secondaire</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>Education Post Secondaire</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Education Post Secondaire</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>Santé de Base</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Santé de Base</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>Maladies non-transmissibles (MNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Maladies non-transmissibles (MNT)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>Distribution d'Eau et Assainissement</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Distribution d'Eau et Assainissement</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>Conflits, Paix et Sécurité</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflits, Paix et Sécurité</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>Infrastructure et Services Sociaux Divers</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Infrastructure et Services Sociaux Divers</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>Transports et Entreposage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transports et Entreposage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>Production d'électricité, sources renouvelables</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Production d'électricité, sources renouvelables</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>Production d'électricité, sources non renouvelables</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Production d'électricité, sources non renouvelables</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>Centrales nucléaires</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrales nucléaires</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>Distribution de l'énergie</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribution de l'énergie</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>Banques et Services Financiers</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banques et Services Financiers</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>Entreprises et Autres Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Entreprises et Autres Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>Sylviculture</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Sylviculture</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>Pêche</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pêche</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Extractives</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Industries Extractives</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,24 +1357,24 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>Politique Commerciale et Réglementations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Politique Commerciale et Réglementations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>Tourisme</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourisme</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>Protection de l'Environnement Général</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protection de l'Environnement Général</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>Autres Multisecteurs</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Autres Multisecteurs</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>Soutien Budgétaire</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Soutien Budgétaire</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>Aide Alimentaire Dévelopmentale</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Aide Alimentaire Dévelopmentale</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>Aide sous forme de Produits, Autre</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Aide sous forme de Produits, Autre</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>Actions se Rapportant a la Dette</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actions se Rapportant a la Dette</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>Intervention d'Urgence</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Intervention d'Urgence</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>Reconstruction &amp; Réhabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction &amp; Réhabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>Prévention catastrophes/Préparation à leur survenue</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prévention catastrophes/Préparation à leur survenue</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>Frais Administratifs des Donneurs</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Frais Administratifs des Donneurs</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>Refugiés dans les Pays Donneurs</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiés dans les Pays Donneurs</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>Non Affecté / Non Specifié</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Non Affecté / Non Specifié</t>
   </si>
   <si>
     <t>99820</t>
@@ -2169,10 +2169,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2192,10 +2192,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2215,10 +2215,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2238,10 +2238,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2261,10 +2261,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2284,10 +2284,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2307,10 +2307,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2330,10 +2330,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2445,10 +2445,10 @@
         <v>45</v>
       </c>
       <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2468,10 +2468,10 @@
         <v>45</v>
       </c>
       <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2491,10 +2491,10 @@
         <v>45</v>
       </c>
       <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2514,10 +2514,10 @@
         <v>45</v>
       </c>
       <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2537,10 +2537,10 @@
         <v>45</v>
       </c>
       <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2560,10 +2560,10 @@
         <v>45</v>
       </c>
       <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2583,10 +2583,10 @@
         <v>45</v>
       </c>
       <c r="F24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2606,10 +2606,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2629,10 +2629,10 @@
         <v>45</v>
       </c>
       <c r="F26" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2652,10 +2652,10 @@
         <v>45</v>
       </c>
       <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2675,10 +2675,10 @@
         <v>45</v>
       </c>
       <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2698,10 +2698,10 @@
         <v>45</v>
       </c>
       <c r="F29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2721,10 +2721,10 @@
         <v>45</v>
       </c>
       <c r="F30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2744,10 +2744,10 @@
         <v>45</v>
       </c>
       <c r="F31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2764,10 +2764,10 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" t="s">
         <v>88</v>
-      </c>
-      <c r="F32" t="s">
-        <v>89</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2787,10 +2787,10 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" t="s">
         <v>88</v>
-      </c>
-      <c r="F33" t="s">
-        <v>89</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2810,10 +2810,10 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" t="s">
         <v>88</v>
-      </c>
-      <c r="F34" t="s">
-        <v>89</v>
       </c>
       <c r="G34" t="s">
         <v>89</v>
@@ -2833,10 +2833,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" t="s">
         <v>88</v>
-      </c>
-      <c r="F35" t="s">
-        <v>89</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
@@ -2856,10 +2856,10 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" t="s">
         <v>88</v>
-      </c>
-      <c r="F36" t="s">
-        <v>89</v>
       </c>
       <c r="G36" t="s">
         <v>89</v>
@@ -2879,10 +2879,10 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
         <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>101</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -2902,10 +2902,10 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" t="s">
         <v>100</v>
-      </c>
-      <c r="F38" t="s">
-        <v>101</v>
       </c>
       <c r="G38" t="s">
         <v>101</v>
@@ -2925,10 +2925,10 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
         <v>100</v>
-      </c>
-      <c r="F39" t="s">
-        <v>101</v>
       </c>
       <c r="G39" t="s">
         <v>101</v>
@@ -2948,10 +2948,10 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
         <v>100</v>
-      </c>
-      <c r="F40" t="s">
-        <v>101</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -2971,10 +2971,10 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
         <v>100</v>
-      </c>
-      <c r="F41" t="s">
-        <v>101</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -2994,10 +2994,10 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
         <v>100</v>
-      </c>
-      <c r="F42" t="s">
-        <v>101</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -3017,10 +3017,10 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
         <v>100</v>
-      </c>
-      <c r="F43" t="s">
-        <v>101</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -3040,10 +3040,10 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
         <v>100</v>
-      </c>
-      <c r="F44" t="s">
-        <v>101</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -3063,10 +3063,10 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" t="s">
         <v>100</v>
-      </c>
-      <c r="F45" t="s">
-        <v>101</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -3086,10 +3086,10 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
         <v>100</v>
-      </c>
-      <c r="F46" t="s">
-        <v>101</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -3109,10 +3109,10 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
         <v>100</v>
-      </c>
-      <c r="F47" t="s">
-        <v>101</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -3503,10 +3503,10 @@
         <v>125</v>
       </c>
       <c r="F64" t="s">
+        <v>126</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3526,10 +3526,10 @@
         <v>125</v>
       </c>
       <c r="F65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3549,10 +3549,10 @@
         <v>125</v>
       </c>
       <c r="F66" t="s">
+        <v>126</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3572,10 +3572,10 @@
         <v>125</v>
       </c>
       <c r="F67" t="s">
+        <v>126</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3595,10 +3595,10 @@
         <v>125</v>
       </c>
       <c r="F68" t="s">
+        <v>126</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3618,10 +3618,10 @@
         <v>125</v>
       </c>
       <c r="F69" t="s">
+        <v>126</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3638,10 +3638,10 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s">
         <v>174</v>
-      </c>
-      <c r="F70" t="s">
-        <v>175</v>
       </c>
       <c r="G70" t="s">
         <v>175</v>
@@ -3661,10 +3661,10 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71" t="s">
         <v>174</v>
-      </c>
-      <c r="F71" t="s">
-        <v>175</v>
       </c>
       <c r="G71" t="s">
         <v>175</v>
@@ -3684,10 +3684,10 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
+        <v>175</v>
+      </c>
+      <c r="F72" t="s">
         <v>174</v>
-      </c>
-      <c r="F72" t="s">
-        <v>175</v>
       </c>
       <c r="G72" t="s">
         <v>175</v>
@@ -3707,10 +3707,10 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" t="s">
         <v>174</v>
-      </c>
-      <c r="F73" t="s">
-        <v>175</v>
       </c>
       <c r="G73" t="s">
         <v>175</v>
@@ -3730,10 +3730,10 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" t="s">
         <v>174</v>
-      </c>
-      <c r="F74" t="s">
-        <v>175</v>
       </c>
       <c r="G74" t="s">
         <v>175</v>
@@ -3753,10 +3753,10 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
+        <v>175</v>
+      </c>
+      <c r="F75" t="s">
         <v>174</v>
-      </c>
-      <c r="F75" t="s">
-        <v>175</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -3776,10 +3776,10 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
+        <v>175</v>
+      </c>
+      <c r="F76" t="s">
         <v>174</v>
-      </c>
-      <c r="F76" t="s">
-        <v>175</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -3799,10 +3799,10 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
+        <v>175</v>
+      </c>
+      <c r="F77" t="s">
         <v>174</v>
-      </c>
-      <c r="F77" t="s">
-        <v>175</v>
       </c>
       <c r="G77" t="s">
         <v>175</v>
@@ -3822,10 +3822,10 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
+        <v>175</v>
+      </c>
+      <c r="F78" t="s">
         <v>174</v>
-      </c>
-      <c r="F78" t="s">
-        <v>175</v>
       </c>
       <c r="G78" t="s">
         <v>175</v>
@@ -3845,10 +3845,10 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
+        <v>175</v>
+      </c>
+      <c r="F79" t="s">
         <v>174</v>
-      </c>
-      <c r="F79" t="s">
-        <v>175</v>
       </c>
       <c r="G79" t="s">
         <v>175</v>
@@ -3868,10 +3868,10 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
+        <v>175</v>
+      </c>
+      <c r="F80" t="s">
         <v>174</v>
-      </c>
-      <c r="F80" t="s">
-        <v>175</v>
       </c>
       <c r="G80" t="s">
         <v>175</v>
@@ -3891,10 +3891,10 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" t="s">
         <v>198</v>
-      </c>
-      <c r="F81" t="s">
-        <v>199</v>
       </c>
       <c r="G81" t="s">
         <v>199</v>
@@ -3914,10 +3914,10 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
+        <v>199</v>
+      </c>
+      <c r="F82" t="s">
         <v>198</v>
-      </c>
-      <c r="F82" t="s">
-        <v>199</v>
       </c>
       <c r="G82" t="s">
         <v>199</v>
@@ -3937,10 +3937,10 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
+        <v>199</v>
+      </c>
+      <c r="F83" t="s">
         <v>198</v>
-      </c>
-      <c r="F83" t="s">
-        <v>199</v>
       </c>
       <c r="G83" t="s">
         <v>199</v>
@@ -3960,10 +3960,10 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
+        <v>199</v>
+      </c>
+      <c r="F84" t="s">
         <v>198</v>
-      </c>
-      <c r="F84" t="s">
-        <v>199</v>
       </c>
       <c r="G84" t="s">
         <v>199</v>
@@ -3983,10 +3983,10 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
+        <v>199</v>
+      </c>
+      <c r="F85" t="s">
         <v>198</v>
-      </c>
-      <c r="F85" t="s">
-        <v>199</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
@@ -4006,10 +4006,10 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" t="s">
         <v>198</v>
-      </c>
-      <c r="F86" t="s">
-        <v>199</v>
       </c>
       <c r="G86" t="s">
         <v>199</v>
@@ -4029,10 +4029,10 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
+        <v>199</v>
+      </c>
+      <c r="F87" t="s">
         <v>198</v>
-      </c>
-      <c r="F87" t="s">
-        <v>199</v>
       </c>
       <c r="G87" t="s">
         <v>199</v>
@@ -4052,10 +4052,10 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
+        <v>215</v>
+      </c>
+      <c r="F88" t="s">
         <v>214</v>
-      </c>
-      <c r="F88" t="s">
-        <v>215</v>
       </c>
       <c r="G88" t="s">
         <v>215</v>
@@ -4075,10 +4075,10 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
+        <v>215</v>
+      </c>
+      <c r="F89" t="s">
         <v>214</v>
-      </c>
-      <c r="F89" t="s">
-        <v>215</v>
       </c>
       <c r="G89" t="s">
         <v>215</v>
@@ -4098,10 +4098,10 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
+        <v>215</v>
+      </c>
+      <c r="F90" t="s">
         <v>214</v>
-      </c>
-      <c r="F90" t="s">
-        <v>215</v>
       </c>
       <c r="G90" t="s">
         <v>215</v>
@@ -4121,10 +4121,10 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
+        <v>215</v>
+      </c>
+      <c r="F91" t="s">
         <v>214</v>
-      </c>
-      <c r="F91" t="s">
-        <v>215</v>
       </c>
       <c r="G91" t="s">
         <v>215</v>
@@ -4239,10 +4239,10 @@
         <v>225</v>
       </c>
       <c r="F96" t="s">
+        <v>226</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4262,10 +4262,10 @@
         <v>225</v>
       </c>
       <c r="F97" t="s">
+        <v>226</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4285,10 +4285,10 @@
         <v>225</v>
       </c>
       <c r="F98" t="s">
+        <v>226</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4308,10 +4308,10 @@
         <v>225</v>
       </c>
       <c r="F99" t="s">
+        <v>226</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4331,10 +4331,10 @@
         <v>225</v>
       </c>
       <c r="F100" t="s">
+        <v>226</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4354,10 +4354,10 @@
         <v>225</v>
       </c>
       <c r="F101" t="s">
+        <v>226</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4377,10 +4377,10 @@
         <v>225</v>
       </c>
       <c r="F102" t="s">
+        <v>226</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4400,10 +4400,10 @@
         <v>225</v>
       </c>
       <c r="F103" t="s">
+        <v>226</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4423,10 +4423,10 @@
         <v>225</v>
       </c>
       <c r="F104" t="s">
+        <v>226</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4446,10 +4446,10 @@
         <v>225</v>
       </c>
       <c r="F105" t="s">
+        <v>226</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4469,10 +4469,10 @@
         <v>225</v>
       </c>
       <c r="F106" t="s">
+        <v>226</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4492,10 +4492,10 @@
         <v>225</v>
       </c>
       <c r="F107" t="s">
+        <v>226</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4515,10 +4515,10 @@
         <v>225</v>
       </c>
       <c r="F108" t="s">
+        <v>226</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4538,10 +4538,10 @@
         <v>225</v>
       </c>
       <c r="F109" t="s">
+        <v>226</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4561,10 +4561,10 @@
         <v>225</v>
       </c>
       <c r="F110" t="s">
+        <v>226</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="G111" t="s">
-        <v>227</v>
+        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4607,10 +4607,10 @@
         <v>225</v>
       </c>
       <c r="F112" t="s">
+        <v>226</v>
+      </c>
+      <c r="G112" t="s">
         <v>274</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4630,10 +4630,10 @@
         <v>225</v>
       </c>
       <c r="F113" t="s">
+        <v>226</v>
+      </c>
+      <c r="G113" t="s">
         <v>278</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4653,10 +4653,10 @@
         <v>225</v>
       </c>
       <c r="F114" t="s">
+        <v>226</v>
+      </c>
+      <c r="G114" t="s">
         <v>278</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4676,10 +4676,10 @@
         <v>225</v>
       </c>
       <c r="F115" t="s">
+        <v>226</v>
+      </c>
+      <c r="G115" t="s">
         <v>278</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4699,10 +4699,10 @@
         <v>225</v>
       </c>
       <c r="F116" t="s">
+        <v>226</v>
+      </c>
+      <c r="G116" t="s">
         <v>278</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4722,10 +4722,10 @@
         <v>225</v>
       </c>
       <c r="F117" t="s">
+        <v>226</v>
+      </c>
+      <c r="G117" t="s">
         <v>278</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4745,10 +4745,10 @@
         <v>225</v>
       </c>
       <c r="F118" t="s">
+        <v>226</v>
+      </c>
+      <c r="G118" t="s">
         <v>278</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4768,10 +4768,10 @@
         <v>225</v>
       </c>
       <c r="F119" t="s">
+        <v>226</v>
+      </c>
+      <c r="G119" t="s">
         <v>278</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4788,10 +4788,10 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
+        <v>294</v>
+      </c>
+      <c r="F120" t="s">
         <v>293</v>
-      </c>
-      <c r="F120" t="s">
-        <v>294</v>
       </c>
       <c r="G120" t="s">
         <v>294</v>
@@ -4811,10 +4811,10 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
+        <v>294</v>
+      </c>
+      <c r="F121" t="s">
         <v>293</v>
-      </c>
-      <c r="F121" t="s">
-        <v>294</v>
       </c>
       <c r="G121" t="s">
         <v>294</v>
@@ -4834,10 +4834,10 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
+        <v>294</v>
+      </c>
+      <c r="F122" t="s">
         <v>293</v>
-      </c>
-      <c r="F122" t="s">
-        <v>294</v>
       </c>
       <c r="G122" t="s">
         <v>294</v>
@@ -4857,10 +4857,10 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
+        <v>294</v>
+      </c>
+      <c r="F123" t="s">
         <v>293</v>
-      </c>
-      <c r="F123" t="s">
-        <v>294</v>
       </c>
       <c r="G123" t="s">
         <v>294</v>
@@ -4880,10 +4880,10 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
+        <v>294</v>
+      </c>
+      <c r="F124" t="s">
         <v>293</v>
-      </c>
-      <c r="F124" t="s">
-        <v>294</v>
       </c>
       <c r="G124" t="s">
         <v>294</v>
@@ -4903,10 +4903,10 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
+        <v>294</v>
+      </c>
+      <c r="F125" t="s">
         <v>293</v>
-      </c>
-      <c r="F125" t="s">
-        <v>294</v>
       </c>
       <c r="G125" t="s">
         <v>294</v>
@@ -4926,10 +4926,10 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
+        <v>308</v>
+      </c>
+      <c r="F126" t="s">
         <v>307</v>
-      </c>
-      <c r="F126" t="s">
-        <v>308</v>
       </c>
       <c r="G126" t="s">
         <v>308</v>
@@ -4949,10 +4949,10 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
+        <v>308</v>
+      </c>
+      <c r="F127" t="s">
         <v>307</v>
-      </c>
-      <c r="F127" t="s">
-        <v>308</v>
       </c>
       <c r="G127" t="s">
         <v>308</v>
@@ -4972,10 +4972,10 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
+        <v>308</v>
+      </c>
+      <c r="F128" t="s">
         <v>307</v>
-      </c>
-      <c r="F128" t="s">
-        <v>308</v>
       </c>
       <c r="G128" t="s">
         <v>308</v>
@@ -4995,10 +4995,10 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
+        <v>308</v>
+      </c>
+      <c r="F129" t="s">
         <v>307</v>
-      </c>
-      <c r="F129" t="s">
-        <v>308</v>
       </c>
       <c r="G129" t="s">
         <v>308</v>
@@ -5435,10 +5435,10 @@
         <v>318</v>
       </c>
       <c r="F148" t="s">
+        <v>319</v>
+      </c>
+      <c r="G148" t="s">
         <v>358</v>
-      </c>
-      <c r="G148" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5458,10 +5458,10 @@
         <v>318</v>
       </c>
       <c r="F149" t="s">
+        <v>319</v>
+      </c>
+      <c r="G149" t="s">
         <v>358</v>
-      </c>
-      <c r="G149" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5481,10 +5481,10 @@
         <v>318</v>
       </c>
       <c r="F150" t="s">
+        <v>319</v>
+      </c>
+      <c r="G150" t="s">
         <v>358</v>
-      </c>
-      <c r="G150" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5504,10 +5504,10 @@
         <v>318</v>
       </c>
       <c r="F151" t="s">
+        <v>319</v>
+      </c>
+      <c r="G151" t="s">
         <v>358</v>
-      </c>
-      <c r="G151" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5527,10 +5527,10 @@
         <v>318</v>
       </c>
       <c r="F152" t="s">
+        <v>319</v>
+      </c>
+      <c r="G152" t="s">
         <v>358</v>
-      </c>
-      <c r="G152" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5550,10 +5550,10 @@
         <v>318</v>
       </c>
       <c r="F153" t="s">
+        <v>319</v>
+      </c>
+      <c r="G153" t="s">
         <v>358</v>
-      </c>
-      <c r="G153" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5573,10 +5573,10 @@
         <v>318</v>
       </c>
       <c r="F154" t="s">
+        <v>319</v>
+      </c>
+      <c r="G154" t="s">
         <v>372</v>
-      </c>
-      <c r="G154" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5596,10 +5596,10 @@
         <v>318</v>
       </c>
       <c r="F155" t="s">
+        <v>319</v>
+      </c>
+      <c r="G155" t="s">
         <v>372</v>
-      </c>
-      <c r="G155" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5619,10 +5619,10 @@
         <v>318</v>
       </c>
       <c r="F156" t="s">
+        <v>319</v>
+      </c>
+      <c r="G156" t="s">
         <v>372</v>
-      </c>
-      <c r="G156" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5642,10 +5642,10 @@
         <v>318</v>
       </c>
       <c r="F157" t="s">
+        <v>319</v>
+      </c>
+      <c r="G157" t="s">
         <v>372</v>
-      </c>
-      <c r="G157" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5665,10 +5665,10 @@
         <v>318</v>
       </c>
       <c r="F158" t="s">
+        <v>319</v>
+      </c>
+      <c r="G158" t="s">
         <v>372</v>
-      </c>
-      <c r="G158" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6125,10 +6125,10 @@
         <v>384</v>
       </c>
       <c r="F178" t="s">
+        <v>385</v>
+      </c>
+      <c r="G178" t="s">
         <v>426</v>
-      </c>
-      <c r="G178" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6148,10 +6148,10 @@
         <v>384</v>
       </c>
       <c r="F179" t="s">
+        <v>385</v>
+      </c>
+      <c r="G179" t="s">
         <v>426</v>
-      </c>
-      <c r="G179" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6171,10 +6171,10 @@
         <v>384</v>
       </c>
       <c r="F180" t="s">
+        <v>385</v>
+      </c>
+      <c r="G180" t="s">
         <v>426</v>
-      </c>
-      <c r="G180" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6194,10 +6194,10 @@
         <v>384</v>
       </c>
       <c r="F181" t="s">
+        <v>385</v>
+      </c>
+      <c r="G181" t="s">
         <v>426</v>
-      </c>
-      <c r="G181" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6217,10 +6217,10 @@
         <v>384</v>
       </c>
       <c r="F182" t="s">
+        <v>385</v>
+      </c>
+      <c r="G182" t="s">
         <v>426</v>
-      </c>
-      <c r="G182" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6240,10 +6240,10 @@
         <v>384</v>
       </c>
       <c r="F183" t="s">
+        <v>385</v>
+      </c>
+      <c r="G183" t="s">
         <v>426</v>
-      </c>
-      <c r="G183" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6263,10 +6263,10 @@
         <v>384</v>
       </c>
       <c r="F184" t="s">
+        <v>385</v>
+      </c>
+      <c r="G184" t="s">
         <v>426</v>
-      </c>
-      <c r="G184" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6286,10 +6286,10 @@
         <v>384</v>
       </c>
       <c r="F185" t="s">
+        <v>385</v>
+      </c>
+      <c r="G185" t="s">
         <v>426</v>
-      </c>
-      <c r="G185" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6309,10 +6309,10 @@
         <v>384</v>
       </c>
       <c r="F186" t="s">
+        <v>385</v>
+      </c>
+      <c r="G186" t="s">
         <v>426</v>
-      </c>
-      <c r="G186" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6332,10 +6332,10 @@
         <v>384</v>
       </c>
       <c r="F187" t="s">
+        <v>385</v>
+      </c>
+      <c r="G187" t="s">
         <v>426</v>
-      </c>
-      <c r="G187" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6355,10 +6355,10 @@
         <v>384</v>
       </c>
       <c r="F188" t="s">
+        <v>385</v>
+      </c>
+      <c r="G188" t="s">
         <v>448</v>
-      </c>
-      <c r="G188" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6375,10 +6375,10 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
+        <v>452</v>
+      </c>
+      <c r="F189" t="s">
         <v>451</v>
-      </c>
-      <c r="F189" t="s">
-        <v>452</v>
       </c>
       <c r="G189" t="s">
         <v>452</v>
@@ -6398,10 +6398,10 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
+        <v>452</v>
+      </c>
+      <c r="F190" t="s">
         <v>451</v>
-      </c>
-      <c r="F190" t="s">
-        <v>452</v>
       </c>
       <c r="G190" t="s">
         <v>452</v>
@@ -6421,10 +6421,10 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
+        <v>452</v>
+      </c>
+      <c r="F191" t="s">
         <v>451</v>
-      </c>
-      <c r="F191" t="s">
-        <v>452</v>
       </c>
       <c r="G191" t="s">
         <v>452</v>
@@ -6444,10 +6444,10 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
+        <v>452</v>
+      </c>
+      <c r="F192" t="s">
         <v>451</v>
-      </c>
-      <c r="F192" t="s">
-        <v>452</v>
       </c>
       <c r="G192" t="s">
         <v>452</v>
@@ -6467,10 +6467,10 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
+        <v>452</v>
+      </c>
+      <c r="F193" t="s">
         <v>451</v>
-      </c>
-      <c r="F193" t="s">
-        <v>452</v>
       </c>
       <c r="G193" t="s">
         <v>452</v>
@@ -6490,10 +6490,10 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
+        <v>452</v>
+      </c>
+      <c r="F194" t="s">
         <v>451</v>
-      </c>
-      <c r="F194" t="s">
-        <v>452</v>
       </c>
       <c r="G194" t="s">
         <v>452</v>
@@ -6513,10 +6513,10 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
+        <v>466</v>
+      </c>
+      <c r="F195" t="s">
         <v>465</v>
-      </c>
-      <c r="F195" t="s">
-        <v>466</v>
       </c>
       <c r="G195" t="s">
         <v>466</v>
@@ -6536,10 +6536,10 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
+        <v>470</v>
+      </c>
+      <c r="F196" t="s">
         <v>469</v>
-      </c>
-      <c r="F196" t="s">
-        <v>470</v>
       </c>
       <c r="G196" t="s">
         <v>470</v>
@@ -6559,10 +6559,10 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
+        <v>470</v>
+      </c>
+      <c r="F197" t="s">
         <v>469</v>
-      </c>
-      <c r="F197" t="s">
-        <v>470</v>
       </c>
       <c r="G197" t="s">
         <v>470</v>
@@ -6582,10 +6582,10 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
+        <v>470</v>
+      </c>
+      <c r="F198" t="s">
         <v>469</v>
-      </c>
-      <c r="F198" t="s">
-        <v>470</v>
       </c>
       <c r="G198" t="s">
         <v>470</v>
@@ -6605,10 +6605,10 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
+        <v>470</v>
+      </c>
+      <c r="F199" t="s">
         <v>469</v>
-      </c>
-      <c r="F199" t="s">
-        <v>470</v>
       </c>
       <c r="G199" t="s">
         <v>470</v>
@@ -6628,10 +6628,10 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
+        <v>470</v>
+      </c>
+      <c r="F200" t="s">
         <v>469</v>
-      </c>
-      <c r="F200" t="s">
-        <v>470</v>
       </c>
       <c r="G200" t="s">
         <v>470</v>
@@ -6651,10 +6651,10 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
+        <v>470</v>
+      </c>
+      <c r="F201" t="s">
         <v>469</v>
-      </c>
-      <c r="F201" t="s">
-        <v>470</v>
       </c>
       <c r="G201" t="s">
         <v>470</v>
@@ -6674,10 +6674,10 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
+        <v>484</v>
+      </c>
+      <c r="F202" t="s">
         <v>483</v>
-      </c>
-      <c r="F202" t="s">
-        <v>484</v>
       </c>
       <c r="G202" t="s">
         <v>484</v>
@@ -6697,10 +6697,10 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
+        <v>484</v>
+      </c>
+      <c r="F203" t="s">
         <v>483</v>
-      </c>
-      <c r="F203" t="s">
-        <v>484</v>
       </c>
       <c r="G203" t="s">
         <v>484</v>
@@ -6720,10 +6720,10 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
+        <v>484</v>
+      </c>
+      <c r="F204" t="s">
         <v>483</v>
-      </c>
-      <c r="F204" t="s">
-        <v>484</v>
       </c>
       <c r="G204" t="s">
         <v>484</v>
@@ -6743,10 +6743,10 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
+        <v>484</v>
+      </c>
+      <c r="F205" t="s">
         <v>483</v>
-      </c>
-      <c r="F205" t="s">
-        <v>484</v>
       </c>
       <c r="G205" t="s">
         <v>484</v>
@@ -6766,10 +6766,10 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
+        <v>484</v>
+      </c>
+      <c r="F206" t="s">
         <v>483</v>
-      </c>
-      <c r="F206" t="s">
-        <v>484</v>
       </c>
       <c r="G206" t="s">
         <v>484</v>
@@ -6789,10 +6789,10 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
+        <v>484</v>
+      </c>
+      <c r="F207" t="s">
         <v>483</v>
-      </c>
-      <c r="F207" t="s">
-        <v>484</v>
       </c>
       <c r="G207" t="s">
         <v>484</v>
@@ -6812,10 +6812,10 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
+        <v>484</v>
+      </c>
+      <c r="F208" t="s">
         <v>483</v>
-      </c>
-      <c r="F208" t="s">
-        <v>484</v>
       </c>
       <c r="G208" t="s">
         <v>484</v>
@@ -6835,10 +6835,10 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
+        <v>484</v>
+      </c>
+      <c r="F209" t="s">
         <v>483</v>
-      </c>
-      <c r="F209" t="s">
-        <v>484</v>
       </c>
       <c r="G209" t="s">
         <v>484</v>
@@ -6858,10 +6858,10 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
+        <v>484</v>
+      </c>
+      <c r="F210" t="s">
         <v>483</v>
-      </c>
-      <c r="F210" t="s">
-        <v>484</v>
       </c>
       <c r="G210" t="s">
         <v>484</v>
@@ -6881,10 +6881,10 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
+        <v>484</v>
+      </c>
+      <c r="F211" t="s">
         <v>483</v>
-      </c>
-      <c r="F211" t="s">
-        <v>484</v>
       </c>
       <c r="G211" t="s">
         <v>484</v>
@@ -6904,10 +6904,10 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
+        <v>506</v>
+      </c>
+      <c r="F212" t="s">
         <v>505</v>
-      </c>
-      <c r="F212" t="s">
-        <v>506</v>
       </c>
       <c r="G212" t="s">
         <v>506</v>
@@ -6927,10 +6927,10 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
+        <v>510</v>
+      </c>
+      <c r="F213" t="s">
         <v>509</v>
-      </c>
-      <c r="F213" t="s">
-        <v>510</v>
       </c>
       <c r="G213" t="s">
         <v>510</v>
@@ -6950,10 +6950,10 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
+        <v>514</v>
+      </c>
+      <c r="F214" t="s">
         <v>513</v>
-      </c>
-      <c r="F214" t="s">
-        <v>514</v>
       </c>
       <c r="G214" t="s">
         <v>514</v>
@@ -6973,10 +6973,10 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
+        <v>514</v>
+      </c>
+      <c r="F215" t="s">
         <v>513</v>
-      </c>
-      <c r="F215" t="s">
-        <v>514</v>
       </c>
       <c r="G215" t="s">
         <v>514</v>
@@ -6996,10 +6996,10 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
+        <v>520</v>
+      </c>
+      <c r="F216" t="s">
         <v>519</v>
-      </c>
-      <c r="F216" t="s">
-        <v>520</v>
       </c>
       <c r="G216" t="s">
         <v>520</v>
@@ -7019,10 +7019,10 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
+        <v>520</v>
+      </c>
+      <c r="F217" t="s">
         <v>519</v>
-      </c>
-      <c r="F217" t="s">
-        <v>520</v>
       </c>
       <c r="G217" t="s">
         <v>520</v>
@@ -7042,10 +7042,10 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
+        <v>520</v>
+      </c>
+      <c r="F218" t="s">
         <v>519</v>
-      </c>
-      <c r="F218" t="s">
-        <v>520</v>
       </c>
       <c r="G218" t="s">
         <v>520</v>
@@ -7065,10 +7065,10 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
+        <v>520</v>
+      </c>
+      <c r="F219" t="s">
         <v>519</v>
-      </c>
-      <c r="F219" t="s">
-        <v>520</v>
       </c>
       <c r="G219" t="s">
         <v>520</v>
@@ -7088,10 +7088,10 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
+        <v>520</v>
+      </c>
+      <c r="F220" t="s">
         <v>519</v>
-      </c>
-      <c r="F220" t="s">
-        <v>520</v>
       </c>
       <c r="G220" t="s">
         <v>520</v>
@@ -7111,10 +7111,10 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
+        <v>520</v>
+      </c>
+      <c r="F221" t="s">
         <v>519</v>
-      </c>
-      <c r="F221" t="s">
-        <v>520</v>
       </c>
       <c r="G221" t="s">
         <v>520</v>
@@ -7134,10 +7134,10 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
+        <v>520</v>
+      </c>
+      <c r="F222" t="s">
         <v>519</v>
-      </c>
-      <c r="F222" t="s">
-        <v>520</v>
       </c>
       <c r="G222" t="s">
         <v>520</v>
@@ -7157,10 +7157,10 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
+        <v>536</v>
+      </c>
+      <c r="F223" t="s">
         <v>535</v>
-      </c>
-      <c r="F223" t="s">
-        <v>536</v>
       </c>
       <c r="G223" t="s">
         <v>536</v>
@@ -7180,10 +7180,10 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
+        <v>536</v>
+      </c>
+      <c r="F224" t="s">
         <v>535</v>
-      </c>
-      <c r="F224" t="s">
-        <v>536</v>
       </c>
       <c r="G224" t="s">
         <v>536</v>
@@ -7203,10 +7203,10 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
+        <v>536</v>
+      </c>
+      <c r="F225" t="s">
         <v>535</v>
-      </c>
-      <c r="F225" t="s">
-        <v>536</v>
       </c>
       <c r="G225" t="s">
         <v>536</v>
@@ -7226,10 +7226,10 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
+        <v>544</v>
+      </c>
+      <c r="F226" t="s">
         <v>543</v>
-      </c>
-      <c r="F226" t="s">
-        <v>544</v>
       </c>
       <c r="G226" t="s">
         <v>544</v>
@@ -7249,10 +7249,10 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
+        <v>548</v>
+      </c>
+      <c r="F227" t="s">
         <v>547</v>
-      </c>
-      <c r="F227" t="s">
-        <v>548</v>
       </c>
       <c r="G227" t="s">
         <v>548</v>
@@ -7272,10 +7272,10 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
+        <v>552</v>
+      </c>
+      <c r="F228" t="s">
         <v>551</v>
-      </c>
-      <c r="F228" t="s">
-        <v>552</v>
       </c>
       <c r="G228" t="s">
         <v>552</v>
@@ -7295,10 +7295,10 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
+        <v>556</v>
+      </c>
+      <c r="F229" t="s">
         <v>555</v>
-      </c>
-      <c r="F229" t="s">
-        <v>556</v>
       </c>
       <c r="G229" t="s">
         <v>556</v>
@@ -7318,10 +7318,10 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
+        <v>560</v>
+      </c>
+      <c r="F230" t="s">
         <v>559</v>
-      </c>
-      <c r="F230" t="s">
-        <v>560</v>
       </c>
       <c r="G230" t="s">
         <v>560</v>
@@ -7341,10 +7341,10 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
+        <v>560</v>
+      </c>
+      <c r="F231" t="s">
         <v>559</v>
-      </c>
-      <c r="F231" t="s">
-        <v>560</v>
       </c>
       <c r="G231" t="s">
         <v>560</v>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
     <t>Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -151,15 +151,15 @@
     <t>Santé, Général</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
     <t>Santé</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -691,15 +691,15 @@
     <t>Politique de l'énergie</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
     <t>Energie</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -970,15 +970,15 @@
     <t>Agriculture</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1168,13 +1168,13 @@
     <t>Industries Manufacturières</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>32120</t>
@@ -2166,13 +2166,13 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2189,13 +2189,13 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2212,13 +2212,13 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2235,13 +2235,13 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2258,13 +2258,13 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2281,13 +2281,13 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2304,13 +2304,13 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2327,13 +2327,13 @@
         <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2442,13 +2442,13 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
         <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2465,13 +2465,13 @@
         <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
         <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2488,13 +2488,13 @@
         <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2511,13 +2511,13 @@
         <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
         <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2534,13 +2534,13 @@
         <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2557,13 +2557,13 @@
         <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2580,13 +2580,13 @@
         <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2603,13 +2603,13 @@
         <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2626,13 +2626,13 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
         <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2649,13 +2649,13 @@
         <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2672,13 +2672,13 @@
         <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
         <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2695,13 +2695,13 @@
         <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
         <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2718,13 +2718,13 @@
         <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2741,13 +2741,13 @@
         <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
         <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2767,10 +2767,10 @@
         <v>89</v>
       </c>
       <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
         <v>88</v>
-      </c>
-      <c r="G32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2790,10 +2790,10 @@
         <v>89</v>
       </c>
       <c r="F33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
         <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2813,10 +2813,10 @@
         <v>89</v>
       </c>
       <c r="F34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
         <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2836,10 +2836,10 @@
         <v>89</v>
       </c>
       <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2859,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="F36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
         <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2882,10 +2882,10 @@
         <v>101</v>
       </c>
       <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
         <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2905,10 +2905,10 @@
         <v>101</v>
       </c>
       <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
         <v>100</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2928,10 +2928,10 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
         <v>100</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2974,10 +2974,10 @@
         <v>101</v>
       </c>
       <c r="F41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" t="s">
         <v>100</v>
-      </c>
-      <c r="G41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2997,10 +2997,10 @@
         <v>101</v>
       </c>
       <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
         <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3020,10 +3020,10 @@
         <v>101</v>
       </c>
       <c r="F43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3043,10 +3043,10 @@
         <v>101</v>
       </c>
       <c r="F44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" t="s">
         <v>100</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>101</v>
       </c>
       <c r="F45" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" t="s">
         <v>100</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3089,10 +3089,10 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" t="s">
         <v>100</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3112,10 +3112,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
         <v>100</v>
-      </c>
-      <c r="G47" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3500,13 +3500,13 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F64" t="s">
         <v>126</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3523,13 +3523,13 @@
         <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
         <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3546,13 +3546,13 @@
         <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
         <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3569,13 +3569,13 @@
         <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
         <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3592,13 +3592,13 @@
         <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
         <v>126</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3615,13 +3615,13 @@
         <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
         <v>126</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3641,10 +3641,10 @@
         <v>175</v>
       </c>
       <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
         <v>174</v>
-      </c>
-      <c r="G70" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3664,10 +3664,10 @@
         <v>175</v>
       </c>
       <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
         <v>174</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3687,10 +3687,10 @@
         <v>175</v>
       </c>
       <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
         <v>174</v>
-      </c>
-      <c r="G72" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3710,10 +3710,10 @@
         <v>175</v>
       </c>
       <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
         <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3733,10 +3733,10 @@
         <v>175</v>
       </c>
       <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3756,10 +3756,10 @@
         <v>175</v>
       </c>
       <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
         <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3779,10 +3779,10 @@
         <v>175</v>
       </c>
       <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
         <v>174</v>
-      </c>
-      <c r="G76" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3802,10 +3802,10 @@
         <v>175</v>
       </c>
       <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
         <v>174</v>
-      </c>
-      <c r="G77" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3825,10 +3825,10 @@
         <v>175</v>
       </c>
       <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>174</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3848,10 +3848,10 @@
         <v>175</v>
       </c>
       <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
         <v>174</v>
-      </c>
-      <c r="G79" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3871,10 +3871,10 @@
         <v>175</v>
       </c>
       <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
         <v>174</v>
-      </c>
-      <c r="G80" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3894,10 +3894,10 @@
         <v>199</v>
       </c>
       <c r="F81" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
         <v>198</v>
-      </c>
-      <c r="G81" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3917,10 +3917,10 @@
         <v>199</v>
       </c>
       <c r="F82" t="s">
+        <v>199</v>
+      </c>
+      <c r="G82" t="s">
         <v>198</v>
-      </c>
-      <c r="G82" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3940,10 +3940,10 @@
         <v>199</v>
       </c>
       <c r="F83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G83" t="s">
         <v>198</v>
-      </c>
-      <c r="G83" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3963,10 +3963,10 @@
         <v>199</v>
       </c>
       <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
         <v>198</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3986,10 +3986,10 @@
         <v>199</v>
       </c>
       <c r="F85" t="s">
+        <v>199</v>
+      </c>
+      <c r="G85" t="s">
         <v>198</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4009,10 +4009,10 @@
         <v>199</v>
       </c>
       <c r="F86" t="s">
+        <v>199</v>
+      </c>
+      <c r="G86" t="s">
         <v>198</v>
-      </c>
-      <c r="G86" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4032,10 +4032,10 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" t="s">
         <v>198</v>
-      </c>
-      <c r="G87" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4055,10 +4055,10 @@
         <v>215</v>
       </c>
       <c r="F88" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" t="s">
         <v>214</v>
-      </c>
-      <c r="G88" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4078,10 +4078,10 @@
         <v>215</v>
       </c>
       <c r="F89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" t="s">
         <v>214</v>
-      </c>
-      <c r="G89" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4101,10 +4101,10 @@
         <v>215</v>
       </c>
       <c r="F90" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" t="s">
         <v>214</v>
-      </c>
-      <c r="G90" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4124,10 +4124,10 @@
         <v>215</v>
       </c>
       <c r="F91" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" t="s">
         <v>214</v>
-      </c>
-      <c r="G91" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4236,13 +4236,13 @@
         <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
         <v>226</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4259,13 +4259,13 @@
         <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
         <v>226</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4282,13 +4282,13 @@
         <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
         <v>226</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4305,13 +4305,13 @@
         <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
         <v>226</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4328,13 +4328,13 @@
         <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
         <v>226</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4351,13 +4351,13 @@
         <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F101" t="s">
         <v>226</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4374,13 +4374,13 @@
         <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F102" t="s">
         <v>226</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4397,13 +4397,13 @@
         <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
         <v>226</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4420,13 +4420,13 @@
         <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
         <v>226</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4443,13 +4443,13 @@
         <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
         <v>226</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4466,13 +4466,13 @@
         <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
         <v>226</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4489,13 +4489,13 @@
         <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
         <v>226</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4512,13 +4512,13 @@
         <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
         <v>226</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4535,13 +4535,13 @@
         <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
         <v>226</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4558,13 +4558,13 @@
         <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
         <v>226</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4581,13 +4581,13 @@
         <v>269</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="F111" t="s">
         <v>226</v>
       </c>
       <c r="G111" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4604,13 +4604,13 @@
         <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="F112" t="s">
         <v>226</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4627,13 +4627,13 @@
         <v>277</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F113" t="s">
         <v>226</v>
       </c>
       <c r="G113" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4650,13 +4650,13 @@
         <v>277</v>
       </c>
       <c r="E114" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F114" t="s">
         <v>226</v>
       </c>
       <c r="G114" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4673,13 +4673,13 @@
         <v>277</v>
       </c>
       <c r="E115" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F115" t="s">
         <v>226</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4696,13 +4696,13 @@
         <v>277</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F116" t="s">
         <v>226</v>
       </c>
       <c r="G116" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4719,13 +4719,13 @@
         <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F117" t="s">
         <v>226</v>
       </c>
       <c r="G117" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4742,13 +4742,13 @@
         <v>277</v>
       </c>
       <c r="E118" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F118" t="s">
         <v>226</v>
       </c>
       <c r="G118" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4765,13 +4765,13 @@
         <v>277</v>
       </c>
       <c r="E119" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F119" t="s">
         <v>226</v>
       </c>
       <c r="G119" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4791,10 +4791,10 @@
         <v>294</v>
       </c>
       <c r="F120" t="s">
+        <v>294</v>
+      </c>
+      <c r="G120" t="s">
         <v>293</v>
-      </c>
-      <c r="G120" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4814,10 +4814,10 @@
         <v>294</v>
       </c>
       <c r="F121" t="s">
+        <v>294</v>
+      </c>
+      <c r="G121" t="s">
         <v>293</v>
-      </c>
-      <c r="G121" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4837,10 +4837,10 @@
         <v>294</v>
       </c>
       <c r="F122" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" t="s">
         <v>293</v>
-      </c>
-      <c r="G122" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4860,10 +4860,10 @@
         <v>294</v>
       </c>
       <c r="F123" t="s">
+        <v>294</v>
+      </c>
+      <c r="G123" t="s">
         <v>293</v>
-      </c>
-      <c r="G123" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4883,10 +4883,10 @@
         <v>294</v>
       </c>
       <c r="F124" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
         <v>293</v>
-      </c>
-      <c r="G124" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4906,10 +4906,10 @@
         <v>294</v>
       </c>
       <c r="F125" t="s">
+        <v>294</v>
+      </c>
+      <c r="G125" t="s">
         <v>293</v>
-      </c>
-      <c r="G125" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4929,10 +4929,10 @@
         <v>308</v>
       </c>
       <c r="F126" t="s">
+        <v>308</v>
+      </c>
+      <c r="G126" t="s">
         <v>307</v>
-      </c>
-      <c r="G126" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4952,10 +4952,10 @@
         <v>308</v>
       </c>
       <c r="F127" t="s">
+        <v>308</v>
+      </c>
+      <c r="G127" t="s">
         <v>307</v>
-      </c>
-      <c r="G127" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4975,10 +4975,10 @@
         <v>308</v>
       </c>
       <c r="F128" t="s">
+        <v>308</v>
+      </c>
+      <c r="G128" t="s">
         <v>307</v>
-      </c>
-      <c r="G128" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4998,10 +4998,10 @@
         <v>308</v>
       </c>
       <c r="F129" t="s">
+        <v>308</v>
+      </c>
+      <c r="G129" t="s">
         <v>307</v>
-      </c>
-      <c r="G129" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5432,13 +5432,13 @@
         <v>357</v>
       </c>
       <c r="E148" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F148" t="s">
         <v>319</v>
       </c>
       <c r="G148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5455,13 +5455,13 @@
         <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F149" t="s">
         <v>319</v>
       </c>
       <c r="G149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5478,13 +5478,13 @@
         <v>357</v>
       </c>
       <c r="E150" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F150" t="s">
         <v>319</v>
       </c>
       <c r="G150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5501,13 +5501,13 @@
         <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F151" t="s">
         <v>319</v>
       </c>
       <c r="G151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5524,13 +5524,13 @@
         <v>357</v>
       </c>
       <c r="E152" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F152" t="s">
         <v>319</v>
       </c>
       <c r="G152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5547,13 +5547,13 @@
         <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F153" t="s">
         <v>319</v>
       </c>
       <c r="G153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5570,13 +5570,13 @@
         <v>371</v>
       </c>
       <c r="E154" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F154" t="s">
         <v>319</v>
       </c>
       <c r="G154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5593,13 +5593,13 @@
         <v>371</v>
       </c>
       <c r="E155" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F155" t="s">
         <v>319</v>
       </c>
       <c r="G155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5616,13 +5616,13 @@
         <v>371</v>
       </c>
       <c r="E156" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F156" t="s">
         <v>319</v>
       </c>
       <c r="G156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5639,13 +5639,13 @@
         <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F157" t="s">
         <v>319</v>
       </c>
       <c r="G157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5662,13 +5662,13 @@
         <v>371</v>
       </c>
       <c r="E158" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
       <c r="F158" t="s">
         <v>319</v>
       </c>
       <c r="G158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6122,13 +6122,13 @@
         <v>425</v>
       </c>
       <c r="E178" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F178" t="s">
         <v>385</v>
       </c>
       <c r="G178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6145,13 +6145,13 @@
         <v>425</v>
       </c>
       <c r="E179" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F179" t="s">
         <v>385</v>
       </c>
       <c r="G179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6168,13 +6168,13 @@
         <v>425</v>
       </c>
       <c r="E180" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F180" t="s">
         <v>385</v>
       </c>
       <c r="G180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6191,13 +6191,13 @@
         <v>425</v>
       </c>
       <c r="E181" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F181" t="s">
         <v>385</v>
       </c>
       <c r="G181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6214,13 +6214,13 @@
         <v>425</v>
       </c>
       <c r="E182" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F182" t="s">
         <v>385</v>
       </c>
       <c r="G182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6237,13 +6237,13 @@
         <v>425</v>
       </c>
       <c r="E183" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F183" t="s">
         <v>385</v>
       </c>
       <c r="G183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6260,13 +6260,13 @@
         <v>425</v>
       </c>
       <c r="E184" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F184" t="s">
         <v>385</v>
       </c>
       <c r="G184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6283,13 +6283,13 @@
         <v>425</v>
       </c>
       <c r="E185" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F185" t="s">
         <v>385</v>
       </c>
       <c r="G185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6306,13 +6306,13 @@
         <v>425</v>
       </c>
       <c r="E186" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F186" t="s">
         <v>385</v>
       </c>
       <c r="G186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6329,13 +6329,13 @@
         <v>425</v>
       </c>
       <c r="E187" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="F187" t="s">
         <v>385</v>
       </c>
       <c r="G187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6352,13 +6352,13 @@
         <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="F188" t="s">
         <v>385</v>
       </c>
       <c r="G188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6378,10 +6378,10 @@
         <v>452</v>
       </c>
       <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="G189" t="s">
         <v>451</v>
-      </c>
-      <c r="G189" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6401,10 +6401,10 @@
         <v>452</v>
       </c>
       <c r="F190" t="s">
+        <v>452</v>
+      </c>
+      <c r="G190" t="s">
         <v>451</v>
-      </c>
-      <c r="G190" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6424,10 +6424,10 @@
         <v>452</v>
       </c>
       <c r="F191" t="s">
+        <v>452</v>
+      </c>
+      <c r="G191" t="s">
         <v>451</v>
-      </c>
-      <c r="G191" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6447,10 +6447,10 @@
         <v>452</v>
       </c>
       <c r="F192" t="s">
+        <v>452</v>
+      </c>
+      <c r="G192" t="s">
         <v>451</v>
-      </c>
-      <c r="G192" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6470,10 +6470,10 @@
         <v>452</v>
       </c>
       <c r="F193" t="s">
+        <v>452</v>
+      </c>
+      <c r="G193" t="s">
         <v>451</v>
-      </c>
-      <c r="G193" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6493,10 +6493,10 @@
         <v>452</v>
       </c>
       <c r="F194" t="s">
+        <v>452</v>
+      </c>
+      <c r="G194" t="s">
         <v>451</v>
-      </c>
-      <c r="G194" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6516,10 +6516,10 @@
         <v>466</v>
       </c>
       <c r="F195" t="s">
+        <v>466</v>
+      </c>
+      <c r="G195" t="s">
         <v>465</v>
-      </c>
-      <c r="G195" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6539,10 +6539,10 @@
         <v>470</v>
       </c>
       <c r="F196" t="s">
+        <v>470</v>
+      </c>
+      <c r="G196" t="s">
         <v>469</v>
-      </c>
-      <c r="G196" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6562,10 +6562,10 @@
         <v>470</v>
       </c>
       <c r="F197" t="s">
+        <v>470</v>
+      </c>
+      <c r="G197" t="s">
         <v>469</v>
-      </c>
-      <c r="G197" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6585,10 +6585,10 @@
         <v>470</v>
       </c>
       <c r="F198" t="s">
+        <v>470</v>
+      </c>
+      <c r="G198" t="s">
         <v>469</v>
-      </c>
-      <c r="G198" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6608,10 +6608,10 @@
         <v>470</v>
       </c>
       <c r="F199" t="s">
+        <v>470</v>
+      </c>
+      <c r="G199" t="s">
         <v>469</v>
-      </c>
-      <c r="G199" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6631,10 +6631,10 @@
         <v>470</v>
       </c>
       <c r="F200" t="s">
+        <v>470</v>
+      </c>
+      <c r="G200" t="s">
         <v>469</v>
-      </c>
-      <c r="G200" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6654,10 +6654,10 @@
         <v>470</v>
       </c>
       <c r="F201" t="s">
+        <v>470</v>
+      </c>
+      <c r="G201" t="s">
         <v>469</v>
-      </c>
-      <c r="G201" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6677,10 +6677,10 @@
         <v>484</v>
       </c>
       <c r="F202" t="s">
+        <v>484</v>
+      </c>
+      <c r="G202" t="s">
         <v>483</v>
-      </c>
-      <c r="G202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6700,10 +6700,10 @@
         <v>484</v>
       </c>
       <c r="F203" t="s">
+        <v>484</v>
+      </c>
+      <c r="G203" t="s">
         <v>483</v>
-      </c>
-      <c r="G203" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6723,10 +6723,10 @@
         <v>484</v>
       </c>
       <c r="F204" t="s">
+        <v>484</v>
+      </c>
+      <c r="G204" t="s">
         <v>483</v>
-      </c>
-      <c r="G204" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6746,10 +6746,10 @@
         <v>484</v>
       </c>
       <c r="F205" t="s">
+        <v>484</v>
+      </c>
+      <c r="G205" t="s">
         <v>483</v>
-      </c>
-      <c r="G205" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>484</v>
       </c>
       <c r="F206" t="s">
+        <v>484</v>
+      </c>
+      <c r="G206" t="s">
         <v>483</v>
-      </c>
-      <c r="G206" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6792,10 +6792,10 @@
         <v>484</v>
       </c>
       <c r="F207" t="s">
+        <v>484</v>
+      </c>
+      <c r="G207" t="s">
         <v>483</v>
-      </c>
-      <c r="G207" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6815,10 +6815,10 @@
         <v>484</v>
       </c>
       <c r="F208" t="s">
+        <v>484</v>
+      </c>
+      <c r="G208" t="s">
         <v>483</v>
-      </c>
-      <c r="G208" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6838,10 +6838,10 @@
         <v>484</v>
       </c>
       <c r="F209" t="s">
+        <v>484</v>
+      </c>
+      <c r="G209" t="s">
         <v>483</v>
-      </c>
-      <c r="G209" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6861,10 +6861,10 @@
         <v>484</v>
       </c>
       <c r="F210" t="s">
+        <v>484</v>
+      </c>
+      <c r="G210" t="s">
         <v>483</v>
-      </c>
-      <c r="G210" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6884,10 +6884,10 @@
         <v>484</v>
       </c>
       <c r="F211" t="s">
+        <v>484</v>
+      </c>
+      <c r="G211" t="s">
         <v>483</v>
-      </c>
-      <c r="G211" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6907,10 +6907,10 @@
         <v>506</v>
       </c>
       <c r="F212" t="s">
+        <v>506</v>
+      </c>
+      <c r="G212" t="s">
         <v>505</v>
-      </c>
-      <c r="G212" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6930,10 +6930,10 @@
         <v>510</v>
       </c>
       <c r="F213" t="s">
+        <v>510</v>
+      </c>
+      <c r="G213" t="s">
         <v>509</v>
-      </c>
-      <c r="G213" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6953,10 +6953,10 @@
         <v>514</v>
       </c>
       <c r="F214" t="s">
+        <v>514</v>
+      </c>
+      <c r="G214" t="s">
         <v>513</v>
-      </c>
-      <c r="G214" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6976,10 +6976,10 @@
         <v>514</v>
       </c>
       <c r="F215" t="s">
+        <v>514</v>
+      </c>
+      <c r="G215" t="s">
         <v>513</v>
-      </c>
-      <c r="G215" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6999,10 +6999,10 @@
         <v>520</v>
       </c>
       <c r="F216" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" t="s">
         <v>519</v>
-      </c>
-      <c r="G216" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7022,10 +7022,10 @@
         <v>520</v>
       </c>
       <c r="F217" t="s">
+        <v>520</v>
+      </c>
+      <c r="G217" t="s">
         <v>519</v>
-      </c>
-      <c r="G217" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7045,10 +7045,10 @@
         <v>520</v>
       </c>
       <c r="F218" t="s">
+        <v>520</v>
+      </c>
+      <c r="G218" t="s">
         <v>519</v>
-      </c>
-      <c r="G218" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7068,10 +7068,10 @@
         <v>520</v>
       </c>
       <c r="F219" t="s">
+        <v>520</v>
+      </c>
+      <c r="G219" t="s">
         <v>519</v>
-      </c>
-      <c r="G219" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7091,10 +7091,10 @@
         <v>520</v>
       </c>
       <c r="F220" t="s">
+        <v>520</v>
+      </c>
+      <c r="G220" t="s">
         <v>519</v>
-      </c>
-      <c r="G220" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7114,10 +7114,10 @@
         <v>520</v>
       </c>
       <c r="F221" t="s">
+        <v>520</v>
+      </c>
+      <c r="G221" t="s">
         <v>519</v>
-      </c>
-      <c r="G221" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7137,10 +7137,10 @@
         <v>520</v>
       </c>
       <c r="F222" t="s">
+        <v>520</v>
+      </c>
+      <c r="G222" t="s">
         <v>519</v>
-      </c>
-      <c r="G222" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7160,10 +7160,10 @@
         <v>536</v>
       </c>
       <c r="F223" t="s">
+        <v>536</v>
+      </c>
+      <c r="G223" t="s">
         <v>535</v>
-      </c>
-      <c r="G223" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7183,10 +7183,10 @@
         <v>536</v>
       </c>
       <c r="F224" t="s">
+        <v>536</v>
+      </c>
+      <c r="G224" t="s">
         <v>535</v>
-      </c>
-      <c r="G224" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7206,10 +7206,10 @@
         <v>536</v>
       </c>
       <c r="F225" t="s">
+        <v>536</v>
+      </c>
+      <c r="G225" t="s">
         <v>535</v>
-      </c>
-      <c r="G225" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7229,10 +7229,10 @@
         <v>544</v>
       </c>
       <c r="F226" t="s">
+        <v>544</v>
+      </c>
+      <c r="G226" t="s">
         <v>543</v>
-      </c>
-      <c r="G226" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7252,10 +7252,10 @@
         <v>548</v>
       </c>
       <c r="F227" t="s">
+        <v>548</v>
+      </c>
+      <c r="G227" t="s">
         <v>547</v>
-      </c>
-      <c r="G227" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7275,10 +7275,10 @@
         <v>552</v>
       </c>
       <c r="F228" t="s">
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
         <v>551</v>
-      </c>
-      <c r="G228" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7298,10 +7298,10 @@
         <v>556</v>
       </c>
       <c r="F229" t="s">
+        <v>556</v>
+      </c>
+      <c r="G229" t="s">
         <v>555</v>
-      </c>
-      <c r="G229" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7321,10 +7321,10 @@
         <v>560</v>
       </c>
       <c r="F230" t="s">
+        <v>560</v>
+      </c>
+      <c r="G230" t="s">
         <v>559</v>
-      </c>
-      <c r="G230" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7344,10 +7344,10 @@
         <v>560</v>
       </c>
       <c r="F231" t="s">
+        <v>560</v>
+      </c>
+      <c r="G231" t="s">
         <v>559</v>
-      </c>
-      <c r="G231" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Distribution d'Eau et Assainissement</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Infrastructure et Services Sociaux Divers</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transports et Entreposage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banques et Services Financiers</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Entreprises et Autres Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Politique Commerciale et Réglementations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourisme</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>Protection de l'Environnement Général</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Autres Multisecteurs</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>Soutien Budgétaire</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Aide Alimentaire Dévelopmentale</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Aide sous forme de Produits, Autre</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Actions se Rapportant a la Dette</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Intervention d'Urgence</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction &amp; Réhabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Prévention catastrophes/Préparation à leur survenue</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Frais Administratifs des Donneurs</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugiés dans les Pays Donneurs</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Non Affecté / Non Specifié</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>39</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>39</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
-      </c>
-      <c r="E18" t="s">
-        <v>57</v>
       </c>
       <c r="F18" t="s">
         <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>57</v>
       </c>
       <c r="F19" t="s">
         <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>57</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
-      </c>
-      <c r="E21" t="s">
-        <v>57</v>
       </c>
       <c r="F21" t="s">
         <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>56</v>
-      </c>
-      <c r="E22" t="s">
-        <v>57</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
-      </c>
-      <c r="E23" t="s">
-        <v>57</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
         <v>56</v>
-      </c>
-      <c r="E24" t="s">
-        <v>57</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>56</v>
-      </c>
-      <c r="E25" t="s">
-        <v>57</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
       </c>
       <c r="G25" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
-      </c>
-      <c r="E26" t="s">
-        <v>75</v>
       </c>
       <c r="F26" t="s">
         <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>74</v>
-      </c>
-      <c r="E27" t="s">
-        <v>75</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
         <v>74</v>
-      </c>
-      <c r="E28" t="s">
-        <v>75</v>
       </c>
       <c r="F28" t="s">
         <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
         <v>74</v>
-      </c>
-      <c r="E29" t="s">
-        <v>75</v>
       </c>
       <c r="F29" t="s">
         <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
         <v>74</v>
-      </c>
-      <c r="E30" t="s">
-        <v>75</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
         <v>74</v>
-      </c>
-      <c r="E31" t="s">
-        <v>75</v>
       </c>
       <c r="F31" t="s">
         <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
         <v>160</v>
-      </c>
-      <c r="E64" t="s">
-        <v>161</v>
       </c>
       <c r="F64" t="s">
         <v>126</v>
       </c>
       <c r="G64" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
         <v>160</v>
-      </c>
-      <c r="E65" t="s">
-        <v>161</v>
       </c>
       <c r="F65" t="s">
         <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
         <v>160</v>
-      </c>
-      <c r="E66" t="s">
-        <v>161</v>
       </c>
       <c r="F66" t="s">
         <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
         <v>160</v>
-      </c>
-      <c r="E67" t="s">
-        <v>161</v>
       </c>
       <c r="F67" t="s">
         <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
         <v>160</v>
-      </c>
-      <c r="E68" t="s">
-        <v>161</v>
       </c>
       <c r="F68" t="s">
         <v>126</v>
       </c>
       <c r="G68" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
         <v>160</v>
-      </c>
-      <c r="E69" t="s">
-        <v>161</v>
       </c>
       <c r="F69" t="s">
         <v>126</v>
       </c>
       <c r="G69" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
         <v>236</v>
-      </c>
-      <c r="E96" t="s">
-        <v>237</v>
       </c>
       <c r="F96" t="s">
         <v>226</v>
       </c>
       <c r="G96" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
         <v>236</v>
-      </c>
-      <c r="E97" t="s">
-        <v>237</v>
       </c>
       <c r="F97" t="s">
         <v>226</v>
       </c>
       <c r="G97" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" t="s">
         <v>236</v>
-      </c>
-      <c r="E98" t="s">
-        <v>237</v>
       </c>
       <c r="F98" t="s">
         <v>226</v>
       </c>
       <c r="G98" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
         <v>236</v>
-      </c>
-      <c r="E99" t="s">
-        <v>237</v>
       </c>
       <c r="F99" t="s">
         <v>226</v>
       </c>
       <c r="G99" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
         <v>236</v>
-      </c>
-      <c r="E100" t="s">
-        <v>237</v>
       </c>
       <c r="F100" t="s">
         <v>226</v>
       </c>
       <c r="G100" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
         <v>236</v>
-      </c>
-      <c r="E101" t="s">
-        <v>237</v>
       </c>
       <c r="F101" t="s">
         <v>226</v>
       </c>
       <c r="G101" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
         <v>236</v>
-      </c>
-      <c r="E102" t="s">
-        <v>237</v>
       </c>
       <c r="F102" t="s">
         <v>226</v>
       </c>
       <c r="G102" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
-      </c>
-      <c r="E103" t="s">
-        <v>237</v>
       </c>
       <c r="F103" t="s">
         <v>226</v>
       </c>
       <c r="G103" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
         <v>236</v>
-      </c>
-      <c r="E104" t="s">
-        <v>237</v>
       </c>
       <c r="F104" t="s">
         <v>226</v>
       </c>
       <c r="G104" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
         <v>256</v>
-      </c>
-      <c r="E105" t="s">
-        <v>257</v>
       </c>
       <c r="F105" t="s">
         <v>226</v>
       </c>
       <c r="G105" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" t="s">
         <v>256</v>
-      </c>
-      <c r="E106" t="s">
-        <v>257</v>
       </c>
       <c r="F106" t="s">
         <v>226</v>
       </c>
       <c r="G106" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
         <v>256</v>
-      </c>
-      <c r="E107" t="s">
-        <v>257</v>
       </c>
       <c r="F107" t="s">
         <v>226</v>
       </c>
       <c r="G107" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
         <v>256</v>
-      </c>
-      <c r="E108" t="s">
-        <v>257</v>
       </c>
       <c r="F108" t="s">
         <v>226</v>
       </c>
       <c r="G108" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
         <v>256</v>
-      </c>
-      <c r="E109" t="s">
-        <v>257</v>
       </c>
       <c r="F109" t="s">
         <v>226</v>
       </c>
       <c r="G109" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
         <v>256</v>
-      </c>
-      <c r="E110" t="s">
-        <v>257</v>
       </c>
       <c r="F110" t="s">
         <v>226</v>
       </c>
       <c r="G110" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
         <v>269</v>
-      </c>
-      <c r="E111" t="s">
-        <v>270</v>
       </c>
       <c r="F111" t="s">
         <v>226</v>
       </c>
       <c r="G111" t="s">
-        <v>227</v>
+        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
         <v>273</v>
-      </c>
-      <c r="E112" t="s">
-        <v>274</v>
       </c>
       <c r="F112" t="s">
         <v>226</v>
       </c>
       <c r="G112" t="s">
-        <v>227</v>
+        <v>274</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
         <v>277</v>
-      </c>
-      <c r="E113" t="s">
-        <v>278</v>
       </c>
       <c r="F113" t="s">
         <v>226</v>
       </c>
       <c r="G113" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
         <v>277</v>
-      </c>
-      <c r="E114" t="s">
-        <v>278</v>
       </c>
       <c r="F114" t="s">
         <v>226</v>
       </c>
       <c r="G114" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
         <v>277</v>
-      </c>
-      <c r="E115" t="s">
-        <v>278</v>
       </c>
       <c r="F115" t="s">
         <v>226</v>
       </c>
       <c r="G115" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
         <v>277</v>
-      </c>
-      <c r="E116" t="s">
-        <v>278</v>
       </c>
       <c r="F116" t="s">
         <v>226</v>
       </c>
       <c r="G116" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
         <v>277</v>
-      </c>
-      <c r="E117" t="s">
-        <v>278</v>
       </c>
       <c r="F117" t="s">
         <v>226</v>
       </c>
       <c r="G117" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
         <v>277</v>
-      </c>
-      <c r="E118" t="s">
-        <v>278</v>
       </c>
       <c r="F118" t="s">
         <v>226</v>
       </c>
       <c r="G118" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
         <v>277</v>
-      </c>
-      <c r="E119" t="s">
-        <v>278</v>
       </c>
       <c r="F119" t="s">
         <v>226</v>
       </c>
       <c r="G119" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
+        <v>317</v>
+      </c>
+      <c r="E148" t="s">
         <v>357</v>
-      </c>
-      <c r="E148" t="s">
-        <v>358</v>
       </c>
       <c r="F148" t="s">
         <v>319</v>
       </c>
       <c r="G148" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
+        <v>317</v>
+      </c>
+      <c r="E149" t="s">
         <v>357</v>
-      </c>
-      <c r="E149" t="s">
-        <v>358</v>
       </c>
       <c r="F149" t="s">
         <v>319</v>
       </c>
       <c r="G149" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
+        <v>317</v>
+      </c>
+      <c r="E150" t="s">
         <v>357</v>
-      </c>
-      <c r="E150" t="s">
-        <v>358</v>
       </c>
       <c r="F150" t="s">
         <v>319</v>
       </c>
       <c r="G150" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>317</v>
+      </c>
+      <c r="E151" t="s">
         <v>357</v>
-      </c>
-      <c r="E151" t="s">
-        <v>358</v>
       </c>
       <c r="F151" t="s">
         <v>319</v>
       </c>
       <c r="G151" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>317</v>
+      </c>
+      <c r="E152" t="s">
         <v>357</v>
-      </c>
-      <c r="E152" t="s">
-        <v>358</v>
       </c>
       <c r="F152" t="s">
         <v>319</v>
       </c>
       <c r="G152" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>317</v>
+      </c>
+      <c r="E153" t="s">
         <v>357</v>
-      </c>
-      <c r="E153" t="s">
-        <v>358</v>
       </c>
       <c r="F153" t="s">
         <v>319</v>
       </c>
       <c r="G153" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>317</v>
+      </c>
+      <c r="E154" t="s">
         <v>371</v>
-      </c>
-      <c r="E154" t="s">
-        <v>372</v>
       </c>
       <c r="F154" t="s">
         <v>319</v>
       </c>
       <c r="G154" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>317</v>
+      </c>
+      <c r="E155" t="s">
         <v>371</v>
-      </c>
-      <c r="E155" t="s">
-        <v>372</v>
       </c>
       <c r="F155" t="s">
         <v>319</v>
       </c>
       <c r="G155" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>317</v>
+      </c>
+      <c r="E156" t="s">
         <v>371</v>
-      </c>
-      <c r="E156" t="s">
-        <v>372</v>
       </c>
       <c r="F156" t="s">
         <v>319</v>
       </c>
       <c r="G156" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>317</v>
+      </c>
+      <c r="E157" t="s">
         <v>371</v>
-      </c>
-      <c r="E157" t="s">
-        <v>372</v>
       </c>
       <c r="F157" t="s">
         <v>319</v>
       </c>
       <c r="G157" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>317</v>
+      </c>
+      <c r="E158" t="s">
         <v>371</v>
-      </c>
-      <c r="E158" t="s">
-        <v>372</v>
       </c>
       <c r="F158" t="s">
         <v>319</v>
       </c>
       <c r="G158" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
+        <v>383</v>
+      </c>
+      <c r="E178" t="s">
         <v>425</v>
-      </c>
-      <c r="E178" t="s">
-        <v>426</v>
       </c>
       <c r="F178" t="s">
         <v>385</v>
       </c>
       <c r="G178" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
+        <v>383</v>
+      </c>
+      <c r="E179" t="s">
         <v>425</v>
-      </c>
-      <c r="E179" t="s">
-        <v>426</v>
       </c>
       <c r="F179" t="s">
         <v>385</v>
       </c>
       <c r="G179" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
+        <v>383</v>
+      </c>
+      <c r="E180" t="s">
         <v>425</v>
-      </c>
-      <c r="E180" t="s">
-        <v>426</v>
       </c>
       <c r="F180" t="s">
         <v>385</v>
       </c>
       <c r="G180" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
+        <v>383</v>
+      </c>
+      <c r="E181" t="s">
         <v>425</v>
-      </c>
-      <c r="E181" t="s">
-        <v>426</v>
       </c>
       <c r="F181" t="s">
         <v>385</v>
       </c>
       <c r="G181" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>383</v>
+      </c>
+      <c r="E182" t="s">
         <v>425</v>
-      </c>
-      <c r="E182" t="s">
-        <v>426</v>
       </c>
       <c r="F182" t="s">
         <v>385</v>
       </c>
       <c r="G182" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6234,16 +6234,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>383</v>
+      </c>
+      <c r="E183" t="s">
         <v>425</v>
-      </c>
-      <c r="E183" t="s">
-        <v>426</v>
       </c>
       <c r="F183" t="s">
         <v>385</v>
       </c>
       <c r="G183" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6257,16 +6257,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>383</v>
+      </c>
+      <c r="E184" t="s">
         <v>425</v>
-      </c>
-      <c r="E184" t="s">
-        <v>426</v>
       </c>
       <c r="F184" t="s">
         <v>385</v>
       </c>
       <c r="G184" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6280,16 +6280,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>383</v>
+      </c>
+      <c r="E185" t="s">
         <v>425</v>
-      </c>
-      <c r="E185" t="s">
-        <v>426</v>
       </c>
       <c r="F185" t="s">
         <v>385</v>
       </c>
       <c r="G185" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6303,16 +6303,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>383</v>
+      </c>
+      <c r="E186" t="s">
         <v>425</v>
-      </c>
-      <c r="E186" t="s">
-        <v>426</v>
       </c>
       <c r="F186" t="s">
         <v>385</v>
       </c>
       <c r="G186" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6326,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>383</v>
+      </c>
+      <c r="E187" t="s">
         <v>425</v>
-      </c>
-      <c r="E187" t="s">
-        <v>426</v>
       </c>
       <c r="F187" t="s">
         <v>385</v>
       </c>
       <c r="G187" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6349,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>383</v>
+      </c>
+      <c r="E188" t="s">
         <v>447</v>
-      </c>
-      <c r="E188" t="s">
-        <v>448</v>
       </c>
       <c r="F188" t="s">
         <v>385</v>
       </c>
       <c r="G188" t="s">
-        <v>386</v>
+        <v>448</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>Distribution d'Eau et Assainissement</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Distribution d'Eau et Assainissement</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>Infrastructure et Services Sociaux Divers</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Infrastructure et Services Sociaux Divers</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>Transports et Entreposage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transports et Entreposage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>Banques et Services Financiers</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banques et Services Financiers</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>Entreprises et Autres Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Entreprises et Autres Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,15 +967,15 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1165,15 +1165,15 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>Politique Commerciale et Réglementations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Politique Commerciale et Réglementations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>Tourisme</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourisme</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>Protection de l'Environnement Général</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protection de l'Environnement Général</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>Autres Multisecteurs</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Autres Multisecteurs</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>Soutien Budgétaire</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Soutien Budgétaire</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>Aide Alimentaire Dévelopmentale</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Aide Alimentaire Dévelopmentale</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>Aide sous forme de Produits, Autre</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Aide sous forme de Produits, Autre</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>Actions se Rapportant a la Dette</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actions se Rapportant a la Dette</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>Intervention d'Urgence</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Intervention d'Urgence</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>Reconstruction &amp; Réhabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction &amp; Réhabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>Prévention catastrophes/Préparation à leur survenue</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prévention catastrophes/Préparation à leur survenue</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>Frais Administratifs des Donneurs</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Frais Administratifs des Donneurs</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>Refugiés dans les Pays Donneurs</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiés dans les Pays Donneurs</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>Non Affecté / Non Specifié</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Non Affecté / Non Specifié</t>
   </si>
   <si>
     <t>99820</t>
@@ -2764,13 +2764,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2787,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2810,13 +2810,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2833,13 +2833,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2856,13 +2856,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2879,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2902,13 +2902,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2925,13 +2925,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2971,13 +2971,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2994,13 +2994,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3017,13 +3017,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3040,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3063,13 +3063,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3086,13 +3086,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3109,13 +3109,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3638,13 +3638,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3661,13 +3661,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3684,13 +3684,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3707,13 +3707,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3730,13 +3730,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3753,13 +3753,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3776,13 +3776,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3799,13 +3799,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3822,13 +3822,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3845,13 +3845,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3868,13 +3868,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3891,13 +3891,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3914,13 +3914,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3937,13 +3937,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3960,13 +3960,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3983,13 +3983,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4006,13 +4006,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4029,13 +4029,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4052,13 +4052,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4075,13 +4075,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4098,13 +4098,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4121,13 +4121,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4788,13 +4788,13 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F120" t="s">
         <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4811,13 +4811,13 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F121" t="s">
         <v>294</v>
       </c>
       <c r="G121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4834,13 +4834,13 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F122" t="s">
         <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4857,13 +4857,13 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F123" t="s">
         <v>294</v>
       </c>
       <c r="G123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4880,13 +4880,13 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F124" t="s">
         <v>294</v>
       </c>
       <c r="G124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4903,13 +4903,13 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F125" t="s">
         <v>294</v>
       </c>
       <c r="G125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4926,13 +4926,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F126" t="s">
         <v>308</v>
       </c>
       <c r="G126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4949,13 +4949,13 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F127" t="s">
         <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4972,13 +4972,13 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F128" t="s">
         <v>308</v>
       </c>
       <c r="G128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4995,13 +4995,13 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F129" t="s">
         <v>308</v>
       </c>
       <c r="G129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6375,13 +6375,13 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F189" t="s">
         <v>452</v>
       </c>
       <c r="G189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6398,13 +6398,13 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F190" t="s">
         <v>452</v>
       </c>
       <c r="G190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6421,13 +6421,13 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F191" t="s">
         <v>452</v>
       </c>
       <c r="G191" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6444,13 +6444,13 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F192" t="s">
         <v>452</v>
       </c>
       <c r="G192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6467,13 +6467,13 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F193" t="s">
         <v>452</v>
       </c>
       <c r="G193" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6490,13 +6490,13 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F194" t="s">
         <v>452</v>
       </c>
       <c r="G194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6513,13 +6513,13 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F195" t="s">
         <v>466</v>
       </c>
       <c r="G195" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6536,13 +6536,13 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F196" t="s">
         <v>470</v>
       </c>
       <c r="G196" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6559,13 +6559,13 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F197" t="s">
         <v>470</v>
       </c>
       <c r="G197" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6582,13 +6582,13 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F198" t="s">
         <v>470</v>
       </c>
       <c r="G198" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6605,13 +6605,13 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F199" t="s">
         <v>470</v>
       </c>
       <c r="G199" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6628,13 +6628,13 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F200" t="s">
         <v>470</v>
       </c>
       <c r="G200" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6651,13 +6651,13 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F201" t="s">
         <v>470</v>
       </c>
       <c r="G201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6674,13 +6674,13 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F202" t="s">
         <v>484</v>
       </c>
       <c r="G202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6697,13 +6697,13 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F203" t="s">
         <v>484</v>
       </c>
       <c r="G203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6720,13 +6720,13 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F204" t="s">
         <v>484</v>
       </c>
       <c r="G204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6743,13 +6743,13 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F205" t="s">
         <v>484</v>
       </c>
       <c r="G205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6766,13 +6766,13 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F206" t="s">
         <v>484</v>
       </c>
       <c r="G206" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6789,13 +6789,13 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F207" t="s">
         <v>484</v>
       </c>
       <c r="G207" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6812,13 +6812,13 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F208" t="s">
         <v>484</v>
       </c>
       <c r="G208" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6835,13 +6835,13 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F209" t="s">
         <v>484</v>
       </c>
       <c r="G209" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6858,13 +6858,13 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F210" t="s">
         <v>484</v>
       </c>
       <c r="G210" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6881,13 +6881,13 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F211" t="s">
         <v>484</v>
       </c>
       <c r="G211" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6904,13 +6904,13 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F212" t="s">
         <v>506</v>
       </c>
       <c r="G212" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6927,13 +6927,13 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F213" t="s">
         <v>510</v>
       </c>
       <c r="G213" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6950,13 +6950,13 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F214" t="s">
         <v>514</v>
       </c>
       <c r="G214" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6973,13 +6973,13 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F215" t="s">
         <v>514</v>
       </c>
       <c r="G215" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6996,13 +6996,13 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F216" t="s">
         <v>520</v>
       </c>
       <c r="G216" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7019,13 +7019,13 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F217" t="s">
         <v>520</v>
       </c>
       <c r="G217" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7042,13 +7042,13 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F218" t="s">
         <v>520</v>
       </c>
       <c r="G218" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7065,13 +7065,13 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F219" t="s">
         <v>520</v>
       </c>
       <c r="G219" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7088,13 +7088,13 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F220" t="s">
         <v>520</v>
       </c>
       <c r="G220" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7111,13 +7111,13 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F221" t="s">
         <v>520</v>
       </c>
       <c r="G221" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7134,13 +7134,13 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F222" t="s">
         <v>520</v>
       </c>
       <c r="G222" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7157,13 +7157,13 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F223" t="s">
         <v>536</v>
       </c>
       <c r="G223" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7180,13 +7180,13 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F224" t="s">
         <v>536</v>
       </c>
       <c r="G224" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7203,13 +7203,13 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F225" t="s">
         <v>536</v>
       </c>
       <c r="G225" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7226,13 +7226,13 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F226" t="s">
         <v>544</v>
       </c>
       <c r="G226" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7249,13 +7249,13 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F227" t="s">
         <v>548</v>
       </c>
       <c r="G227" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7272,13 +7272,13 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F228" t="s">
         <v>552</v>
       </c>
       <c r="G228" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7295,13 +7295,13 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F229" t="s">
         <v>556</v>
       </c>
       <c r="G229" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7318,13 +7318,13 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F230" t="s">
         <v>560</v>
       </c>
       <c r="G230" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7341,13 +7341,13 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F231" t="s">
         <v>560</v>
       </c>
       <c r="G231" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
+    <t>codeforiati:category-code</t>
   </si>
   <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>Education, Niveau non spécifié</t>
+    <t>111</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
     <t>Santé</t>
   </si>
   <si>
-    <t>Santé, Général</t>
+    <t>121</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
+    <t>151</t>
   </si>
   <si>
     <t>150</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
     <t>Energie</t>
   </si>
   <si>
-    <t>Politique de l'énergie</t>
+    <t>231</t>
   </si>
   <si>
     <t>230</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
-    <t>Agriculture</t>
+    <t>311</t>
   </si>
   <si>
     <t>310</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1165,16 +1165,16 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
-    <t>Industries Manufacturières</t>
+    <t>321</t>
   </si>
   <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>32120</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="E111" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="G111" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
-        <v>273</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G116" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E118" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G118" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E119" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="G119" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E148" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F148" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F149" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E150" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F150" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F151" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E152" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F152" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F153" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E154" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F154" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E155" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F155" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F156" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F157" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E158" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="F158" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E178" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F178" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E179" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F179" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E180" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F180" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E181" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F181" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E182" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F182" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G182" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6234,16 +6234,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E183" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F183" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G183" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6257,16 +6257,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E184" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F184" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G184" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6280,16 +6280,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E185" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F185" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G185" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6303,16 +6303,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E186" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F186" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G186" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6326,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E187" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="F187" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G187" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6349,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>447</v>
+        <v>384</v>
       </c>
       <c r="F188" t="s">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="G188" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>Santé, Général</t>
   </si>
   <si>
-    <t>Santé</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Distribution d'Eau et Assainissement</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Infrastructure et Services Sociaux Divers</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transports et Entreposage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banques et Services Financiers</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Entreprises et Autres Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Politique Commerciale et Réglementations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourisme</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>Protection de l'Environnement Général</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Autres Multisecteurs</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>Soutien Budgétaire</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Aide Alimentaire Dévelopmentale</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Aide sous forme de Produits, Autre</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Actions se Rapportant a la Dette</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Intervention d'Urgence</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction &amp; Réhabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Prévention catastrophes/Préparation à leur survenue</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Frais Administratifs des Donneurs</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugiés dans les Pays Donneurs</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Non Affecté / Non Specifié</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" t="s">
         <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" t="s">
         <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" t="s">
         <v>57</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" t="s">
         <v>57</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" t="s">
         <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28" t="s">
         <v>75</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s">
         <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s">
         <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s">
         <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2764,13 +2764,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2787,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2810,13 +2810,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2833,13 +2833,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2856,13 +2856,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2879,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2902,13 +2902,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2925,13 +2925,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2971,13 +2971,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2994,13 +2994,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3017,13 +3017,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3040,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3063,13 +3063,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3086,13 +3086,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3109,13 +3109,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
+        <v>160</v>
+      </c>
+      <c r="G64" t="s">
         <v>161</v>
-      </c>
-      <c r="G64" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
+        <v>160</v>
+      </c>
+      <c r="G65" t="s">
         <v>161</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
+        <v>160</v>
+      </c>
+      <c r="G66" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
+        <v>160</v>
+      </c>
+      <c r="G67" t="s">
         <v>161</v>
-      </c>
-      <c r="G67" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
+        <v>160</v>
+      </c>
+      <c r="G68" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
+        <v>160</v>
+      </c>
+      <c r="G69" t="s">
         <v>161</v>
-      </c>
-      <c r="G69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3638,13 +3638,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3661,13 +3661,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3684,13 +3684,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3707,13 +3707,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3730,13 +3730,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3753,13 +3753,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3776,13 +3776,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3799,13 +3799,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3822,13 +3822,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3845,13 +3845,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3868,13 +3868,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3891,13 +3891,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3914,13 +3914,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3937,13 +3937,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3960,13 +3960,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3983,13 +3983,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4006,13 +4006,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4029,13 +4029,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4052,13 +4052,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4075,13 +4075,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4098,13 +4098,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4121,13 +4121,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
+        <v>236</v>
+      </c>
+      <c r="G96" t="s">
         <v>237</v>
-      </c>
-      <c r="G96" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
+        <v>236</v>
+      </c>
+      <c r="G97" t="s">
         <v>237</v>
-      </c>
-      <c r="G97" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
+        <v>236</v>
+      </c>
+      <c r="G98" t="s">
         <v>237</v>
-      </c>
-      <c r="G98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
+        <v>236</v>
+      </c>
+      <c r="G99" t="s">
         <v>237</v>
-      </c>
-      <c r="G99" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
+        <v>236</v>
+      </c>
+      <c r="G100" t="s">
         <v>237</v>
-      </c>
-      <c r="G100" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
+        <v>236</v>
+      </c>
+      <c r="G101" t="s">
         <v>237</v>
-      </c>
-      <c r="G101" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
+        <v>236</v>
+      </c>
+      <c r="G102" t="s">
         <v>237</v>
-      </c>
-      <c r="G102" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
+        <v>236</v>
+      </c>
+      <c r="G103" t="s">
         <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
+        <v>236</v>
+      </c>
+      <c r="G104" t="s">
         <v>237</v>
-      </c>
-      <c r="G104" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
+        <v>256</v>
+      </c>
+      <c r="G105" t="s">
         <v>257</v>
-      </c>
-      <c r="G105" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
+        <v>256</v>
+      </c>
+      <c r="G106" t="s">
         <v>257</v>
-      </c>
-      <c r="G106" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
+        <v>256</v>
+      </c>
+      <c r="G107" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
+        <v>256</v>
+      </c>
+      <c r="G108" t="s">
         <v>257</v>
-      </c>
-      <c r="G108" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
+        <v>256</v>
+      </c>
+      <c r="G109" t="s">
         <v>257</v>
-      </c>
-      <c r="G109" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
+        <v>256</v>
+      </c>
+      <c r="G110" t="s">
         <v>257</v>
-      </c>
-      <c r="G110" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>269</v>
+        <v>224</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
+        <v>269</v>
+      </c>
+      <c r="G111" t="s">
         <v>270</v>
-      </c>
-      <c r="G111" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
+        <v>273</v>
+      </c>
+      <c r="G112" t="s">
         <v>274</v>
-      </c>
-      <c r="G112" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
+        <v>277</v>
+      </c>
+      <c r="G113" t="s">
         <v>278</v>
-      </c>
-      <c r="G113" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
+        <v>277</v>
+      </c>
+      <c r="G114" t="s">
         <v>278</v>
-      </c>
-      <c r="G114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
+        <v>277</v>
+      </c>
+      <c r="G115" t="s">
         <v>278</v>
-      </c>
-      <c r="G115" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
+        <v>277</v>
+      </c>
+      <c r="G116" t="s">
         <v>278</v>
-      </c>
-      <c r="G116" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
+        <v>277</v>
+      </c>
+      <c r="G117" t="s">
         <v>278</v>
-      </c>
-      <c r="G117" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
+        <v>277</v>
+      </c>
+      <c r="G118" t="s">
         <v>278</v>
-      </c>
-      <c r="G118" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
+        <v>277</v>
+      </c>
+      <c r="G119" t="s">
         <v>278</v>
-      </c>
-      <c r="G119" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4788,13 +4788,13 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F120" t="s">
         <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4811,13 +4811,13 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F121" t="s">
         <v>294</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4834,13 +4834,13 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F122" t="s">
         <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4857,13 +4857,13 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F123" t="s">
         <v>294</v>
       </c>
       <c r="G123" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4880,13 +4880,13 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F124" t="s">
         <v>294</v>
       </c>
       <c r="G124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4903,13 +4903,13 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F125" t="s">
         <v>294</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4926,13 +4926,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F126" t="s">
         <v>308</v>
       </c>
       <c r="G126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4949,13 +4949,13 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4972,13 +4972,13 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
         <v>308</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4995,13 +4995,13 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F129" t="s">
         <v>308</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E148" t="s">
         <v>318</v>
       </c>
       <c r="F148" t="s">
+        <v>357</v>
+      </c>
+      <c r="G148" t="s">
         <v>358</v>
-      </c>
-      <c r="G148" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E149" t="s">
         <v>318</v>
       </c>
       <c r="F149" t="s">
+        <v>357</v>
+      </c>
+      <c r="G149" t="s">
         <v>358</v>
-      </c>
-      <c r="G149" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E150" t="s">
         <v>318</v>
       </c>
       <c r="F150" t="s">
+        <v>357</v>
+      </c>
+      <c r="G150" t="s">
         <v>358</v>
-      </c>
-      <c r="G150" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E151" t="s">
         <v>318</v>
       </c>
       <c r="F151" t="s">
+        <v>357</v>
+      </c>
+      <c r="G151" t="s">
         <v>358</v>
-      </c>
-      <c r="G151" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E152" t="s">
         <v>318</v>
       </c>
       <c r="F152" t="s">
+        <v>357</v>
+      </c>
+      <c r="G152" t="s">
         <v>358</v>
-      </c>
-      <c r="G152" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E153" t="s">
         <v>318</v>
       </c>
       <c r="F153" t="s">
+        <v>357</v>
+      </c>
+      <c r="G153" t="s">
         <v>358</v>
-      </c>
-      <c r="G153" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E154" t="s">
         <v>318</v>
       </c>
       <c r="F154" t="s">
+        <v>371</v>
+      </c>
+      <c r="G154" t="s">
         <v>372</v>
-      </c>
-      <c r="G154" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E155" t="s">
         <v>318</v>
       </c>
       <c r="F155" t="s">
+        <v>371</v>
+      </c>
+      <c r="G155" t="s">
         <v>372</v>
-      </c>
-      <c r="G155" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E156" t="s">
         <v>318</v>
       </c>
       <c r="F156" t="s">
+        <v>371</v>
+      </c>
+      <c r="G156" t="s">
         <v>372</v>
-      </c>
-      <c r="G156" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E157" t="s">
         <v>318</v>
       </c>
       <c r="F157" t="s">
+        <v>371</v>
+      </c>
+      <c r="G157" t="s">
         <v>372</v>
-      </c>
-      <c r="G157" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="E158" t="s">
         <v>318</v>
       </c>
       <c r="F158" t="s">
+        <v>371</v>
+      </c>
+      <c r="G158" t="s">
         <v>372</v>
-      </c>
-      <c r="G158" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E178" t="s">
         <v>384</v>
       </c>
       <c r="F178" t="s">
+        <v>425</v>
+      </c>
+      <c r="G178" t="s">
         <v>426</v>
-      </c>
-      <c r="G178" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E179" t="s">
         <v>384</v>
       </c>
       <c r="F179" t="s">
+        <v>425</v>
+      </c>
+      <c r="G179" t="s">
         <v>426</v>
-      </c>
-      <c r="G179" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E180" t="s">
         <v>384</v>
       </c>
       <c r="F180" t="s">
+        <v>425</v>
+      </c>
+      <c r="G180" t="s">
         <v>426</v>
-      </c>
-      <c r="G180" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E181" t="s">
         <v>384</v>
       </c>
       <c r="F181" t="s">
+        <v>425</v>
+      </c>
+      <c r="G181" t="s">
         <v>426</v>
-      </c>
-      <c r="G181" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E182" t="s">
         <v>384</v>
       </c>
       <c r="F182" t="s">
+        <v>425</v>
+      </c>
+      <c r="G182" t="s">
         <v>426</v>
-      </c>
-      <c r="G182" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6234,16 +6234,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E183" t="s">
         <v>384</v>
       </c>
       <c r="F183" t="s">
+        <v>425</v>
+      </c>
+      <c r="G183" t="s">
         <v>426</v>
-      </c>
-      <c r="G183" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6257,16 +6257,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E184" t="s">
         <v>384</v>
       </c>
       <c r="F184" t="s">
+        <v>425</v>
+      </c>
+      <c r="G184" t="s">
         <v>426</v>
-      </c>
-      <c r="G184" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6280,16 +6280,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E185" t="s">
         <v>384</v>
       </c>
       <c r="F185" t="s">
+        <v>425</v>
+      </c>
+      <c r="G185" t="s">
         <v>426</v>
-      </c>
-      <c r="G185" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6303,16 +6303,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E186" t="s">
         <v>384</v>
       </c>
       <c r="F186" t="s">
+        <v>425</v>
+      </c>
+      <c r="G186" t="s">
         <v>426</v>
-      </c>
-      <c r="G186" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6326,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="E187" t="s">
         <v>384</v>
       </c>
       <c r="F187" t="s">
+        <v>425</v>
+      </c>
+      <c r="G187" t="s">
         <v>426</v>
-      </c>
-      <c r="G187" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6349,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>447</v>
+        <v>383</v>
       </c>
       <c r="E188" t="s">
         <v>384</v>
       </c>
       <c r="F188" t="s">
+        <v>447</v>
+      </c>
+      <c r="G188" t="s">
         <v>448</v>
-      </c>
-      <c r="G188" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6375,13 +6375,13 @@
         <v>451</v>
       </c>
       <c r="E189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s">
         <v>452</v>
       </c>
       <c r="G189" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6398,13 +6398,13 @@
         <v>451</v>
       </c>
       <c r="E190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F190" t="s">
         <v>452</v>
       </c>
       <c r="G190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6421,13 +6421,13 @@
         <v>451</v>
       </c>
       <c r="E191" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F191" t="s">
         <v>452</v>
       </c>
       <c r="G191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6444,13 +6444,13 @@
         <v>451</v>
       </c>
       <c r="E192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F192" t="s">
         <v>452</v>
       </c>
       <c r="G192" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6467,13 +6467,13 @@
         <v>451</v>
       </c>
       <c r="E193" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>452</v>
       </c>
       <c r="G193" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6490,13 +6490,13 @@
         <v>451</v>
       </c>
       <c r="E194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F194" t="s">
         <v>452</v>
       </c>
       <c r="G194" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6513,13 +6513,13 @@
         <v>465</v>
       </c>
       <c r="E195" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F195" t="s">
         <v>466</v>
       </c>
       <c r="G195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6536,13 +6536,13 @@
         <v>469</v>
       </c>
       <c r="E196" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F196" t="s">
         <v>470</v>
       </c>
       <c r="G196" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6559,13 +6559,13 @@
         <v>469</v>
       </c>
       <c r="E197" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F197" t="s">
         <v>470</v>
       </c>
       <c r="G197" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6582,13 +6582,13 @@
         <v>469</v>
       </c>
       <c r="E198" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F198" t="s">
         <v>470</v>
       </c>
       <c r="G198" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6605,13 +6605,13 @@
         <v>469</v>
       </c>
       <c r="E199" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F199" t="s">
         <v>470</v>
       </c>
       <c r="G199" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6628,13 +6628,13 @@
         <v>469</v>
       </c>
       <c r="E200" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F200" t="s">
         <v>470</v>
       </c>
       <c r="G200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6651,13 +6651,13 @@
         <v>469</v>
       </c>
       <c r="E201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
         <v>470</v>
       </c>
       <c r="G201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6674,13 +6674,13 @@
         <v>483</v>
       </c>
       <c r="E202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F202" t="s">
         <v>484</v>
       </c>
       <c r="G202" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6697,13 +6697,13 @@
         <v>483</v>
       </c>
       <c r="E203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F203" t="s">
         <v>484</v>
       </c>
       <c r="G203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6720,13 +6720,13 @@
         <v>483</v>
       </c>
       <c r="E204" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F204" t="s">
         <v>484</v>
       </c>
       <c r="G204" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6743,13 +6743,13 @@
         <v>483</v>
       </c>
       <c r="E205" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F205" t="s">
         <v>484</v>
       </c>
       <c r="G205" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6766,13 +6766,13 @@
         <v>483</v>
       </c>
       <c r="E206" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F206" t="s">
         <v>484</v>
       </c>
       <c r="G206" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6789,13 +6789,13 @@
         <v>483</v>
       </c>
       <c r="E207" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F207" t="s">
         <v>484</v>
       </c>
       <c r="G207" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6812,13 +6812,13 @@
         <v>483</v>
       </c>
       <c r="E208" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F208" t="s">
         <v>484</v>
       </c>
       <c r="G208" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6835,13 +6835,13 @@
         <v>483</v>
       </c>
       <c r="E209" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F209" t="s">
         <v>484</v>
       </c>
       <c r="G209" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6858,13 +6858,13 @@
         <v>483</v>
       </c>
       <c r="E210" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F210" t="s">
         <v>484</v>
       </c>
       <c r="G210" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6881,13 +6881,13 @@
         <v>483</v>
       </c>
       <c r="E211" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F211" t="s">
         <v>484</v>
       </c>
       <c r="G211" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6904,13 +6904,13 @@
         <v>505</v>
       </c>
       <c r="E212" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F212" t="s">
         <v>506</v>
       </c>
       <c r="G212" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6927,13 +6927,13 @@
         <v>509</v>
       </c>
       <c r="E213" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F213" t="s">
         <v>510</v>
       </c>
       <c r="G213" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6950,13 +6950,13 @@
         <v>513</v>
       </c>
       <c r="E214" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F214" t="s">
         <v>514</v>
       </c>
       <c r="G214" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6973,13 +6973,13 @@
         <v>513</v>
       </c>
       <c r="E215" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F215" t="s">
         <v>514</v>
       </c>
       <c r="G215" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6996,13 +6996,13 @@
         <v>519</v>
       </c>
       <c r="E216" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F216" t="s">
         <v>520</v>
       </c>
       <c r="G216" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7019,13 +7019,13 @@
         <v>519</v>
       </c>
       <c r="E217" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F217" t="s">
         <v>520</v>
       </c>
       <c r="G217" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7042,13 +7042,13 @@
         <v>519</v>
       </c>
       <c r="E218" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F218" t="s">
         <v>520</v>
       </c>
       <c r="G218" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7065,13 +7065,13 @@
         <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
         <v>520</v>
       </c>
       <c r="G219" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7088,13 +7088,13 @@
         <v>519</v>
       </c>
       <c r="E220" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F220" t="s">
         <v>520</v>
       </c>
       <c r="G220" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7111,13 +7111,13 @@
         <v>519</v>
       </c>
       <c r="E221" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F221" t="s">
         <v>520</v>
       </c>
       <c r="G221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7134,13 +7134,13 @@
         <v>519</v>
       </c>
       <c r="E222" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F222" t="s">
         <v>520</v>
       </c>
       <c r="G222" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7157,13 +7157,13 @@
         <v>535</v>
       </c>
       <c r="E223" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F223" t="s">
         <v>536</v>
       </c>
       <c r="G223" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7180,13 +7180,13 @@
         <v>535</v>
       </c>
       <c r="E224" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F224" t="s">
         <v>536</v>
       </c>
       <c r="G224" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7203,13 +7203,13 @@
         <v>535</v>
       </c>
       <c r="E225" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F225" t="s">
         <v>536</v>
       </c>
       <c r="G225" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7226,13 +7226,13 @@
         <v>543</v>
       </c>
       <c r="E226" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F226" t="s">
         <v>544</v>
       </c>
       <c r="G226" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7249,13 +7249,13 @@
         <v>547</v>
       </c>
       <c r="E227" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F227" t="s">
         <v>548</v>
       </c>
       <c r="G227" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7272,13 +7272,13 @@
         <v>551</v>
       </c>
       <c r="E228" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F228" t="s">
         <v>552</v>
       </c>
       <c r="G228" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7295,13 +7295,13 @@
         <v>555</v>
       </c>
       <c r="E229" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F229" t="s">
         <v>556</v>
       </c>
       <c r="G229" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7318,13 +7318,13 @@
         <v>559</v>
       </c>
       <c r="E230" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F230" t="s">
         <v>560</v>
       </c>
       <c r="G230" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7341,13 +7341,13 @@
         <v>559</v>
       </c>
       <c r="E231" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F231" t="s">
         <v>560</v>
       </c>
       <c r="G231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
+    <t>codeforiati:category-code</t>
   </si>
   <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
+    <t>111</t>
   </si>
   <si>
     <t>Education, Niveau non spécifié</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Enseignement primaire</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>Education de Base</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>Enseignement secondaire</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Education Secondaire</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Enseignement supérieur</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>Education Post Secondaire</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>Santé</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Santé</t>
+    <t>121</t>
   </si>
   <si>
     <t>Santé, Général</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Soins et services de santé de base</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Santé de Base</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>Lutte contre les MNT, général</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Maladies non-transmissibles (MNT)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>Distribution d'Eau et Assainissement</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Distribution d'Eau et Assainissement</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>Gouvernement &amp; Société Civile</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gouvernement &amp; Société Civile</t>
+    <t>151</t>
   </si>
   <si>
     <t>Gouvernement &amp; Société Civile-général</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Gestion et réforme des systèmes de sécurité</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflits, Paix et Sécurité</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>Infrastructure et Services Sociaux Divers</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Infrastructure et Services Sociaux Divers</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>Transports et Entreposage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transports et Entreposage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>Energie</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energie</t>
+    <t>231</t>
   </si>
   <si>
     <t>Politique de l'énergie</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Production d'énergie, sources renouvelables - multiples technologies</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources renouvelables</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -784,12 +784,12 @@
     <t>Production d'énergie, sources non renouvelables - non spécifié</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Production d'électricité, sources non renouvelables</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -835,24 +835,24 @@
     <t>Centrales nucléaires et sûreté nucléaire</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>Centrales nucléaires</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Production de chaleur seule</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Distribution de l'énergie</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>Banques et Services Financiers</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banques et Services Financiers</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>Entreprises et Autres Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Entreprises et Autres Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>Agriculture, Sylviculture, Pêche</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Sylviculture, Pêche</t>
+    <t>311</t>
   </si>
   <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1087,12 +1087,12 @@
     <t>Politique de la sylviculture et gestion administrative</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Sylviculture</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1129,12 +1129,12 @@
     <t>Politique de la pêche et gestion administrative</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Pêche</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>Industries Manufacturières, Extractives, Construct</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Industries Manufacturières, Extractives, Construct</t>
+    <t>321</t>
   </si>
   <si>
     <t>Industries Manufacturières</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1291,12 +1291,12 @@
     <t>Politique de l'industrie extractive et gestion administrative</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Industries Extractives</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1357,24 +1357,24 @@
     <t>Politique de la construction et gestion administrative</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>Politique Commerciale et Réglementations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Politique Commerciale et Réglementations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>Tourisme</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourisme</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>Protection de l'Environnement Général</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protection de l'Environnement Général</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>Autres Multisecteurs</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Autres Multisecteurs</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>Soutien Budgétaire</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Soutien Budgétaire</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>Aide Alimentaire Dévelopmentale</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Aide Alimentaire Dévelopmentale</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>Aide sous forme de Produits, Autre</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Aide sous forme de Produits, Autre</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>Actions se Rapportant a la Dette</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actions se Rapportant a la Dette</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>Intervention d'Urgence</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Intervention d'Urgence</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>Reconstruction &amp; Réhabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction &amp; Réhabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>Prévention catastrophes/Préparation à leur survenue</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prévention catastrophes/Préparation à leur survenue</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>Frais Administratifs des Donneurs</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Frais Administratifs des Donneurs</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>Refugiés dans les Pays Donneurs</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiés dans les Pays Donneurs</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>Non Affecté / Non Specifié</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Non Affecté / Non Specifié</t>
   </si>
   <si>
     <t>99820</t>
@@ -4584,10 +4584,10 @@
         <v>225</v>
       </c>
       <c r="F111" t="s">
+        <v>270</v>
+      </c>
+      <c r="G111" t="s">
         <v>269</v>
-      </c>
-      <c r="G111" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:7">

--- a/api/xlsx/fr/SectorGroup.xlsx
+++ b/api/xlsx/fr/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education, Niveau non spécifié</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>Education, Niveau non spécifié</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -148,18 +148,18 @@
     <t>Politique de la santé et gestion administrative</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Santé, Général</t>
+  </si>
+  <si>
     <t>Santé</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>Santé, Général</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Politique/programmes en matière de population et gestion administrative</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Politique en Matière de Population/Santé&amp;Fertilité</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -316,12 +316,12 @@
     <t>Politique et gestion administrative du secteur de l'eau</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Distribution d'Eau et Assainissement</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t>Politiques publiques et gestion administrative</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Gouvernement &amp; Société Civile-général</t>
+  </si>
+  <si>
     <t>Gouvernement &amp; Société Civile</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Gouvernement &amp; Société Civile-général</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -538,12 +538,12 @@
     <t>Protection sociale</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Infrastructure et Services Sociaux Divers</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -610,12 +610,12 @@
     <t>Politique des transports et gestion administrative</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transports et Entreposage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -658,12 +658,12 @@
     <t>Politique des communications et gestion administrative</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -688,18 +688,18 @@
     <t>Politique énergétique et gestion administrative</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Politique de l'énergie</t>
+  </si>
+  <si>
     <t>Energie</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Politique de l'énergie</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Politique des finances et gestion administrative</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banques et Services Financiers</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>Politique commerciale et administration</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Entreprises et Autres Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t>Politique agricole et gestion administrative</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>Agriculture, Sylviculture, Pêche</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1165,18 +1165,18 @@
     <t>Politique de l'industrie et gestion administrative</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industries Manufacturières</t>
+  </si>
+  <si>
     <t>Industries Manufacturières, Extractives, Construct</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Industries Manufacturières</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1369,12 +1369,12 @@
     <t>Politique commerciale et gestion administrative</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>Politique Commerciale et Réglementations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1411,24 +1411,24 @@
     <t>Politique du tourisme et gestion administrative</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourisme</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Politique de l'environnement et gestion administrative</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>Protection de l'Environnement Général</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1465,12 +1465,12 @@
     <t>Aide plurisectorielle</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Autres Multisecteurs</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1531,36 +1531,36 @@
     <t>Aide relative au soutien budgétaire général</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>Soutien Budgétaire</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistance alimentaire</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Aide Alimentaire Dévelopmentale</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Subventions à l'importation (biens d'équipement)</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Aide sous forme de Produits, Autre</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1573,12 +1573,12 @@
     <t>Actions se rapportant à la dette</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Actions se Rapportant a la Dette</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1621,12 +1621,12 @@
     <t>Assistance matérielle et services d'urgence</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Intervention d'Urgence</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1645,58 +1645,58 @@
     <t>Reconstruction et réhabilitation immédiate post-urgence</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction &amp; Réhabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Préparation aux interventions multi-risques</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Prévention catastrophes/Préparation à leur survenue</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Frais administratifs (non alloués par secteur)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Frais Administratifs des Donneurs</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiés/demandeurs d'asile dans les pays donneurs (non alloués)</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugiés dans les Pays Donneurs</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Secteur non spécifié</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Non Affecté / Non Specifié</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -2163,16 +2163,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2186,16 +2186,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2209,16 +2209,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2232,16 +2232,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2255,16 +2255,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2278,16 +2278,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2301,16 +2301,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2324,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2439,16 +2439,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2462,16 +2462,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2485,16 +2485,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2508,16 +2508,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2554,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2577,16 +2577,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2600,16 +2600,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2623,16 +2623,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2646,16 +2646,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
         <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2669,16 +2669,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2692,16 +2692,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2715,16 +2715,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
         <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2738,16 +2738,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2764,13 +2764,13 @@
         <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2787,13 +2787,13 @@
         <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2810,13 +2810,13 @@
         <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2833,13 +2833,13 @@
         <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2856,13 +2856,13 @@
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2879,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2902,13 +2902,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>101</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2925,13 +2925,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>101</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
         <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2971,13 +2971,13 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2994,13 +2994,13 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" t="s">
         <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3017,13 +3017,13 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3040,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3063,13 +3063,13 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3086,13 +3086,13 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
         <v>101</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3109,13 +3109,13 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
         <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3497,16 +3497,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3520,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
         <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E66" t="s">
         <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3566,16 +3566,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E67" t="s">
         <v>125</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
         <v>125</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3612,16 +3612,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
         <v>125</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3638,13 +3638,13 @@
         <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F70" t="s">
         <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3661,13 +3661,13 @@
         <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
         <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3684,13 +3684,13 @@
         <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3707,13 +3707,13 @@
         <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3730,13 +3730,13 @@
         <v>174</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3753,13 +3753,13 @@
         <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3776,13 +3776,13 @@
         <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>175</v>
       </c>
       <c r="G76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3799,13 +3799,13 @@
         <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
         <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3822,13 +3822,13 @@
         <v>174</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
         <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3845,13 +3845,13 @@
         <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3868,13 +3868,13 @@
         <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
         <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3891,13 +3891,13 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
         <v>199</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3914,13 +3914,13 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F82" t="s">
         <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3937,13 +3937,13 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F83" t="s">
         <v>199</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3960,13 +3960,13 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
         <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3983,13 +3983,13 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4006,13 +4006,13 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
         <v>199</v>
       </c>
       <c r="G86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4029,13 +4029,13 @@
         <v>198</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F87" t="s">
         <v>199</v>
       </c>
       <c r="G87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4052,13 +4052,13 @@
         <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
       </c>
       <c r="G88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4075,13 +4075,13 @@
         <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
       </c>
       <c r="G89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4098,13 +4098,13 @@
         <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
       </c>
       <c r="G90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4121,13 +4121,13 @@
         <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
       </c>
       <c r="G91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4233,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
         <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G96" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4256,16 +4256,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
         <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G97" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4279,16 +4279,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
         <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G98" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4302,16 +4302,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
         <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G99" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4325,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
         <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G100" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4348,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E101" t="s">
         <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4371,16 +4371,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
         <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4394,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
         <v>225</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4417,16 +4417,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
         <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4440,16 +4440,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E105" t="s">
         <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4463,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4486,16 +4486,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G107" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E108" t="s">
         <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4532,16 +4532,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
         <v>225</v>
       </c>
       <c r="F109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4555,16 +4555,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
         <v>225</v>
       </c>
       <c r="F110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4578,16 +4578,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G111" t="s">
-        <v>269</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4601,16 +4601,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
         <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4624,16 +4624,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
         <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4647,16 +4647,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E114" t="s">
         <v>225</v>
       </c>
       <c r="F114" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4670,16 +4670,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
       </c>
       <c r="F115" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4693,16 +4693,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G116" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4716,16 +4716,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
         <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4739,16 +4739,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
       </c>
       <c r="F118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G118" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4762,16 +4762,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E119" t="s">
         <v>225</v>
       </c>
       <c r="F119" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G119" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4788,13 +4788,13 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F120" t="s">
         <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4811,13 +4811,13 @@
         <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F121" t="s">
         <v>294</v>
       </c>
       <c r="G121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4834,13 +4834,13 @@
         <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F122" t="s">
         <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4857,13 +4857,13 @@
         <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F123" t="s">
         <v>294</v>
       </c>
       <c r="G123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4880,13 +4880,13 @@
         <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F124" t="s">
         <v>294</v>
       </c>
       <c r="G124" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4903,13 +4903,13 @@
         <v>293</v>
       </c>
       <c r="E125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F125" t="s">
         <v>294</v>
       </c>
       <c r="G125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4926,13 +4926,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F126" t="s">
         <v>308</v>
       </c>
       <c r="G126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4949,13 +4949,13 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F127" t="s">
         <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4972,13 +4972,13 @@
         <v>307</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F128" t="s">
         <v>308</v>
       </c>
       <c r="G128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4995,13 +4995,13 @@
         <v>307</v>
       </c>
       <c r="E129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F129" t="s">
         <v>308</v>
       </c>
       <c r="G129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5429,16 +5429,16 @@
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E148" t="s">
         <v>318</v>
       </c>
       <c r="F148" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G148" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5452,16 +5452,16 @@
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
         <v>318</v>
       </c>
       <c r="F149" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G149" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5475,16 +5475,16 @@
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E150" t="s">
         <v>318</v>
       </c>
       <c r="F150" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G150" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5498,16 +5498,16 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E151" t="s">
         <v>318</v>
       </c>
       <c r="F151" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G151" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5521,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E152" t="s">
         <v>318</v>
       </c>
       <c r="F152" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G152" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5544,16 +5544,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
         <v>318</v>
       </c>
       <c r="F153" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E154" t="s">
         <v>318</v>
       </c>
       <c r="F154" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G154" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5590,16 +5590,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E155" t="s">
         <v>318</v>
       </c>
       <c r="F155" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G155" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5613,16 +5613,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
         <v>318</v>
       </c>
       <c r="F156" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G156" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5636,16 +5636,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
         <v>318</v>
       </c>
       <c r="F157" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G157" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="E158" t="s">
         <v>318</v>
       </c>
       <c r="F158" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G158" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6119,16 +6119,16 @@
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E178" t="s">
         <v>384</v>
       </c>
       <c r="F178" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G178" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6142,16 +6142,16 @@
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E179" t="s">
         <v>384</v>
       </c>
       <c r="F179" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G179" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6165,16 +6165,16 @@
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E180" t="s">
         <v>384</v>
       </c>
       <c r="F180" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G180" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6188,16 +6188,16 @@
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E181" t="s">
         <v>384</v>
       </c>
       <c r="F181" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G181" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6211,16 +6211,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E1